--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -8,11 +8,15 @@
     <sheet name="North Vancouver, BC" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Low Confidence - Review" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Victoria, BC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Richmond, BC" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'North Vancouver, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Low Confidence - Review'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Victoria, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Richmond, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -102,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -128,6 +132,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3820,7 +3827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -3959,6 +3966,90 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Victoria, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Gregory C. Marshall Naval Architect Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Gregory_C._Marshall_Naval_Architect</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Victoria-based naval architecture firm since 1994, but focused on styling/engineering for private luxury yachts (400+ vessels) rather than heavy industrial, offshore or commercial marine structures - core AH Structures fit (heavy lift, FEA, fatigue, sea fastening) is less obviously applicable.</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether any commercial/workboat or heavy-structural work exists alongside the yacht design practice before treating as an active prospect.</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Gregory_C._Marshall_Naval_Architect</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Richmond, BC</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Marcon Metalfab Inc.</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>https://www.zoominfo.com/c/marcon-metalfab-inc/345949109</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>30+ year custom steel fabricator for transportation, construction and utilities sectors; sources disagree on whether its primary facility is in Delta or Richmond, BC (a 2025 move was reported), so city attribution is unconfirmed pending verification.</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Confirm current primary address before assigning to a specific city sheet (candidate for the Delta, BC batch if Delta is confirmed as HQ).</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>https://www.yelp.ca/biz/marcon-metalfab-delta ; https://www.metalline.info/company-marcon-metalfab-inc-in-richmond-1571</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3971,7 +4062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -4145,7 +4236,905 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Batch 2: Victoria, BC &amp; Richmond, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>1. Point Hope Maritime Ltd. (Victoria) - Score 9, Priority A - major repair/refit shipyard, named General Manager, recent (2019) capacity-expanding acquisition of Esquimalt Dry Dock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2. Ebco Industries Ltd. (Richmond) - Score 9, Priority A - large heavy fabrication/machining manufacturer explicitly serving Marine &amp; Offshore, Mining and Power sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>3. 3GA Marine Ltd. (Victoria) - Score 7, Priority B - naval architecture partnership serving the ferry sector; named principals not yet confidently matched to titles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>4. Bracewell Boatworks Ltd. (Richmond) - Score 6, Priority C - Fraser River vessel repair/refit yard with in-house fabrication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Shipyards and heavy fabricators with an explicit marine/offshore service line. Both A-priority prospects this batch (Point Hope Maritime, Ebco Industries) are physical yards/fabricators handling large commercial assemblies, not design boutiques - a different profile from batch 1's naval-architecture consultancies, but an equally strong fit for structural verification and lifting/rigging engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Lead with independent verification, not overflow drafting: both A-priority prospects are fabrication/repair yards whose core business is building or fixing large structures, not producing engineering calculations themselves. Position AH Structures as the independent structural/lifting-engineering check their yard, their client, or a class society may require on a given job - not as replacing an in-house team they don't have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Point Hope Maritime Ltd. - 2019 acquisition of Esquimalt Dry Dock Company clearly expanded project scope and likely strained available in-house engineering support at times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Ebco Industries Ltd. - heavy fabricated marine/offshore and mining/power assemblies are a strong match for structural/FEA verification work; 3GA Marine Ltd. - ferry structural design/refit work is FEA-adjacent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Point Hope Maritime Ltd. and Ebco Industries Ltd. both routinely handle large fabricated/refit assemblies that require lifting-lug, pad-eye and load-out engineering during shipyard or fabrication-shop handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Point Hope Maritime Ltd. (Riccardo Regosa, General Manager - re-verify title first) and Ebco Industries Ltd. (via general contact, requesting the engineering/production leadership contact rather than CEO Richard Eppich directly for a first approach). Follow with 3GA Marine Ltd. once a named principal is confirmed via their staff page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Marcon Metalfab Inc. was researched for Richmond but sources conflict on its primary address (Delta vs. Richmond, with a reported 2025 move) - routed to the Low Confidence - Review sheet pending confirmation rather than assigned to either city sheet. Gregory C. Marshall Naval Architect Ltd. (Victoria) was excluded from the main sheet as a recreational-yacht-focused practice with a less direct fit to AH Structures' heavy-lift/offshore/commercial-marine core, and is in the Review sheet instead. No email address was guessed; only publicly published general inboxes are recorded, clearly labelled as such.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Victoria, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Point Hope Maritime Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://pointhopemaritime.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/point-hope-maritime-limited</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Shipyard (Repair, Refit &amp; Conversion)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Shipbuilding / Ship Repair</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Vessel repair, conversion, refit and maintenance up to 360 m; access to in-house steel/aluminum fabrication and machine shop (United Engineering Ltd., a fellow Ralmax Group company)</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Full-service shipyard handling large commercial vessel repair/refit/conversion work with an in-house fabrication and machine shop; conversion and refit projects routinely need structural verification, lifting/rigging engineering, and load-out or sea-fastening calculations that can exceed in-house capacity at peak times.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Acquired the Esquimalt Dry Dock Company (EDC) in 2019, expanding access to the federally owned Esquimalt Graving Dock and clearly growing project scope/capacity. Source: https://bctugboat.com/a-proud-shipyard-history/ ; https://bctugboat.com/point-hope-maritime-in-victoria-bc/</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Over a hundred years of continuous shipyard operation on Victoria's harbour; up to 300 people working on site including 175 permanent employees plus sub-contractors. Source: https://pointhopemaritime.com/ ; https://bctugboat.com/a-proud-shipyard-history/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Riccardo Regosa</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://pointhopemaritime.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Web search snippet citing Riccardo Regosa as General Manager since 2016 (ZoomInfo-corroborated); not independently opened</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://pointhopemaritime.com/ ; https://bctugboat.com/a-proud-shipyard-history/ ; https://bctugboat.com/point-hope-maritime-in-victoria-bc/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Position AH Structures as flexible external structural/FEA and lifting-engineering capacity for repair, refit and conversion projects, complementing in-house fabrication capacity during peak workload following the 2019 EDC acquisition.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Riccardo Regosa as General Manager is drawn from a web search snippet, not a directly opened source - confirm current title before outreach. No dedicated 'engineering manager' title identified; General Manager is the most senior operational contact found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Victoria, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>3GA Marine Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>http://3gamarine.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/3ga-marine-limited</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Engineering Consultancy (Naval Architecture &amp; Marine Engineering)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Naval Architecture</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Naval architecture, marine engineering, ferry design (conventional, cable and hybrid propulsion), refits and production support</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Victoria-headquartered naval architecture and marine engineering partnership serving the ferry and workboat sector; ferry refit/newbuild and production-support work regularly needs structural analysis and engineering calculations a small partnership may not carry in-house at all times.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No current hiring or expansion signal identified in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>ISO 9001:2015-certified naval architecture and marine engineering firm headquartered at 208-1497 Admirals Rd, Victoria, BC, with a second office in Burnaby; serves ferry, workboat, energy and shipping clients. Source: https://3gamarine.com/ ; https://web.victoriachamber.ca/Naval-Architects/3GA-Marine-Limited-4942</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://3gamarine.com/staff/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>https://3gamarine.com/staff/</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://3gamarine.com/ ; https://3gamarine.com/engineering/ ; https://web.victoriachamber.ca/Naval-Architects/3GA-Marine-Limited-4942</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural/FEA support as an independent extension of a small partnership's engineering bench for ferry refit or newbuild production-support phases.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Named principals only partially confirmed this pass (a founding naval architect with 40+ years and a VP/senior partner who joined 2013 are both referenced in search results, alongside staff named David Mietla and Daniel McIntyre, without a clear title-to-name match). Confirm via https://3gamarine.com/staff/ before outreach rather than naming an individual now.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Richmond, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Ebco Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://ebco.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/ebco-industries-ltd.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Fabrication &amp; Machining Manufacturer</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial / Marine &amp; Offshore / Mining / Power</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy fabrication, heavy machining, precision sheet metal and turnkey assembly for large equipment and structures</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>One of the largest heavy fabrication and machining facilities on the West Coast, explicitly serving Marine &amp; Offshore, Mining &amp; Aggregates, and Power &amp; Hydro Generation among its industries; large fabricated assemblies for these sectors routinely require structural verification, lifting-lug design, and load calculations.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No current hiring or expansion signal identified in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Founded 1956; 240,000 sq ft facility on a 13-acre site in Richmond, BC; self-described industries served include Marine &amp; Offshore and Mining &amp; Aggregates. Source: https://ebco.com/ ; https://ebco.com/machining/ ; https://en.wikipedia.org/wiki/Ebco_Industries</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Richard Eppich</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://ebco.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Web search snippet (Wikipedia-corroborated); not independently opened</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://ebco.com/ ; https://ebco.com/machining/ ; https://en.wikipedia.org/wiki/Ebco_Industries</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Offer independent structural verification and lifting/rigging engineering (pad-eye, lifting-lug, load-out) for large marine, offshore and heavy-industrial fabricated assemblies, positioned as a check independent of Ebco's own production engineering.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No dedicated engineering-department contact identified this pass; Richard Eppich (CEO) is the most senior confirmed contact for a mid-size private manufacturer per the master prompt's guidance to use an owner/founder-level contact for smaller companies. Worth a follow-up LinkedIn search for an Engineering Manager or Chief Engineer title before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Richmond, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Bracewell Boatworks Ltd. (Bracewell Marine Group)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bracewellmarinegroup.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Marine Fabrication &amp; Refit Yard</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Vessel Repair &amp; Refit</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Aluminum and stainless-steel fabrication and welding, vessel repair/refit for craft up to ~150 tons</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Fraser River boatyard with in-house aluminum/stainless fabrication and welding for vessel refit and repair; larger refit or structural repair jobs can require structural verification or engineering sign-off beyond the yard's own trades staff.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No hiring or expansion signal identified in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Located at Shelter Island Marina, 185-6831 Graybar Road, Richmond, BC; in-house fabrication, welding and repair departments serving vessels up to approximately 150 tons. Source: https://newswire.com/bracewell-boatworks-richmond-bc/31811 ; https://www.yellowpages.ca/bus/British-Columbia/Richmond/Bracewell-Boatworks/2136508.html</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bracewellmarinegroup.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@bracewellboatworks.com (general company inbox)</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Company website / Yellow Pages listing</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://newswire.com/bracewell-boatworks-richmond-bc/31811 ; https://www.bracewellmarinegroup.com/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Offer occasional structural verification or repair-scope engineering sign-off for larger refit jobs, positioned as lower-cost, on-call support rather than a standing arrangement.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Smaller repair/refit yard without a clearly design-heavy scope; treat as a lower-probability, occasional-verification prospect rather than a recurring overflow-capacity one. No named owner/manager identified this pass.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -10,6 +10,8 @@
     <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Victoria, BC" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Richmond, BC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Burnaby, BC" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Surrey, BC" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -17,6 +19,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Low Confidence - Review'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Victoria, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Richmond, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Burnaby, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Surrey, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3827,7 +3831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4050,6 +4054,90 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Burnaby, BC</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>OceanWorks International Corporation</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>https://oceanworks.com/</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Burnaby-based designer/manufacturer of manned and unmanned underwater work systems with genuine marine/offshore engineering depth - but its own site names Oil &amp; Gas as a leading market (a house-rule exclusion) and the military as a customer base of nearly three decades (defense exclusion), with no clearly separate non-O&amp;G, non-defense commercial division identified.</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether any purely commercial, non-oil-and-gas, non-defense project line exists (e.g. scientific/research or offshore-wind subsea work) before treating as a prospect; as researched, it conflicts with two separate AH Structures guardrails at once.</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>https://oceanworks.com/about/ ; https://oceanworks.com/about/customers/customers-oil-gas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Surrey, BC</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>AI Industries</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>https://www.ai-industries.com/</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia's largest commercial structural steel fabricator by volume (12,000+ tons/year), but its described project mix is schools, offices, shopping-mall renovations and military barracks/hangars in BC, Washington, Oregon, Alaska and Hawaii - a general commercial/institutional building fabricator, not a marine, offshore or heavy-lift specialist.</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether any marine, offshore or heavy-industrial (non-building) fabrication work exists before treating as a prospect; as researched this is a building-construction fit, not an AH Structures core fit.</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>https://www.ai-industries.com/about-us</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4062,7 +4150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -4373,6 +4461,146 @@
       <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Marcon Metalfab Inc. was researched for Richmond but sources conflict on its primary address (Delta vs. Richmond, with a reported 2025 move) - routed to the Low Confidence - Review sheet pending confirmation rather than assigned to either city sheet. Gregory C. Marshall Naval Architect Ltd. (Victoria) was excluded from the main sheet as a recreational-yacht-focused practice with a less direct fit to AH Structures' heavy-lift/offshore/commercial-marine core, and is in the Review sheet instead. No email address was guessed; only publicly published general inboxes are recorded, clearly labelled as such.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Batch 3: Burnaby, BC &amp; Surrey, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>1. Global Rigging &amp; Transport (GRT) Canada Corp. (Surrey) - Score 9, Priority A - Surrey-HQ'd international heavy-lift/transport specialist, named President/Director, recent large-scale dismantling project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>2. Kiewit Infrastructure Engineers, Burnaby office - Score 9, Priority A - established Temporary Works Group with multiple current structural/coastal postings; the closest direct match to AH Structures' scope found so far.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>3. DP World Fraser Surrey (Surrey) - Score 8, Priority A - named Director of Engineering &amp; Terminal Development, active July 2026 capacity-expansion announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>4. Ausenco, Burnaby office Marine and Coastal Group - Score 7, Priority B - confirmed group and location, but only a stale (2023) hiring signal found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Temporary-works and heavy-lift/transport engineering. This batch's two strongest fits (Kiewit's Temporary Works Group and GRT) sit closer to AH Structures' actual named service lines - lifting, rigging, and construction-stage structural verification - than the naval-architecture and shipyard prospects found in prior batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Lead with named, current work: Kiewit's live Temporary Works postings and DP World's just-announced capacity expansion are both specific, dated hooks - reference them directly rather than a generic capabilities pitch, since both show a live, current reason to need extra structural/engineering capacity right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Kiewit Infrastructure Engineers, Burnaby (multiple concurrent live Temporary Works and coastal-hydraulic postings); DP World Fraser Surrey (July 2026 capacity-expansion announcement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Kiewit's Temporary Works Group (construction-stage structural verification); Ausenco's Marine and Coastal Group (port/coastal structural design) - though the latter's current demand is unconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Global Rigging &amp; Transport (core business is heavy lift/engineered transport with an explicit custom-engineering service line); DP World Fraser Surrey (quay-crane and terminal equipment handling large structural cargo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Global Rigging &amp; Transport (Andrew Johnson, President/Director - re-verify title first) and Kiewit's Temporary Works Group (via the live job posting's contact channel, or a named Temporary Works Manager once identified). Follow with DP World Fraser Surrey (Jurgen Franke, Director of Engineering &amp; Terminal Development) and Ausenco's Marine and Coastal Group once a current opening or named lead is confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>OceanWorks International (Burnaby) was excluded from the main sheet despite genuine marine-engineering depth: its own site names Oil &amp; Gas and Military as leading markets, conflicting with two separate house guardrails (no oil &amp; gas; defense exclusion) at once - routed to Review instead. AI Industries (Surrey), despite being BC's largest commercial steel fabricator by volume, was excluded as a schools/offices/military-barracks building fabricator rather than a marine/offshore/heavy-lift one. Carlson Construction Group (heavy civil/marine/industrial, multiple divisions) surfaced during this batch's research but is headquartered in North Vancouver, not Burnaby or Surrey - flagging it here rather than retroactively editing the already-reviewed North Vancouver, BC sheet; let me know if you'd like it added there.</t>
         </is>
       </c>
     </row>
@@ -5137,4 +5365,762 @@
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Burnaby, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Kiewit Infrastructure Engineers (Burnaby office)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kiewit.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/kiewit</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Engineering Consultancy (within a major contractor)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Civil / Marine / Structural Infrastructure Engineering</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural, civil, coastal/hydraulic and temporary-works engineering; marine engineering capability within the group</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Burnaby office runs an established Temporary Works Group plus coastal/hydraulic engineering roles - temporary-works engineering (formwork, shoring, lifting and construction-stage structures) is a direct, close match to AH Structures' core scope, and live multiple concurrent postings show current workload.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Concurrent live postings found: 'Structural EIT - Temporary Works' and 'Sr Structural Engineer - Temporary Works' (Burnaby, BC), plus 'Senior Coastal Hydraulic Engineer'. Source: https://kiewitcareers.kiewit.com/job/Burnaby-Structural-EIT-Temporary-Works-(Burnaby,-BC)-2026-Brit/1355010800/ ; https://ca.linkedin.com/jobs/view/sr-structural-engineer-temporary-works-kiewit-infrastructure-engineers-at-kiewit-3811076424</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Kiewit Canada's Burnaby division covers structural, civil, piping, mechanical, process, electrical, instrument and control disciplines, with marine engineering design work confirmed as part of its scope.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/kiewit</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Kiewit careers site / LinkedIn job postings</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://kiewitcareers.kiewit.com/ ; https://ca.linkedin.com/jobs/kiewit-jobs-burnaby-bc</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Reference the Temporary Works Group's current hiring directly - offer AH Structures as flexible external capacity for temporary-works structural verification, lifting/rigging calculations or FEA on active project phases while Kiewit fills permanent roles.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No named Temporary Works Group manager identified this pass; large contractor, so the realistic entry point is a specific project's temporary-works lead rather than a cold general approach. Worth a follow-up LinkedIn search for 'Kiewit' + 'Temporary Works Manager' before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Burnaby, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Ausenco (Burnaby office, Marine and Coastal Group)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ausenco.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/ausenco</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Engineering Consultancy</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Coastal / Port Infrastructure Engineering</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Marine and port structural design (wharves, jetties, piers, coastal protection), concept through detailed design</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed dedicated Marine and Coastal Group based out of the Burnaby office, designing port and coastal structures - a plausible source of periodic structural/FEA overflow work, though the only posting found is from December 2023 so treat as a confirmed capability rather than a current hiring signal.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>A 'Marine Structural Engineer' posting for the Burnaby office was found dated December 2023 - this confirms the group's existence and location but is too old to treat as a current overflow signal. Source: https://www.engineeringcareers.ca/job/2023170/marine-structural-engineer-burnaby/</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Global EPCM engineering firm; Marine and Coastal Group supports planning, design and delivery of port, coastal and marine infrastructure projects including concept through detailed design and construction support.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/ausenco</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Job posting aggregators (LinkedIn, Indeed, SimplyHired, engineeringcareers.ca)</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.engineeringcareers.ca/job/2023170/marine-structural-engineer-burnaby/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Position as independent marine/coastal structural capacity for peak workload on active port and coastal projects, given the group's confirmed scope and location.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No named group lead identified this pass, and the only direct evidence found is a stale (2023) posting - re-check for current Burnaby marine/coastal openings before treating this as a live overflow opportunity.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Surrey, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Global Rigging &amp; Transport (GRT) Canada Corp.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.globalrigging.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/globalriggingandtransport</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Lift &amp; Heavy Transport Contractor</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Lift / Heavy Transport</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy lift, engineered transport, crane moving/modification/repair/assembly/dismantling, load testing, custom engineering</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Surrey-headquartered international heavy-lift and heavy-transport specialist that explicitly offers 'custom engineering' as part of its service line - a strong, direct fit for lifting, rigging, pad-eye and sea-fastening calculation work, especially at peak project load across its worldwide project sites.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Current live postings found (Safety Officer; Office Administration Assistant, Port Kells/Surrey facility) confirm active operations, but no engineering-specific hiring signal was found in this pass. Source: https://ca.indeed.com/cmp/Global-Rigging-&amp;-Transport/locations/BC/Surrey</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Recent project: demolition of a 170ft, 1200-ton STS crane on Vancouver Island, BC - demonstrates large-scale heavy-lift/dismantling capability. Source: https://www.globalrigging.com/post/global-rigging-transport-grt-successfully-demolishes-170ft-1200-ton-sts-crane-in-vancouver-islan</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Andrew Johnson</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President / Director</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.globalrigging.com/about-grt</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website / business directory listings (CWB Group, BBB)</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.globalrigging.com/about-grt ; https://www.cwbgroup.org/directory/certified-companies/2c228c48-b569-e811-a965-000d3af3dfc5</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Position AH Structures as independent lift/rigging engineering capacity (pad-eye, sea-fastening, load calculations) that can flex with GRT's project-by-project engineering demand on named heavy-lift and dismantling jobs.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Andrew Johnson's title was drawn from web search snippets, not a directly opened source - confirm current role before outreach. Thomas Felch (VP/Director) and Erin Johnson (Business Development Manager) are alternative named contacts worth considering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Surrey, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>DP World Fraser Surrey (Fraser Surrey Docks)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dp-world</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Marine Terminal Operator</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Port Infrastructure</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Marine terminal operations handling structural products (steel plate, coil, pipe, beam) and quay-crane cargo up to 70 tons; in-house Engineering &amp; Terminal Development function</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Largest multi-purpose marine terminal on the North American West Coast with a confirmed, named Director of Engineering &amp; Terminal Development - terminal infrastructure, berth/quay-crane structures and equipment upgrades plausibly need structural verification or lifting-engineering support beyond the in-house team's day-to-day capacity.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>DP World announced (July 2026) it is unlocking up to 2 million tonnes of additional export capacity at Fraser Surrey Terminal, indicating an active capacity-expansion program that plausibly requires structural/terminal engineering support beyond business-as-usual. Source: https://www.dpworld.com/en/news/usa/2026_07_09_fraser-surrey-training-wall</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Terminal features 6 deep-sea berths, a dolphin berth, a hydraulic barge ramp, and 3 quay cranes up to 70 tons; handles significant volumes of imported structural steel products. Source: https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Jurgen Franke</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Director, Engineering &amp; Terminal Development</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Web search snippet corroborated by company org context (Craft.co executives listing)</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dpworld.com/en/news/usa/2026_07_09_fraser-surrey-training-wall ; https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Reference the recently announced capacity-expansion program directly - offer AH Structures as independent structural/lifting-engineering verification capacity for terminal infrastructure and equipment work tied to that expansion.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Jurgen Franke's title/name was drawn from a web search snippet, not a directly opened source - confirm current role before outreach. DP World is a very large global operator; a terminal-level contact like this is the right altitude rather than corporate head office.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -6,21 +6,25 @@
     <sheet name="CitiesTown in Canada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Vancouver, BC" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="North Vancouver, BC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Low Confidence - Review" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Victoria, BC" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Richmond, BC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Burnaby, BC" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Surrey, BC" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Victoria, BC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Richmond, BC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Burnaby, BC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Surrey, BC" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Delta, BC" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="New Westminster, BC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Low Confidence - Review" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'North Vancouver, BC'!$A$1:$X$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Low Confidence - Review'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Victoria, BC'!$A$1:$X$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Richmond, BC'!$A$1:$X$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Burnaby, BC'!$A$1:$X$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Surrey, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Victoria, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Richmond, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Burnaby, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Surrey, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Delta, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'New Westminster, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Low Confidence - Review'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2635,6 +2639,758 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>New Westminster, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Fraser River Pile &amp; Dredge (GP) Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://frpd.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/frpdconstruction</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Marine Construction &amp; Dredging Contractor</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine Construction / Dredging / Land Foundation</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Marine construction, dredging, environmental remediation and land-foundation work using a fleet of cutter suction/hopper dredges, spud barges, cranes, dump barges and flat scows</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Canada's largest marine construction and dredging contractor, with a large owned fleet of marine construction equipment; a pending change of ownership (acquisition by a large public contractor) is exactly the kind of transition that can strain or reshape in-house engineering capacity, creating a window for external structural/marine engineering support.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Bird Construction Inc. signed a definitive agreement (announced September 2025) to acquire FRPD for approximately $82.3 million, expected to close Q4 2025 - an ownership transition of this scale often creates transitional engineering resourcing needs. Source: https://www.bird.ca/news/2025/09/03/bird-to-acquire-canadas-largest-marine-infrastructure-land-foundation-and-dredging-company-for-82-3-million-catalyst-for-future-growth/</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>300+ employees; successor to Fraser River Pile Driving Company (founded 1911); operations mainly in Western Canada and the Northwest Territories. Source: https://frpd.com/ ; https://dredgepoint.org/dredging-database/owners/fraser-river-pile-dredge-gp-inc</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Sarah Clark</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://frpd.com/management-team/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>https://frpd.com/management-team/ ; https://www.pilingcanada.ca/breaking-the-mould/</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://frpd.com/ ; https://www.bird.ca/news/2025/09/03/bird-to-acquire-canadas-largest-marine-infrastructure-land-foundation-and-dredging-company-for-82-3-million-catalyst-for-future-growth/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Reference the Bird Construction acquisition directly and offer AH Structures as independent marine/structural engineering capacity to help absorb any transitional workload or new-owner project requirements during integration.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Sarah Clark has been President &amp; CEO since August 2017 per a Piling Canada profile and the company's own management-team page - reasonably well corroborated, but re-confirm given the pending ownership change may affect reporting lines or the point of contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>New Westminster, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Amix Group (Amix Marine Services)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://amixgroup.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/amix-group</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Marine Operator / Heavy Lift &amp; Marine Services Group</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Heavy Lift / Marine Transportation</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Tug and barge operations, marine transportation and support services, with facilities in Port Alberni, Howe Sound, Prince Rupert and Nanaimo alongside the New Westminster head office</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>New Westminster-headquartered marine operator running its own tug/barge fleet across multiple BC coastal facilities; vessel and barge fleets of this scale periodically need structural surveys, load calculations and naval-architecture-adjacent engineering support beyond routine maintenance.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Group includes Amix Heavy Lift Ltd. (Chamber of Shipping member) alongside Amix Marine Services; head office at Suite 425, 625 Agnes Street, New Westminster, BC. Source: https://amixgroup.ca/marine-services/ ; https://shippingmatters.ca/about-cos/membership-directory/2221/amix-heavy-lift-ltd/</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Tony Marra</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>President (Amix Group)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://amixgroup.ca/contact/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@amixgroup.ca (general company inbox)</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://amixgroup.ca/ ; https://amixgroup.ca/marine-services/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural/naval-architecture-adjacent verification support (barge load calculations, structural surveys) for the group's tug/barge fleet and heavy-lift division.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Tony Marra is confirmed as President of Amix Group overall (via web search); no marine-services-specific general manager was identified this pass, so confirm the right divisional contact - likely someone under Amix Heavy Lift Ltd. or Amix Marine Services specifically - before outreach.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="3" min="1" max="1"/>
+    <col width="14" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="26" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="40" customWidth="1" style="3" min="6" max="6"/>
+    <col width="40" customWidth="1" style="3" min="7" max="7"/>
+    <col width="34" customWidth="1" style="3" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="3">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Why It's Borderline</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>What To Verify Before Outreach</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Vancouver, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>NaviForm Consulting &amp; Research Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.naviform.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Full-scope ship design house (feasibility through Class approval to production data) - plausible structural/FEA overlap, but no current overflow signal (hiring, expansion, project win) or named decision-maker found in this pass.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Search for named principal/technical lead and any current job postings or recent project announcements before treating as an active prospect.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.naviform.com/about-us.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Vancouver, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Adrenalin Marine</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://adrenalinmarine.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Custom steel &amp; aluminum fabrication for marine craft - likely a small fabrication/boat-building shop; project scale and complexity not established, so unclear whether it ever needs outside structural/FEA support.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Confirm typical project size and whether any structural engineering (in-house or outsourced) is currently used.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>https://adrenalinmarine.ca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Victoria, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Gregory C. Marshall Naval Architect Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Gregory_C._Marshall_Naval_Architect</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Victoria-based naval architecture firm since 1994, but focused on styling/engineering for private luxury yachts (400+ vessels) rather than heavy industrial, offshore or commercial marine structures - core AH Structures fit (heavy lift, FEA, fatigue, sea fastening) is less obviously applicable.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Confirm whether any commercial/workboat or heavy-structural work exists alongside the yacht design practice before treating as an active prospect.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Gregory_C._Marshall_Naval_Architect</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Burnaby, BC</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>OceanWorks International Corporation</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>https://oceanworks.com/</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Burnaby-based designer/manufacturer of manned and unmanned underwater work systems with genuine marine/offshore engineering depth - but its own site names Oil &amp; Gas as a leading market (a house-rule exclusion) and the military as a customer base of nearly three decades (defense exclusion), with no clearly separate non-O&amp;G, non-defense commercial division identified.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Confirm whether any purely commercial, non-oil-and-gas, non-defense project line exists (e.g. scientific/research or offshore-wind subsea work) before treating as a prospect; as researched, it conflicts with two separate AH Structures guardrails at once.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>https://oceanworks.com/about/ ; https://oceanworks.com/about/customers/customers-oil-gas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Surrey, BC</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>AI Industries</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ai-industries.com/</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia's largest commercial structural steel fabricator by volume (12,000+ tons/year), but its described project mix is schools, offices, shopping-mall renovations and military barracks/hangars in BC, Washington, Oregon, Alaska and Hawaii - a general commercial/institutional building fabricator, not a marine, offshore or heavy-lift specialist.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Confirm whether any marine, offshore or heavy-industrial (non-building) fabrication work exists before treating as a prospect; as researched this is a building-construction fit, not an AH Structures core fit.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ai-industries.com/about-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Delta, BC</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Ideal Welders Ltd.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.idealwelders.com/</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Major Annacis Island heavy fabricator (steel structures up to 8,000 tons) with a dedicated marine department - but that marine work is explicitly a long-standing strategic-supplier relationship to Seaspan (Ahmad's own, anonymised current employer group), including work on Joint Support Ship bulbous bows under Canada's National Shipbuilding Strategy (a naval/defense program).</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>This overlaps two separate guardrails at once (employer conflict of interest; defense-program work) - exclude from outreach entirely unless Ahmad confirms a fully independent, non-Seaspan, non-defense project line exists.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.seaspan.com/stories/supplier-spotlight-joining-forces-with-ideal-welders/ ; https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/reports/2021-annual/ideal-welders.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Delta, BC</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ISM (Industrial Steel &amp; Manufacturing Inc.)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>https://ismbc.ca/</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Sizeable Delta fabricator (2.6-acre facility with direct waterway/rail access) but described project experience is commercial/LEED-certified construction and general industrial work - no marine, offshore or heavy-lift-specific evidence found in this pass.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Confirm whether any marine, offshore or heavy-lift project work exists before treating as a prospect.</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>https://ismbc.ca/services/ ; https://ismbc.ca/fabrication-shop/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3831,315 +4587,601 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:A87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="3" min="1" max="1"/>
-    <col width="14" customWidth="1" style="3" min="2" max="2"/>
-    <col width="10" customWidth="1" style="3" min="3" max="3"/>
-    <col width="26" customWidth="1" style="3" min="4" max="4"/>
-    <col width="26" customWidth="1" style="3" min="5" max="5"/>
-    <col width="40" customWidth="1" style="3" min="6" max="6"/>
-    <col width="40" customWidth="1" style="3" min="7" max="7"/>
-    <col width="34" customWidth="1" style="3" min="8" max="8"/>
+    <col width="110" customWidth="1" style="3" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="3">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Province/State</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Company Name</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Company Website</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>Why It's Borderline</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>What To Verify Before Outreach</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>Sources</t>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Batch 1: Vancouver, BC &amp; North Vancouver, BC</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Vancouver, BC</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>British Columbia</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>NaviForm Consulting &amp; Research Ltd.</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.naviform.com/</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Full-scope ship design house (feasibility through Class approval to production data) - plausible structural/FEA overlap, but no current overflow signal (hiring, expansion, project win) or named decision-maker found in this pass.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Search for named principal/technical lead and any current job postings or recent project announcements before treating as an active prospect.</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.naviform.com/about-us.php</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Vancouver, BC</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>British Columbia</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Adrenalin Marine</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>https://adrenalinmarine.ca/</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Custom steel &amp; aluminum fabrication for marine craft - likely a small fabrication/boat-building shop; project scale and complexity not established, so unclear whether it ever needs outside structural/FEA support.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Confirm typical project size and whether any structural engineering (in-house or outsourced) is currently used.</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>https://adrenalinmarine.ca/</t>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>1. Vard Marine Inc. (Vancouver) - Score 10, Priority A - named Engineering Manager, live structural/naval-architecture roles, stated growth phase.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Victoria, BC</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>British Columbia</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Gregory C. Marshall Naval Architect Ltd.</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Gregory_C._Marshall_Naval_Architect</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Victoria-based naval architecture firm since 1994, but focused on styling/engineering for private luxury yachts (400+ vessels) rather than heavy industrial, offshore or commercial marine structures - core AH Structures fit (heavy lift, FEA, fatigue, sea fastening) is less obviously applicable.</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>Confirm whether any commercial/workboat or heavy-structural work exists alongside the yacht design practice before treating as an active prospect.</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Gregory_C._Marshall_Naval_Architect</t>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>2. Allied Shipbuilders Ltd. (North Vancouver) - Score 8, Priority A - independent shipyard, named President, own engineering function.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Richmond, BC</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>British Columbia</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Marcon Metalfab Inc.</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>https://www.zoominfo.com/c/marcon-metalfab-inc/345949109</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>30+ year custom steel fabricator for transportation, construction and utilities sectors; sources disagree on whether its primary facility is in Delta or Richmond, BC (a 2025 move was reported), so city attribution is unconfirmed pending verification.</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Confirm current primary address before assigning to a specific city sheet (candidate for the Delta, BC batch if Delta is confirmed as HQ).</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>https://www.yelp.ca/biz/marcon-metalfab-delta ; https://www.metalline.info/company-marcon-metalfab-inc-in-richmond-1571</t>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>3. Capilano Maritime Design Ltd. (North Vancouver) - Score 8, Priority A - boutique naval architecture firm, named President, recent ownership/team growth.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Burnaby, BC</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>British Columbia</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>OceanWorks International Corporation</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>https://oceanworks.com/</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Burnaby-based designer/manufacturer of manned and unmanned underwater work systems with genuine marine/offshore engineering depth - but its own site names Oil &amp; Gas as a leading market (a house-rule exclusion) and the military as a customer base of nearly three decades (defense exclusion), with no clearly separate non-O&amp;G, non-defense commercial division identified.</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Confirm whether any purely commercial, non-oil-and-gas, non-defense project line exists (e.g. scientific/research or offshore-wind subsea work) before treating as a prospect; as researched, it conflicts with two separate AH Structures guardrails at once.</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>https://oceanworks.com/about/ ; https://oceanworks.com/about/customers/customers-oil-gas/</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>4. Robert Allan Ltd. (Vancouver) - Score 9, Priority A - Canada's senior private naval architecture firm, multiple live technical postings.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Surrey, BC</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>British Columbia</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>AI Industries</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>https://www.ai-industries.com/</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>British Columbia's largest commercial structural steel fabricator by volume (12,000+ tons/year), but its described project mix is schools, offices, shopping-mall renovations and military barracks/hangars in BC, Washington, Oregon, Alaska and Hawaii - a general commercial/institutional building fabricator, not a marine, offshore or heavy-lift specialist.</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Confirm whether any marine, offshore or heavy-industrial (non-building) fabrication work exists before treating as a prospect; as researched this is a building-construction fit, not an AH Structures core fit.</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>https://www.ai-industries.com/about-us</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>5. Hatch Ltd., Vancouver office - Score 7, Priority B - live marine/coastal structural postings, but very large firm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>6. Sarens, Vancouver office - Score 7, Priority B - newer regional office (est. 2019), heavy-lift/rigging fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>7. Mammoet Canada, Vancouver/Western Canada - Score 7, Priority B - heavy-lift/transport fit, but deep in-house engineering bench.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>8. JFC Steel Ltd. (North Vancouver) - Score 6, Priority C - marine/structural fabricator, engineering function unconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Marine / naval architecture consultancies. Vancouver and North Vancouver's strongest, most evidence-backed fits are independent naval architecture firms (Vard Marine, Robert Allan, Capilano Maritime Design) - all show either live technical hiring or recent growth, and all plausibly lack deep in-house FEA/fatigue specialization at all times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Lead with schedule risk relief: several of the strongest-fit firms (Vard Marine, Robert Allan, Capilano Maritime Design) show direct, current evidence of growing technical workload (open roles, ownership/team growth). Position AH Structures as ready-now overflow structural/FEA capacity that absorbs peak load on a specific vessel project without the lead time or overhead of a permanent hire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Vard Marine Inc. (stated growth phase + concurrent structural/naval-architecture postings); Robert Allan Ltd. (concurrent structural/marine technical postings); Capilano Maritime Design Ltd. (recent ownership/team growth); Sarens (newer Vancouver office opened 2019 to grow the region).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Vard Marine Inc.; Robert Allan Ltd.; Hatch Ltd. (Vancouver marine/coastal group) - all show direct evidence of structural/FEA-adjacent technical roles currently open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Mammoet Canada and Sarens (Vancouver offices) - both fit heavy lift/rigging/SPMT services, though the most credible angle for each is independent third-party verification rather than overflow drafting capacity, given their in-house engineering depth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Vard Marine Inc. (Ron Ogoniek, Engineering Manager - re-verify title first), Robert Allan Ltd. (via apply@ral.ca to find the right technical contact), Allied Shipbuilders Ltd. (Chuck Ko, President), Capilano Maritime Design Ltd. (Chris Mulder, President). Follow with Hatch, Sarens and Mammoet as broader, longer-cycle prospects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>No email address was guessed or pattern-generated; only publicly published general inboxes are recorded, clearly labelled as such. No decision-maker's LinkedIn profile was directly opened (no browser access in this session) - every named contact is flagged for re-verification before outreach. Seaspan Shipyards / Vancouver Shipyards / Vancouver Drydock were deliberately excluded from both sheets as Ahmad's own (anonymised) current employer group - a conflict of interest, not a prospect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Batch 2: Victoria, BC &amp; Richmond, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>1. Point Hope Maritime Ltd. (Victoria) - Score 9, Priority A - major repair/refit shipyard, named General Manager, recent (2019) capacity-expanding acquisition of Esquimalt Dry Dock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2. Ebco Industries Ltd. (Richmond) - Score 9, Priority A - large heavy fabrication/machining manufacturer explicitly serving Marine &amp; Offshore, Mining and Power sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>3. 3GA Marine Ltd. (Victoria) - Score 7, Priority B - naval architecture partnership serving the ferry sector; named principals not yet confidently matched to titles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>4. Bracewell Boatworks Ltd. (Richmond) - Score 6, Priority C - Fraser River vessel repair/refit yard with in-house fabrication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Shipyards and heavy fabricators with an explicit marine/offshore service line. Both A-priority prospects this batch (Point Hope Maritime, Ebco Industries) are physical yards/fabricators handling large commercial assemblies, not design boutiques - a different profile from batch 1's naval-architecture consultancies, but an equally strong fit for structural verification and lifting/rigging engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Lead with independent verification, not overflow drafting: both A-priority prospects are fabrication/repair yards whose core business is building or fixing large structures, not producing engineering calculations themselves. Position AH Structures as the independent structural/lifting-engineering check their yard, their client, or a class society may require on a given job - not as replacing an in-house team they don't have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Point Hope Maritime Ltd. - 2019 acquisition of Esquimalt Dry Dock Company clearly expanded project scope and likely strained available in-house engineering support at times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Ebco Industries Ltd. - heavy fabricated marine/offshore and mining/power assemblies are a strong match for structural/FEA verification work; 3GA Marine Ltd. - ferry structural design/refit work is FEA-adjacent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Point Hope Maritime Ltd. and Ebco Industries Ltd. both routinely handle large fabricated/refit assemblies that require lifting-lug, pad-eye and load-out engineering during shipyard or fabrication-shop handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Point Hope Maritime Ltd. (Riccardo Regosa, General Manager - re-verify title first) and Ebco Industries Ltd. (via general contact, requesting the engineering/production leadership contact rather than CEO Richard Eppich directly for a first approach). Follow with 3GA Marine Ltd. once a named principal is confirmed via their staff page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Marcon Metalfab Inc. was researched for Richmond but sources conflict on its primary address (Delta vs. Richmond, with a reported 2025 move) - routed to the Low Confidence - Review sheet pending confirmation rather than assigned to either city sheet. Gregory C. Marshall Naval Architect Ltd. (Victoria) was excluded from the main sheet as a recreational-yacht-focused practice with a less direct fit to AH Structures' heavy-lift/offshore/commercial-marine core, and is in the Review sheet instead. No email address was guessed; only publicly published general inboxes are recorded, clearly labelled as such.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Batch 3: Burnaby, BC &amp; Surrey, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>1. Global Rigging &amp; Transport (GRT) Canada Corp. (Surrey) - Score 9, Priority A - Surrey-HQ'd international heavy-lift/transport specialist, named President/Director, recent large-scale dismantling project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>2. Kiewit Infrastructure Engineers, Burnaby office - Score 9, Priority A - established Temporary Works Group with multiple current structural/coastal postings; the closest direct match to AH Structures' scope found so far.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>3. DP World Fraser Surrey (Surrey) - Score 8, Priority A - named Director of Engineering &amp; Terminal Development, active July 2026 capacity-expansion announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>4. Ausenco, Burnaby office Marine and Coastal Group - Score 7, Priority B - confirmed group and location, but only a stale (2023) hiring signal found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Temporary-works and heavy-lift/transport engineering. This batch's two strongest fits (Kiewit's Temporary Works Group and GRT) sit closer to AH Structures' actual named service lines - lifting, rigging, and construction-stage structural verification - than the naval-architecture and shipyard prospects found in prior batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Lead with named, current work: Kiewit's live Temporary Works postings and DP World's just-announced capacity expansion are both specific, dated hooks - reference them directly rather than a generic capabilities pitch, since both show a live, current reason to need extra structural/engineering capacity right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Kiewit Infrastructure Engineers, Burnaby (multiple concurrent live Temporary Works and coastal-hydraulic postings); DP World Fraser Surrey (July 2026 capacity-expansion announcement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Kiewit's Temporary Works Group (construction-stage structural verification); Ausenco's Marine and Coastal Group (port/coastal structural design) - though the latter's current demand is unconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Global Rigging &amp; Transport (core business is heavy lift/engineered transport with an explicit custom-engineering service line); DP World Fraser Surrey (quay-crane and terminal equipment handling large structural cargo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Global Rigging &amp; Transport (Andrew Johnson, President/Director - re-verify title first) and Kiewit's Temporary Works Group (via the live job posting's contact channel, or a named Temporary Works Manager once identified). Follow with DP World Fraser Surrey (Jurgen Franke, Director of Engineering &amp; Terminal Development) and Ausenco's Marine and Coastal Group once a current opening or named lead is confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>OceanWorks International (Burnaby) was excluded from the main sheet despite genuine marine-engineering depth: its own site names Oil &amp; Gas and Military as leading markets, conflicting with two separate house guardrails (no oil &amp; gas; defense exclusion) at once - routed to Review instead. AI Industries (Surrey), despite being BC's largest commercial steel fabricator by volume, was excluded as a schools/offices/military-barracks building fabricator rather than a marine/offshore/heavy-lift one. Carlson Construction Group (heavy civil/marine/industrial, multiple divisions) surfaced during this batch's research but is headquartered in North Vancouver, not Burnaby or Surrey - flagging it here rather than retroactively editing the already-reviewed North Vancouver, BC sheet; let me know if you'd like it added there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Batch 4: Delta, BC &amp; New Westminster, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>1. Fraser River Pile &amp; Dredge (GP) Inc. (New Westminster) - Score 9, Priority A - Canada's largest marine construction/dredging contractor, named President &amp; CEO Sarah Clark, pending $82.3M acquisition by Bird Construction (announced Sept 2025) creating a plausible transitional-engineering window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>2. Blue Water Systems Ltd. (Delta) - Score 8, Priority A - 35+ year marine construction/barge fabricator with engineer-reviewed designs, no defense or oil &amp; gas exposure found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>3. Amix Group / Amix Marine Services (New Westminster) - Score 7, Priority B - tug/barge operator across multiple BC coastal facilities, named Group President Tony Marra (divisional contact still to confirm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>4. Marcon Metalfab Inc. (Delta) - Score 6, Priority C - general industrial fabricator; address question from batch 2 resolved (confirmed Delta, not Richmond).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Marine construction and dredging contractors. This batch's strongest fit, FRPD, is a different profile again from prior batches: a large, established marine civil-works contractor mid-acquisition, rather than a naval architecture boutique, shipyard, or heavy-lift specialist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>For FRPD specifically, reference the pending Bird Construction acquisition directly - ownership transitions are a concrete, dated reason a company's engineering resourcing may be in flux. For Blue Water Systems and Amix, lead with the marine-structural review need implied by their own barge/vessel fleet work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>Fraser River Pile &amp; Dredge (GP) Inc. - pending ownership change (Bird Construction acquisition, announced Sept 2025) is the clearest dated overflow-adjacent signal found in any batch so far.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>Blue Water Systems Ltd. - engineer-reviewed barge and marine-infrastructure designs are a direct structural/FEA-adjacent fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>Amix Group's Amix Heavy Lift Ltd. division (Chamber of Shipping member) - a dedicated heavy-lift business line within the same New Westminster-headquartered group as Amix Marine Services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Fraser River Pile &amp; Dredge (Sarah Clark, President &amp; CEO) and Blue Water Systems Ltd. (via general contact, to identify the current owner/principal). Follow with Amix Group once a marine-services or heavy-lift-specific divisional contact is confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>The Richmond-vs-Delta address question flagged for Marcon Metalfab in batch 2 is resolved: a March 2026 listing confirms Delta as its current primary facility, so it has been moved from the Low Confidence - Review sheet into the Delta, BC sheet. Ideal Welders Ltd. (Delta) was excluded despite genuine heavy marine-fabrication scale, because its marine work is explicitly built on a long-standing Seaspan supplier relationship (Ahmad's own anonymised employer group - a conflict of interest) and includes Joint Support Ship (naval/defense) work - both separate guardrails, both triggered at once. 'Fabrication Delta,' which surfaced in Delta-BC search results as a wind-turbine-tower fabricator, was discarded entirely rather than added anywhere: it is actually headquartered in New Richmond, Quebec, and has no connection to Delta, BC beyond the name.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4150,461 +5192,375 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A66"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" style="3" min="1" max="1"/>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Batch 1: Vancouver, BC &amp; North Vancouver, BC</t>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Top prospects (this batch, ranked)</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Victoria, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Point Hope Maritime Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://pointhopemaritime.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/point-hope-maritime-limited</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Shipyard (Repair, Refit &amp; Conversion)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Shipbuilding / Ship Repair</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Vessel repair, conversion, refit and maintenance up to 360 m; access to in-house steel/aluminum fabrication and machine shop (United Engineering Ltd., a fellow Ralmax Group company)</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Full-service shipyard handling large commercial vessel repair/refit/conversion work with an in-house fabrication and machine shop; conversion and refit projects routinely need structural verification, lifting/rigging engineering, and load-out or sea-fastening calculations that can exceed in-house capacity at peak times.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Acquired the Esquimalt Dry Dock Company (EDC) in 2019, expanding access to the federally owned Esquimalt Graving Dock and clearly growing project scope/capacity. Source: https://bctugboat.com/a-proud-shipyard-history/ ; https://bctugboat.com/point-hope-maritime-in-victoria-bc/</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Over a hundred years of continuous shipyard operation on Victoria's harbour; up to 300 people working on site including 175 permanent employees plus sub-contractors. Source: https://pointhopemaritime.com/ ; https://bctugboat.com/a-proud-shipyard-history/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Riccardo Regosa</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://pointhopemaritime.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Web search snippet citing Riccardo Regosa as General Manager since 2016 (ZoomInfo-corroborated); not independently opened</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://pointhopemaritime.com/ ; https://bctugboat.com/a-proud-shipyard-history/ ; https://bctugboat.com/point-hope-maritime-in-victoria-bc/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Position AH Structures as flexible external structural/FEA and lifting-engineering capacity for repair, refit and conversion projects, complementing in-house fabrication capacity during peak workload following the 2019 EDC acquisition.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Riccardo Regosa as General Manager is drawn from a web search snippet, not a directly opened source - confirm current title before outreach. No dedicated 'engineering manager' title identified; General Manager is the most senior operational contact found.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>1. Vard Marine Inc. (Vancouver) - Score 10, Priority A - named Engineering Manager, live structural/naval-architecture roles, stated growth phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>2. Allied Shipbuilders Ltd. (North Vancouver) - Score 8, Priority A - independent shipyard, named President, own engineering function.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>3. Capilano Maritime Design Ltd. (North Vancouver) - Score 8, Priority A - boutique naval architecture firm, named President, recent ownership/team growth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>4. Robert Allan Ltd. (Vancouver) - Score 9, Priority A - Canada's senior private naval architecture firm, multiple live technical postings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>5. Hatch Ltd., Vancouver office - Score 7, Priority B - live marine/coastal structural postings, but very large firm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>6. Sarens, Vancouver office - Score 7, Priority B - newer regional office (est. 2019), heavy-lift/rigging fit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>7. Mammoet Canada, Vancouver/Western Canada - Score 7, Priority B - heavy-lift/transport fit, but deep in-house engineering bench.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>8. JFC Steel Ltd. (North Vancouver) - Score 6, Priority C - marine/structural fabricator, engineering function unconfirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Best industry segment</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Marine / naval architecture consultancies. Vancouver and North Vancouver's strongest, most evidence-backed fits are independent naval architecture firms (Vard Marine, Robert Allan, Capilano Maritime Design) - all show either live technical hiring or recent growth, and all plausibly lack deep in-house FEA/fatigue specialization at all times.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Best outreach angle for this city pair</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Lead with schedule risk relief: several of the strongest-fit firms (Vard Marine, Robert Allan, Capilano Maritime Design) show direct, current evidence of growing technical workload (open roles, ownership/team growth). Position AH Structures as ready-now overflow structural/FEA capacity that absorbs peak load on a specific vessel project without the lead time or overhead of a permanent hire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Overflow opportunities (strongest evidence)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Vard Marine Inc. (stated growth phase + concurrent structural/naval-architecture postings); Robert Allan Ltd. (concurrent structural/marine technical postings); Capilano Maritime Design Ltd. (recent ownership/team growth); Sarens (newer Vancouver office opened 2019 to grow the region).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Specialized FEA opportunities</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Vard Marine Inc.; Robert Allan Ltd.; Hatch Ltd. (Vancouver marine/coastal group) - all show direct evidence of structural/FEA-adjacent technical roles currently open.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Heavy lift / transport opportunities</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Mammoet Canada and Sarens (Vancouver offices) - both fit heavy lift/rigging/SPMT services, though the most credible angle for each is independent third-party verification rather than overflow drafting capacity, given their in-house engineering depth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Recommended outreach priority (this batch)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Contact first: Vard Marine Inc. (Ron Ogoniek, Engineering Manager - re-verify title first), Robert Allan Ltd. (via apply@ral.ca to find the right technical contact), Allied Shipbuilders Ltd. (Chuck Ko, President), Capilano Maritime Design Ltd. (Chris Mulder, President). Follow with Hatch, Sarens and Mammoet as broader, longer-cycle prospects.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Quality-control notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>No email address was guessed or pattern-generated; only publicly published general inboxes are recorded, clearly labelled as such. No decision-maker's LinkedIn profile was directly opened (no browser access in this session) - every named contact is flagged for re-verification before outreach. Seaspan Shipyards / Vancouver Shipyards / Vancouver Drydock were deliberately excluded from both sheets as Ahmad's own (anonymised) current employer group - a conflict of interest, not a prospect.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Batch 2: Victoria, BC &amp; Richmond, BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Top prospects (this batch, ranked)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>1. Point Hope Maritime Ltd. (Victoria) - Score 9, Priority A - major repair/refit shipyard, named General Manager, recent (2019) capacity-expanding acquisition of Esquimalt Dry Dock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2. Ebco Industries Ltd. (Richmond) - Score 9, Priority A - large heavy fabrication/machining manufacturer explicitly serving Marine &amp; Offshore, Mining and Power sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>3. 3GA Marine Ltd. (Victoria) - Score 7, Priority B - naval architecture partnership serving the ferry sector; named principals not yet confidently matched to titles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>4. Bracewell Boatworks Ltd. (Richmond) - Score 6, Priority C - Fraser River vessel repair/refit yard with in-house fabrication.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Best industry segment</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Shipyards and heavy fabricators with an explicit marine/offshore service line. Both A-priority prospects this batch (Point Hope Maritime, Ebco Industries) are physical yards/fabricators handling large commercial assemblies, not design boutiques - a different profile from batch 1's naval-architecture consultancies, but an equally strong fit for structural verification and lifting/rigging engineering.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Best outreach angle for this city pair</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Lead with independent verification, not overflow drafting: both A-priority prospects are fabrication/repair yards whose core business is building or fixing large structures, not producing engineering calculations themselves. Position AH Structures as the independent structural/lifting-engineering check their yard, their client, or a class society may require on a given job - not as replacing an in-house team they don't have.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Overflow opportunities (strongest evidence)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Point Hope Maritime Ltd. - 2019 acquisition of Esquimalt Dry Dock Company clearly expanded project scope and likely strained available in-house engineering support at times.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Specialized FEA opportunities</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Ebco Industries Ltd. - heavy fabricated marine/offshore and mining/power assemblies are a strong match for structural/FEA verification work; 3GA Marine Ltd. - ferry structural design/refit work is FEA-adjacent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>Heavy lift / transport opportunities</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Point Hope Maritime Ltd. and Ebco Industries Ltd. both routinely handle large fabricated/refit assemblies that require lifting-lug, pad-eye and load-out engineering during shipyard or fabrication-shop handling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>Recommended outreach priority (this batch)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Contact first: Point Hope Maritime Ltd. (Riccardo Regosa, General Manager - re-verify title first) and Ebco Industries Ltd. (via general contact, requesting the engineering/production leadership contact rather than CEO Richard Eppich directly for a first approach). Follow with 3GA Marine Ltd. once a named principal is confirmed via their staff page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>Quality-control notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>Marcon Metalfab Inc. was researched for Richmond but sources conflict on its primary address (Delta vs. Richmond, with a reported 2025 move) - routed to the Low Confidence - Review sheet pending confirmation rather than assigned to either city sheet. Gregory C. Marshall Naval Architect Ltd. (Victoria) was excluded from the main sheet as a recreational-yacht-focused practice with a less direct fit to AH Structures' heavy-lift/offshore/commercial-marine core, and is in the Review sheet instead. No email address was guessed; only publicly published general inboxes are recorded, clearly labelled as such.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>Batch 3: Burnaby, BC &amp; Surrey, BC</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Top prospects (this batch, ranked)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>1. Global Rigging &amp; Transport (GRT) Canada Corp. (Surrey) - Score 9, Priority A - Surrey-HQ'd international heavy-lift/transport specialist, named President/Director, recent large-scale dismantling project.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>2. Kiewit Infrastructure Engineers, Burnaby office - Score 9, Priority A - established Temporary Works Group with multiple current structural/coastal postings; the closest direct match to AH Structures' scope found so far.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>3. DP World Fraser Surrey (Surrey) - Score 8, Priority A - named Director of Engineering &amp; Terminal Development, active July 2026 capacity-expansion announcement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>4. Ausenco, Burnaby office Marine and Coastal Group - Score 7, Priority B - confirmed group and location, but only a stale (2023) hiring signal found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>Best industry segment</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>Temporary-works and heavy-lift/transport engineering. This batch's two strongest fits (Kiewit's Temporary Works Group and GRT) sit closer to AH Structures' actual named service lines - lifting, rigging, and construction-stage structural verification - than the naval-architecture and shipyard prospects found in prior batches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Best outreach angle for this city pair</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>Lead with named, current work: Kiewit's live Temporary Works postings and DP World's just-announced capacity expansion are both specific, dated hooks - reference them directly rather than a generic capabilities pitch, since both show a live, current reason to need extra structural/engineering capacity right now.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Overflow opportunities (strongest evidence)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>Kiewit Infrastructure Engineers, Burnaby (multiple concurrent live Temporary Works and coastal-hydraulic postings); DP World Fraser Surrey (July 2026 capacity-expansion announcement).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>Specialized FEA opportunities</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>Kiewit's Temporary Works Group (construction-stage structural verification); Ausenco's Marine and Coastal Group (port/coastal structural design) - though the latter's current demand is unconfirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>Heavy lift / transport opportunities</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>Global Rigging &amp; Transport (core business is heavy lift/engineered transport with an explicit custom-engineering service line); DP World Fraser Surrey (quay-crane and terminal equipment handling large structural cargo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>Recommended outreach priority (this batch)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="inlineStr">
-        <is>
-          <t>Contact first: Global Rigging &amp; Transport (Andrew Johnson, President/Director - re-verify title first) and Kiewit's Temporary Works Group (via the live job posting's contact channel, or a named Temporary Works Manager once identified). Follow with DP World Fraser Surrey (Jurgen Franke, Director of Engineering &amp; Terminal Development) and Ausenco's Marine and Coastal Group once a current opening or named lead is confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>Quality-control notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="9" t="inlineStr">
-        <is>
-          <t>OceanWorks International (Burnaby) was excluded from the main sheet despite genuine marine-engineering depth: its own site names Oil &amp; Gas and Military as leading markets, conflicting with two separate house guardrails (no oil &amp; gas; defense exclusion) at once - routed to Review instead. AI Industries (Surrey), despite being BC's largest commercial steel fabricator by volume, was excluded as a schools/offices/military-barracks building fabricator rather than a marine/offshore/heavy-lift one. Carlson Construction Group (heavy civil/marine/industrial, multiple divisions) surfaced during this batch's research but is headquartered in North Vancouver, not Burnaby or Surrey - flagging it here rather than retroactively editing the already-reviewed North Vancouver, BC sheet; let me know if you'd like it added there.</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Victoria, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>3GA Marine Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>http://3gamarine.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/3ga-marine-limited</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Engineering Consultancy (Naval Architecture &amp; Marine Engineering)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Naval Architecture</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Naval architecture, marine engineering, ferry design (conventional, cable and hybrid propulsion), refits and production support</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Victoria-headquartered naval architecture and marine engineering partnership serving the ferry and workboat sector; ferry refit/newbuild and production-support work regularly needs structural analysis and engineering calculations a small partnership may not carry in-house at all times.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No current hiring or expansion signal identified in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>ISO 9001:2015-certified naval architecture and marine engineering firm headquartered at 208-1497 Admirals Rd, Victoria, BC, with a second office in Burnaby; serves ferry, workboat, energy and shipping clients. Source: https://3gamarine.com/ ; https://web.victoriachamber.ca/Naval-Architects/3GA-Marine-Limited-4942</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://3gamarine.com/staff/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>https://3gamarine.com/staff/</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://3gamarine.com/ ; https://3gamarine.com/engineering/ ; https://web.victoriachamber.ca/Naval-Architects/3GA-Marine-Limited-4942</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural/FEA support as an independent extension of a small partnership's engineering bench for ferry refit or newbuild production-support phases.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Named principals only partially confirmed this pass (a founding naval architect with 40+ years and a VP/senior partner who joined 2013 are both referenced in search results, alongside staff named David Mietla and Daniel McIntyre, without a clear title-to-name match). Confirm via https://3gamarine.com/staff/ before outreach rather than naming an individual now.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4769,7 +5725,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Victoria, BC</t>
+          <t>Richmond, BC</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -4784,79 +5740,79 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Point Hope Maritime Ltd.</t>
+          <t>Ebco Industries Ltd.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://pointhopemaritime.com/</t>
+          <t>https://ebco.com/</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/company/point-hope-maritime-limited</t>
+          <t>https://ca.linkedin.com/company/ebco-industries-ltd.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Shipyard (Repair, Refit &amp; Conversion)</t>
+          <t>Heavy Fabrication &amp; Machining Manufacturer</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Marine / Shipbuilding / Ship Repair</t>
+          <t>Industrial / Marine &amp; Offshore / Mining / Power</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Vessel repair, conversion, refit and maintenance up to 360 m; access to in-house steel/aluminum fabrication and machine shop (United Engineering Ltd., a fellow Ralmax Group company)</t>
+          <t>Heavy fabrication, heavy machining, precision sheet metal and turnkey assembly for large equipment and structures</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Full-service shipyard handling large commercial vessel repair/refit/conversion work with an in-house fabrication and machine shop; conversion and refit projects routinely need structural verification, lifting/rigging engineering, and load-out or sea-fastening calculations that can exceed in-house capacity at peak times.</t>
+          <t>One of the largest heavy fabrication and machining facilities on the West Coast, explicitly serving Marine &amp; Offshore, Mining &amp; Aggregates, and Power &amp; Hydro Generation among its industries; large fabricated assemblies for these sectors routinely require structural verification, lifting-lug design, and load calculations.</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Acquired the Esquimalt Dry Dock Company (EDC) in 2019, expanding access to the federally owned Esquimalt Graving Dock and clearly growing project scope/capacity. Source: https://bctugboat.com/a-proud-shipyard-history/ ; https://bctugboat.com/point-hope-maritime-in-victoria-bc/</t>
+          <t>No current hiring or expansion signal identified in this pass.</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Over a hundred years of continuous shipyard operation on Victoria's harbour; up to 300 people working on site including 175 permanent employees plus sub-contractors. Source: https://pointhopemaritime.com/ ; https://bctugboat.com/a-proud-shipyard-history/</t>
+          <t>Founded 1956; 240,000 sq ft facility on a 13-acre site in Richmond, BC; self-described industries served include Marine &amp; Offshore and Mining &amp; Aggregates. Source: https://ebco.com/ ; https://ebco.com/machining/ ; https://en.wikipedia.org/wiki/Ebco_Industries</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>Riccardo Regosa</t>
+          <t>Richard Eppich</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="P2" s="5" t="inlineStr"/>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>https://pointhopemaritime.com/</t>
+          <t>https://ebco.com/</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Web search snippet citing Riccardo Regosa as General Manager since 2016 (ZoomInfo-corroborated); not independently opened</t>
+          <t>Web search snippet (Wikipedia-corroborated); not independently opened</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>https://pointhopemaritime.com/ ; https://bctugboat.com/a-proud-shipyard-history/ ; https://bctugboat.com/point-hope-maritime-in-victoria-bc/</t>
+          <t>https://ebco.com/ ; https://ebco.com/machining/ ; https://en.wikipedia.org/wiki/Ebco_Industries</t>
         </is>
       </c>
       <c r="U2" s="5" t="n">
@@ -4869,19 +5825,19 @@
       </c>
       <c r="W2" s="5" t="inlineStr">
         <is>
-          <t>Position AH Structures as flexible external structural/FEA and lifting-engineering capacity for repair, refit and conversion projects, complementing in-house fabrication capacity during peak workload following the 2019 EDC acquisition.</t>
+          <t>Offer independent structural verification and lifting/rigging engineering (pad-eye, lifting-lug, load-out) for large marine, offshore and heavy-industrial fabricated assemblies, positioned as a check independent of Ebco's own production engineering.</t>
         </is>
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>Riccardo Regosa as General Manager is drawn from a web search snippet, not a directly opened source - confirm current title before outreach. No dedicated 'engineering manager' title identified; General Manager is the most senior operational contact found.</t>
+          <t>No dedicated engineering-department contact identified this pass; Richard Eppich (CEO) is the most senior confirmed contact for a mid-size private manufacturer per the master prompt's guidance to use an owner/founder-level contact for smaller companies. Worth a follow-up LinkedIn search for an Engineering Manager or Chief Engineer title before outreach.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Victoria, BC</t>
+          <t>Richmond, BC</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4896,37 +5852,33 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>3GA Marine Ltd.</t>
+          <t>Bracewell Boatworks Ltd. (Bracewell Marine Group)</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>http://3gamarine.com/</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>https://ca.linkedin.com/company/3ga-marine-limited</t>
-        </is>
-      </c>
+          <t>https://www.bracewellmarinegroup.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Engineering Consultancy (Naval Architecture &amp; Marine Engineering)</t>
+          <t>Marine Fabrication &amp; Refit Yard</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Marine / Naval Architecture</t>
+          <t>Marine / Vessel Repair &amp; Refit</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Naval architecture, marine engineering, ferry design (conventional, cable and hybrid propulsion), refits and production support</t>
+          <t>Aluminum and stainless-steel fabrication and welding, vessel repair/refit for craft up to ~150 tons</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Victoria-headquartered naval architecture and marine engineering partnership serving the ferry and workboat sector; ferry refit/newbuild and production-support work regularly needs structural analysis and engineering calculations a small partnership may not carry in-house at all times.</t>
+          <t>Fraser River boatyard with in-house aluminum/stainless fabrication and welding for vessel refit and repair; larger refit or structural repair jobs can require structural verification or engineering sign-off beyond the yard's own trades staff.</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -4936,12 +5888,12 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>No current hiring or expansion signal identified in this pass.</t>
+          <t>No hiring or expansion signal identified in this pass.</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>ISO 9001:2015-certified naval architecture and marine engineering firm headquartered at 208-1497 Admirals Rd, Victoria, BC, with a second office in Burnaby; serves ferry, workboat, energy and shipping clients. Source: https://3gamarine.com/ ; https://web.victoriachamber.ca/Naval-Architects/3GA-Marine-Limited-4942</t>
+          <t>Located at Shelter Island Marina, 185-6831 Graybar Road, Richmond, BC; in-house fabrication, welding and repair departments serving vessels up to approximately 150 tons. Source: https://newswire.com/bracewell-boatworks-richmond-bc/31811 ; https://www.yellowpages.ca/bus/British-Columbia/Richmond/Bracewell-Boatworks/2136508.html</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr"/>
@@ -4949,36 +5901,40 @@
       <c r="P3" s="5" t="inlineStr"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>https://3gamarine.com/staff/</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr"/>
+          <t>https://www.bracewellmarinegroup.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@bracewellboatworks.com (general company inbox)</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>https://3gamarine.com/staff/</t>
+          <t>Company website / Yellow Pages listing</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>https://3gamarine.com/ ; https://3gamarine.com/engineering/ ; https://web.victoriachamber.ca/Naval-Architects/3GA-Marine-Limited-4942</t>
+          <t>https://newswire.com/bracewell-boatworks-richmond-bc/31811 ; https://www.bracewellmarinegroup.com/</t>
         </is>
       </c>
       <c r="U3" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W3" s="5" t="inlineStr">
         <is>
-          <t>Offer structural/FEA support as an independent extension of a small partnership's engineering bench for ferry refit or newbuild production-support phases.</t>
+          <t>Offer occasional structural verification or repair-scope engineering sign-off for larger refit jobs, positioned as lower-cost, on-call support rather than a standing arrangement.</t>
         </is>
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Named principals only partially confirmed this pass (a founding naval architect with 40+ years and a VP/senior partner who joined 2013 are both referenced in search results, alongside staff named David Mietla and Daniel McIntyre, without a clear title-to-name match). Confirm via https://3gamarine.com/staff/ before outreach rather than naming an individual now.</t>
+          <t>Smaller repair/refit yard without a clearly design-heavy scope; treat as a lower-probability, occasional-verification prospect rather than a recurring overflow-capacity one. No named owner/manager identified this pass.</t>
         </is>
       </c>
     </row>
@@ -5148,7 +6104,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Richmond, BC</t>
+          <t>Burnaby, BC</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -5163,79 +6119,71 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Ebco Industries Ltd.</t>
+          <t>Kiewit Infrastructure Engineers (Burnaby office)</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://ebco.com/</t>
+          <t>https://www.kiewit.com/</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/company/ebco-industries-ltd.</t>
+          <t>https://ca.linkedin.com/company/kiewit</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Heavy Fabrication &amp; Machining Manufacturer</t>
+          <t>Multidisciplinary Engineering Consultancy (within a major contractor)</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Industrial / Marine &amp; Offshore / Mining / Power</t>
+          <t>Civil / Marine / Structural Infrastructure Engineering</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Heavy fabrication, heavy machining, precision sheet metal and turnkey assembly for large equipment and structures</t>
+          <t>Structural, civil, coastal/hydraulic and temporary-works engineering; marine engineering capability within the group</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>One of the largest heavy fabrication and machining facilities on the West Coast, explicitly serving Marine &amp; Offshore, Mining &amp; Aggregates, and Power &amp; Hydro Generation among its industries; large fabricated assemblies for these sectors routinely require structural verification, lifting-lug design, and load calculations.</t>
+          <t>Burnaby office runs an established Temporary Works Group plus coastal/hydraulic engineering roles - temporary-works engineering (formwork, shoring, lifting and construction-stage structures) is a direct, close match to AH Structures' core scope, and live multiple concurrent postings show current workload.</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>No current hiring or expansion signal identified in this pass.</t>
+          <t>Concurrent live postings found: 'Structural EIT - Temporary Works' and 'Sr Structural Engineer - Temporary Works' (Burnaby, BC), plus 'Senior Coastal Hydraulic Engineer'. Source: https://kiewitcareers.kiewit.com/job/Burnaby-Structural-EIT-Temporary-Works-(Burnaby,-BC)-2026-Brit/1355010800/ ; https://ca.linkedin.com/jobs/view/sr-structural-engineer-temporary-works-kiewit-infrastructure-engineers-at-kiewit-3811076424</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Founded 1956; 240,000 sq ft facility on a 13-acre site in Richmond, BC; self-described industries served include Marine &amp; Offshore and Mining &amp; Aggregates. Source: https://ebco.com/ ; https://ebco.com/machining/ ; https://en.wikipedia.org/wiki/Ebco_Industries</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>Richard Eppich</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>Kiewit Canada's Burnaby division covers structural, civil, piping, mechanical, process, electrical, instrument and control disciplines, with marine engineering design work confirmed as part of its scope.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
       <c r="P2" s="5" t="inlineStr"/>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>https://ebco.com/</t>
+          <t>https://ca.linkedin.com/company/kiewit</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Web search snippet (Wikipedia-corroborated); not independently opened</t>
+          <t>Kiewit careers site / LinkedIn job postings</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>https://ebco.com/ ; https://ebco.com/machining/ ; https://en.wikipedia.org/wiki/Ebco_Industries</t>
+          <t>https://kiewitcareers.kiewit.com/ ; https://ca.linkedin.com/jobs/kiewit-jobs-burnaby-bc</t>
         </is>
       </c>
       <c r="U2" s="5" t="n">
@@ -5248,19 +6196,19 @@
       </c>
       <c r="W2" s="5" t="inlineStr">
         <is>
-          <t>Offer independent structural verification and lifting/rigging engineering (pad-eye, lifting-lug, load-out) for large marine, offshore and heavy-industrial fabricated assemblies, positioned as a check independent of Ebco's own production engineering.</t>
+          <t>Reference the Temporary Works Group's current hiring directly - offer AH Structures as flexible external capacity for temporary-works structural verification, lifting/rigging calculations or FEA on active project phases while Kiewit fills permanent roles.</t>
         </is>
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>No dedicated engineering-department contact identified this pass; Richard Eppich (CEO) is the most senior confirmed contact for a mid-size private manufacturer per the master prompt's guidance to use an owner/founder-level contact for smaller companies. Worth a follow-up LinkedIn search for an Engineering Manager or Chief Engineer title before outreach.</t>
+          <t>No named Temporary Works Group manager identified this pass; large contractor, so the realistic entry point is a specific project's temporary-works lead rather than a cold general approach. Worth a follow-up LinkedIn search for 'Kiewit' + 'Temporary Works Manager' before outreach.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Richmond, BC</t>
+          <t>Burnaby, BC</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -5275,33 +6223,37 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Bracewell Boatworks Ltd. (Bracewell Marine Group)</t>
+          <t>Ausenco (Burnaby office, Marine and Coastal Group)</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>https://www.bracewellmarinegroup.com/</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr"/>
+          <t>https://www.ausenco.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/ausenco</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Marine Fabrication &amp; Refit Yard</t>
+          <t>Multidisciplinary Engineering Consultancy</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Marine / Vessel Repair &amp; Refit</t>
+          <t>Marine / Coastal / Port Infrastructure Engineering</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Aluminum and stainless-steel fabrication and welding, vessel repair/refit for craft up to ~150 tons</t>
+          <t>Marine and port structural design (wharves, jetties, piers, coastal protection), concept through detailed design</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Fraser River boatyard with in-house aluminum/stainless fabrication and welding for vessel refit and repair; larger refit or structural repair jobs can require structural verification or engineering sign-off beyond the yard's own trades staff.</t>
+          <t>Confirmed dedicated Marine and Coastal Group based out of the Burnaby office, designing port and coastal structures - a plausible source of periodic structural/FEA overflow work, though the only posting found is from December 2023 so treat as a confirmed capability rather than a current hiring signal.</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -5311,12 +6263,12 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>No hiring or expansion signal identified in this pass.</t>
+          <t>A 'Marine Structural Engineer' posting for the Burnaby office was found dated December 2023 - this confirms the group's existence and location but is too old to treat as a current overflow signal. Source: https://www.engineeringcareers.ca/job/2023170/marine-structural-engineer-burnaby/</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Located at Shelter Island Marina, 185-6831 Graybar Road, Richmond, BC; in-house fabrication, welding and repair departments serving vessels up to approximately 150 tons. Source: https://newswire.com/bracewell-boatworks-richmond-bc/31811 ; https://www.yellowpages.ca/bus/British-Columbia/Richmond/Bracewell-Boatworks/2136508.html</t>
+          <t>Global EPCM engineering firm; Marine and Coastal Group supports planning, design and delivery of port, coastal and marine infrastructure projects including concept through detailed design and construction support.</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr"/>
@@ -5324,40 +6276,36 @@
       <c r="P3" s="5" t="inlineStr"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>https://www.bracewellmarinegroup.com/contact-us/</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>info@bracewellboatworks.com (general company inbox)</t>
-        </is>
-      </c>
+          <t>https://ca.linkedin.com/company/ausenco</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Company website / Yellow Pages listing</t>
+          <t>Job posting aggregators (LinkedIn, Indeed, SimplyHired, engineeringcareers.ca)</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>https://newswire.com/bracewell-boatworks-richmond-bc/31811 ; https://www.bracewellmarinegroup.com/</t>
+          <t>https://www.engineeringcareers.ca/job/2023170/marine-structural-engineer-burnaby/</t>
         </is>
       </c>
       <c r="U3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W3" s="5" t="inlineStr">
         <is>
-          <t>Offer occasional structural verification or repair-scope engineering sign-off for larger refit jobs, positioned as lower-cost, on-call support rather than a standing arrangement.</t>
+          <t>Position as independent marine/coastal structural capacity for peak workload on active port and coastal projects, given the group's confirmed scope and location.</t>
         </is>
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Smaller repair/refit yard without a clearly design-heavy scope; treat as a lower-probability, occasional-verification prospect rather than a recurring overflow-capacity one. No named owner/manager identified this pass.</t>
+          <t>No named group lead identified this pass, and the only direct evidence found is a stale (2023) posting - re-check for current Burnaby marine/coastal openings before treating this as a live overflow opportunity.</t>
         </is>
       </c>
     </row>
@@ -5527,7 +6475,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Burnaby, BC</t>
+          <t>Surrey, BC</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -5542,71 +6490,79 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Kiewit Infrastructure Engineers (Burnaby office)</t>
+          <t>Global Rigging &amp; Transport (GRT) Canada Corp.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://www.kiewit.com/</t>
+          <t>https://www.globalrigging.com/</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/company/kiewit</t>
+          <t>https://www.linkedin.com/company/globalriggingandtransport</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Multidisciplinary Engineering Consultancy (within a major contractor)</t>
+          <t>Heavy Lift &amp; Heavy Transport Contractor</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Civil / Marine / Structural Infrastructure Engineering</t>
+          <t>Heavy Lift / Heavy Transport</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Structural, civil, coastal/hydraulic and temporary-works engineering; marine engineering capability within the group</t>
+          <t>Heavy lift, engineered transport, crane moving/modification/repair/assembly/dismantling, load testing, custom engineering</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Burnaby office runs an established Temporary Works Group plus coastal/hydraulic engineering roles - temporary-works engineering (formwork, shoring, lifting and construction-stage structures) is a direct, close match to AH Structures' core scope, and live multiple concurrent postings show current workload.</t>
+          <t>Surrey-headquartered international heavy-lift and heavy-transport specialist that explicitly offers 'custom engineering' as part of its service line - a strong, direct fit for lifting, rigging, pad-eye and sea-fastening calculation work, especially at peak project load across its worldwide project sites.</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Concurrent live postings found: 'Structural EIT - Temporary Works' and 'Sr Structural Engineer - Temporary Works' (Burnaby, BC), plus 'Senior Coastal Hydraulic Engineer'. Source: https://kiewitcareers.kiewit.com/job/Burnaby-Structural-EIT-Temporary-Works-(Burnaby,-BC)-2026-Brit/1355010800/ ; https://ca.linkedin.com/jobs/view/sr-structural-engineer-temporary-works-kiewit-infrastructure-engineers-at-kiewit-3811076424</t>
+          <t>Current live postings found (Safety Officer; Office Administration Assistant, Port Kells/Surrey facility) confirm active operations, but no engineering-specific hiring signal was found in this pass. Source: https://ca.indeed.com/cmp/Global-Rigging-&amp;-Transport/locations/BC/Surrey</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Kiewit Canada's Burnaby division covers structural, civil, piping, mechanical, process, electrical, instrument and control disciplines, with marine engineering design work confirmed as part of its scope.</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr"/>
+          <t>Recent project: demolition of a 170ft, 1200-ton STS crane on Vancouver Island, BC - demonstrates large-scale heavy-lift/dismantling capability. Source: https://www.globalrigging.com/post/global-rigging-transport-grt-successfully-demolishes-170ft-1200-ton-sts-crane-in-vancouver-islan</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Andrew Johnson</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President / Director</t>
+        </is>
+      </c>
       <c r="P2" s="5" t="inlineStr"/>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/company/kiewit</t>
+          <t>https://www.globalrigging.com/about-grt</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Kiewit careers site / LinkedIn job postings</t>
+          <t>Company website / business directory listings (CWB Group, BBB)</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>https://kiewitcareers.kiewit.com/ ; https://ca.linkedin.com/jobs/kiewit-jobs-burnaby-bc</t>
+          <t>https://www.globalrigging.com/about-grt ; https://www.cwbgroup.org/directory/certified-companies/2c228c48-b569-e811-a965-000d3af3dfc5</t>
         </is>
       </c>
       <c r="U2" s="5" t="n">
@@ -5619,19 +6575,19 @@
       </c>
       <c r="W2" s="5" t="inlineStr">
         <is>
-          <t>Reference the Temporary Works Group's current hiring directly - offer AH Structures as flexible external capacity for temporary-works structural verification, lifting/rigging calculations or FEA on active project phases while Kiewit fills permanent roles.</t>
+          <t>Position AH Structures as independent lift/rigging engineering capacity (pad-eye, sea-fastening, load calculations) that can flex with GRT's project-by-project engineering demand on named heavy-lift and dismantling jobs.</t>
         </is>
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>No named Temporary Works Group manager identified this pass; large contractor, so the realistic entry point is a specific project's temporary-works lead rather than a cold general approach. Worth a follow-up LinkedIn search for 'Kiewit' + 'Temporary Works Manager' before outreach.</t>
+          <t>Andrew Johnson's title was drawn from web search snippets, not a directly opened source - confirm current role before outreach. Thomas Felch (VP/Director) and Erin Johnson (Business Development Manager) are alternative named contacts worth considering.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Burnaby, BC</t>
+          <t>Surrey, BC</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -5646,89 +6602,97 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Ausenco (Burnaby office, Marine and Coastal Group)</t>
+          <t>DP World Fraser Surrey (Fraser Surrey Docks)</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>https://www.ausenco.com/</t>
+          <t>https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/company/ausenco</t>
+          <t>https://www.linkedin.com/company/dp-world</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Multidisciplinary Engineering Consultancy</t>
+          <t>Marine Terminal Operator</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Marine / Coastal / Port Infrastructure Engineering</t>
+          <t>Marine / Port Infrastructure</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Marine and port structural design (wharves, jetties, piers, coastal protection), concept through detailed design</t>
+          <t>Marine terminal operations handling structural products (steel plate, coil, pipe, beam) and quay-crane cargo up to 70 tons; in-house Engineering &amp; Terminal Development function</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Confirmed dedicated Marine and Coastal Group based out of the Burnaby office, designing port and coastal structures - a plausible source of periodic structural/FEA overflow work, though the only posting found is from December 2023 so treat as a confirmed capability rather than a current hiring signal.</t>
+          <t>Largest multi-purpose marine terminal on the North American West Coast with a confirmed, named Director of Engineering &amp; Terminal Development - terminal infrastructure, berth/quay-crane structures and equipment upgrades plausibly need structural verification or lifting-engineering support beyond the in-house team's day-to-day capacity.</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>A 'Marine Structural Engineer' posting for the Burnaby office was found dated December 2023 - this confirms the group's existence and location but is too old to treat as a current overflow signal. Source: https://www.engineeringcareers.ca/job/2023170/marine-structural-engineer-burnaby/</t>
+          <t>DP World announced (July 2026) it is unlocking up to 2 million tonnes of additional export capacity at Fraser Surrey Terminal, indicating an active capacity-expansion program that plausibly requires structural/terminal engineering support beyond business-as-usual. Source: https://www.dpworld.com/en/news/usa/2026_07_09_fraser-surrey-training-wall</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Global EPCM engineering firm; Marine and Coastal Group supports planning, design and delivery of port, coastal and marine infrastructure projects including concept through detailed design and construction support.</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr"/>
+          <t>Terminal features 6 deep-sea berths, a dolphin berth, a hydraulic barge ramp, and 3 quay cranes up to 70 tons; handles significant volumes of imported structural steel products. Source: https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Jurgen Franke</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Director, Engineering &amp; Terminal Development</t>
+        </is>
+      </c>
       <c r="P3" s="5" t="inlineStr"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/company/ausenco</t>
+          <t>https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr"/>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Job posting aggregators (LinkedIn, Indeed, SimplyHired, engineeringcareers.ca)</t>
+          <t>Web search snippet corroborated by company org context (Craft.co executives listing)</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>https://www.engineeringcareers.ca/job/2023170/marine-structural-engineer-burnaby/</t>
+          <t>https://www.dpworld.com/en/news/usa/2026_07_09_fraser-surrey-training-wall ; https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
         </is>
       </c>
       <c r="U3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="W3" s="5" t="inlineStr">
         <is>
-          <t>Position as independent marine/coastal structural capacity for peak workload on active port and coastal projects, given the group's confirmed scope and location.</t>
+          <t>Reference the recently announced capacity-expansion program directly - offer AH Structures as independent structural/lifting-engineering verification capacity for terminal infrastructure and equipment work tied to that expansion.</t>
         </is>
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>No named group lead identified this pass, and the only direct evidence found is a stale (2023) posting - re-check for current Burnaby marine/coastal openings before treating this as a live overflow opportunity.</t>
+          <t>Jurgen Franke's title/name was drawn from a web search snippet, not a directly opened source - confirm current role before outreach. DP World is a very large global operator; a terminal-level contact like this is the right altitude rather than corporate head office.</t>
         </is>
       </c>
     </row>
@@ -5898,7 +6862,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Surrey, BC</t>
+          <t>Delta, BC</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -5913,37 +6877,33 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Global Rigging &amp; Transport (GRT) Canada Corp.</t>
+          <t>Blue Water Systems Ltd.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://www.globalrigging.com/</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/globalriggingandtransport</t>
-        </is>
-      </c>
+          <t>https://bluewatersystems.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Heavy Lift &amp; Heavy Transport Contractor</t>
+          <t>Marine Construction &amp; Fabrication</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Heavy Lift / Heavy Transport</t>
+          <t>Marine / Marine Infrastructure</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Heavy lift, engineered transport, crane moving/modification/repair/assembly/dismantling, load testing, custom engineering</t>
+          <t>Design, fabrication and installation of marine infrastructure: barges, docks, floats, piers, ramps and bridges</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Surrey-headquartered international heavy-lift and heavy-transport specialist that explicitly offers 'custom engineering' as part of its service line - a strong, direct fit for lifting, rigging, pad-eye and sea-fastening calculation work, especially at peak project load across its worldwide project sites.</t>
+          <t>Delta-based marine construction specialist whose barge and marine-structure designs are engineer-reviewed; a 35+ year track record of custom marine fabrication is a direct, non-defense, non-oil-and-gas fit for structural verification and design-review support.</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -5953,43 +6913,35 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Current live postings found (Safety Officer; Office Administration Assistant, Port Kells/Surrey facility) confirm active operations, but no engineering-specific hiring signal was found in this pass. Source: https://ca.indeed.com/cmp/Global-Rigging-&amp;-Transport/locations/BC/Surrey</t>
+          <t>No current hiring or expansion signal identified in this pass.</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Recent project: demolition of a 170ft, 1200-ton STS crane on Vancouver Island, BC - demonstrates large-scale heavy-lift/dismantling capability. Source: https://www.globalrigging.com/post/global-rigging-transport-grt-successfully-demolishes-170ft-1200-ton-sts-crane-in-vancouver-islan</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>Andrew Johnson</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>President / Director</t>
-        </is>
-      </c>
+          <t>Over 35 years building steel and aluminum barges, pontoon platforms, work barges, docks, floats and piers on the West Coast; company states barge designs are reviewed by engineers. Source: https://bluewatersystems.ca/about-us/ ; https://bluewatersystems.ca/barges</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
       <c r="P2" s="5" t="inlineStr"/>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>https://www.globalrigging.com/about-grt</t>
+          <t>https://bluewatersystems.ca/about-us/</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website / business directory listings (CWB Group, BBB)</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>https://www.globalrigging.com/about-grt ; https://www.cwbgroup.org/directory/certified-companies/2c228c48-b569-e811-a965-000d3af3dfc5</t>
+          <t>https://bluewatersystems.ca/ ; https://bluewatersystems.ca/about-us/ ; https://bluewatersystems.ca/barges</t>
         </is>
       </c>
       <c r="U2" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V2" s="5" t="inlineStr">
         <is>
@@ -5998,19 +6950,19 @@
       </c>
       <c r="W2" s="5" t="inlineStr">
         <is>
-          <t>Position AH Structures as independent lift/rigging engineering capacity (pad-eye, sea-fastening, load calculations) that can flex with GRT's project-by-project engineering demand on named heavy-lift and dismantling jobs.</t>
+          <t>Offer structural design/verification support for barge and marine-infrastructure projects, positioned as the engineering review partner referenced in their own marketing.</t>
         </is>
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>Andrew Johnson's title was drawn from web search snippets, not a directly opened source - confirm current role before outreach. Thomas Felch (VP/Director) and Erin Johnson (Business Development Manager) are alternative named contacts worth considering.</t>
+          <t>Founded by Lane Rud in 1988; current ownership/leadership not confirmed in this pass (no name found for 2024-2026). Confirm the current owner/principal via a direct call before outreach.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Surrey, BC</t>
+          <t>Delta, BC</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -6025,97 +6977,93 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>DP World Fraser Surrey (Fraser Surrey Docks)</t>
+          <t>Marcon Metalfab Inc.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
+          <t>https://www.marconmetalfab.com/</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/dp-world</t>
+          <t>https://ca.linkedin.com/company/marcon-metalfab</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Marine Terminal Operator</t>
+          <t>Custom Steel Fabricator</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Marine / Port Infrastructure</t>
+          <t>Industrial / Transportation / Utilities Fabrication</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Marine terminal operations handling structural products (steel plate, coil, pipe, beam) and quay-crane cargo up to 70 tons; in-house Engineering &amp; Terminal Development function</t>
+          <t>Custom-fabricated steel and rubber products for transportation, building construction and utilities industries</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Largest multi-purpose marine terminal on the North American West Coast with a confirmed, named Director of Engineering &amp; Terminal Development - terminal infrastructure, berth/quay-crane structures and equipment upgrades plausibly need structural verification or lifting-engineering support beyond the in-house team's day-to-day capacity.</t>
+          <t>Over 30 years as a Western Canada custom steel fabricator; large fabricated transportation and utility assemblies can require structural verification or lifting-engineering support the shop may not staff in-house.</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>DP World announced (July 2026) it is unlocking up to 2 million tonnes of additional export capacity at Fraser Surrey Terminal, indicating an active capacity-expansion program that plausibly requires structural/terminal engineering support beyond business-as-usual. Source: https://www.dpworld.com/en/news/usa/2026_07_09_fraser-surrey-training-wall</t>
+          <t>Not established in this pass.</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Terminal features 6 deep-sea berths, a dolphin berth, a hydraulic barge ramp, and 3 quay cranes up to 70 tons; handles significant volumes of imported structural steel products. Source: https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>Jurgen Franke</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>Director, Engineering &amp; Terminal Development</t>
-        </is>
-      </c>
+          <t>Primary facility confirmed at 7156 Brown St, Delta, BC as of March 2026 (a 2025 office move was reported but the Delta address remains current per recent listings). Source: https://www.yelp.ca/biz/marcon-metalfab-delta</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr"/>
+          <t>https://www.zoominfo.com/c/marcon-metalfab-inc/345949109</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@marconmetalfab.com (general company inbox)</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Web search snippet corroborated by company org context (Craft.co executives listing)</t>
+          <t>Company website / directory listings</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>https://www.dpworld.com/en/news/usa/2026_07_09_fraser-surrey-training-wall ; https://www.dpworld.com/en/ports-terminals/canada/fraser-surrey-docks</t>
+          <t>https://www.yelp.ca/biz/marcon-metalfab-delta ; https://www.zoominfo.com/c/marcon-metalfab-inc/345949109</t>
         </is>
       </c>
       <c r="U3" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W3" s="5" t="inlineStr">
         <is>
-          <t>Reference the recently announced capacity-expansion program directly - offer AH Structures as independent structural/lifting-engineering verification capacity for terminal infrastructure and equipment work tied to that expansion.</t>
+          <t>Offer structural verification or lifting-engineering support for larger transportation/utility fabrication packages.</t>
         </is>
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Jurgen Franke's title/name was drawn from a web search snippet, not a directly opened source - confirm current role before outreach. DP World is a very large global operator; a terminal-level contact like this is the right altitude rather than corporate head office.</t>
+          <t>Previously flagged in the Low Confidence - Review sheet (batch 2) with an unconfirmed Delta-vs-Richmond address; now resolved - a March 2026 listing confirms Delta as the current primary facility, so this entry replaces that review-sheet flag. Not a marine/heavy-lift specialist; general industrial fabrication fit only.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -14,6 +14,8 @@
     <sheet name="Delta, BC" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="New Westminster, BC" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Low Confidence - Review" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Coquitlam, BC" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Port Coquitlam, BC" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -25,6 +27,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Delta, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'New Westminster, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Low Confidence - Review'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Coquitlam, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Port Coquitlam, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3391,6 +3395,660 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Coquitlam, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Kay-Son Steel Fabricators Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kay-son.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/kay-son-steel-fabricators-ltd-</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Industrial Steel Fabricator</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial / Marine / Institutional Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel fabrication (AISC/CWB certified) for bulk material handling, environmental, mining/minerals, processing plants, pulp &amp; paper, and marine sectors</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>60-year Coquitlam fabricator whose self-described sector list explicitly includes marine, alongside bulk-material-handling and processing-plant work - large fabricated marine/industrial assemblies can require structural verification and lifting-lug/rigging calculations beyond in-house capacity.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>In continuous operation since 1965; AISC 201-06 and CWB (CSA W47.1 Division 1) certified; self-describes fabrication work across commercial, institutional, marine and other heavy-industrial sectors. Source: https://www.kay-son.com/about-us</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Paul Buchmann</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kay-son.com/about-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>admin@kay-son.com (general company inbox)</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (management team listing)</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kay-son.com/ ; https://www.kay-son.com/about-us</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural verification, lifting-lug and rigging calculations for the marine and bulk-material-handling portions of their fabrication work specifically - a generalist fabricator across many sectors, so lead with the marine/industrial angle rather than a broad pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Kay-Son's own materials list processing-plant sectors including oil/gas and pulp &amp; paper alongside marine - per AH Structures' house convention of never framing its own services around oil &amp; gas, any outreach or case-study material used with this contact should reference the marine/bulk-handling side of their work only. No individual decision-maker's title was confirmed beyond General Manager; re-verify Paul Buchmann's current role before outreach.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Port Coquitlam, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>The Portal Crane Group</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://theportalcranegroup.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Crane &amp; Hoist Sales, Service and Certification</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial / Heavy Lift Equipment</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Certification, inspection and service of container cranes, rubber-tyre and rail-mounted gantry cranes, stacker-reclaimers and ship loaders; crane braking systems</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Port Coquitlam-headquartered crane and hoist specialist with a dedicated in-house Engineering role - certifying and servicing large port/industrial cranes routinely requires structural load calculations, inspection engineering and lifting-capacity verification, a close match to AH Structures' core scope.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Serving the crane and hoist industry since 1987; three divisions (Portal Crane, Precision Crane, BRELX); certifies and services container cranes, gantry cranes, stacker-reclaimers and ship loaders. Source: https://theportalcranegroup.com/about-us</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Timothy McCullough</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Manager, Engineering</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://theportalcranegroup.com/about-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>ZoomInfo (contact listing corroborated by company website's stated Engineering function)</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://theportalcranegroup.com/ ; https://theportalcranegroup.com/about-us</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach the named Engineering Manager directly, offering AH Structures as independent structural/lifting-capacity verification support for crane certification and inspection work during peak periods.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Timothy McCullough's title was drawn from a ZoomInfo listing, not a directly opened source - confirm current role before outreach. Steve Robinson (General Manager) is an alternative named contact if the engineering-specific route doesn't land.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Port Coquitlam, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>MTEC Engineering</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://mtecengineeringco.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Engineering Consultancy (boutique)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Industrial / Structural &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Structural engineering (steel, concrete, timber structures, cranes, lifting devices, fall-arrest systems) and mechanical engineering (conveying/bulk-handling systems and machinery) for Lower Mainland industrial clients</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Small Port Coquitlam-based industrial engineering consultancy whose stated scope - cranes, lifting devices, fall-arrest systems, bulk-handling machinery - overlaps closely with AH Structures' own services; a plausible peer-to-peer overflow-subcontracting relationship rather than a typical client, similar to the naval-architecture boutiques found in earlier batches.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>8 years of engineering experience in structural/mechanical industrial services; member of Engineers and Geoscientists of BC (EGBC); serves Lower Mainland industrial clients from a central Port Coquitlam location. Source: https://mtecengineeringco.com/ ; https://mtecengineeringco.com/mechanical-structural-services/</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://mtecengineeringco.com/contact-engineering-company-port-coquitlam/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>adriaan@mtecengineeringco.com (appears to be a named principal's address, but the full name was not confirmed)</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://mtecengineeringco.com/ ; https://mtecengineeringco.com/mechanical-structural-services/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a fellow small industrial engineering practice - propose an overflow-subcontracting arrangement (AH Structures picking up FEA/heavy-lift-adjacent scopes MTEC doesn't have current bandwidth for) rather than a standard prime-to-vendor pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>The 'adriaan@' contact email suggests a principal named Adriaan, but the surname was not confirmed in this pass - verify via the contact page before using a personal name in outreach.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4587,7 +5245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A87"/>
+  <dimension ref="A1:A107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -5178,6 +5836,139 @@
       <c r="A87" s="9" t="inlineStr">
         <is>
           <t>The Richmond-vs-Delta address question flagged for Marcon Metalfab in batch 2 is resolved: a March 2026 listing confirms Delta as its current primary facility, so it has been moved from the Low Confidence - Review sheet into the Delta, BC sheet. Ideal Welders Ltd. (Delta) was excluded despite genuine heavy marine-fabrication scale, because its marine work is explicitly built on a long-standing Seaspan supplier relationship (Ahmad's own anonymised employer group - a conflict of interest) and includes Joint Support Ship (naval/defense) work - both separate guardrails, both triggered at once. 'Fabrication Delta,' which surfaced in Delta-BC search results as a wind-turbine-tower fabricator, was discarded entirely rather than added anywhere: it is actually headquartered in New Richmond, Quebec, and has no connection to Delta, BC beyond the name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Batch 5: Coquitlam, BC &amp; Port Coquitlam, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>1. The Portal Crane Group (Port Coquitlam) - Score 9, Priority A - crane/hoist certification and service specialist since 1987, with a named in-house Engineering Manager (Timothy McCullough) - one of the closest role-title matches to AH Structures' own scope found in any batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>2. Kay-Son Steel Fabricators Ltd. (Coquitlam) - Score 7, Priority B - 60-year heavy industrial fabricator explicitly listing marine among its served sectors, named General Manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>3. MTEC Engineering (Port Coquitlam) - Score 7, Priority B - small industrial structural/mechanical consultancy covering cranes, lifting devices and fall-arrest systems; best approached peer-to-peer for overflow subcontracting rather than as a typical client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>Crane, hoist and lifting-equipment engineering. Portal Crane Group's dedicated Engineering function for crane certification and structural inspection is arguably the single closest scope match to AH Structures found across all five batches so far.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>For Portal Crane Group, approach the named Engineering Manager directly with a structural/lifting-verification capacity pitch tied to crane certification and inspection work. For Kay-Son, lead specifically with the marine and bulk-material-handling side of their fabrication work. For MTEC, propose a peer-level overflow-subcontracting arrangement rather than a standard vendor pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current hiring/expansion signal this batch - all three prospects are included on structural fit and named-contact strength rather than an active overflow trigger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>The Portal Crane Group (crane structural certification/inspection); MTEC Engineering (lifting-device and crane structural design).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>The Portal Crane Group is the clearest heavy-lift-equipment fit this batch - its core business is certifying and servicing the very lifting equipment (container cranes, gantry cranes, ship loaders) whose structural integrity AH Structures' services would support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: The Portal Crane Group (Timothy McCullough, Manager, Engineering - re-verify title first). Follow with Kay-Son Steel Fabricators (Paul Buchmann, General Manager) and MTEC Engineering (confirm the 'Adriaan' contact's full name and title before outreach).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>Two companies that surfaced in Coquitlam-scoped searches were discarded entirely rather than misfiled: 'FEA Consultants' (founder Yannick Banaszak) turned out to be Quebec-based (418 area code), not BC; West Coast Steel (Coquitlam) was excluded as a general commercial/institutional building fabricator (schools, aquatic centres, warehouses) with no marine or heavy-industrial evidence. Kay-Son's own materials list oil/gas and pulp &amp; paper among its served sectors alongside marine - per AH Structures' house convention against ever framing its own services around oil &amp; gas, any outreach material for this contact should reference only the marine/bulk-handling side of their work.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -16,6 +16,8 @@
     <sheet name="Low Confidence - Review" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Coquitlam, BC" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Port Coquitlam, BC" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Port Moody, BC" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Langley, BC" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -29,6 +31,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Low Confidence - Review'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Coquitlam, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Port Coquitlam, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Port Moody, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Langley, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4049,6 +4053,772 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Port Moody, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Pacific Coast Terminals Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://pct.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Marine Bulk Terminal Operator</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Port Infrastructure / Bulk Handling</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Marine terminal operations handling dry bulk (sulphur, potash) and bulk liquids (canola, ethylene glycol); ship loading for 180+ vessels per year</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Advanced bulk marine terminal with a confirmed, named Manager of Maintenance and Engineering - dock structures, ship loaders and conveyor/handling systems at this scale periodically need structural verification or lifting-engineering support beyond routine maintenance.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>One of the most advanced bulk terminals globally; handles up to 6 million tonnes of dry bulk and 1.5 million tonnes of bulk liquids annually across 180+ vessel calls. Source: https://bcmarineterminals.com/pacific-coast-terminals/ ; https://pct.ca/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Curtis Rutherford</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Manager, Maintenance and Engineering</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/curtis-rutherford-b37492a/</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://pct.ca/contact/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn public profile / ZoomInfo (corroborated)</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://bcmarineterminals.com/pacific-coast-terminals/ ; https://pct.ca/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach Curtis Rutherford directly, offering independent structural/lifting-engineering verification support for terminal infrastructure (ship loaders, conveyors, dock structures) during maintenance or upgrade cycles.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Terminal handles sulphur among its bulk commodities, which can be a refinery byproduct - per AH Structures' house convention of never framing its own work around oil &amp; gas, any outreach material should describe the relationship purely in terms of marine terminal/bulk-handling infrastructure, not the cargo's origin industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Port Moody, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Ratio Structural Engineering Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ratiostructural.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Engineering Consultancy (Heavy-Civil Structural, boutique)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Heavy Civil / Structural Engineering</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Marine temporary works, method engineering, heavy lift design &amp; planning, bridge erection engineering, custom devices</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Port Moody-based structural engineering boutique whose service list - marine temporary works, heavy lift design &amp; planning, method engineering - is close to a direct match for AH Structures' own core scope; a plausible peer-to-peer overflow-subcontracting relationship, similar to other small structural/lifting-focused consultancies found in earlier batches.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Services explicitly listed include Marine Temporary Works, Method Engineering, Heavy Lift Design &amp; Planning and Bridge Erection Engineering, alongside general building design. Source: https://www.ratiostructural.com/marine-structures-naval-architecture ; https://www.ratiostructural.com/method-engineering</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ratiostructural.com/about-us</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ratiostructural.com/ ; https://www.ratiostructural.com/about-us</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a fellow specialist practice - propose an overflow-subcontracting or joint-venture arrangement on marine temporary-works or heavy-lift-design scopes where either firm's bandwidth is stretched.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No named principal or owner was confirmed in this pass despite several searches; contact via the company's general inquiry channel and ask for the principal engineer directly.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Langley, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>L E Steel Fabricators Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lesteel.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/le-steel-fabricators-ltd</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Marine &amp; Structural Steel Fabricator</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Structural Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom engineered structural steel, aluminum and stainless-steel fabrication specializing in the marine industry, including dock structures and ferry-landing components</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Langley-based fabricator (est. 1989) that explicitly specializes in the marine industry, with named ownership - dock structures and ferry-landing components are exactly the kind of fabricated marine assemblies that need structural verification, lifting-lug design and load calculations.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>In continuous operation since 1989; self-described expertise in fabrication of dock structures and ferry-landing components for the marine industry, from an 11,000 sq ft Langley facility. Source: https://www.lesteel.com/ ; https://www.metalline.info/company-l-e-steel-fabricators-ltd-in-langley-8780</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Laurence Elliott</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lesteel.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@lesteel.com (general company inbox)</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website / business directory listings</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lesteel.com/ ; https://www.yellowpages.ca/bus/British-Columbia/Langley/L-E-Steel-Fabricators-Ltd/100154608.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach Laurence Elliott directly, offering structural verification and lifting-lug/load calculations for dock-structure and ferry-landing fabrication projects, positioned as a direct extension of a marine specialty this small shop already claims.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Small, owner-run shop (up to ~20 staff) - Laurence Elliott as Owner is the right altitude of contact per the master prompt's guidance for smaller companies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Langley, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>RKM Crane Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://rkmcrane.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/rkm-crane-services</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Crane Rental &amp; Heavy Lift Contractor</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Lift / Crane Services</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Mobile crane rental (boom truck, rough-terrain, all-terrain and crawler cranes, 8.5 to 500 tons) and rigging support</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Langley-headquartered crane rental and heavy-lift contractor with capacity up to 500 tons; lifts at this scale routinely require rigging plans, lift-engineering calculations and pad-eye/lug verification.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Corporate office in Langley, BC with additional yards on Vancouver Island and in Kamloops; crane fleet spans 8.5 to 500 ton capacity. Source: https://rkmcrane.com/about-us/</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Matt Blackwell</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://rkmcrane.com/about-us/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Web search snippet (ZoomInfo-corroborated)</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://rkmcrane.com/ ; https://rkmcrane.com/about-us/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Offer independent lift-engineering and rigging-calculation support (pad-eye, load charts, lift plans) for the heavier end of RKM's crane fleet capacity, positioned as an on-call resource rather than a standing arrangement.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Matt Blackwell (General Manager) and Ryan Minnick (Owner, RKM Services Ltd.) were both found as possible contacts - confirm which is the right person for engineering/lift-planning matters before outreach.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5245,7 +6015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A107"/>
+  <dimension ref="A1:A128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -5969,6 +6739,146 @@
       <c r="A107" s="9" t="inlineStr">
         <is>
           <t>Two companies that surfaced in Coquitlam-scoped searches were discarded entirely rather than misfiled: 'FEA Consultants' (founder Yannick Banaszak) turned out to be Quebec-based (418 area code), not BC; West Coast Steel (Coquitlam) was excluded as a general commercial/institutional building fabricator (schools, aquatic centres, warehouses) with no marine or heavy-industrial evidence. Kay-Son's own materials list oil/gas and pulp &amp; paper among its served sectors alongside marine - per AH Structures' house convention against ever framing its own services around oil &amp; gas, any outreach material for this contact should reference only the marine/bulk-handling side of their work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>Batch 6: Port Moody, BC &amp; Langley, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>1. Ratio Structural Engineering Inc. (Port Moody) - Score 8, Priority A - boutique structural firm whose service list (marine temporary works, heavy lift design &amp; planning, method engineering) is arguably the closest direct scope match to AH Structures found in any batch; no named principal confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>2. Pacific Coast Terminals Co. Ltd. (Port Moody) - Score 8, Priority A - major bulk marine terminal, named Manager of Maintenance and Engineering (Curtis Rutherford, LinkedIn-verified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>3. L E Steel Fabricators Ltd. (Langley) - Score 8, Priority A - marine-specialty fabricator (dock structures, ferry-landing components) since 1989, named Owner Laurence Elliott.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>4. RKM Crane Services Ltd. (Langley) - Score 6, Priority B - Langley-HQ'd crane/heavy-lift contractor up to 500-ton capacity, named General Manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>Boutique structural/marine-temporary-works engineering. Ratio Structural's service list is close enough to AH Structures' own that this batch reinforces a pattern first seen with MTEC Engineering (batch 5): small BC structural practices already doing marine/heavy-lift-adjacent work are strong overflow-subcontract partners, not just typical clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>For Ratio Structural, propose a peer-level overflow/joint-venture arrangement given the near-identical scope. For Pacific Coast Terminals and L E Steel, both have named, verifiable technical contacts (Curtis Rutherford; Laurence Elliott) - approach them directly rather than through a general inquiry channel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current hiring/expansion signal this batch - all four prospects are included on structural fit and named-contact strength.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>Ratio Structural Engineering (marine temporary works, heavy lift design) and Pacific Coast Terminals (terminal infrastructure) are the strongest FEA-adjacent fits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>RKM Crane Services (500-ton crane capacity, rigging support) and Ratio Structural's own Heavy Lift Design &amp; Planning service line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Pacific Coast Terminals (Curtis Rutherford, Manager Maintenance and Engineering) and L E Steel Fabricators (Laurence Elliott, Owner) - both have solid, corroborated named contacts. Follow with Ratio Structural Engineering (find the principal via direct inquiry) and RKM Crane Services (confirm whether Matt Blackwell or Ryan Minnick is the right contact).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>Harbourside Engineering Group surfaced in Port Moody-scoped search results (marine/bridge structural engineering) but was confirmed to have no British Columbia office at all - it is headquartered in Dartmouth, Nova Scotia with offices only in NS/PEI/NL/ON - so it was discarded entirely rather than misfiled, the third such out-of-province false lead after 'Fabrication Delta' and 'FEA Consultants' in earlier batches. Pacific Coast Terminals handles sulphur among its bulk commodities (often a refinery byproduct); per AH Structures' house convention against framing its own work around oil &amp; gas, any outreach to this contact should describe the relationship purely in terms of marine terminal/bulk-handling infrastructure.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -18,6 +18,8 @@
     <sheet name="Port Coquitlam, BC" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Port Moody, BC" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Langley, BC" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Township of Langley, BC" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Maple Ridge, BC" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -33,6 +35,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Port Coquitlam, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Port Moody, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Langley, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Township of Langley, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Maple Ridge, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3044,7 +3048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -3390,6 +3394,90 @@
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>https://ismbc.ca/services/ ; https://ismbc.ca/fabrication-shop/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Langley, BC</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Cutting Edge Fabrication Ltd.</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metalshop.cc/</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Genuine Langley City (not Township) fabricator since 1995, confirming real industrial activity in Langley City proper - but its described industries served (mining, agriculture, grain handling, sawmill/wood processing) show no marine, offshore or heavy-lift evidence.</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether any marine or heavy-lift-adjacent project work exists before treating as a prospect; as researched this is a generalist industrial fabricator fit, not an AH Structures core fit.</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>https://www.zoominfo.com/c/cutting-edge-fabrication-ltd/527187590</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Maple Ridge, BC</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Fabricoat Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>https://fabricoat.ca/</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Sizeable Maple Ridge metal fabricator, but sources conflict on its served industries - one describes 'construction, mining, marine, aerospace, agriculture' while another (from the same company's own site) describes 'construction, energy, electrical, military, and mining' with no marine mentioned. The military reference raises a potential defense-guardrail conflict that needs resolving before outreach.</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Confirm directly with the company which industries it actually serves and whether any work is defense-related, before treating this as a marine/heavy-lift prospect.</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>https://fabricoat.ca/fabricoat/ ; https://fabricoat.ca/</t>
         </is>
       </c>
     </row>
@@ -4434,6 +4522,169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4588,7 +4839,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Langley, BC</t>
+          <t>Township of Langley, BC</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -4633,7 +4884,7 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Langley-based fabricator (est. 1989) that explicitly specializes in the marine industry, with named ownership - dock structures and ferry-landing components are exactly the kind of fabricated marine assemblies that need structural verification, lifting-lug design and load calculations.</t>
+          <t>Fabricator (est. 1989) that explicitly specializes in the marine industry, with named ownership - dock structures and ferry-landing components are exactly the kind of fabricated marine assemblies that need structural verification, lifting-lug design and load calculations.</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -4648,7 +4899,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>In continuous operation since 1989; self-described expertise in fabrication of dock structures and ferry-landing components for the marine industry, from an 11,000 sq ft Langley facility. Source: https://www.lesteel.com/ ; https://www.metalline.info/company-l-e-steel-fabricators-ltd-in-langley-8780</t>
+          <t>In continuous operation since 1989; self-described expertise in fabrication of dock structures and ferry-landing components for the marine industry, from an 11,000 sq ft facility in the Aldergrove area. Source: https://www.lesteel.com/ ; https://www.metalline.info/company-l-e-steel-fabricators-ltd-in-langley-8780</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
@@ -4697,14 +4948,14 @@
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>Small, owner-run shop (up to ~20 staff) - Laurence Elliott as Owner is the right altitude of contact per the master prompt's guidance for smaller companies.</t>
+          <t>Corrected from batch 6: the 5484-267th St address (Aldergrove) is in the Township of Langley, not Langley City - this entry was moved here from the 'Langley, BC' sheet, not duplicated. Small, owner-run shop (up to ~20 staff) - Laurence Elliott as Owner is the right altitude of contact.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Langley, BC</t>
+          <t>Township of Langley, BC</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4749,7 +5000,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Langley-headquartered crane rental and heavy-lift contractor with capacity up to 500 tons; lifts at this scale routinely require rigging plans, lift-engineering calculations and pad-eye/lug verification.</t>
+          <t>Crane rental and heavy-lift contractor with capacity up to 500 tons; lifts at this scale routinely require rigging plans, lift-engineering calculations and pad-eye/lug verification.</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -4764,7 +5015,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Corporate office in Langley, BC with additional yards on Vancouver Island and in Kamloops; crane fleet spans 8.5 to 500 ton capacity. Source: https://rkmcrane.com/about-us/</t>
+          <t>Corporate office at 5363 273A St (Gloucester Industrial Estates), Township of Langley, BC, with additional yards on Vancouver Island and in Kamloops; crane fleet spans 8.5 to 500 ton capacity. Source: https://rkmcrane.com/about-us/</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -4809,7 +5060,270 @@
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Matt Blackwell (General Manager) and Ryan Minnick (Owner, RKM Services Ltd.) were both found as possible contacts - confirm which is the right person for engineering/lift-planning matters before outreach.</t>
+          <t>Corrected from batch 6: the 5363 273A St address (Gloucester) is in the Township of Langley, not Langley City - this entry was moved here from the 'Langley, BC' sheet, not duplicated. Matt Blackwell (General Manager) and Ryan Minnick (Owner, RKM Services Ltd.) were both found as possible contacts - confirm which is right for engineering/lift-planning matters before outreach.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Maple Ridge, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Supreme Structural Transport Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.supremehm.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Transport &amp; Industrial Moving Contractor</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Transport / Structural Moving</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural building/house moving, heavy haulage and project-cargo transport, with an in-house engineering team designing specialized transport equipment</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Maple Ridge-based heavy-structural-transport specialist, operating since 1945, with a confirmed in-house engineering team that designs specialized equipment for its own heavy-lift and structural-transport projects - close overlap with AH Structures' heavy transport and SPMT-adjacent scope.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>In continuous operation since 1945 from 23660 River Road, Maple Ridge, BC; in-house engineering team designs and builds specialized equipment for heavy lift and structural transport projects. Source: https://www.supremehm.com/industrial/supreme-structural-transport/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.supremehm.com/industrial/supreme-structural-transport/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.supremehm.com/ ; https://www.supremehm.com/industrial/supreme-structural-transport/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Offer independent structural/transport-engineering verification support (load calculations, structural checks) to complement the in-house engineering team during peak project periods, or for a second, independent check on complex moves.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No individual decision-maker's name was confirmed in this pass despite an in-house engineering team being confirmed to exist - contact via the company's general channel and ask for the engineering lead directly. Originally identified during batch 2 research (Richmond, BC) as serving that area from this Maple Ridge base; this entry places it in its actual home city.</t>
         </is>
       </c>
     </row>
@@ -6015,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A128"/>
+  <dimension ref="A1:A150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -6879,6 +7393,153 @@
       <c r="A128" s="9" t="inlineStr">
         <is>
           <t>Harbourside Engineering Group surfaced in Port Moody-scoped search results (marine/bridge structural engineering) but was confirmed to have no British Columbia office at all - it is headquartered in Dartmouth, Nova Scotia with offices only in NS/PEI/NL/ON - so it was discarded entirely rather than misfiled, the third such out-of-province false lead after 'Fabrication Delta' and 'FEA Consultants' in earlier batches. Pacific Coast Terminals handles sulphur among its bulk commodities (often a refinery byproduct); per AH Structures' house convention against framing its own work around oil &amp; gas, any outreach to this contact should describe the relationship purely in terms of marine terminal/bulk-handling infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>Batch 7: Township of Langley, BC &amp; Maple Ridge, BC (plus a Langley, BC correction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>Correction carried over from batch 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>L E Steel Fabricators Ltd. and RKM Crane Services Ltd. were originally placed in the 'Langley, BC' sheet, but their addresses (5484-267th St, Aldergrove; 5363 273A St, Gloucester) are confirmed to be in the Township of Langley, not Langley City. Both entries have been moved to the new 'Township of Langley, BC' sheet below (not duplicated); the 'Langley, BC' sheet is now empty pending a genuine Langley-City-proper qualified prospect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>1. L E Steel Fabricators Ltd. (Township of Langley) - Score 8, Priority A - marine specialty fabricator since 1989, named Owner (carried over, city-corrected).</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>2. Supreme Structural Transport Ltd. (Maple Ridge) - Score 8, Priority A - heavy structural/transport mover since 1945 with a confirmed in-house engineering team; originally surfaced during batch 2 (Richmond) research as a company serving that area, now placed in its actual home city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>3. RKM Crane Services Ltd. (Township of Langley) - Score 6, Priority B - carried over, city-corrected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>Heavy structural transport and marine fabrication. Supreme Structural Transport's in-house engineering team for heavy-lift/transport equipment design is one of the more direct scope overlaps found so far, alongside the marine-fabrication pattern seen with L E Steel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>For Supreme Structural Transport, position AH Structures as independent verification/second-check capacity to complement (not replace) their existing in-house engineering team, especially on complex or high-value moves. For the Township of Langley entries, the angles carried over from batch 6 still apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>Supreme Structural Transport Ltd. (structural/transport engineering for heavy moves).</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>Supreme Structural Transport Ltd. is the standout heavy-transport fit for this batch; RKM Crane Services (Township of Langley) remains relevant from batch 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Supreme Structural Transport (via general contact, requesting the engineering lead) and L E Steel Fabricators (Laurence Elliott, Owner, carried over). Township of Langley entries otherwise follow the batch 6 priority order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>Cutting Edge Fabrication Ltd. (genuinely Langley City, established 1995) was found but routed to Review - its served industries (mining, agriculture, grain handling, sawmill) show no marine or heavy-lift evidence, so Langley, BC's main sheet remains empty rather than being filled with a weak fit. Fabricoat Industries Ltd. (Maple Ridge) was also routed to Review: two sources gave conflicting served-industry lists for the same company, one mentioning marine and another mentioning military with no marine at all - the military reference needs resolving against the defense-exclusion guardrail before this company could be treated as a prospect either way.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -20,6 +20,8 @@
     <sheet name="Langley, BC" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Township of Langley, BC" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Maple Ridge, BC" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Abbotsford, BC" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Chilliwack, BC" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -37,6 +39,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Langley, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Township of Langley, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Maple Ridge, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Abbotsford, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Chilliwack, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3048,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -3478,6 +3482,132 @@
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>https://fabricoat.ca/fabricoat/ ; https://fabricoat.ca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Abbotsford, BC</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Clearbrook Iron Works Ltd.</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>https://cliron.com/</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Well-established (since 1956), reputable structural steel fabricator (~50 employees, named owner Paul Unger) with 85% of business in large, technically demanding projects - but every documented project (Abbotsford Regional Hospital, McCallum Junction, general commercial/institutional/high-rise work) is building construction, with no marine, offshore or heavy-industrial-equipment evidence found despite two search passes.</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Confirm directly whether any non-building industrial, marine or heavy-lift-adjacent project work exists before treating as a prospect.</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>https://www.abbotsford.ca/council/your-council-community/blog/learning-how-clearbrook-iron-works-works ; https://cliron.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Abbotsford, BC</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Krahn Engineering Ltd.</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>https://www.krahnengineering.com/</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>40-year Abbotsford structural engineering firm, but self-described project sectors (commercial, industrial, institutional, residential, agricultural, recreational and parks) are general building-and-site engineering with no marine, offshore or heavy-lift-specific evidence.</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether any marine, heavy-lift or FEA-specific project work exists before treating as a prospect.</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Web search summary of company's own service description (no single authoritative URL captured this pass - re-verify at krahnengineering.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Chilliwack, BC</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Mussell Crane Manufacturing</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>https://www.mussellcrane.com/</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Aboriginal-owned crane and material-handling equipment manufacturer (overhead bridge cranes, gantry cranes, jib cranes) since 1991, founder Fred Mussell - a strong technical fit, and the company already collaborates with third-party registered engineering firms on a turn-key basis, which is close to AH Structures' overflow model. However, the company's own site names 'commercial, military, and government sectors' as its three served markets, with no separately identified non-military division.</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Confirm directly what proportion of Mussell's business is military/defense-related and whether any purely commercial engineering-support work could be scoped independently of that, before treating as a prospect - this is a genuine judgment call given the strength of the technical fit against the defense-exclusion guardrail.</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>https://www.mussellcrane.com/about ; https://www.mussellcrane.com/</t>
         </is>
       </c>
     </row>
@@ -5333,6 +5463,436 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Chilliwack, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>S.T.I. Steeltec Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://steeltec.net/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabricator</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial / Energy / Infrastructure / Marine (boat repair)</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural and miscellaneous steel fabrication, plus boat repair services</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified Chilliwack fabricator since 1987 serving commercial, industrial, energy and infrastructure clients, with boat repair listed among its own services - a genuine, if modest, marine touchpoint alongside a solid heavy-industrial fabrication base.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>In continuous operation since 1987; self-describes service across Commercial, Healthcare, Industrial and Energy, Infrastructure, Institutional and Residential sectors, plus boat repair and welding services. Source: https://business.chilliwackchamber.com/member-directory/Details/steeltec-industries-ltd-4245295 ; https://steeltec.net/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://steeltec.net/contact/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>inquiries@steeltec.net (general company inbox)</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website / Chilliwack Chamber of Commerce directory</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://steeltec.net/ ; https://business.chilliwackchamber.com/member-directory/Details/steeltec-industries-ltd-4245295</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lead with the boat-repair/marine side of their work when offering structural verification or lifting-engineering support, since that is the clearest point of overlap with AH Structures' core scope.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No individual decision-maker's name was confirmed in this pass. Industrial/energy sector work is the larger part of their business; marine is a secondary, not primary, service line - moderate rather than strong fit.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6529,7 +7089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A150"/>
+  <dimension ref="A1:A169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -7540,6 +8100,132 @@
       <c r="A150" s="9" t="inlineStr">
         <is>
           <t>Cutting Edge Fabrication Ltd. (genuinely Langley City, established 1995) was found but routed to Review - its served industries (mining, agriculture, grain handling, sawmill) show no marine or heavy-lift evidence, so Langley, BC's main sheet remains empty rather than being filled with a weak fit. Fabricoat Industries Ltd. (Maple Ridge) was also routed to Review: two sources gave conflicting served-industry lists for the same company, one mentioning marine and another mentioning military with no marine at all - the military reference needs resolving against the defense-exclusion guardrail before this company could be treated as a prospect either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>Batch 8: Abbotsford, BC &amp; Chilliwack, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>1. S.T.I. Steeltec Industries Ltd. (Chilliwack) - Score 6, Priority C - CWB-certified fabricator since 1987 with boat repair among its services, a modest but genuine marine touchpoint alongside industrial/energy fabrication work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>No qualified (score &gt;= 6) main-sheet company was found for Abbotsford, BC this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>This was the thinnest batch for direct fit so far. Neither city produced a strong marine/heavy-lift/offshore-specific company; Chilliwack's Steeltec is a moderate industrial-fabrication fit with a secondary marine service line, which is the best this batch offers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>For Steeltec, lead with the boat-repair side of their business specifically rather than a broad industrial pitch, since that is the one point of genuine overlap with AH Structures' marine-adjacent scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>None identified this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>None identified this batch at a score &gt;= 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>None identified this batch at a score &gt;= 6 - Mussell Crane Manufacturing (Chilliwack) would otherwise be the standout, but is held in Review pending resolution of its defense-market exposure (see Quality-control notes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>Contact Steeltec Industries via general inquiry, framed around their boat-repair service line. Both Abbotsford entries and Mussell Crane are in Review, not ready for outreach without further verification - see notes below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>Abbotsford, BC's main sheet is empty this pass, by design rather than oversight: Clearbrook Iron Works (well-established, named owner, ~50 employees) and Krahn Engineering (40-year structural firm) were both found and researched in depth, but both are general building-construction fabricators/engineers with no marine, offshore or heavy-lift evidence after multiple search passes - both routed to Review rather than forced into the main sheet. Wesbridge Steelworks surfaced in Chilliwack-scoped search results but is actually headquartered in Delta, BC (7480 Wilson Ave) - not added anywhere, since it is also a general building-construction fabricator with no marine evidence, so it would not have qualified even under its correct city. Mussell Crane Manufacturing (Chilliwack) is the one genuine judgment call this batch: a strong technical fit (crane/material-handling manufacturer that already subcontracts engineering to third parties) held back by its own website naming 'military' as one of three core served markets, with no separate commercial-only division identified - routed to Review rather than decided either way, since this is closer to a real dual-use ambiguity than the clearer defense/oil-and-gas cases excluded in earlier batches.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -22,6 +22,8 @@
     <sheet name="Maple Ridge, BC" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Abbotsford, BC" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Chilliwack, BC" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Mission, BC" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="White Rock, BC" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -41,6 +43,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Maple Ridge, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Abbotsford, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Chilliwack, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Mission, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'White Rock, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3052,7 +3056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -3608,6 +3612,90 @@
       <c r="H13" s="10" t="inlineStr">
         <is>
           <t>https://www.mussellcrane.com/about ; https://www.mussellcrane.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Mission, BC</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>CRS Construction Ltd.</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>https://crsconstruction.net/</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Mission-based steel erector specializing in 'difficult access, precarious installations' - an interesting engineering-adjacent niche - but every documented project (Shangri-La Vancouver, Fairmont Waterfront, the former Vancouver Sears building) is high-rise/commercial building construction, with no marine, offshore or heavy-industrial evidence.</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether any non-building, marine or heavy-lift-adjacent project work exists before treating as a prospect.</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>https://crsconstruction.net/projects/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Mission, BC</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Cimtex Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>https://cimtexindustries.com/</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Mission-based precision CNC machining/fabrication shop (named President Darren Fulkco) serving Aerospace, Telecommunications, Scientific and High-Tech industries - real engineering-adjacent capability, but search summaries describe it as serving both 'aerospace and defense' sectors without a clearly separate non-defense division, which conflicts with the defense-exclusion guardrail.</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Confirm directly what proportion of Cimtex's aerospace work is defense-related versus purely commercial/scientific before treating as a prospect.</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>https://cimtexindustries.com/ ; https://www.zoominfo.com/c/cimtex-industries-ltd/354651964</t>
         </is>
       </c>
     </row>
@@ -6596,6 +6684,332 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7089,7 +7503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A169"/>
+  <dimension ref="A1:A183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -8226,6 +8640,97 @@
       <c r="A169" s="9" t="inlineStr">
         <is>
           <t>Abbotsford, BC's main sheet is empty this pass, by design rather than oversight: Clearbrook Iron Works (well-established, named owner, ~50 employees) and Krahn Engineering (40-year structural firm) were both found and researched in depth, but both are general building-construction fabricators/engineers with no marine, offshore or heavy-lift evidence after multiple search passes - both routed to Review rather than forced into the main sheet. Wesbridge Steelworks surfaced in Chilliwack-scoped search results but is actually headquartered in Delta, BC (7480 Wilson Ave) - not added anywhere, since it is also a general building-construction fabricator with no marine evidence, so it would not have qualified even under its correct city. Mussell Crane Manufacturing (Chilliwack) is the one genuine judgment call this batch: a strong technical fit (crane/material-handling manufacturer that already subcontracts engineering to third parties) held back by its own website naming 'military' as one of three core served markets, with no separate commercial-only division identified - routed to Review rather than decided either way, since this is closer to a real dual-use ambiguity than the clearer defense/oil-and-gas cases excluded in earlier batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>Batch 9: Mission, BC &amp; White Rock, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>None. Both cities' main sheets are empty this pass - the second time this has happened (after Abbotsford in batch 8), and for the same reason: real, well-documented local companies exist, but none show marine/heavy-lift/offshore/industrial-FEA evidence once checked in depth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>Not applicable this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>Not applicable this batch - nothing cleared the bar for outreach-ready status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>None identified this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>None - see Review sheet for the two borderline Mission companies if the user wants to verify them further before writing them off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>CRS Construction Ltd. (Mission) has a genuinely interesting specialty - 'difficult access, precarious installations' steel erection - but every documented project (Shangri-La Vancouver, Fairmont Waterfront) is high-rise building construction; routed to Review rather than forced in. Cimtex Industries Ltd. (Mission, named President Darren Fulkco) is a real precision-machining shop but search summaries describe it serving both aerospace and defense with no separate non-defense division identified - routed to Review as a defense-exclusion judgment call, same treatment as Mussell Crane in batch 8. White Rock Iron Products Ltd., which surfaced in a White-Rock-scoped search, turned out to be headquartered in Delta, BC (not White Rock) - the fourth city/province mix-up caught in this project so far - and would not have qualified on fit even in its correct city (general residential/commercial/industrial fabrication, no marine evidence), so it was discarded entirely rather than misfiled a second time.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -24,6 +24,8 @@
     <sheet name="Chilliwack, BC" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Mission, BC" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="White Rock, BC" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Pitt Meadows, BC" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Squamish, BC" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -45,6 +47,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Chilliwack, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Mission, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'White Rock, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Pitt Meadows, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Squamish, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7010,6 +7014,652 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Pitt Meadows, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Taylor Metals Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.taylormetals.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Metal Fabricator</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial / Resource / Marine Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy-duty enclosures, hoppers, chutes and custom fabricated components for resource and marine applications; engineering, fabrication and field-install services in-house</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Pitt Meadows fabricator explicitly serving 'resource and marine applications' with in-house engineering and field-install capability - a genuine, if modest, marine/industrial fit with named ownership.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Modern fabrication facility (TRUMPF fiber laser, CNC press brakes, CWB W47.1 certified welding) at 19055 Airport Way, Pitt Meadows; self-describes output for resource and marine applications. Source: https://www.taylormetals.ca/pages/about-us</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Daniel Taylor</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.taylormetals.ca/pages/about-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Business registry / directory listings (BBB)</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.taylormetals.ca/ ; https://www.bbb.org/ca/bc/pitt-meadows/profile/metal-fabrication/taylor-metals-ltd-0037-2430424</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach Daniel Taylor directly, offering structural verification and lifting-lug/load calculations for the resource and marine end of their fabricated-component work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Founded 2011. A LinkedIn profile for a 'Keith Bailey - President at Taylor Metal' also surfaced in search results - this appears to be a different, similarly-named company, not Taylor Metals Ltd. of Pitt Meadows; Daniel Taylor is the confirmed contact for this entry.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Squamish, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Squamish Terminals Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sqterminals.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/squamish-terminals-ltd-</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Marine Break-Bulk Terminal Operator</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Port Infrastructure / Break-Bulk Cargo</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Deep-water break-bulk terminal operations (forestry products, steel, project cargoes), stevedoring, loading/unloading of ocean vessels and barges</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Deep-water break-bulk terminal in continuous operation since 1972, handling heavy materials and project cargo - dock/berth structures and cargo-handling equipment at this scale periodically need structural verification or lifting-engineering support beyond routine maintenance.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established as a current signal - an ownership change (Western Stevedoring/Carrix acquiring from Grieg Star) and associated leadership restructuring occurred in 2018 and is too dated to treat as a present-day overflow signal.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>60-acre site, two berths, three warehouses at the north end of Howe Sound; handles heavy materials, break-bulk and project cargo bound for North America and worldwide. Source: https://bcmarineterminals.com/squamish-terminals/ ; https://investsquamish.ca/why-squamish/international-access</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Nicholas Knight</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sqterminals.com/contact-us/overview/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Web search snippet (single source - not independently corroborated)</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://bcmarineterminals.com/squamish-terminals/ ; https://www.sqterminals.com/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach Nicholas Knight directly, offering independent structural/lifting-engineering verification support for terminal infrastructure and cargo-handling equipment.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Nicholas Knight's title was drawn from a single web search snippet, not corroborated by a second source or directly opened page - confirm current General Manager before outreach, especially given the terminal's history of ownership-driven leadership changes (2018 acquisition by Western Stevedoring/Carrix; a 2024 rebrand to the SSA Marine name).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Squamish, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Carson's Custom MFG</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://carsonscustom.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Custom Fabrication Shop</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Industrial Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>MIG/TIG welding, CNC machining, metal fabrication and site installation for marine, industrial and recreational demands, including structural repairs and custom assemblies</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Small Squamish shop that explicitly markets structural repair and custom-assembly work as standing up to 'marine, industrial and recreational demands' - a direct, if small-scale, marine-fabrication fit for the Sea-to-Sky corridor.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Serves Squamish, Whistler and the Sea-to-Sky Corridor with structural repairs and custom assemblies for marine, industrial and recreational clients. Source: https://carsonscustom.com/</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://carsonscustom.com/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://carsonscustom.com/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Offer occasional structural verification for marine repair/custom-assembly jobs, positioned as lower-cost, on-call support given the shop's small scale.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No named owner/principal identified this pass - contact via the company's general channel.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7503,7 +8153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A183"/>
+  <dimension ref="A1:A203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -8731,6 +9381,139 @@
       <c r="A183" s="9" t="inlineStr">
         <is>
           <t>CRS Construction Ltd. (Mission) has a genuinely interesting specialty - 'difficult access, precarious installations' steel erection - but every documented project (Shangri-La Vancouver, Fairmont Waterfront) is high-rise building construction; routed to Review rather than forced in. Cimtex Industries Ltd. (Mission, named President Darren Fulkco) is a real precision-machining shop but search summaries describe it serving both aerospace and defense with no separate non-defense division identified - routed to Review as a defense-exclusion judgment call, same treatment as Mussell Crane in batch 8. White Rock Iron Products Ltd., which surfaced in a White-Rock-scoped search, turned out to be headquartered in Delta, BC (not White Rock) - the fourth city/province mix-up caught in this project so far - and would not have qualified on fit even in its correct city (general residential/commercial/industrial fabrication, no marine evidence), so it was discarded entirely rather than misfiled a second time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>Batch 10: Pitt Meadows, BC &amp; Squamish, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>1. Squamish Terminals Ltd. (Squamish) - Score 8, Priority A - deep-water break-bulk terminal since 1972, named General Manager (single-source, needs re-verification).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>2. Taylor Metals Ltd. (Pitt Meadows) - Score 7, Priority B - fabricator explicitly serving 'resource and marine applications,' named President Daniel Taylor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>3. Carson's Custom MFG (Squamish) - Score 6, Priority C - small Sea-to-Sky shop explicitly marketing marine structural-repair work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="9" t="inlineStr">
+        <is>
+          <t>Marine terminal and resource/marine fabrication. This batch breaks the empty streak from batches 8-9: Squamish's break-bulk terminal and Pitt Meadows' resource/marine fabricator are both genuine, evidenced fits rather than borderline calls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>For Squamish Terminals, position AH Structures as independent structural/lifting verification for terminal infrastructure and cargo-handling equipment. For Taylor Metals and Carson's Custom MFG, lead specifically with the marine/resource side of their fabrication work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
+          <t>None with a current, dated signal this batch - Squamish Terminals' 2018 ownership change and 2024 SSA Marine rebrand are real but too old to treat as live overflow triggers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>Squamish Terminals Ltd. (terminal/berth structural infrastructure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>Squamish Terminals Ltd. (break-bulk and project cargo handling, stevedoring).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Squamish Terminals (Nicholas Knight, General Manager - re-verify given the terminal's history of ownership-driven leadership changes) and Taylor Metals (Daniel Taylor, President). Carson's Custom MFG is a smaller, lower-priority follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="9" t="inlineStr">
+        <is>
+          <t>A LinkedIn profile for a 'Keith Bailey - President at Taylor Metal' surfaced alongside Taylor Metals Ltd. in search results - treated as a likely different, similarly-named company rather than conflated with this entry's confirmed contact (Daniel Taylor). Squamish Terminals' General Manager name came from a single, uncorroborated web search snippet - flagged for re-verification given the terminal changed ownership in 2018 and rebranded under SSA Marine in 2024, both of which could have since changed the specific named contact.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -26,6 +26,8 @@
     <sheet name="White Rock, BC" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="Pitt Meadows, BC" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Squamish, BC" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Whistler, BC" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Sechelt, BC" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -49,6 +51,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'White Rock, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Pitt Meadows, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Squamish, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Whistler, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Sechelt, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3060,7 +3064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -3700,6 +3704,48 @@
       <c r="H15" s="10" t="inlineStr">
         <is>
           <t>https://cimtexindustries.com/ ; https://www.zoominfo.com/c/cimtex-industries-ltd/354651964</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Whistler, BC</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Whistler Welding Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>https://www.whistlerweldingservices.com/</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Well-established (35+ years) structural steel fabricator in the Sea-to-Sky corridor (based in Pemberton, serving Whistler) - but described work is seismic upgrades, custom fabrications and architectural elements for residential/commercial/public-works projects, with no marine or heavy-industrial evidence. Sources also disagree on the current President's name (Sierra Townley per one listing, Sandy Ryan per another).</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether any marine or heavy-industrial project work exists, and resolve the conflicting leadership names, before treating as a prospect.</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>https://www.whistlerweldingservices.com/team ; https://www.bbb.org/ca/bc/pemberton/profile/steel-fabrication/whistler-welding-services-ltd-0037-1281014</t>
         </is>
       </c>
     </row>
@@ -7660,6 +7706,432 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Sechelt, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Quantum Marine</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.quantummarineco.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Marine Service &amp; Transport Company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Boat Service &amp; Transport</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Boat service, maintenance, repairs, custom fabrication, and haul &amp; transport (vessels up to 45 ft) across the Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Sechelt-based marine services company covering vessel haul, transport and custom fabrication across the Sunshine Coast (Sechelt, Gibsons, Madeira Park, Powell River) - genuine marine-sector activity, though at a modest, small-craft scale rather than heavy industrial.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Locally owned and operated; hauls vessels up to 45 ft locally and as far as Vancouver's Lower Mainland; offers custom fabrication alongside repair and haul services. Source: https://www.quantummarineco.com/ ; https://www.quantummarineco.com/services/overview</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.quantummarineco.com/contact</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.quantummarineco.com/ ; https://www.quantummarineco.com/location/location-sechelt</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Offer occasional structural/fabrication verification support for larger repair or haul jobs, positioned as on-call support given the company's modest, small-craft scale.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No named owner/principal identified this pass - contact via the company's general channel. Scale is small-craft/recreational-adjacent rather than heavy industrial; a modest fit.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8153,7 +8625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A203"/>
+  <dimension ref="A1:A218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -9514,6 +9986,104 @@
       <c r="A203" s="9" t="inlineStr">
         <is>
           <t>A LinkedIn profile for a 'Keith Bailey - President at Taylor Metal' surfaced alongside Taylor Metals Ltd. in search results - treated as a likely different, similarly-named company rather than conflated with this entry's confirmed contact (Daniel Taylor). Squamish Terminals' General Manager name came from a single, uncorroborated web search snippet - flagged for re-verification given the terminal changed ownership in 2018 and rebranded under SSA Marine in 2024, both of which could have since changed the specific named contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>Batch 11: Whistler, BC &amp; Sechelt, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="9" t="inlineStr">
+        <is>
+          <t>1. Quantum Marine (Sechelt) - Score 6, Priority C - Sunshine Coast marine service/haul/fabrication company, modest small-craft scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="inlineStr">
+        <is>
+          <t>No qualified company was found for Whistler, BC this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>As anticipated: Whistler is a resort town with no marine/heavy-industrial fit, and Sechelt's Sunshine Coast marine-service sector is real but modest in scale (small-craft haul and repair, not heavy industrial lift).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>For Quantum Marine, position AH Structures as occasional, on-call structural/fabrication verification for larger repair jobs, given the company's modest scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="inlineStr">
+        <is>
+          <t>None identified this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="inlineStr">
+        <is>
+          <t>Quantum Marine only, and as a lower-tier, opportunistic contact rather than a priority target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="9" t="inlineStr">
+        <is>
+          <t>Whistler Welding Services Ltd. (Sea-to-Sky corridor, 35+ years) was found and researched but routed to Review: well-documented work is seismic upgrades and architectural steel for residential/commercial/public-works projects, with no marine or heavy-industrial evidence, and sources disagree on the current President's name (Sierra Townley vs. Sandy Ryan) - both issues need resolving before this could be a prospect either way.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -28,6 +28,8 @@
     <sheet name="Squamish, BC" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="Whistler, BC" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="Sechelt, BC" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Gibsons, BC" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Powell River, BC" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -53,6 +55,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Squamish, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Whistler, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Sechelt, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Gibsons, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Powell River, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8132,6 +8136,756 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Gibsons, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Coastal Craft Yachts Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://coastalcraft.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/coastalcraft</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Boatbuilder (Naval Architecture / Custom Aluminum Vessels)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Vessel Design &amp; Construction</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Design and construction of custom aluminum workboats and yachts, from rugged commercial vessels to boutique motor yachts</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Gibsons-founded (1996) custom aluminum vessel builder with 120+ vessels delivered over two decades, evolving from working watercraft (water taxis, tugs) to boutique yachts - custom aluminum hull design and construction is a direct, evidence-rich match for structural/naval-architecture verification and fatigue-adjacent engineering support.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Founded 1996 by Jeff Rhodes; built more than 120 custom aluminum vessels; founder's background includes captaining tugs and barges to Alaska before transitioning to building water-taxi and workboat vessels. Source: https://passagemaker.com/technical/coastal-craft-a-product-of-passion/ ; https://coastalcraft.com/manufacturing/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Jeff Rhodes</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Founder &amp; President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://coastalcraft.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Industry profile (Passagemaker magazine) corroborated by company website</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://passagemaker.com/technical/coastal-craft-a-product-of-passion/ ; https://coastalcraft.com/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach Jeff Rhodes directly, offering structural verification, fatigue analysis or FEA support for custom aluminum hull and superstructure design across their vessel range.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Strongest fit found in a Fraser Valley/Sunshine Coast batch so far - a genuine boutique naval-architecture-adjacent builder, not just a fabrication shop. Title confirmed via a detailed third-party industry profile rather than a directory listing alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Gibsons, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Dolphin Marine Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>http://www.dolphinmarine.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Marine Services &amp; Fabrication Company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Dock &amp; Wharf Construction</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Wharf head, dock and float construction/installation; certified aluminum welding and marine fabrication; salvage, towing and marine construction support</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Gibsons-based marine services company with 35+ years in the commercial marine industry, building docks, floats and wharf structures - marine structural fabrication of this kind periodically needs load/structural verification beyond the crew's own trades expertise.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Owner Tom Stenner has over 35 years in the commercial marine industry; company has built many docks and floats of varying styles. Source: https://www.dolphinmarine.ca/ ; https://www.dolphinmarine.ca/services</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Tom Stenner</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dolphinmarine.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dolphinmarine.ca/ ; https://www.dolphinmarine.ca/services</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural verification for larger dock/wharf/float construction projects, positioned as an occasional independent check on load and structural design.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No dedicated engineering department - Tom Stenner as Owner is the right altitude of contact for a company this size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Gibsons, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Tideline Boats (Gibsons, BC)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://tidelineboats.ca/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Boatbuilder (semi-custom aluminum)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Vessel Design &amp; Construction</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Design and construction of semi-custom welded aluminum recreational, sport and commercial boats; full-service marine yard</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Sunshine Coast semi-custom aluminum boat builder and yard - a smaller-scale but genuine complement to Coastal Craft's boutique yacht work, in the same marine-fabrication niche AH Structures targets.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Located in Gibsons, BC; builds recreational, sport and commercial welded aluminum boats and operates a full-service yard. Source: https://tidelineboats.ca/</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://tidelineboats.ca/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://tidelineboats.ca/</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural/hull-design verification support for semi-custom aluminum boat builds, as a smaller-scale complement to outreach at Coastal Craft.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>IMPORTANT: search results also surfaced a separate 'Tideline Boats, Inc.' based in Wilson, NC / Edenton, MD, USA (tidelineboats.com, contacts George Stronach and Michael Collins with a 252 area code) - this appears to be an unrelated US company with a similar name. Do NOT use those US contacts for this Gibsons, BC entry; no BC-specific decision-maker was confirmed in this pass.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Powell River, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Coastal Custom Fabrication</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.canpages.ca/page/BC/powell-river/coastal-custom-fabrication/101416752</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Structural, Industrial &amp; Marine Welding Shop</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial / Marine Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural, industrial and marine welding and fabrication (aluminum, stainless, steel), including mobile welding services performed on the water</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Powell River fabricator explicitly offering structural, industrial and marine welding, including on-water mobile welding - a direct, if small-scale, fit for AH Structures' marine/industrial structural scope, in a coastal town with a genuine industrial history.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified; offers on-site fabrication and repairs in aluminum, stainless and steel; markets on-water mobile welding services. Source: https://www.canpages.ca/page/BC/powell-river/coastal-custom-fabrication/101416752 ; https://powellriverconnect.com/listing/welders/coastal-custom-fabrication/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Pat Haist</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Associated with the business (35 years welding/fabrication experience; exact title unconfirmed)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Business directory listings (Canpages, Powell River Community Directory)</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.canpages.ca/page/BC/powell-river/coastal-custom-fabrication/101416752 ; https://powellriverconnect.com/listing/welders/coastal-custom-fabrication/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural verification and lifting/load calculations for marine and industrial fabrication jobs, especially on-water repair work where an independent check adds value.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Pat Haist's exact title (owner vs. lead tradesperson) was not confirmed in this pass - verify before outreach. The former Powell River pulp mill site (Catalyst Paper/Paper Excellence, permanently closed 2023, now being redeveloped as Cranberry Business Park) was also researched but is not itself an active engineering client at present, so it was not added as a prospect.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8625,7 +9379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A218"/>
+  <dimension ref="A1:A235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -10084,6 +10838,118 @@
       <c r="A218" s="9" t="inlineStr">
         <is>
           <t>Whistler Welding Services Ltd. (Sea-to-Sky corridor, 35+ years) was found and researched but routed to Review: well-documented work is seismic upgrades and architectural steel for residential/commercial/public-works projects, with no marine or heavy-industrial evidence, and sources disagree on the current President's name (Sierra Townley vs. Sandy Ryan) - both issues need resolving before this could be a prospect either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t>Batch 12: Gibsons, BC &amp; Powell River, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>1. Coastal Craft Yachts Ltd. (Gibsons) - Score 9, Priority A - the strongest small-town find yet: a boutique custom aluminum vessel builder (120+ vessels since 1996), named Founder/President Jeff Rhodes, well-documented via a third-party industry profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>2. Dolphin Marine Services Ltd. (Gibsons) - Score 7, Priority B - dock/wharf/marine construction and fabrication, named Owner Tom Stenner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="inlineStr">
+        <is>
+          <t>3. Coastal Custom Fabrication (Powell River) - Score 7, Priority B - structural/industrial/marine welding including on-water mobile service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="9" t="inlineStr">
+        <is>
+          <t>4. Tideline Boats (Gibsons) - Score 6, Priority C - semi-custom aluminum boat builder and yard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="9" t="inlineStr">
+        <is>
+          <t>Custom aluminum vessel building. This batch overturned the expectation set going in (that Gibsons would be thin like Sechelt) - Coastal Craft Yachts is a genuine boutique naval-architecture-adjacent builder, arguably the strongest single-company fit found in any small-town batch so far.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="inlineStr">
+        <is>
+          <t>For Coastal Craft, approach founder Jeff Rhodes directly with a structural/fatigue/FEA pitch tailored to custom aluminum hull and superstructure work - this is a company where the fit is strong enough to justify a founder-level approach rather than a general inquiry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch, but Coastal Craft's ongoing custom-build model (each vessel effectively a new design) is a structurally recurring rather than one-off need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Coastal Craft Yachts (Jeff Rhodes, Founder &amp; President). Follow with Dolphin Marine Services (Tom Stenner, Owner) and Coastal Custom Fabrication (confirm Pat Haist's exact title first).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="9" t="inlineStr">
+        <is>
+          <t>A name-collision risk was caught and avoided: search results for 'Tideline Boats' (Gibsons, BC) also surfaced contact details (George Stronach, Michael Collins) for what is almost certainly a separate, unrelated US company, 'Tideline Boats, Inc.' of Wilson, NC / Edenton, MD (different domain, different area code) - those contacts were deliberately excluded from this entry rather than misattributed. The former Powell River pulp mill site (Catalyst Paper/Paper Excellence, permanently closed 2023) was researched but not added, since it is not currently an operating engineering client - only redevelopment plans exist.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -30,6 +30,8 @@
     <sheet name="Sechelt, BC" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="Gibsons, BC" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="Powell River, BC" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Nanaimo, BC" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Parksville, BC" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -57,6 +59,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Sechelt, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Gibsons, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Powell River, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Nanaimo, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Parksville, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8886,6 +8890,768 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Nanaimo, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Herold Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.heroldengineering.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/herold-engineering-limited</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Engineering Consultancy (Structural &amp; Civil)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Industrial / Bridge Engineering</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural and civil engineering for marine, industrial and bridge projects, including highway and logging bridge engineering</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Nanaimo-headquartered consultancy with an explicit marine/industrial/bridge structural practice, live hiring for exactly that specialty, and a recent acquisition by a much larger firm - a strong, current-evidence overflow-subcontracting fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Live posting for 'Intermediate Structural Engineer (Bridge or Marine)' (Nanaimo or Victoria, BC); acquired by Englobe Corporation in May 2025, an ownership transition that can create transitional capacity needs even as the firm keeps its own structure. Source: https://engineersnovascotia.ca/careers/view/?career.id=841 ; https://www.jobbank.gc.ca/jobsearch/jobposting/50107624</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Founded 1994 by Mike Herold; corporate office in Nanaimo with additional offices in Victoria and Ucluelet; over 70 employees serving Vancouver Island and BC-wide clients across marine, industrial and bridge engineering scopes.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.heroldengineering.com/careers/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website / job postings</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.heroldengineering.com/ ; https://www.heroldengineering.com/wp-content/uploads/2020/06/HEL_Nanaimo_Bridges_10PE-1.pdf</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Reference the live Bridge/Marine structural engineering posting directly - offer AH Structures as flexible external capacity for marine/industrial structural or FEA scopes while Herold fills the permanent role, and note the firm's recent acquisition as a period where external support can smooth workload transitions.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No individual decision-maker's name was confirmed this pass beyond founder Mike Herold (now operating within Englobe post-acquisition) - identify the current Nanaimo office lead before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nanaimo, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Nanaimo Port Authority (Duke Point Terminal)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://npa.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Marine Port Authority / Terminal Operator</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Port Infrastructure / Bulk &amp; Project Cargo</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Deep-sea terminal operations (product exports, container handling, kaolin and salt discharge, fuel transfer, project cargo); recent investment in a 104-tonne mobile harbour crane</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Active port authority operating Duke Point terminal, with a recently upgraded heavy-lift crane and an ongoing Duke Point Terminal Expansion project under environmental review - both are concrete signals of current and near-term infrastructure and equipment work that periodically needs structural/lifting engineering support.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Duke Point Terminal Expansion project is under federal environmental assessment (Pomerleau listed as a project partner); a new 104-tonne-capacity Liebherr mobile harbour crane was recently added to expand project/breakbulk cargo handling. Source: https://iaac-aeic.gc.ca/050/evaluations/proj/82909 ; https://www.heavyliftpfi.com/sectors/nanaimo-gets-a-lift/9938.article</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Terminal features a barge berth, a 170 m deep-sea berth, and handles product exports, kaolin/salt discharge, fuel transfer and project cargo. Source: https://npa.ca/ ; https://deepsea.npa.ca/en/terminal-facilities/cargo-facilities/duke-point/</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>John Darbyshire</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Manager, Vancouver Island Stevedoring &amp; Duke Point Operations</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://npa.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Web search snippet (single source)</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://npa.ca/ ; https://iaac-aeic.gc.ca/050/evaluations/proj/82909</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Reference the Duke Point Terminal Expansion and recent crane upgrade directly - offer independent structural/lifting-engineering verification support for terminal infrastructure and cargo-handling equipment tied to that expansion.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>John Darbyshire's title (stevedoring/operations, not engineering) suggests he may not be the right technical contact for structural/FEA work specifically - useful as an entry point, but confirm whether the Port Authority has a distinct engineering/infrastructure lead before a technical pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nanaimo, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Westshore Structural Engineering Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.westshoreeng.ca/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Engineering Consultancy (Structural, boutique)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Industrial / Marine Infrastructure</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Structural engineering design and construction services for industrial and marine infrastructure, private and public sector</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Nanaimo/Langford-based boutique structural firm with an explicit industrial and marine infrastructure practice and a named principal - a smaller-scale peer to Herold Engineering, in the same overflow-subcontracting category as similar boutique firms found in earlier batches.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Operating out of Nanaimo and Langford, BC; self-describes work across industrial and marine infrastructure for private and public sector clients. Source: https://www.westshoreeng.ca/ ; https://members.nanaimochamber.bc.ca/list/member/westshore-structural-engineering-ltd-2150</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Brian Lange</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Principal, Structural Engineer</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/brian-lange-33757841</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.westshoreeng.ca/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Public LinkedIn profile (search snippet)</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.westshoreeng.ca/ ; https://members.nanaimochamber.bc.ca/list/member/westshore-structural-engineering-ltd-2150</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Approach Brian Lange as a peer-level structural practice, proposing an overflow-subcontracting arrangement for marine/industrial-infrastructure scopes.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>Brian Lange's title was read from a public LinkedIn search snippet only (profile not directly opened) - confirm current role before outreach.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Parksville, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Macon Industries Inc. (Macon Fabrication)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://maconfabrication.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/macon-industries-inc</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial Equipment Manufacturer &amp; Fabricator</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Mining / Drilling Equipment / Industrial Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Machining, CAD design, custom metal fabrication, mobile fabrication and installation, mechanical/electrical assembly and industrial coatings; mining and drilling equipment manufacturing</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Parksville-based (with a Chemainus shop) industrial fabricator and equipment manufacturer with a confirmed named President; large fabricated mining/drilling equipment assemblies can require structural verification and lifting-lug/load calculations, though no marine-specific evidence was found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Two related entities share the Parksville address and appear connected: Macon Fabrication (metal fabrication services) and Macon Industries Inc. (mining and drilling equipment manufacturing). Source: https://maconfabrication.com/ ; https://maconindustries.com/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Matt Conley</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President (Macon Industries Inc.)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://maconindustries.com/our-company/contact/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Web search snippet (ZoomInfo/company site corroborated for Macon Industries Inc. specifically)</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://maconfabrication.com/ ; https://maconindustries.com/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural verification and lifting-engineering support for mining/drilling equipment fabrication, positioned around the industrial (not marine) side of their business.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Matt Conley is confirmed as President of Macon Industries Inc. specifically - it is not fully confirmed whether this is the same legal entity as 'Macon Fabrication' or a closely related sister company at the same address; verify the correct entity and contact before outreach.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9379,7 +10145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A235"/>
+  <dimension ref="A1:A256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -10950,6 +11716,146 @@
       <c r="A235" s="9" t="inlineStr">
         <is>
           <t>A name-collision risk was caught and avoided: search results for 'Tideline Boats' (Gibsons, BC) also surfaced contact details (George Stronach, Michael Collins) for what is almost certainly a separate, unrelated US company, 'Tideline Boats, Inc.' of Wilson, NC / Edenton, MD (different domain, different area code) - those contacts were deliberately excluded from this entry rather than misattributed. The former Powell River pulp mill site (Catalyst Paper/Paper Excellence, permanently closed 2023) was researched but not added, since it is not currently an operating engineering client - only redevelopment plans exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="7" t="inlineStr">
+        <is>
+          <t>Batch 13: Nanaimo, BC &amp; Parksville, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="9" t="inlineStr">
+        <is>
+          <t>1. Herold Engineering Limited (Nanaimo) - Score 9, Priority A - marine/bridge/industrial structural consultancy, live hiring for exactly that specialty, recently acquired by Englobe Corporation (May 2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>2. Nanaimo Port Authority / Duke Point Terminal (Nanaimo) - Score 8, Priority A - active terminal expansion under environmental review plus a recent 104-tonne crane upgrade, named operations contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="inlineStr">
+        <is>
+          <t>3. Westshore Structural Engineering Ltd. (Nanaimo) - Score 7, Priority B - boutique industrial/marine structural firm, named Principal Brian Lange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="inlineStr">
+        <is>
+          <t>4. Macon Industries Inc. / Macon Fabrication (Parksville) - Score 6, Priority C - mining/drilling equipment manufacturer and fabricator, named President Matt Conley.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="9" t="inlineStr">
+        <is>
+          <t>Marine/industrial/bridge structural engineering consultancies. Confirming the pre-batch expectation, Nanaimo delivered this project's strongest single-city batch: two named structural consultancies with explicit marine practices, one with a live matching job posting and a recent acquisition, plus an active port terminal expansion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="9" t="inlineStr">
+        <is>
+          <t>For Herold Engineering, reference the live Bridge/Marine posting and the recent Englobe acquisition directly. For Nanaimo Port Authority, reference the Duke Point expansion and crane upgrade. Both are dated, concrete hooks rather than generic capability pitches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="9" t="inlineStr">
+        <is>
+          <t>Herold Engineering Limited (live Bridge/Marine structural posting, recent acquisition); Nanaimo Port Authority (active Duke Point Terminal Expansion under federal environmental review).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="9" t="inlineStr">
+        <is>
+          <t>Herold Engineering Limited and Westshore Structural Engineering Ltd. - both explicit marine/industrial structural practices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="9" t="inlineStr">
+        <is>
+          <t>Nanaimo Port Authority / Duke Point Terminal - new 104-tonne mobile harbour crane and active terminal expansion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Herold Engineering Limited (find the current Nanaimo office lead post-acquisition) and Nanaimo Port Authority (confirm whether a distinct engineering/infrastructure contact exists beyond John Darbyshire's operations role). Follow with Westshore Structural Engineering (Brian Lange) and Macon Industries (Matt Conley, confirm correct entity first).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="9" t="inlineStr">
+        <is>
+          <t>Macon Fabrication and Macon Industries Inc. appear to be closely related entities sharing a Parksville address, but it was not fully confirmed whether they are the same legal entity - flagged for verification before outreach rather than assumed. This is the strongest batch of the project so far by named-contact density and evidence quality, consistent with Nanaimo's real scale as a Vancouver Island port and engineering hub.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -32,6 +32,8 @@
     <sheet name="Powell River, BC" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="Nanaimo, BC" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="Parksville, BC" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Qualicum Beach, BC" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Courtenay, BC" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -61,6 +63,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Powell River, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Nanaimo, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Parksville, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Qualicum Beach, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Courtenay, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3072,7 +3076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -3754,6 +3758,48 @@
       <c r="H16" s="10" t="inlineStr">
         <is>
           <t>https://www.whistlerweldingservices.com/team ; https://www.bbb.org/ca/bc/pemberton/profile/steel-fabrication/whistler-welding-services-ltd-0037-1281014</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Courtenay, BC</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>McElhanney</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>https://www.mcelhanney.com/locations/courtenay-british-columbia/</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Large, well-regarded Western Canadian multidisciplinary consultancy (30+ locations) with a genuine 40+ person bridge/marine practice and multiple current 'Senior Marine Structural Engineer' postings - but those specific live postings are for Surrey, Victoria, Coquitlam and North Vancouver, not Courtenay, and it was not confirmed whether the Courtenay office itself carries marine structural work.</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether the Courtenay office specifically does marine/structural engineering work, or whether that practice sits only in McElhanney's larger urban offices, before treating this as a Courtenay-specific prospect.</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>https://www.mcelhanney.com/locations/courtenay-british-columbia/ ; https://www.theladders.com/job/senior-marine-structural-engineer-mcelhanney-victoria-bc_87192114</t>
         </is>
       </c>
     </row>
@@ -10139,13 +10185,539 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Qualicum Beach, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Whiskey Creek Marine</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.whiskeycreekmarine.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Aluminum Boatbuilder</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Vessel Fabrication &amp; Repair</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom aluminum boat fabrication, repairs and modifications</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Qualicum Beach-area aluminum boat builder (associated with E &amp; D Manufacturing Ltd.) - a genuine, if small-scale, marine fabrication fit for structural/repair verification work.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Located at 3684 Alberni Hwy, Qualicum Beach, BC; specializes in custom aluminum vessel fabrication, repairs and modifications. Source: https://www.whiskeycreekmarine.ca/ ; https://www.hotfrog.ca/company/1074585365803008/whiskey-creek-marine/qualicum-beach/boats</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.whiskeycreekmarine.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website / directory listings</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.whiskeycreekmarine.ca/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Offer occasional structural verification for aluminum hull repairs or custom fabrication jobs, positioned as low-cost, on-call support given the shop's small scale.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No named owner/principal identified this pass - contact via the company's general channel. Associated entity 'E &amp; D Manufacturing Ltd.' was noted but not independently verified.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Courtenay, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Ocean Metal Custom Fabricators Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://oceanmetal.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Marine Metal Fabricator</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Vessel Fabrication &amp; Repair</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Red Seal-certified custom metal fabrication and repair (aluminum, stainless, bronze, mild steel) for pleasure craft and commercial vessels</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Courtenay-based, Red Seal-certified marine metal fabricator explicitly serving both pleasure craft and commercial vessels in the Comox Valley - a direct, evidenced marine-fabrication fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Located at 2441 Cousins Ave #5, Courtenay, BC; repairs and replaces metal components for pleasure craft and commercial vessels working in aluminum, stainless, bronze and mild steel. Source: https://oceanmetal.ca/about-us/ ; https://oceanmetal.ca/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://oceanmetal.ca/contact/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://oceanmetal.ca/ ; https://oceanmetal.ca/about-us/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural verification and repair-scope engineering support for commercial vessel work specifically, since that side of their business is closer to AH Structures' core scope than the pleasure-craft side.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No named owner/principal identified this pass - contact via the company's general channel.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A256"/>
+  <dimension ref="A1:A271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -11856,6 +12428,104 @@
       <c r="A256" s="9" t="inlineStr">
         <is>
           <t>Macon Fabrication and Macon Industries Inc. appear to be closely related entities sharing a Parksville address, but it was not fully confirmed whether they are the same legal entity - flagged for verification before outreach rather than assumed. This is the strongest batch of the project so far by named-contact density and evidence quality, consistent with Nanaimo's real scale as a Vancouver Island port and engineering hub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="7" t="inlineStr">
+        <is>
+          <t>Batch 14: Qualicum Beach, BC &amp; Courtenay, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="9" t="inlineStr">
+        <is>
+          <t>1. Ocean Metal Custom Fabricators Inc. (Courtenay) - Score 7, Priority B - Red Seal-certified marine metal fabricator serving both pleasure craft and commercial vessels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="inlineStr">
+        <is>
+          <t>2. Whiskey Creek Marine (Qualicum Beach) - Score 6, Priority C - small aluminum boatbuilder/repair shop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="9" t="inlineStr">
+        <is>
+          <t>Small-scale marine metal fabrication. Both cities produced modest but genuine marine-fabrication fits rather than heavy-industrial or FEA-specific ones - consistent with the smaller, less industrialized profile of these two towns relative to Nanaimo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>For Ocean Metal, lead with the commercial-vessel side of their work specifically, since that is closer to AH Structures' core scope than pleasure-craft repair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="9" t="inlineStr">
+        <is>
+          <t>None identified this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="9" t="inlineStr">
+        <is>
+          <t>Contact Ocean Metal Custom Fabricators first (via general inquiry); Whiskey Creek Marine as a smaller, secondary follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="9" t="inlineStr">
+        <is>
+          <t>McElhanney, a large and genuinely strong Western Canadian consultancy with a real 40+ person marine/bridge practice and multiple current 'Senior Marine Structural Engineer' postings, was found via its Courtenay office listing - but those specific live postings are for Surrey, Victoria, Coquitlam and North Vancouver, not Courtenay, and it could not be confirmed whether the Courtenay office itself carries marine structural work. Routed to Review rather than assumed, to avoid overstating a city-specific fit that the evidence doesn't actually support - a similar caution to the Ausenco office-specific verification in batch 3. CFB Comox (19 Wing) construction opportunities were reviewed and excluded outright as Department of National Defence work, not researched further.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -34,6 +34,8 @@
     <sheet name="Parksville, BC" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="Qualicum Beach, BC" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="Courtenay, BC" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Comox, BC" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Campbell River, BC" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -65,6 +67,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Parksville, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Qualicum Beach, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Courtenay, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'Comox, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'Campbell River, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3076,7 +3080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -3800,6 +3804,48 @@
       <c r="H17" s="10" t="inlineStr">
         <is>
           <t>https://www.mcelhanney.com/locations/courtenay-british-columbia/ ; https://www.theladders.com/job/senior-marine-structural-engineer-mcelhanney-victoria-bc_87192114</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Comox, BC</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Comox Marine &amp; Woodworking Ltd.</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>https://www.comoxmarine.ca/</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Genuinely Comox-based marine business (est. 2011), but its actual work is marine electrical/electronics installation, woodworking/varnishing/cabinetry, and van/tiny-home conversions - a retail and light-repair marine business, not structural or heavy fabrication.</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether any structural or heavy-fabrication work exists before treating as a prospect; as researched, this is not an AH Structures core fit.</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>https://www.comoxmarine.ca/contact/</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="3" min="1" max="1"/>
@@ -10705,6 +10751,872 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Courtenay, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Coastline Fabricators</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coastlinefabricators.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Marine Metal Fabricator</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Vessel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Marine aluminum and steel fabrication tailored to individual client applications</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>20+ year Courtenay-area marine fabricator (found during Comox research, but its actual address places it in Courtenay) - a second, genuine marine-fabrication fit alongside Ocean Metal Custom Fabricators in the same city.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Serving the Comox Valley and greater Vancouver Island for over 20 years, specializing in marine aluminum and steel fabrication. Source: https://www.coastlinefabricators.ca/</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coastlinefabricators.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Company website / directory listing (Yellow Pages)</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coastlinefabricators.ca/ ; https://www.yellowpages.ca/bus/British-Columbia/Courtenay/Coastline-Fabricators/104459123.html</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural verification for marine aluminum/steel fabrication projects, as a secondary contact alongside Ocean Metal Custom Fabricators in the same city.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Initially surfaced during Comox, BC research but confirmed to be Courtenay-based (3224 Royston Rd) - added to this sheet rather than Comox to keep city attribution accurate. No named owner/principal identified this pass.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Campbell River, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>T-MAR Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://t-mar.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial Design, Engineering &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Forestry / Mining / Marine / Hydroelectric / Pulp &amp; Paper</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Design, engineering and industrial manufacturing of heavy-duty forestry, mining, marine, hydroelectric and pulp-and-paper equipment</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Campbell River-founded (1984) engineering and fabrication house explicitly serving the marine sector alongside forestry, mining, hydro and pulp &amp; paper - large fabricated heavy equipment across these sectors routinely needs structural verification and lifting/rigging calculations.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Founded 1984 by George Lambert and Gord Olafsen to serve BC's logging industry with mechanical, machining and welding services; today designs and remanufactures logging and heavy-industrial equipment across Forestry, Hydroelectric, Mining, Marine and Pulp &amp; Paper sectors. Source: https://t-mar.com/about/ ; https://t-mar.com/about-2/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>George Lambert</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://t-mar.com/contact/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>inquiries@t-mar.com (general company inbox)</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website / business directory (RocketReach corroborated)</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://t-mar.com/ ; https://t-mar.com/about/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach George Lambert directly, offering structural verification, FEA and lifting-engineering support for the marine and heavy-equipment side of T-MAR's design and fabrication work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Strong, well-documented fit across multiple heavy-industrial sectors including marine; one of the more diversified heavy-equipment engineering houses found in any batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Campbell River, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>StoneCroft Engineering Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.stonecroftengineering.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/stonecroft-project-engineering</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Engineering Consultancy (Structural, boutique)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Industrial / Forestry Infrastructure</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Conceptual and detailed structural design for road/pedestrian bridges, industrial structures, marine structures and foundations, including marine and dryland log transfer facilities</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Campbell River-based structural consultancy with a specific, well-documented marine-structures practice (100+ marine and dryland log transfer facilities designed across coastal BC) - a precise, evidence-rich fit for structural/FEA overflow work.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Designed and constructed over 100 marine and dryland log transfer facilities across coastal BC; current Principal &amp; Managing Engineer Lee Deslauriers took over from founder G. Glen Beaton in 2011. Source: https://www.stonecroftengineering.ca/structural-engineering/ ; https://businessexaminer.ca/victoria-articles/item/stonecroft-engineering-expand-their-repertoire-with-bc-bred-talent/</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Lee Deslauriers</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Principal &amp; Managing Engineer</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/janice-mathers-40b08029</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.stonecroftengineering.ca/crew/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>lee@stonecroftengineering.ca</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (crew page) / industry press (Business Examiner)</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.stonecroftengineering.ca/ ; https://businessexaminer.ca/victoria-articles/item/stonecroft-engineering-expand-their-repertoire-with-bc-bred-talent/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach Lee Deslauriers directly, proposing a peer/overflow-subcontracting arrangement for marine structural design or FEA scopes during busy periods, given the closely overlapping specialty.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Note: the LinkedIn URL in the Decision Maker LinkedIn column is for Janice Mathers, listed elsewhere as 'Principal &amp; General Manager' at StoneCroft - the firm may have more than one principal; Lee Deslauriers' direct email (lee@stonecroftengineering.ca) was independently confirmed via the company's own crew page, so is the more reliable named contact here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Campbell River, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Ocean Pacific Marine Supply Ltd. (Ocean Pacific Marine Store &amp; Boatyard)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://oceanpacificmarine.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Marine Repair Yard &amp; Boatyard</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Vessel Repair, Refit &amp; Life-Extension</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Repair, refit and life-extension services for government, commercial and recreational vessels; 150-ton travelift; full-service boatyard and marine retail store</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Largest marine repair yard north of Victoria (operating since 1985, ISO 9001 and CWB certified), currently being acquired by a Canadian investment fund - an active ownership transition is a concrete, dated signal that engineering/technical capacity needs may be in flux.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Ocean Pacific Marine Supply Ltd. has entered into an agreement with Regenerative Capital Group, a Canadian investment fund, to be acquired - a live ownership transition. Source: https://businessexaminer.ca/vancouver-island-articles/item/canadian-investment-fund-acquiring-ocean-pacific-marine-supply/</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Operating since 1985 in Discovery Harbour Marina; services commercial vessels requiring outfitting, equipment installation, upgrades, modifications, maintenance and structural work; repairs wood, fiberglass, aluminum and steel hulls. Source: https://oceanpacificmarine.com/about-us/</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://oceanpacificmarine.com/contact/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Company website / industry press (Business Examiner)</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://oceanpacificmarine.com/ ; https://businessexaminer.ca/vancouver-island-articles/item/canadian-investment-fund-acquiring-ocean-pacific-marine-supply/</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Reference the pending acquisition directly - offer AH Structures as independent structural verification capacity to help manage any transitional engineering workload during the ownership change.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>No named owner/GM identified this pass - contact via general channel and reference the pending Regenerative Capital Group transaction to establish relevance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Campbell River, BC</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Campbell River Marine Terminal Ltd. (incl. Menzies Marine)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>https://crmt.ca/</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Marine Terminal &amp; Boatyard Operator</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Port Infrastructure / Tug &amp; Barge</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>All-tide ramp/bulkhead access for tug and barge operations, ro-ro load/unload for vessels and barges; Menzies Marine division offers a 150-ton travel lift and full-service boatyard</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Full-service marine terminal serving the tug and barge community with heavy ro-ro equipment ramps, plus a boatyard division - terminal ramp/bulkhead structures and vessel-lift operations periodically need structural/lifting verification.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Provides four ramp/bulkhead configurations for high and low profile shot-rock ramps and two concrete bulkheads for tide-independent ro-ro operations; Menzies Marine division launched September 2019. Source: https://crmt.ca/about-us/ ; https://menziesmarine.ca/</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Ann Adams</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>http://crmt.ca/contact-us/</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>ZoomInfo (contact listing)</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>https://crmt.ca/ ; https://www.zoominfo.com/p/Ann-Adams/2634018572</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural verification for ramp/bulkhead infrastructure and boatyard lift operations, positioned as an occasional independent check.</t>
+        </is>
+      </c>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>Ann Adams' title (Owner) was drawn from a ZoomInfo listing, not directly corroborated by the company's own site - confirm before outreach.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10717,7 +11629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A271"/>
+  <dimension ref="A1:A293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -12526,6 +13438,153 @@
       <c r="A271" s="9" t="inlineStr">
         <is>
           <t>McElhanney, a large and genuinely strong Western Canadian consultancy with a real 40+ person marine/bridge practice and multiple current 'Senior Marine Structural Engineer' postings, was found via its Courtenay office listing - but those specific live postings are for Surrey, Victoria, Coquitlam and North Vancouver, not Courtenay, and it could not be confirmed whether the Courtenay office itself carries marine structural work. Routed to Review rather than assumed, to avoid overstating a city-specific fit that the evidence doesn't actually support - a similar caution to the Ausenco office-specific verification in batch 3. CFB Comox (19 Wing) construction opportunities were reviewed and excluded outright as Department of National Defence work, not researched further.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="7" t="inlineStr">
+        <is>
+          <t>Batch 15: Comox, BC &amp; Campbell River, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="9" t="inlineStr">
+        <is>
+          <t>1. T-MAR Industries Ltd. (Campbell River) - Score 9, Priority A - diversified heavy-equipment engineering/fabrication house (forestry, mining, marine, hydro, pulp &amp; paper) since 1984, named President George Lambert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="9" t="inlineStr">
+        <is>
+          <t>2. StoneCroft Engineering Ltd. (Campbell River) - Score 9, Priority A - structural consultancy with a precise, well-documented marine-structures practice (100+ marine/log-transfer facilities), named Principal Lee Deslauriers with a direct email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>3. Ocean Pacific Marine Supply Ltd. (Campbell River) - Score 8, Priority A - largest marine repair yard north of Victoria, currently being acquired by a Canadian investment fund (Regenerative Capital Group).</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="9" t="inlineStr">
+        <is>
+          <t>4. Campbell River Marine Terminal Ltd. / Menzies Marine (Campbell River) - Score 7, Priority B - full-service marine terminal and boatyard, named Owner Ann Adams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="9" t="inlineStr">
+        <is>
+          <t>No qualified company was found for Comox, BC this pass; Coastline Fabricators, initially thought to be Comox-based, was confirmed Courtenay-based and added to that city's existing sheet instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="9" t="inlineStr">
+        <is>
+          <t>Marine structural engineering and diversified heavy-equipment fabrication. Campbell River matched Nanaimo as the project's strongest single-city batch: two named consultancies/fabricators with explicit, well-evidenced marine practices, plus an active acquisition and a working marine terminal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="9" t="inlineStr">
+        <is>
+          <t>For StoneCroft, approach peer-to-peer given the near-identical marine-structures specialty. For T-MAR, lead with the marine side of their diversified heavy-equipment work. For Ocean Pacific Marine Supply, reference the pending acquisition directly as a reason extra engineering capacity may be useful during the transition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="8" t="inlineStr">
+        <is>
+          <t>Overflow opportunities (strongest evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="inlineStr">
+        <is>
+          <t>Ocean Pacific Marine Supply Ltd. - active, named acquisition (Regenerative Capital Group) in progress, a concrete and current transition signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="8" t="inlineStr">
+        <is>
+          <t>Specialized FEA opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="inlineStr">
+        <is>
+          <t>StoneCroft Engineering Ltd. and T-MAR Industries Ltd. - both maintain genuine marine/heavy-structural engineering practices with named, verifiable contacts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="8" t="inlineStr">
+        <is>
+          <t>Heavy lift / transport opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="9" t="inlineStr">
+        <is>
+          <t>Campbell River Marine Terminal Ltd. / Menzies Marine - ro-ro ramp/bulkhead infrastructure and a 150-ton travel lift boatyard operation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: StoneCroft Engineering (Lee Deslauriers, direct email confirmed) and T-MAR Industries (George Lambert, President). Follow with Ocean Pacific Marine Supply (reference the pending acquisition) and Campbell River Marine Terminal (confirm Ann Adams' title first).</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="inlineStr">
+        <is>
+          <t>Coastline Fabricators surfaced during Comox research but its actual address (3224 Royston Rd) places it in Courtenay - added to the existing Courtenay, BC sheet as a second entry rather than misfiled under Comox, the same correction pattern used for Marcon Metalfab (batch 4) and the Township of Langley mix-up (batch 7). Comox Marine &amp; Woodworking (genuinely Comox-based) was routed to Review: it is a marine electrical/woodworking retail and light-repair business, not a structural or heavy-fabrication fit. CFB Comox (19 Wing) construction opportunities were excluded outright as Department of National Defence work, per the guardrail applied since batch 14.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -36,6 +36,8 @@
     <sheet name="Courtenay, BC" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="Comox, BC" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="Campbell River, BC" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Port Alberni, BC" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Duncan, BC" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -69,6 +71,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Courtenay, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'Comox, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'Campbell River, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'Port Alberni, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'Duncan, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11623,13 +11627,659 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Port Alberni, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Canadian Maritime Engineering Ltd. (CME) - Port Alberni / West Coast Division</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://cmewestcoast.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/canadian-maritime-engineering-ltd.-cme-</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Shipyard &amp; Marine/Industrial Services</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Shipbuilding / Ship Repair</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Full-service shipyard (up to 450-ton haul out, marine railway, two synchro-lifts), machining, mechanical, welding, fabrication and specialty coatings; developing a new full-service shipyard at a 5-acre Canal Beach waterfront facility</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Deep-water Port Alberni shipyard with a marine industrial heritage dating to 1914 (as Canadian Alberni Engineering, 150+ vessels built), now operating as CME's West Coast division with 40,000 sq ft of indoor manufacturing/new-vessel construction - a strong, historically rich fit for structural/FEA and repair-scope engineering support.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established as a current-dated signal in this pass, though the company is actively developing new shipyard facilities (Canal Beach).</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Historically operated as Canadian Alberni Engineering (est. 1914), a shipbuilder with 150+ vessels delivered up to 95 ft, later becoming CME's Port Alberni/West Coast operation; CME's parent company is headquartered in Dartmouth, Nova Scotia, with the Port Alberni site as one of its West Coast facilities. Source: https://cmewestcoast.com/about-us/ ; https://www.alberni-cae.com/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://cmewestcoast.com/about-us/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>office@cmelimited.com (parent company general inbox)</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company websites (cmewestcoast.com, alberni-cae.com) / directory listings</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://cmewestcoast.com/ ; https://cmewestcoast.com/about-us/ ; https://www.alberni-cae.com/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach the Port Alberni/West Coast facility directly (not the Nova Scotia head office) offering structural/FEA and repair-scope engineering support for shipyard haul-out, repair and new-construction work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>CME's head office is in Dartmouth, NS (a national company with a West Coast division) - no Port Alberni-specific named contact was confirmed in this pass; Mark Hall, found as 'General Manager - Central Canada' on LinkedIn, is NOT the right West Coast contact and should not be used. The historical link between Canadian Alberni Engineering and the current CME West Coast operation, both at 3101 Bird Ave, was inferred from matching addresses and services - worth confirming directly.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Duncan, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Pacific Industrial &amp; Marine Ltd. (PIM)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://pimltd.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Marine Construction &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Bridge Construction</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Marine systems and bridge construction: custom steel pontoon docks, engineered aluminum bridges, pile installation; steel and aluminum fabrication shops and pre-cast concrete area on an 8-acre facility</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Cowichan Bay-based marine and bridge construction company with a large (8-acre) dedicated facility and CWB-certified fabrication shops - a direct, evidence-rich fit for marine/bridge structural verification and FEA support.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Facility includes steel and aluminum fabrication shops, a pre-cast concrete area, and a large dock-construction zone; staff include certified skippers, crane operators, bridgemen, pile drivers, carpenters and steel/aluminum welders. Source: https://pimltd.ca/about-us/ ; https://pimltd.ca/metal-fabrication/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President (B.Comm; owner since 2004)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://pimltd.ca/contact-us/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@pimltd.ca (general company inbox)</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website / business directory listings</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://pimltd.ca/ ; https://www.dnb.com/business-directory/company-profiles.pacific_industrial__marine_ltd.eddd774aa4749421984110526805e266.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach the President/owner directly, offering structural verification and FEA support for marine and bridge construction projects, given the scale and certification depth of their operation.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>The President's name was not confirmed in this pass despite multiple searches - only that they hold a B.Comm and have owned the company since 2004; contact via info@pimltd.ca and ask for the President by role. West Coast Floatation Systems (also researched this batch) shares this exact address (5105 Tzouhalem Rd) and appears to be a closely related, possibly co-located, sister company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Duncan, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>West Coast Floatation Systems</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://wcfltd.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/west-coast-floatation</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Marine Systems Manufacturer</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Floatation Systems</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Design and fabrication of custom aluminum, steel and concrete floatation installations (docks, platforms) for waterways</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Duncan-based marine floatation systems manufacturer, founded 2004, sharing an address with Pacific Industrial &amp; Marine Ltd. - a related or co-located marine fabrication operation, adding a second point of contact in the same facility.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Self-owned since founding in 2004; designs and fabricates custom aluminum, steel and concrete installations in and around waterways, including floating platforms. Source: https://wcfltd.ca/ ; https://wcfltd.ca/platforms/</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://wcfltd.ca/contact-us/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://wcfltd.ca/ ; https://wcfltd.ca/contact-us/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Offer structural/load verification for floatation platform designs, positioned as a complementary contact to Pacific Industrial &amp; Marine Ltd. at the same facility.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Shares the exact address (5105 Tzouhalem Rd, Duncan, BC) with Pacific Industrial &amp; Marine Ltd. - likely a related or affiliated company; no named owner confirmed in this pass, and it is not confirmed whether this is a fully separate legal entity or a division of PIM.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A293"/>
+  <dimension ref="A1:A309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -13585,6 +14235,111 @@
       <c r="A293" s="9" t="inlineStr">
         <is>
           <t>Coastline Fabricators surfaced during Comox research but its actual address (3224 Royston Rd) places it in Courtenay - added to the existing Courtenay, BC sheet as a second entry rather than misfiled under Comox, the same correction pattern used for Marcon Metalfab (batch 4) and the Township of Langley mix-up (batch 7). Comox Marine &amp; Woodworking (genuinely Comox-based) was routed to Review: it is a marine electrical/woodworking retail and light-repair business, not a structural or heavy-fabrication fit. CFB Comox (19 Wing) construction opportunities were excluded outright as Department of National Defence work, per the guardrail applied since batch 14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="7" t="inlineStr">
+        <is>
+          <t>Batch 16: Port Alberni, BC &amp; Duncan, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="9" t="inlineStr">
+        <is>
+          <t>1. Pacific Industrial &amp; Marine Ltd. (Duncan) - Score 9, Priority A - large (8-acre) CWB-certified marine and bridge construction facility, President/owner since 2004 (name unconfirmed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="9" t="inlineStr">
+        <is>
+          <t>2. Canadian Maritime Engineering Ltd., Port Alberni/West Coast Division (Port Alberni) - Score 9, Priority A - full-service shipyard with a marine industrial heritage dating to 1914, part of a national company headquartered in Dartmouth, NS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="9" t="inlineStr">
+        <is>
+          <t>3. West Coast Floatation Systems (Duncan) - Score 7, Priority B - marine floatation systems manufacturer, likely related to Pacific Industrial &amp; Marine at the same address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="9" t="inlineStr">
+        <is>
+          <t>Marine construction and shipyard services. Both cities confirmed the pre-batch expectation of a strong industrial/marine base, continuing the pattern from Nanaimo and Campbell River - this stretch of Vancouver Island (Nanaimo through Duncan) has been the most consistently productive part of the master list so far.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="9" t="inlineStr">
+        <is>
+          <t>For Pacific Industrial &amp; Marine, lead with the scale and certification depth of their marine/bridge construction operation. For CME Port Alberni, approach the local West Coast facility directly rather than the Nova Scotia head office, given the company's national structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch, though CME is actively developing a new shipyard facility (Canal Beach) which may create future capacity needs worth revisiting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Pacific Industrial &amp; Marine Ltd. (ask for the President by role via info@pimltd.ca) and CME's Port Alberni/West Coast division directly (not the Dartmouth, NS head office). Follow with West Coast Floatation Systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="9" t="inlineStr">
+        <is>
+          <t>Canadian Maritime Engineering Ltd. is a national company headquartered in Dartmouth, Nova Scotia; its Port Alberni presence was verified as a genuine West Coast division/facility (matching the historical Canadian Alberni Engineering address and shipbuilding heritage), similar in structure to how Kiewit's Burnaby office was verified in batch 3 - the entry targets the local facility, not the head office. A LinkedIn contact (Mark Hall, 'General Manager - Central Canada') was found during research but deliberately excluded as the wrong regional contact. West Coast Floatation Systems shares an identical address with Pacific Industrial &amp; Marine Ltd. - flagged as a likely related/co-located company rather than confirmed as fully independent.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -38,6 +38,8 @@
     <sheet name="Campbell River, BC" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="Port Alberni, BC" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="Duncan, BC" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Ladysmith, BC" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Sidney, BC" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -73,6 +75,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'Campbell River, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'Port Alberni, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'Duncan, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'Ladysmith, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'Sidney, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3084,7 +3088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -3850,6 +3854,44 @@
       <c r="H18" s="10" t="inlineStr">
         <is>
           <t>https://www.comoxmarine.ca/contact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Sidney, BC</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>J.R. Elkington (marine consultant)</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>A genuine, Transport Canada-listed marine consultant for vessel stability assessment, surfaced during Sidney research - but the address on file (117 Cypress Road) is in North Saanich, BC, an adjacent but distinct municipality not on the master city list.</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>If North Saanich is ever added as a target city, revisit this consultant directly; otherwise this is out of scope for the current Sidney entry.</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>https://tc.canada.ca/en/marine-transportation/vessel-design-construction-maintenance/list-marine-consultants-assessing-vessel-stability</t>
         </is>
       </c>
     </row>
@@ -12273,13 +12315,547 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Ladysmith, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Ladysmith Marine Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://ladysmithmarineservices.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Marine Repair &amp; Haul-Out Yard</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Vessel Repair &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Haul-out, storage and repair for wood, steel, aluminum and fibreglass vessels up to 20 tons/48 ft; steel, stainless and aluminum marine welding</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Family-owned Ladysmith Harbour boatyard (since 2006) offering structural welding and repair for wood/steel/aluminum/fibreglass vessels - a modest but genuine marine-fabrication fit at small-craft scale.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Located at Fisherman's Wharf, Ladysmith; equipped for haul-outs up to 20 tons, 48 ft length, 6 ft draft; provides commercial boat repairs and steel/stainless/aluminum marine welding. Source: https://ladysmithmarineservices.com/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://ladysmithmarineservices.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://ladysmithmarineservices.com/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Offer occasional structural verification for larger repair jobs, positioned as low-cost, on-call support given the yard's small-vessel scale.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No named owner/principal identified this pass - contact via the company's general channel. Norman Ironworks (Ladysmith, est. 2018) was also found but shows no marine-specific evidence and no named contact - not included as a prospect.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Sidney, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Liquid Metal Marine Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://liquidmetalmarine.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Boatbuilder (Aluminum Commercial &amp; Recreational Vessels)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine / Vessel Design &amp; Construction</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Design and fabrication of custom aluminum vessels including commercial workboats (crew boats, harbour patrol, research support, fast-response, RHIBs) across several named series</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Sidney-based aluminum boatbuilder (20+ years), founded by Kristi Benwell, building genuine commercial workboats for crew transport, harbour patrol and research support alongside recreational and sport-fishing vessels - a direct, evidence-rich naval-architecture-adjacent fit similar to Coastal Craft Yachts in batch 12.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Not established in this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Founded by Kristi Benwell after training at Armstrong Marine's Sidney facility; over 20 years building custom aluminum boats for West Coast conditions across multiple named series (Knight, Maquinna, Lagara, Barclay, Clayoquot, Nootka), including commercial crew/patrol/research vessels. Source: https://liquidmetalmarine.com/about-us/ ; https://www.proboat.com/2016/11/liquid-metals-rapid-expansion/</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Kristi Benwell</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://liquidmetalmarine.com/about-us/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Industry profile (Professional BoatBuilder / IBEX Technical Journal) corroborated by company website</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://liquidmetalmarine.com/ ; https://www.proboat.com/2016/11/liquid-metals-rapid-expansion/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach Kristi Benwell directly, offering structural/fatigue verification or FEA support for commercial workboat designs specifically (crew boats, patrol vessels), given their genuine commercial vessel line.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>A second-hand marine consultant, J.R. Elkington (Transport Canada-listed for vessel stability assessment), surfaced during this research but is based in North Saanich, BC - an adjacent but distinct municipality from Sidney, not on the master city list - so was not added here; see the Low Confidence - Review sheet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A309"/>
+  <dimension ref="A1:A324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -14340,6 +14916,104 @@
       <c r="A309" s="9" t="inlineStr">
         <is>
           <t>Canadian Maritime Engineering Ltd. is a national company headquartered in Dartmouth, Nova Scotia; its Port Alberni presence was verified as a genuine West Coast division/facility (matching the historical Canadian Alberni Engineering address and shipbuilding heritage), similar in structure to how Kiewit's Burnaby office was verified in batch 3 - the entry targets the local facility, not the head office. A LinkedIn contact (Mark Hall, 'General Manager - Central Canada') was found during research but deliberately excluded as the wrong regional contact. West Coast Floatation Systems shares an identical address with Pacific Industrial &amp; Marine Ltd. - flagged as a likely related/co-located company rather than confirmed as fully independent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="7" t="inlineStr">
+        <is>
+          <t>Batch 17: Ladysmith, BC &amp; Sidney, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="9" t="inlineStr">
+        <is>
+          <t>1. Liquid Metal Marine Ltd. (Sidney) - Score 8, Priority A - 20+ year aluminum boatbuilder with a genuine commercial-workboat line (crew boats, harbour patrol, research support), named Founder Kristi Benwell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="9" t="inlineStr">
+        <is>
+          <t>2. Ladysmith Marine Services Ltd. (Ladysmith) - Score 6, Priority C - small family-owned marine repair/haul-out yard since 2006.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="9" t="inlineStr">
+        <is>
+          <t>Aluminum commercial workboat building. Liquid Metal Marine's crew/patrol/research vessel line is a strong, evidence-backed fit - a second example (after Coastal Craft Yachts in batch 12) of a boutique BC aluminum boatbuilder being one of the more precise matches for AH Structures' naval-architecture-adjacent scope, even in a small town.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="9" t="inlineStr">
+        <is>
+          <t>For Liquid Metal Marine, approach Kristi Benwell directly with a structural/fatigue/FEA pitch tailored to the commercial workboat series specifically, distinct from their recreational lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Liquid Metal Marine (Kristi Benwell, Founder). Ladysmith Marine Services as a smaller, secondary follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="9" t="inlineStr">
+        <is>
+          <t>J.R. Elkington, a Transport Canada-listed marine stability consultant, surfaced during Sidney research but is actually based in North Saanich, BC - an adjacent but distinct municipality not on the master city list - so was routed to Review rather than added to the Sidney sheet, continuing the project's discipline around exact city attribution. Norman Ironworks (Ladysmith) was found but shows no marine-specific evidence and no named contact, so was not added anywhere.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -40,6 +40,8 @@
     <sheet name="Duncan, BC" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="Ladysmith, BC" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="Sidney, BC" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Saanich, BC" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Langford, BC" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -77,6 +79,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'Duncan, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'Ladysmith, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'Sidney, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'Saanich, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'Langford, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3088,7 +3092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -3892,6 +3896,86 @@
       <c r="H19" s="10" t="inlineStr">
         <is>
           <t>https://tc.canada.ca/en/marine-transportation/vessel-design-construction-maintenance/list-marine-consultants-assessing-vessel-stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Langford, BC</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Accord Metal Fabricators</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Genuinely Langford-based (1256 Glenshire Drive), CWB-certified structural steel fabricator - but its described product line (handrails, guardrails, moment frames, beams) reads as building-construction structural steel, not marine or heavy-industrial work.</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether any marine or heavy-industrial (non-building) fabrication work exists before treating as a prospect.</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Business directory listings (Yelp, Canpages) - no company website found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Saanich, BC</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Alliance Engineering Works Ltd.</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>https://alliance-works.com/</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Strong, well-established (since 1985) structural steel fabricator serving Vancouver Island's marine/forestry/mining/industrial sectors - but its confirmed address (6793 Kirkpatrick Cres, Keating Industrial Park) is in Saanichton, which is within the District of Central Saanich, not the District of Saanich itself. A similar issue applies to Industra Construction's branch office, also in Saanichton.</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>If Central Saanich is ever added as a target city, revisit this company (and Industra Construction's Saanichton branch) directly; both were excluded here purely on municipal-boundary grounds, not fit.</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>https://alliance-works.com/about/ ; https://www.yelp.ca/biz/alliance-engineering-works-saanichton</t>
         </is>
       </c>
     </row>
@@ -12849,13 +12933,339 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A324"/>
+  <dimension ref="A1:A332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -15014,6 +15424,55 @@
       <c r="A324" s="9" t="inlineStr">
         <is>
           <t>J.R. Elkington, a Transport Canada-listed marine stability consultant, surfaced during Sidney research but is actually based in North Saanich, BC - an adjacent but distinct municipality not on the master city list - so was routed to Review rather than added to the Sidney sheet, continuing the project's discipline around exact city attribution. Norman Ironworks (Ladysmith) was found but shows no marine-specific evidence and no named contact, so was not added anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="7" t="inlineStr">
+        <is>
+          <t>Batch 18: Saanich, BC &amp; Langford, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="9" t="inlineStr">
+        <is>
+          <t>None. Both main sheets are empty this pass - a genuine municipal-fragmentation effect specific to Greater Victoria, not a research gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="9" t="inlineStr">
+        <is>
+          <t>Not applicable - the Saanich Peninsula's marine/industrial companies cluster almost entirely in North Saanich, Central Saanich (Saanichton), and Sidney (all covered or noted elsewhere), while the District of Saanich itself is predominantly institutional/residential (University of Victoria, hospitals) with little working waterfront. Langford is similarly residential/suburban with only building-focused steel fabrication found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="9" t="inlineStr">
+        <is>
+          <t>Multiple strong marine/industrial companies surfaced during this batch's research but were excluded on strict municipal-boundary grounds, continuing this project's city-attribution discipline: Ramsay Machine Works (110+ year heavy-industry fabricator) is actually in Sidney, BC (already covered in batch 17) and, per news archives, appears to have wound down/been absorbed by Ralmax Group around 2015 - not treated as an active prospect either way. Alliance Engineering Works Ltd. (est. 1985, strong marine/forestry/mining fit) and Industra Construction's marine-construction branch are both in Saanichton, within the District of Central Saanich - a distinct municipality from the District of Saanich - and were routed to Review rather than the Saanich sheet. Reyse Marine, Blackline Marine, and Fraser Engineering all surfaced but are in North Saanich, the same adjacent-municipality issue flagged for J.R. Elkington in batch 17. Westshore Structural Engineering Ltd. (already recorded under Nanaimo, batch 13) was reconfirmed to also operate a Langford office - not duplicated here since it is the same company already captured, but noted for completeness.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -42,6 +42,8 @@
     <sheet name="Sidney, BC" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="Saanich, BC" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="Langford, BC" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Colwood, BC" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Esquimalt, BC" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -81,6 +83,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'Sidney, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'Saanich, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'Langford, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'Colwood, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'Esquimalt, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3092,7 +3096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -3976,6 +3980,86 @@
       <c r="H21" s="10" t="inlineStr">
         <is>
           <t>https://alliance-works.com/about/ ; https://www.yelp.ca/biz/alliance-engineering-works-saanichton</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Colwood, BC</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Scott Engineering Inc.</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Genuinely Colwood-based structural engineering firm (3148 Antrobus Cres) - but no website, service description, marine/industrial evidence, or named principal was found in this pass; category listing alone ('structural engineer') is not enough to establish fit.</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Call directly (250-391-8682) to confirm services and any marine/industrial work before treating as a prospect.</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.ca/bus/British-Columbia/Colwood/Scott-Engineering-Inc/2525765.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Esquimalt, BC</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Intercon Marine Inc.</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>https://www.interconmarine.com/</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Independent (non-Seaspan), BC-owned marine rigging/heavy-lift/structural-repair company since 1994, based at the Esquimalt Graving Dock - a strong technical fit (heavy-lift hoisting, structural repairs, specialized coatings). However, its own client list mixes commercial work (cruise ships, cargo ships, BC Ferries) with Canadian Navy and Canadian Coast Guard work, and the services themselves (rigging, structural repair) are not separated into distinct commercial vs. defense divisions.</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>This is a genuine judgment call, similar to Mussell Crane (batch 8) and Cimtex Industries (batch 9): confirm directly what proportion of Intercon's work is Navy-related versus commercial/Coast Guard/ferry work before deciding whether to pursue.</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>https://www.interconmarine.com/ ; https://www.zoominfo.com/p/Colin-Spivey/-1322812477</t>
         </is>
       </c>
     </row>
@@ -13265,7 +13349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A332"/>
+  <dimension ref="A1:A342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -15476,7 +15560,396 @@
         </is>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" s="7" t="inlineStr">
+        <is>
+          <t>Batch 19: Colwood, BC &amp; Esquimalt, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="9" t="inlineStr">
+        <is>
+          <t>None. Both main sheets are empty this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="8" t="inlineStr">
+        <is>
+          <t>Why Esquimalt was thin</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="9" t="inlineStr">
+        <is>
+          <t>Esquimalt's working harbour is dominated by two entities excluded on guardrail grounds: Victoria Shipyards is confirmed to be a Seaspan entity (conflict of interest with Ahmad's own anonymised employer group, same treatment as Vancouver/North Vancouver Seaspan entities); Babcock Canada Inc. is confirmed predominantly defense-focused, holding the Victoria-Class submarine In-Service Support Contract for the Royal Canadian Navy as a named 'Team Victoria-Class' partner alongside Seaspan - a clear-cut defense exclusion, not an ambiguous case. Intercon Marine Inc., an independent BC-owned rigging/heavy-lift company at the Esquimalt Graving Dock, is a genuine judgment call - its client list mixes commercial work (cruise ships, cargo ships, BC Ferries) with Canadian Navy and Coast Guard work with no separate divisions - routed to Review rather than decided either way, consistent with the Mussell Crane/Cimtex Industries precedent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="8" t="inlineStr">
+        <is>
+          <t>Why Colwood was thin</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="9" t="inlineStr">
+        <is>
+          <t>Colwood is predominantly residential/suburban Greater Victoria; the one structural engineering firm confirmed to be Colwood-based (Scott Engineering Inc.) had no website, service description, or marine/industrial evidence found - routed to Review pending a direct call rather than assumed either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="9" t="inlineStr">
+        <is>
+          <t>Salish Sea Industrial Services Ltd. - a genuinely interesting Indigenous-owned (Songhees and Esquimalt Nations) marine construction joint venture with the Ralmax Group, operating a 145-ft barge and 150-tonne crawler crane for dredging, pile driving and derelict-vessel removal - was researched during this batch but is actually based at Point Hope Maritime on Victoria's Upper Harbour, not Esquimalt specifically, and Point Hope Maritime itself was already covered in batch 2 (Victoria, BC). Not added here to avoid misattribution or near-duplication of an already-covered Ralmax-family entity.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -2938,10 +2938,14 @@
           <t>https://frpd.com/management-team/</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@frpd.com</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>https://frpd.com/management-team/ ; https://www.pilingcanada.ca/breaking-the-mould/</t>
+          <t>https://frpd.com/management-team/ ; https://www.pilingcanada.ca/breaking-the-mould/ | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -2964,7 +2968,7 @@
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>Sarah Clark has been President &amp; CEO since August 2017 per a Piling Canada profile and the company's own management-team page - reasonably well corroborated, but re-confirm given the pending ownership change may affect reporting lines or the point of contact.</t>
+          <t>Sarah Clark has been President &amp; CEO since August 2017 per a Piling Canada profile and the company's own management-team page - reasonably well corroborated, but re-confirm given the pending ownership change may affect reporting lines or the point of contact. | Title discrepancy found for Sarah Clark: one new source lists her role as 'Chief Operating Officer' rather than the previously recorded 'President &amp; CEO'. Not overwritten since the original title came from a reasonably credible source too; verify directly before outreach.</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3061,7 @@
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -4315,7 +4319,7 @@
       </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website (management team listing)</t>
+          <t>Company website (management team listing) | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -4583,10 +4587,14 @@
           <t>https://theportalcranegroup.com/about-us</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@portalcrane.com</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>ZoomInfo (contact listing corroborated by company website's stated Engineering function)</t>
+          <t>ZoomInfo (contact listing corroborated by company website's stated Engineering function) | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -4965,7 +4973,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn public profile / ZoomInfo (corroborated)</t>
+          <t>LinkedIn public profile / ZoomInfo (corroborated) | No usable public email found; a source claimed an email-naming pattern ('first.last@pct.ca') but this was not used, per this project's no-guessing/no-pattern-inference policy - only Curtis Rutherford's name/title are recorded.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -5062,10 +5070,14 @@
           <t>https://www.ratiostructural.com/about-us</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@ratiostructural.com</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -5507,7 +5519,7 @@
       </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website / business directory listings</t>
+          <t>Company website / business directory listings | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -5616,10 +5628,14 @@
           <t>https://rkmcrane.com/about-us/</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>sales@rkmcrane.com</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Web search snippet (ZoomInfo-corroborated)</t>
+          <t>Web search snippet (ZoomInfo-corroborated) | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -5882,7 +5898,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | No publicly available email found in this pass (only phone/address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -6312,7 +6328,7 @@
       </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website / Chilliwack Chamber of Commerce directory</t>
+          <t>Company website / Chilliwack Chamber of Commerce directory | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -6583,7 +6599,7 @@
       </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>https://ral.ca/contact/ ; https://ral.ca/career-opportunities/</t>
+          <t>https://ral.ca/contact/ ; https://ral.ca/career-opportunities/ | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -6696,10 +6712,14 @@
           <t>https://vardmarine.com/about/team/</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@vardmarineinc.com</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Public LinkedIn profile title (search snippet); https://vardmarine.com/about/team/</t>
+          <t>Public LinkedIn profile title (search snippet); https://vardmarine.com/about/team/ | General company inbox (not verified as an individual's address); found via company contact listings.</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -6722,7 +6742,7 @@
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Ron Ogoniek's title was read from a public LinkedIn search snippet only (profile itself was not opened - no browser access in this session). Re-confirm current title immediately before outreach.</t>
+          <t>Ron Ogoniek's title was read from a public LinkedIn search snippet only (profile itself was not opened - no browser access in this session). Re-confirm current title immediately before outreach. | Title/location discrepancy found for Ron Ogoniek: some sources list his role as 'Manager, Projects &amp; Programs' / 'Head of Projects and Programs', based in Ottawa, ON, rather than the previously recorded 'Engineering Manager'. Not overwritten since the original title came from a reasonably credible source too; verify directly before outreach.</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6823,7 @@
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.hatch.com/ (Vancouver postings)</t>
+          <t>https://jobs.hatch.com/ (Vancouver postings) | No publicly available email found in this pass (only phone/fax for the Vancouver office).</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
@@ -6907,7 +6927,7 @@
       <c r="R5" s="5" t="inlineStr"/>
       <c r="S5" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | No publicly available email found in this pass for the Vancouver/Western Canada office specifically.</t>
         </is>
       </c>
       <c r="T5" s="5" t="inlineStr">
@@ -7015,7 +7035,7 @@
       </c>
       <c r="S6" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T6" s="5" t="inlineStr">
@@ -7887,7 +7907,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Web search snippet (single source - not independently corroborated)</t>
+          <t>Web search snippet (single source - not independently corroborated) | No usable public email found; a source claimed an email-naming pattern but this was not used, per this project's no-guessing/no-pattern-inference policy.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -7984,10 +8004,14 @@
           <t>https://carsonscustom.com/</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>carsonscustommfg@gmail.com</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -8413,7 +8437,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | No publicly available email found in this pass (only phone/address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -8688,7 +8712,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Industry profile (Passagemaker magazine) corroborated by company website</t>
+          <t>Industry profile (Passagemaker magazine) corroborated by company website | The company website appears to display an email, but search results returned it only as an anti-scraping placeholder that did not resolve to a real address; not recorded per this project's no-guessing policy. Only phone/address confirmed.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -8793,10 +8817,14 @@
           <t>https://www.dolphinmarine.ca/</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>dolphinmarine@telus.net</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -8896,7 +8924,7 @@
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | No publicly available email found for the BC (Gibsons) entity in this pass; an email surfaced in search results but was for a different, unrelated Tideline Boats company in North Carolina and was not used.</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
@@ -9163,7 +9191,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Business directory listings (Canpages, Powell River Community Directory)</t>
+          <t>Business directory listings (Canpages, Powell River Community Directory) | No publicly available email found in this pass (only phone/address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -9427,10 +9455,14 @@
           <t>https://www.heroldengineering.com/careers/</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>mail@heroldengineering.com</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website / job postings</t>
+          <t>Company website / job postings | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -9535,10 +9567,14 @@
           <t>https://npa.ca/</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>JMichell@npa.ca</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Web search snippet (single source)</t>
+          <t>Web search snippet (single source) | Publicly listed direct email for a named individual, Jason Michell (VP, Business Development).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -9561,7 +9597,7 @@
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>John Darbyshire's title (stevedoring/operations, not engineering) suggests he may not be the right technical contact for structural/FEA work specifically - useful as an entry point, but confirm whether the Port Authority has a distinct engineering/infrastructure lead before a technical pitch.</t>
+          <t>John Darbyshire's title (stevedoring/operations, not engineering) suggests he may not be the right technical contact for structural/FEA work specifically - useful as an entry point, but confirm whether the Port Authority has a distinct engineering/infrastructure lead before a technical pitch. | Note: this is a different named contact than previously recorded (John Darbyshire, Manager, Vancouver Island Stevedoring &amp; Duke Point Operations). Both appear to be legitimate Port Authority contacts; recommend verifying which is the better entry point for Duke Point terminal outreach specifically. The Port Authority's general inbox (per@npa.ca) is a fallback if neither individual responds.</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9686,7 @@
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>Public LinkedIn profile (search snippet)</t>
+          <t>Public LinkedIn profile (search snippet) | A search result returned an email/contact name ('Ted Sorensen') that did not match this company's name and appears to belong to a different, unrelated business at a similar address; not used. No verified email found for Westshore Structural Engineering Ltd. itself.</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
@@ -9925,7 +9961,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Web search snippet (ZoomInfo/company site corroborated for Macon Industries Inc. specifically)</t>
+          <t>Web search snippet (ZoomInfo/company site corroborated for Macon Industries Inc. specifically) | Search results returned only an anti-scraping placeholder in place of the email, which did not resolve to a real address; not recorded per this project's no-guessing policy. Only phone/address confirmed.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -10200,7 +10236,7 @@
       </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>https://www.yellowpages.ca/bus/British-Columbia/North-Vancouver/Allied-Shipbuilders-Ltd/2085098.html</t>
+          <t>https://www.yellowpages.ca/bus/British-Columbia/North-Vancouver/Allied-Shipbuilders-Ltd/2085098.html | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -10309,10 +10345,14 @@
           <t>https://www.capilanomaritime.com/team/</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>cmulder@capilanomaritime.com</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>https://www.capilanomaritime.com/team/ ; https://www.capilanomaritime.com/about/</t>
+          <t>https://www.capilanomaritime.com/team/ ; https://www.capilanomaritime.com/about/ | Sourced from a business directory listing, not independently verified on the company's own website; treat as medium-high confidence, not confirmed.</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -10409,10 +10449,14 @@
           <t>https://jfcsteel.ca/about-us/</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>jfcsteeloffice@gmail.com</t>
+        </is>
+      </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | General company inbox (not verified as an individual's address); found via public listings.</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
@@ -10675,7 +10719,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website / directory listings</t>
+          <t>Company website / directory listings | No publicly available email found in this pass (only phone/address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -10938,7 +10982,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | No publicly available email found in this pass (only phone/address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -11035,10 +11079,14 @@
           <t>https://www.coastlinefabricators.ca/</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>coastlinefabricators@shaw.ca</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Company website / directory listing (Yellow Pages)</t>
+          <t>Company website / directory listing (Yellow Pages) | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -11476,7 +11524,7 @@
       </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website / business directory (RocketReach corroborated)</t>
+          <t>Company website / business directory (RocketReach corroborated) | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -11696,7 +11744,7 @@
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>Company website / industry press (Business Examiner)</t>
+          <t>Company website / industry press (Business Examiner) | No publicly available email found in this pass (only phone/address).</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
@@ -11804,7 +11852,7 @@
       <c r="R5" s="5" t="inlineStr"/>
       <c r="S5" s="5" t="inlineStr">
         <is>
-          <t>ZoomInfo (contact listing)</t>
+          <t>ZoomInfo (contact listing) | No publicly available email found in this pass (only phone/address); the company website has a contact page but its email could not be confirmed without direct page access.</t>
         </is>
       </c>
       <c r="T5" s="5" t="inlineStr">
@@ -12075,7 +12123,7 @@
       </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company websites (cmewestcoast.com, alberni-cae.com) / directory listings</t>
+          <t>Company websites (cmewestcoast.com, alberni-cae.com) / directory listings | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -12346,7 +12394,7 @@
       </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website / business directory listings</t>
+          <t>Company website / business directory listings | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -12447,10 +12495,14 @@
           <t>https://wcfltd.ca/contact-us/</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@wcfltd.ca</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -12713,7 +12765,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | No publicly available email found in this pass (only phone/fax); a Chamber of Commerce listing references an email contact option but does not display the address itself.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -12981,10 +13033,14 @@
           <t>https://liquidmetalmarine.com/about-us/</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>admin@liquidmetalmarine.com</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Industry profile (Professional BoatBuilder / IBEX Technical Journal) corroborated by company website</t>
+          <t>Industry profile (Professional BoatBuilder / IBEX Technical Journal) corroborated by company website | General company inbox (not verified as an individual's address); Kristi Benwell's personal email is listed only in masked form on directory sites (e.g. 'k***@liquidmetalmarine.com') and was not used, per this project's no-guessing policy.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -16193,10 +16249,14 @@
           <t>https://pointhopemaritime.com/</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@pointhopemaritime.com</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Web search snippet citing Riccardo Regosa as General Manager since 2016 (ZoomInfo-corroborated); not independently opened</t>
+          <t>Web search snippet citing Riccardo Regosa as General Manager since 2016 (ZoomInfo-corroborated); not independently opened | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -16297,10 +16357,14 @@
           <t>https://3gamarine.com/staff/</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@3gamarine.com</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>https://3gamarine.com/staff/</t>
+          <t>https://3gamarine.com/staff/ | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -16572,10 +16636,14 @@
           <t>https://ebco.com/</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@ebco.com</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Web search snippet (Wikipedia-corroborated); not independently opened</t>
+          <t>Web search snippet (Wikipedia-corroborated); not independently opened | General company inbox (not verified as an individual's address); Richard Eppich's personal email remains masked/unconfirmed on directory sites and was not used.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -16679,7 +16747,7 @@
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Company website / Yellow Pages listing</t>
+          <t>Company website / Yellow Pages listing | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -16943,10 +17011,14 @@
           <t>https://ca.linkedin.com/company/kiewit</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@Kiewit.com</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Kiewit careers site / LinkedIn job postings</t>
+          <t>Kiewit careers site / LinkedIn job postings | General corporate inbox (not verified as an individual's address, and not Burnaby-office-specific).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -17047,10 +17119,14 @@
           <t>https://ca.linkedin.com/company/ausenco</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>denise.mullen@ausenco.com</t>
+        </is>
+      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Job posting aggregators (LinkedIn, Indeed, SimplyHired, engineeringcareers.ca)</t>
+          <t>Job posting aggregators (LinkedIn, Indeed, SimplyHired, engineeringcareers.ca) | Found associated with Ausenco's Vancouver-area office listing; role/title and whether this is the correct contact for the Burnaby office specifically are unconfirmed. Treat as low-medium confidence.</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -17322,10 +17398,14 @@
           <t>https://www.globalrigging.com/about-grt</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>a.johnson@globalrigging.com</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website / business directory listings (CWB Group, BBB)</t>
+          <t>Company website / business directory listings (CWB Group, BBB) | Sourced from a third-party (Port Strategy) supplier directory listing with a cell number, not independently verified on the company's own website; treat as medium confidence.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -17348,7 +17428,7 @@
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>Andrew Johnson's title was drawn from web search snippets, not a directly opened source - confirm current role before outreach. Thomas Felch (VP/Director) and Erin Johnson (Business Development Manager) are alternative named contacts worth considering.</t>
+          <t>Andrew Johnson's title was drawn from web search snippets, not a directly opened source - confirm current role before outreach. Thomas Felch (VP/Director) and Erin Johnson (Business Development Manager) are alternative named contacts worth considering. | Title discrepancy found for Andrew Johnson: one new source lists his role as 'Operations Manager' rather than the previously recorded 'President / Director'. Not overwritten since the original title came from a reasonably credible source too; verify directly before outreach.</t>
         </is>
       </c>
     </row>
@@ -17437,7 +17517,7 @@
       <c r="R3" s="5" t="inlineStr"/>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Web search snippet corroborated by company org context (Craft.co executives listing)</t>
+          <t>Web search snippet corroborated by company org context (Craft.co executives listing) | No usable public email found; the site displays a JavaScript-obfuscated address that did not resolve to plaintext, so it was not recorded per this project's no-guessing policy.</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -17697,10 +17777,14 @@
           <t>https://bluewatersystems.ca/about-us/</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@bluewatersystems.ca</t>
+        </is>
+      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company website | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -17808,7 +17892,7 @@
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Company website / directory listings</t>
+          <t>Company website / directory listings | General company inbox (not verified as an individual's address).</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -44,6 +44,8 @@
     <sheet name="Langford, BC" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="Colwood, BC" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="Esquimalt, BC" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Prince George, BC" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="Terrace, BC" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -85,6 +87,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'Langford, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'Colwood, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'Esquimalt, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'Prince George, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'Terrace, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13405,7 +13409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A342"/>
+  <dimension ref="A1:A359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -15676,6 +15680,118 @@
       <c r="A342" s="9" t="inlineStr">
         <is>
           <t>Salish Sea Industrial Services Ltd. - a genuinely interesting Indigenous-owned (Songhees and Esquimalt Nations) marine construction joint venture with the Ralmax Group, operating a 145-ft barge and 150-tonne crawler crane for dredging, pile driving and derelict-vessel removal - was researched during this batch but is actually based at Point Hope Maritime on Victoria's Upper Harbour, not Esquimalt specifically, and Point Hope Maritime itself was already covered in batch 2 (Victoria, BC). Not added here to avoid misattribution or near-duplication of an already-covered Ralmax-family entity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="7" t="inlineStr">
+        <is>
+          <t>Batch 20: Prince George, BC &amp; Terrace, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="9" t="inlineStr">
+        <is>
+          <t>1. Fraser Custom Equipment Ltd. (Prince George) - Score 7, Priority B - explicitly designs/fabricates lifting devices and structural steel for mining/industrial clients, the closest scope match to AH Structures found in this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="9" t="inlineStr">
+        <is>
+          <t>2. Western Pacific Metalworks Ltd. (Terrace) - Score 6, Priority C - its own service description states it works with outside engineers/designers for certification and signed approvals on custom fabrication, a direct evidence-based overflow-engineering pathway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="9" t="inlineStr">
+        <is>
+          <t>3. Farr Fabricating (1985) Ltd. (Prince George) - Score 7, Priority B - established heavy-industrial fabricator serving pulp &amp; paper, mining, chemical and hydroelectric clients across BC/AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="9" t="inlineStr">
+        <is>
+          <t>4. Sterling Crane, Prince George Branch - Score 6, Priority C - national heavy-lift company whose own marketing highlights project analysis, pre-planning and heavy-lift feasibility studies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="9" t="inlineStr">
+        <is>
+          <t>Northern BC heavy-industrial fabrication tied to forestry/mining/pulp &amp; paper plant work, plus a first look at inland heavy-lift/rigging companies (Sterling Crane) as a distinct overflow-engineering category alongside the coastal marine cluster covered in earlier batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="9" t="inlineStr">
+        <is>
+          <t>For Fraser Custom Equipment and Western Pacific Metalworks, lead with structural/FEA support for lifting-device design and fabrication certification specifically - both companies have direct, stated evidence of exactly this kind of need, rather than a generic industrial-fabrication pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="9" t="inlineStr">
+        <is>
+          <t>Fraser Custom Equipment (lifting-device design/fabrication) and Sterling Crane (heavy-lift project analysis, pre-planning and feasibility studies) are the two clearest overflow-engineering signals found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Fraser Custom Equipment and Farr Fabricating (Prince George), then Western Pacific Metalworks (Terrace). Struo Consulting, Terrace Steel Works, TW Industrial Group, Sterling Crane, and Johnny's Welding as secondary follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="9" t="inlineStr">
+        <is>
+          <t>Two building-focused structural engineering firms (Access Engineering Consultants and Scouten Engineering, both Prince George) were found but not added: their described scope is residential/commercial/industrial building design, with no marine or heavy-industrial-plant evidence, consistent with this project's recurring exclusion of building-code-only structural engineers. Central Interior Piping &amp; Maintenance Ltd. (Prince George) was found but excluded as a mechanical/piping contractor serving pulpmills, chemical plants, refineries and mining - a different discipline than AH Structures' structural/FEA scope, and its refinery client base sits close to this project's oil &amp; gas exclusion. Several named-contact conflicts were flagged rather than silently resolved: Sterling Crane's Prince George branch manager is listed as both Colin Cote (LinkedIn) and Jeff Walter (an older-looking directory listing); Farr Fabricating's ownership is described inconsistently across sources (John Pateman as an owner/partner vs. Ray Fortier as Manager); and two contacts (Fraser Custom Equipment's 'Mark' and Struo Consulting's 'Tomas') were recorded by email address only, with no confirmed surname or title. This is the first batch outside the Lower Mainland/Vancouver Island coastal cluster; Prince George and Terrace's industrial base (forestry, mining, and - for Terrace - proximity to Kitimat's LNG and aluminum-smelting industry) produced a genuine but thinner set of prospects than the coastal batches, reflecting real sectoral differences rather than a research gap.</t>
         </is>
       </c>
     </row>
@@ -16010,6 +16126,1192 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Prince George, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>TW Industrial Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.twindustrial.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication / Industrial Construction</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CSA W47.1-certified structural steel fabrication, installation, welding and millwrighting for industrial and commercial clients</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Growing northern BC industrial fabricator that began in the forest industry and has diversified into mining and renewable-energy-sector structural steel work - the kind of multi-sector heavy-industrial fabricator that periodically needs outside structural/FEA capacity for larger or more complex jobs.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from a diversified, growing industrial fabrication client base spanning several sectors.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company materials describe structural steelwork for mining, renewable energy, and other industrial clients across BC.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Kelly Sheptak</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.twindustrial.ca/about/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No public email found for Kelly Sheptak or a general company inbox in this pass; only phone confirmed (250-564-6857/250-649-1252).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.twindustrial.ca/about/ ; https://www.bpcmag.com/case-studies/kelly-sheptak-tw-industrial-group/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Position AH Structures as overflow structural/FEA capacity for a growing regional fabricator whose client base spans multiple industrial sectors.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Note: company materials mention serving mining, oil and gas, and renewable-energy clients among others - oil &amp; gas is one of several sectors served, not this company's core/primary market, so it is not treated as an oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Prince George, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Farr Fabricating (1985) Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.farrfabricating.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication / Heavy Industrial</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel, storage tanks, stainless steel fabrication, custom fabrication and field construction</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established heavy-industrial fabricator serving pulp &amp; paper, mining, chemical and hydroelectric clients across BC and Alberta - a strong-fit client base for structural/FEA overflow work given the scale and complexity of that plant-side fabrication.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the scale and technical complexity of its named client sectors (pulp &amp; paper, mining, hydroelectric).</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company site and directory listings describe structural steel, storage tank and field construction work for pulp &amp; paper, mining, chemical and hydroelectric clients in BC and Alberta.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Ray Fortier</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.farrfabricating.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>farrfab@telus.net</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.farrfabricating.ca/ ; https://www.yellowpages.ca/bus/British-Columbia/Prince-George/Farr-Fabricating-1985-Ltd/2264137.html</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA capacity pitch tailored to large-scale plant fabrication (storage tanks, structural steel) for pulp &amp; paper, mining and hydroelectric clients.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>One source names John Pateman as an owner/partner (also linked to unrelated insurance and construction businesses) with Ray Fortier as Manager; Ray Fortier was used as the primary contact since his role is directly operational, but this should be confirmed before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Prince George, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Fraser Custom Equipment Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://frasercustomequipment.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication / Lifting Devices</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Custom metal fabrication, welding, structural steel and lifting-device design/fabrication for mining and industrial clients</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>One of the more precise fits found in this batch: explicitly designs and fabricates lifting devices (not just general fabrication) for mining and industrial clients in northern BC - directly adjacent to AH Structures' structural/lifting-equipment scope.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Company markets itself specifically around lifting devices and structural steel for heavy industrial/mining clients - a natural overflow-FEA fit for load-rated lifting equipment design and verification.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (frasercustomequipment.com/projects/) describes industrial and commercial engineering services including structural steel and lifting devices for the mining and industrial sectors.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://frasercustomequipment.com/about/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>mark@frasercustomequipment.com</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Email address associated with a contact identified only as 'Mark' in search results; full name and title were not confirmed in this pass, so no Decision Maker Name/Title is recorded.</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://frasercustomequipment.com/projects/ ; https://frasercustomequipment.com/contact/</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA pitch specifically for lifting-device design and load verification work, the closest match to AH Structures' own scope found in Prince George.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>Confirm the name and title of 'Mark' (the contact behind mark@frasercustomequipment.com) before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Prince George, BC</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Struo Consulting Inc.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>https://struo.ca/</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Structural Engineering Consulting</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Structural design and engineering, steel connection design, BIM; works with fabrication shops across Canada</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>A structural engineering consultancy (not a fabricator) that specifically offers steel connection design and works directly with fabrication shops - a genuine, if partial, overlap with AH Structures' structural/FEA scope, though its own marketing also describes residential and commercial building work.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Steel connection design work performed in partnership with fabrication shops is the kind of scope that could plausibly be shared or overflowed with an outside structural engineering partner on larger or more complex jobs.</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Company website and directory listings describe steel connection design and structural engineering services provided to fabrication shops across Canada.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>https://struo.ca/about/</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>tomas@struo.ca</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>Email address associated with a contact identified only by first name ('Tomas') in a client testimonial; full name and title were not confirmed in this pass, so no Decision Maker Name/Title is recorded.</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>https://struo.ca/ ; https://www.princegeorgecitizen.com/directory/engineering/struo-consulting-inc-107470</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>If pursued, frame outreach narrowly around steel connection design/verification work, since the firm's broader marketing leans toward residential and commercial building engineering rather than heavy industrial or marine work.</t>
+        </is>
+      </c>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>Mixed signal on fit: one source describes the firm as focused on 'Heavy Timber Construction, Structural Design and Engineering... BIM' with steel-connection-design work for fabrication shops (a good fit), while another describes it more generally as residential &amp; commercial engineering (a weaker fit). Confirm the actual balance of work before treating as a strong prospect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Prince George, BC</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Sterling Crane (Prince George Branch)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sterlingcrane.com/prince-george-branch/</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/colin-cote-2b8b04152</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Branch of national company</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Lift / Crane Services</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Mobile crane rental, rigging, and heavy-lift project analysis, pre-planning and feasibility studies</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>National heavy-lift and crane services company with a permanent Prince George branch; its own marketing highlights project analysis, pre-planning and transportation/heavy-lift feasibility studies - the same overflow-heavy-lift-engineering category as other rigging/crane companies already recorded in this project (e.g. RKM Crane Services, Global Rigging &amp; Transport).</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Company markets 'comprehensive project analysis, pre-planning as well as feasibility studies for transportation and heavy lift studies' - work that plausibly requires outside structural/engineering support on complex lifts.</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sterlingcrane.com/company-profile/ describes heavy-lift feasibility and pre-planning services company-wide.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Colin Cote</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>Branch Manager, Prince George</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/colin-cote-2b8b04152</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sterlingcrane.com/prince-george-branch/</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>No public email found for Colin Cote or a Prince George branch inbox in this pass; a stated email-naming-pattern claim ('FLast@sterlingcrane.com') was found but not used, per this project's no-guessing/no-pattern-inference policy. Only branch phone confirmed (250-561-1501).</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sterlingcrane.com/prince-george-branch/ ; https://ca.linkedin.com/in/colin-cote-2b8b04152</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a potential engineering-support partner for heavy-lift planning and feasibility studies, rather than as a direct fabrication/structural client.</t>
+        </is>
+      </c>
+      <c r="X6" s="5" t="inlineStr">
+        <is>
+          <t>A second, apparently older business-directory listing names a different individual, Jeff Walter, as 'Branch Manager' for this same Prince George branch. Colin Cote (sourced from a current LinkedIn profile) was used as the more likely current contact, but this should be verified before outreach.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Terrace, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Terrace Steel Works Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://terracesteelworks.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Steel Fabrication / Heavy Equipment Repair</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Fabrication, welding, machining, structural steel repairs, heavy equipment repair, mobile welding</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1979) Northwest BC industrial fabricator serving Terrace, Kitimat and Prince Rupert - a region with major heavy industry (LNG Canada, Rio Tinto's Kitimat aluminum smelter) nearby, giving it a plausible heavy-industrial client base for structural/FEA overflow work.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the scale of nearby heavy industry (LNG, aluminum smelting) the company is positioned to serve.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website describes structural steel repairs, fabrication and heavy equipment repair serving Terrace, Kitimat and the Northwest BC region.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Vic Dean</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://terracesteelworks.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@terracesteel.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://terracesteelworks.com/ ; https://www.macraesbluebook.com/search/company.cfm?company=16548</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to the region's major heavy-industrial facilities (LNG, aluminum smelting) rather than Terrace itself.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>A separate source lists Juliana Angelo as 'Manager, Business' with a masked email (j***@terracesteel.com); this was not used, per this project's no-guessing policy on masked addresses. Vic Dean is recorded as the primary named contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Terrace, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Western Pacific Metalworks Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>http://www.wpm-bc.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Custom Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Custom metal fabrication and equipment modifications, with connections to engineers/designers for certification and signed approvals</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Locally owned Northwest BC fabricator (since 1981) that explicitly notes it works with outside engineers/designers for certification and signed approvals on custom fabrication and equipment modifications - a direct, evidence-based overflow-engineering fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Company's own service description states it 'utilizes connections with engineers and designers for certification and signed approvals where necessary' - a specific, named overflow-engineering pathway rather than an inferred one.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>http://www.wpm-bc.com/structural.html and http://www.wpm-bc.com/services.html describe custom fabrication work requiring outside engineering certification.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>http://www.wpm-bc.com/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; the company website displays only an anti-scraping placeholder in place of the email, which did not resolve to a real address, so it was not recorded per this project's no-guessing policy. Only phone/mobile confirmed (250-635-9523 / 250-638-7137).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>http://www.wpm-bc.com/contact.html</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly as an outside structural/certification engineering partner - the company's own materials describe exactly this kind of need.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No named owner/president was found in this pass; company is described only as 'locally owned' since 1981.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Terrace, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Johnny's Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.johnnyswelding.ca/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Fabrication / Heavy Equipment Repair</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; fabrication, hydraulic cylinder manufacturing and repair, steel &amp; aluminum sales, heavy equipment repairs, mobile welding</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1961) Northwest BC welding/fabrication and heavy equipment repair company; hydraulic cylinder manufacturing and heavy equipment repair work suggests some mechanical/structural design-adjacent capability, though no direct structural-engineering-overflow evidence was found.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; the company appears to be a fabrication/repair shop rather than one commissioning outside structural/FEA engineering work.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website and directory listings describe welding, fabrication, hydraulic cylinder work and heavy equipment repair since 1961.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.johnnyswelding.ca/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>kelly@johnnyswelding.ca</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Email address associated with a contact identified only by first name ('Kelly') in search results; full name and title were not confirmed in this pass, so no Decision Maker Name/Title is recorded.</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.johnnyswelding.ca/contact-us ; https://www.zoominfo.com/p/Johnny-Patterson/8809802741</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm whether any structural design or engineering-adjacent work exists beyond fabrication and repair before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>A search result also names a 'Johnny Patterson' as a welder at the company (masked email); not used as the primary contact since role and relevance to outreach are unclear.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -46,6 +46,8 @@
     <sheet name="Esquimalt, BC" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="Prince George, BC" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="Terrace, BC" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="Kitimat, BC" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="Prince Rupert, BC" sheetId="45" state="visible" r:id="rId45"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -89,6 +91,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'Esquimalt, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'Prince George, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'Terrace, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'Kitimat, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'Prince Rupert, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3104,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4068,6 +4072,48 @@
       <c r="H23" s="10" t="inlineStr">
         <is>
           <t>https://www.interconmarine.com/ ; https://www.zoominfo.com/p/Colin-Spivey/-1322812477</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Kitimat, BC</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>KTSG (Kitamaat Technical Services Group) / ServcoCanada</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>https://ktsgcorp.com/</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>A First Nation joint venture (Novus, Well Services Group, and the Kitimat-based ServcoCanada) providing EPC, commissioning, and O&amp;M services, actively bidding on LNG Canada pre-commissioning/commissioning/O&amp;M contracts. ServcoCanada's own structural/mechanical/piping services could be relevant, but the joint venture's core business is described specifically as energy/LNG-sector project services - close to this project's oil &amp; gas exclusion even though LNG is natural gas rather than oil - and it operates at a large EPC/O&amp;M contractor scale rather than as a smaller structural-engineering client.</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Clarify what proportion of ServcoCanada/KTSG's actual day-to-day work is LNG-sector-core (which would trigger this project's oil &amp; gas-adjacent exclusion) versus general industrial structural/mechanical services, and whether a company of this scale would plausibly outsource structural/FEA work rather than handling it in-house or through its EPC partners.</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>https://ktsgcorp.com/about-us/ ; https://ktsgcorp.com/projects/ ; https://lngjournal.com/index.php/latest-news-mainmenu-47/item/107089-energy-services-companies-in-british-columbia-to-target-lng-work-in-partnership-with-haisla-first-nation</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A359"/>
+  <dimension ref="A1:A375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -15792,6 +15838,111 @@
       <c r="A359" s="9" t="inlineStr">
         <is>
           <t>Two building-focused structural engineering firms (Access Engineering Consultants and Scouten Engineering, both Prince George) were found but not added: their described scope is residential/commercial/industrial building design, with no marine or heavy-industrial-plant evidence, consistent with this project's recurring exclusion of building-code-only structural engineers. Central Interior Piping &amp; Maintenance Ltd. (Prince George) was found but excluded as a mechanical/piping contractor serving pulpmills, chemical plants, refineries and mining - a different discipline than AH Structures' structural/FEA scope, and its refinery client base sits close to this project's oil &amp; gas exclusion. Several named-contact conflicts were flagged rather than silently resolved: Sterling Crane's Prince George branch manager is listed as both Colin Cote (LinkedIn) and Jeff Walter (an older-looking directory listing); Farr Fabricating's ownership is described inconsistently across sources (John Pateman as an owner/partner vs. Ray Fortier as Manager); and two contacts (Fraser Custom Equipment's 'Mark' and Struo Consulting's 'Tomas') were recorded by email address only, with no confirmed surname or title. This is the first batch outside the Lower Mainland/Vancouver Island coastal cluster; Prince George and Terrace's industrial base (forestry, mining, and - for Terrace - proximity to Kitimat's LNG and aluminum-smelting industry) produced a genuine but thinner set of prospects than the coastal batches, reflecting real sectoral differences rather than a research gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="7" t="inlineStr">
+        <is>
+          <t>Batch 21: Kitimat, BC &amp; Prince Rupert, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="9" t="inlineStr">
+        <is>
+          <t>1. Broadwater Industries (2011) Ltd. (Prince Rupert) - Score 7, Priority B - marine construction/fabrication company with directly marine-relevant scope (structural steel assemblies, breakwater and dock repair, boat/marina construction).</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="9" t="inlineStr">
+        <is>
+          <t>2. ZanRon Fabrication &amp; Machine Co. Ltd. (Kitimat) - Score 6, Priority C - established, ISO 9001-certified independent industrial fabricator positioned near Kitimat's major industrial anchors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="9" t="inlineStr">
+        <is>
+          <t>3. Harbour Machining and Progressive Steel Industries (both Prince Rupert) - Score 5, Priority C - established general industrial fabrication/machining shops with less specific marine-structural evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="9" t="inlineStr">
+        <is>
+          <t>Prince Rupert's port-industrial marine fabrication/repair cluster (Broadwater Industries, Harbour Machining, McLean's Shipyard) is a stronger fit for AH Structures than Kitimat's smelter/LNG-adjacent industrial base, where the largest players (LNG Canada's EPC joint venture, KTSG/ServcoCanada) are either too large-scale or sit close to this project's oil &amp; gas/LNG exclusion boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="9" t="inlineStr">
+        <is>
+          <t>For Broadwater Industries, lead with a structural/FEA pitch tied specifically to marine structural work (breakwaters, docks, structural steel assemblies) - the clearest scope overlap found in this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch; Broadwater Industries' marine structural repair/construction scope is the closest plausible fit, assessed as a Medium (not High) overflow opportunity given the absence of a specific named project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Broadwater Industries (Prince Rupert). ZanRon Fabrication (Kitimat) as a secondary follow-up. Harbour Machining, Progressive Steel Industries and McLean's Shipyard as lower-priority follow-ups pending further confirmation of marine/structural scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="9" t="inlineStr">
+        <is>
+          <t>Kitimat's LNG Canada project and its major EPC/O&amp;M contractors (the JGC Fluor BC LNG Joint Venture, Bridgemans/PMC, and the Kitamaat Technical Services Group/ServcoCanada joint venture) were reviewed but not added as direct prospects: the EPC joint venture operates at a scale where AH Structures-style outside structural/FEA support is unlikely to be sought directly, and KTSG/ServcoCanada's core business is LNG-sector project services - close enough to this project's oil &amp; gas exclusion boundary, even though LNG is natural gas rather than oil, that it was routed to the Low Confidence - Review sheet rather than the main Kitimat sheet. Prince Rupert Port Authority's terminal operators (Trigon Pacific Terminals, AltaGas's Ridley Island Propane Export Terminal) were also reviewed but not added: no named contact or specific structural/engineering-need signal was found for either in this pass, unlike the comparable Nanaimo Port Authority case in batch 13 where a named operations contact surfaced directly.</t>
         </is>
       </c>
     </row>
@@ -17312,6 +17463,844 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Kitimat, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>ZanRon Fabrication &amp; Machine Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://zanron.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/zanronmechanicalservices</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural/Mechanical Fabrication &amp; Machining</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>ISO 9001-certified fabrication and machining for commercial and industrial applications; full machine shop, fabrication shop, and paint/sandblasting facilities</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1985), independently owned Kitimat industrial fabricator positioned to serve the region's major industrial base (Rio Tinto aluminum smelter, LNG Canada) - a plausible source of structural/FEA overflow work given its scale (50-100 employees) and ISO 9001 certification.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the company's scale, ISO 9001 certification, and positioning to serve Kitimat's major industrial anchor tenants.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (zanron.com/about) describes fabrication and machining services for commercial and industrial applications from its Kitimat Industrial Center facility.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Ed Rooney</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://zanron.com/about/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>zanron@zanron.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://zanron.com/ ; https://www.dnb.com/business-directory/company-profiles.zanron_fabrication__machine_co_ltd.298120e70f4c14fe84a4e982e866237a.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to Kitimat's major industrial base (aluminum smelting, LNG); confirm current ownership/leadership before outreach given the company was founded 40 years ago.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Ed Rooney is recorded as the company's founder (1985); current ownership/leadership was not independently reconfirmed in this pass.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Prince Rupert, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Broadwater Industries (2011) Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.broadwaterindustries.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine Construction &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom steel/stainless/aluminum fabrication, structural steel assemblies, pressure welding, piping and repairs; builds new boats and marinas, repairs breakwaters and docks</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Independent marine construction and fabrication company with a 12,000 sq ft shop and directly marine-relevant scope (structural steel assemblies, breakwater and dock repair, boat/marina construction) - one of the stronger marine-adjacent structural fits found outside the Lower Mainland/Vancouver Island cluster.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the range and complexity of structural marine fabrication and repair work described (breakwaters, docks, structural steel assemblies).</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (broadwaterindustries.ca/shop-fabrication--installations) describes structural steel assemblies, pressure welding, and marine construction including breakwater/dock repair.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.broadwaterindustries.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>bw@bwindustries.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.broadwaterindustries.ca/ ; https://www.yellowpages.ca/bus/British-Columbia/Prince-Rupert/Broadwater-Industries-2011-Ltd/2139968.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA pitch specifically tied to marine structural work - breakwaters, docks, and structural steel assemblies - the closest overlap with AH Structures' scope found in Prince Rupert.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No named owner/principal was found in this pass; company is registered as '(2011) Ltd.', suggesting a reorganization or ownership change around 2011 that was not independently confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Prince Rupert, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Harbour Machining</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://harbourmachining.net/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Machining, Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Full-service machining, welding and fabrication facility at the Prince Rupert Industrial Site, operating since 1979</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Long-established industrial machining/fabrication shop serving Prince Rupert's port-industrial base - a general industrial fit, though with less specific marine or structural-overflow evidence than Broadwater Industries.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website and directory listings describe machining, welding and fabrication services since 1979 at the Prince Rupert Industrial Site.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://harbourmachining.net/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; company has a contact page (harbourmachining.net/contact-us) but the address was not displayed in search results. Only phone confirmed (250-624-3253).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://harbourmachining.net/contact-us</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm what proportion of work is marine/structural versus general machining before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Prince Rupert, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Progressive Steel Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://progressivesteel.net/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Steel Fabrication &amp; Welding</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Welding and fabrication in an 8,000 sq ft shop with 37-foot ceilings, operating since 2004</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Established, well-equipped Prince Rupert steel fabricator with the shop scale (high ceilings, 3 acres of property) to handle larger structural components - a general heavy-industrial fit for the Prince Rupert Industrial Park.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (progressivesteel.net) and directory listings describe welding and fabrication capacity at the Prince Rupert Industrial Park.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://progressivesteel.net/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; company has a contact page (progressivesteel.net/contact-us) but the address was not displayed in search results. Only phone confirmed (250-627-4733).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://progressivesteel.net/contact-us/</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm what proportion of work is marine/structural versus general fabrication before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Prince Rupert, BC</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>McLean's Shipyard (McLean's West Coast Launch Shipyard)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mcleansshipyard.com/</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Ship Repair</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Ship/boat repair on a marine railway at Seal Cove, next to the Canadian Coast Guard base; primarily fish boats and yachts</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Family-run Prince Rupert shipyard tradition dating to 1909 - a genuine marine-repair business, though its described scope (fish boats and yachts on a marine railway) is smaller-scale/recreational-and-fishing-fleet-focused rather than the larger commercial/structural work AH Structures typically targets.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nauticapedia.ca/Gallery/McLean_Shipyard.php and https://www.mcleansshipyard.com/history.html describe the shipyard's history and current fish-boat/yacht repair focus.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mcleansshipyard.com/</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (250-624-3142).</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mcleansshipyard.com/ ; https://northcoastreview.blogspot.com/2020/01/mcleans-shipyard-charts-next-century.html</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up given its smaller-scale, fishing-fleet/recreational repair focus; confirm any larger commercial vessel work before a tailored structural/FEA pitch.</t>
+        </is>
+      </c>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>Ownership was recently transferred (per a 2020 local news article) to the Davis family of Prince Rupert, who also own Adventure Tours and Westcoast Launch; no individual owner name was confirmed for direct outreach.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -48,6 +48,8 @@
     <sheet name="Terrace, BC" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="Kitimat, BC" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="Prince Rupert, BC" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="Smithers, BC" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="Quesnel, BC" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -93,6 +95,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'Terrace, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'Kitimat, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'Prince Rupert, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'Smithers, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'Quesnel, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3108,7 +3112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4114,6 +4118,48 @@
       <c r="H24" s="10" t="inlineStr">
         <is>
           <t>https://ktsgcorp.com/about-us/ ; https://ktsgcorp.com/projects/ ; https://lngjournal.com/index.php/latest-news-mainmenu-47/item/107089-energy-services-companies-in-british-columbia-to-target-lng-work-in-partnership-with-haisla-first-nation</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Smithers, BC</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Black Fox Enterprises</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>https://blackfoxent.ca/</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Custom fabrication and maintenance services (welding, millwrighting) ranging from small maintenance jobs to large-scale industrial projects, marketed as serving Smithers and Northern BC - but a separate directory source lists the company's location as Houston, BC, a distinct nearby town not on this project's current city list. Location could not be confirmed either way in this pass.</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Confirm the company's actual base location (Smithers vs. Houston, BC) before adding to either city's sheet or treating it as a Smithers-specific prospect.</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>https://blackfoxent.ca/ ; https://www.britishcolumbialocal.ca/biz/24903/black-fox-enterprises</t>
         </is>
       </c>
     </row>
@@ -13455,7 +13501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A375"/>
+  <dimension ref="A1:A391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -15943,6 +15989,111 @@
       <c r="A375" s="9" t="inlineStr">
         <is>
           <t>Kitimat's LNG Canada project and its major EPC/O&amp;M contractors (the JGC Fluor BC LNG Joint Venture, Bridgemans/PMC, and the Kitamaat Technical Services Group/ServcoCanada joint venture) were reviewed but not added as direct prospects: the EPC joint venture operates at a scale where AH Structures-style outside structural/FEA support is unlikely to be sought directly, and KTSG/ServcoCanada's core business is LNG-sector project services - close enough to this project's oil &amp; gas exclusion boundary, even though LNG is natural gas rather than oil, that it was routed to the Low Confidence - Review sheet rather than the main Kitimat sheet. Prince Rupert Port Authority's terminal operators (Trigon Pacific Terminals, AltaGas's Ridley Island Propane Export Terminal) were also reviewed but not added: no named contact or specific structural/engineering-need signal was found for either in this pass, unlike the comparable Nanaimo Port Authority case in batch 13 where a named operations contact surfaced directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="7" t="inlineStr">
+        <is>
+          <t>Batch 22: Smithers, BC &amp; Quesnel, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="9" t="inlineStr">
+        <is>
+          <t>1. Royalite Industrial Maintenance Ltd. (Quesnel) - Score 7, Priority B - CWB-certified specifically for structural steel, lifting devices, cranes and monorails to CSA standards; a precise, evidence-based fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="9" t="inlineStr">
+        <is>
+          <t>2. Parallel Welding Fabrication Ltd. (Quesnel) - Score 7, Priority B - well-equipped heavy-industrial fabricator (shops in Quesnel and Chilliwack) offering structural steel builds and complete mill construction for mines/mills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="9" t="inlineStr">
+        <is>
+          <t>3. Quesnel Iron and Northern Metals Fabricating &amp; Machining (Smithers) - Score 4, Priority C - established general machine shops/fabricators with no marine or structural-overflow-specific evidence found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="9" t="inlineStr">
+        <is>
+          <t>Quesnel's mining/forestry-focused heavy fabrication cluster produced two of this project's clearer CSA/CWB-certified structural and lifting-equipment fits (Royalite Industrial Maintenance, Parallel Welding Fabrication). Smithers, by contrast, was thin - its welding/fabrication shops appear oriented toward general repair and residential/commercial work rather than heavy industrial or marine-adjacent structural engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="9" t="inlineStr">
+        <is>
+          <t>For Royalite Industrial Maintenance, lead directly with structural/FEA support for lifting-device, crane and monorail design/verification work - the company's own CWB/CSA certification describes exactly this scope, the same angle that worked well for Fraser Custom Equipment in batch 20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="9" t="inlineStr">
+        <is>
+          <t>Royalite Industrial Maintenance's CSA-standard lifting-device/crane/monorail certification is the clearest, most specific overflow-engineering signal found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Royalite Industrial Maintenance and Parallel Welding Fabrication (Quesnel). Quesnel Iron and Northern Metals Fabricating &amp; Machining (Smithers) as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="9" t="inlineStr">
+        <is>
+          <t>Black Fox Enterprises, initially found under a Smithers search, was routed to Review rather than added to the Smithers sheet: one directory source lists its actual location as Houston, BC, a distinct nearby town not currently on this project's city list, continuing this project's discipline around exact city attribution (the same issue previously flagged for J.R. Elkington in batch 17 and several Saanich Peninsula companies in batches 17-18). Jeremy Dumais Welding &amp; Fabrication (Quesnel) was found but not added given its apparent small, single-operator scale and no evidence of structural-engineering-scale work.</t>
         </is>
       </c>
     </row>
@@ -18301,6 +18452,732 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Smithers, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Northern Metals Fabricating &amp; Machining Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Machining</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified welding and machining, repair and fabrication for the Bulkley Valley/Northwest BC region</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established, independently owned industrial welding/machining shop serving Smithers and the surrounding Bulkley Valley - a modest general industrial fit; no marine or heavy structural-engineering-specific evidence was found, so treated as a lower-confidence prospect.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (Yellow Pages, Canpages) describe CWB-certified welding, machining, repair and fabrication services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Mark McKay</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone/fax confirmed (250-847-3428 / 250-847-5645).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.ca/bus/British-Columbia/Smithers/Northern-Metals-Fabricating-Machining-Ltd/1144274.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm scope of work (structural vs. general repair/machining) before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Quesnel, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Parallel Welding Fabrication Ltd. (Parallel)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.paralleldiv.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Industrial Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Heavy fabrication, custom design-builds, structural steel builds, rotating/static machinery, precision CNC machining, complete mill construction, for plants, mines and mills</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Well-equipped heavy-industrial fabricator with shops in both Quesnel and Chilliwack, explicitly offering structural steel builds and complete mill construction for the mining/forestry sector - a strong heavy-industrial structural fit, similar in scale and scope to companies already recorded in earlier batches (e.g. Farr Fabricating, TW Industrial Group).</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the range of heavy fabrication and structural steel work described for mines and mills across BC/Alberta-adjacent markets.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (paralleldiv.com) describes heavy fabrication, structural steel builds and complete mill construction for plants, mines and mills.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Tracy Mero</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President &amp; Principal &amp; Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.paralleldiv.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a directory source displayed only a masked address (t***@parallelwelding.com), which was not used per this project's no-guessing policy on masked addresses. Only phone confirmed (250-992-9433).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.paralleldiv.com/ ; https://www.zoominfo.com/p/Tracy-Mero/2515463785</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to mill construction and heavy fabrication for mining/forestry clients.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Quesnel, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Royalite Industrial Maintenance Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.royaliteindustrial.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Equipment &amp; Structural Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Heavy duty equipment welding, commercial transport repair, and steel fabrication; CWB-certified to fabricate and install structural steel, lifting devices, cranes and monorails to CSA standards</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>One of the more precise fits found in this batch: explicitly CWB-certified for structural steel, lifting devices, cranes and monorails to CSA standards - directly adjacent to AH Structures' structural/lifting-equipment scope, similar to Fraser Custom Equipment (Prince George, batch 20) and Royalite Industrial Maintenance's CSA-standard certification is a specific, verifiable signal rather than a general fabrication claim.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>CWB certification specifically for lifting devices, cranes and monorails to CSA standards is a direct, named overflow-engineering pathway (load-rated equipment design/verification) rather than an inferred one.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (royaliteindustrial.com/about-us) describes CWB certification for structural steel, lifting devices, cranes and monorails to CSA standards.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Jeff</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Owner (surname not confirmed)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.royaliteindustrial.com/about-us</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>jeff@royaliteindustrial.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Publicly listed email for a named individual ('Jeff'), described in search results as the owner; full surname was not confirmed in this pass.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.royaliteindustrial.com/ ; https://www.whodoyou.com/biz/1594717/royalite-industrial-maintenance-ltd-quesnel-bc</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly with a structural/FEA pitch for lifting-device, crane and monorail design/verification work - the company's own CWB/CSA certification describes exactly this scope.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Confirm 'Jeff's' full surname and exact title before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Quesnel, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Quesnel Iron</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Machine Shop / General Fabrication</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Full-service machine shop serving logging, mining, sawmill and construction industries; general and high-pressure welding of aluminum and stainless steel</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Established general industrial machine shop serving Quesnel's forestry/mining client base - a plausible but less specific fit than Parallel Welding Fabrication or Royalite Industrial Maintenance, with no named structural-engineering-overflow evidence found.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (Yelp, Fyple) describe machine-shop services for logging, mining, sawmill and construction clients.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (250-992-5151).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.yelp.ca/biz/quesnel-iron-quesnel ; https://www.fyple.ca/company/quesnel-iron-3fddv07/</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm any structural/design-engineering-adjacent work exists beyond general machining.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -50,6 +50,8 @@
     <sheet name="Prince Rupert, BC" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="Smithers, BC" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="Quesnel, BC" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="Williams Lake, BC" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="Fort St. John, BC" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -97,6 +99,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'Prince Rupert, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'Smithers, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'Quesnel, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'Williams Lake, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'Fort St. John, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3112,7 +3116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4160,6 +4164,48 @@
       <c r="H25" s="10" t="inlineStr">
         <is>
           <t>https://blackfoxent.ca/ ; https://www.britishcolumbialocal.ca/biz/24903/black-fox-enterprises</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Fort St. John, BC</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Precision North Machining Inc.</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>https://precisionnorthmachining.ca/</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>60+ year Fort St. John fabrication/machining/welding/field-repair company operating a 40,000 sq ft shop - a genuinely large, well-established regional fabricator, but its own marketing explicitly names 'gas compressor overhauls' among its core field services and describes serving 'oil and gas, forestry and mining sectors,' with oil &amp; gas listed first and most specifically. This sits close to this project's oil &amp; gas core-market exclusion.</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Confirm what proportion of Precision North Machining's actual revenue/work is oil &amp; gas-specific (e.g. gas compressor overhauls) versus forestry/mining/general fabrication before deciding whether this is a hard exclusion or a genuine multi-sector fit.</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>https://precisionnorthmachining.ca/ ; https://precisionnorthmachining.ca/field-services/field-welding</t>
         </is>
       </c>
     </row>
@@ -13501,7 +13547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A391"/>
+  <dimension ref="A1:A407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -16094,6 +16140,111 @@
       <c r="A391" s="9" t="inlineStr">
         <is>
           <t>Black Fox Enterprises, initially found under a Smithers search, was routed to Review rather than added to the Smithers sheet: one directory source lists its actual location as Houston, BC, a distinct nearby town not currently on this project's city list, continuing this project's discipline around exact city attribution (the same issue previously flagged for J.R. Elkington in batch 17 and several Saanich Peninsula companies in batches 17-18). Jeremy Dumais Welding &amp; Fabrication (Quesnel) was found but not added given its apparent small, single-operator scale and no evidence of structural-engineering-scale work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="7" t="inlineStr">
+        <is>
+          <t>Batch 23: Williams Lake, BC &amp; Fort St. John, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="9" t="inlineStr">
+        <is>
+          <t>1. Cariboo Steel &amp; Machine Ltd. (Williams Lake) - Score 6, Priority C - well-established, CWB-certified fabricator/machine shop serving forestry and mining clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="9" t="inlineStr">
+        <is>
+          <t>2. Priority Steel Erectors Ltd. (Fort St. John) - Score 6, Priority C - Indigenous-owned structural steel erector with a genuinely diversified, multi-sector client base rather than an oil &amp; gas-only business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="9" t="inlineStr">
+        <is>
+          <t>3. Mueller Enterprises Ltd. and Monster Industries Ltd. (Williams Lake), Fusion Fabricating &amp; Custom Design (Fort St. John) - Score 5, Priority C - established regional industrial contractors with a plausible but less specific fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="9" t="inlineStr">
+        <is>
+          <t>Williams Lake's forestry/mining fabrication cluster was a cleaner, more straightforward fit than Fort St. John, where the region's oil &amp; gas-dominated economy meant most candidate fabricators either named oil &amp; gas as a primary/core service line (and were excluded or routed to Review) or required careful confirmation of how diversified their actual client base really is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="9" t="inlineStr">
+        <is>
+          <t>For Fort St. John prospects specifically, any outreach should explicitly frame AH Structures' interest around the company's non-oil-and-gas sectors (mining, hydroelectric, forestry, aviation) given how central oil &amp; gas is to the regional economy - a generic industrial pitch risks being read as (or actually becoming) oil &amp; gas-adjacent work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Cariboo Steel &amp; Machine (Williams Lake) and Priority Steel Erectors (Fort St. John). Mueller Enterprises, Monster Industries, and Fusion Fabricating as secondary follow-ups, each pending confirmation of sector fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="9" t="inlineStr">
+        <is>
+          <t>Fab All North Services Inc. (Fort St. John) was found but excluded outright rather than routed to Review: its own marketing explicitly states it serves 'drilling rigs and the oil and gas industry' with 24-hour mobile welding trucks for that purpose - a clear-cut oil &amp; gas core-market case, not a borderline one. Precision North Machining Inc. (Fort St. John), a large 60+ year regional fabricator, was routed to Review instead: its marketing names 'gas compressor overhauls' among its core field services and lists oil &amp; gas first among its served sectors, which sits close to but is not as unambiguous as the Fab All North case. Monster Industries Ltd. was confirmed to be headquartered in Houston, BC with a genuine, separately-addressed Williams Lake division (named local contact Dan Herzog) - unlike the Black Fox Enterprises location ambiguity flagged in batch 22, this is a confirmed branch relationship, so it was recorded under Williams Lake rather than routed to Review. Priority Steel Erectors Ltd.'s corporate office was found to be in Chilliwack, BC (already covered in batch 8), but it maintains a genuine Fort St. John operating location, so it was recorded there rather than treated as a duplicate.</t>
         </is>
       </c>
     </row>
@@ -19178,6 +19329,848 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Williams Lake, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Cariboo Steel &amp; Machine Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://cariboosteel.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Steel Fabrication &amp; Machining</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Metal fabrication, machining, hydraulic cylinder repair and welding from a 16,000 sq ft shop; CWB-certified with Red Seal-certified staff</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Well-established (leading Cariboo-region) fabricator and machine shop serving forestry, mining and other industrial contractors - a solid general heavy-industrial fit, similar in scale to Farr Fabricating and Parallel Welding Fabrication in earlier batches.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the shop's scale and CWB/Red Seal certification serving forestry and mining clients.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (cariboosteel.com) and a 2020 local business profile (Williams Lake Tribune) describe fabrication, machining and hydraulic repair services for forestry, mining and industrial-contractor clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Jason Rowley</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner and Machine Shop Foreman</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://cariboosteel.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>admin@cariboosteel.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://cariboosteel.com/ ; https://www.wltribune.com/business/spotlight-on-business-2020-cariboo-steel-and-machine-ltd-5526359</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to forestry and mining plant fabrication work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Williams Lake, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Mueller Enterprises Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.muellerenterprises.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Industrial Electrical &amp; Millwrighting</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Industrial electrical, millwrighting and welding services, plus forestry-specific solutions (power systems and equipment support for mills and off-grid forestry operations), serving Williams Lake and remote sites across Western Canada and Yukon</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established (45+ years) industrial services company with a mining and forestry client base - a plausible but more electrical/millwright-oriented fit than a pure structural/FEA one; included as a secondary prospect.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; the company's core scope (electrical, millwrighting) is adjacent to rather than squarely within AH Structures' structural/FEA focus.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (muellerenterprises.ca) describes industrial electrical, millwrighting, welding and forestry equipment-support services across BC and Yukon.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.muellerenterprises.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>karen@muellerenterprises.ca</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Email associated with a contact identified only by first name ('Karen'); full name, title and whether this is the appropriate decision-maker contact were not confirmed in this pass.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.muellerenterprises.ca/contact/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm whether any structural/design engineering work (versus electrical/millwrighting) is relevant before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Williams Lake, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Monster Industries Ltd. (Williams Lake Division)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.monsterindustries.ca/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Branch of regional company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Industrial Construction &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Bonded general contractor, CWB certified, providing welding and fabrication services to mines, process facilities, pulpmills, sawmills and energy plants</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Established regional heavy-industrial contractor with a dedicated Williams Lake division and a named local contact - a general industrial fit, though its 'energy plants' client category was not specific enough to rule out some oil &amp; gas-adjacent exposure.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (monsterindustries.ca) and directory listings describe welding/fabrication services to mines, process facilities, pulpmills, sawmills and energy plants.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Dan Herzog</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Principal Contact, Williams Lake Division</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.monsterindustries.ca/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone/fax confirmed (250-845-3240 / 250-845-3245).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.profilecanada.com/companydetail.cfm?company=2152825_Monster_Industries_Ltd_Houston_BC ; https://www.resourceconnector.ca/monster-industries-ltd-williams-lake</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm the proportion of 'energy plants' work that is oil &amp; gas-related before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>Company headquarters is in Houston, BC (PO Box 1446), with Williams Lake operated as a division with its own local contact (Dan Herzog) and address; recorded under Williams Lake since that is where its named local contact and operations are based.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Fort St. John, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Priority Steel Erectors Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.prioritysteelerectors.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/priority-steel-erectors-ltd</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Installation / Pre-Engineered Buildings</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel installations, pre-engineered steel buildings, heavy hauling, crane services, welding and custom fabrication across BC and Western Canada</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Indigenous-owned structural steel erector with a genuine Fort St. John operating presence, serving a diversified client base (mining, commercial, hydroelectric, aviation, and oil &amp; gas among others) rather than an oil &amp; gas-only business.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the range of structural steel and heavy-hauling/crane work described across multiple sectors.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (prioritysteelerectors.com) and directory listings describe structural steel installation, pre-engineered buildings, heavy hauling and crane services for mining, commercial, hydroelectric, oil &amp; gas and aviation clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.prioritysteelerectors.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Company has a contact page but the address was not displayed in search results.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.prioritysteelerectors.com/ ; https://www.thebluebook.com/iProView/1828031/0/0/locations-contacts/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its non-oil-and-gas sectors specifically (mining, hydroelectric, aviation) given the company's diversified, multi-sector client base.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Company's corporate office is in Chilliwack, BC (already covered in this project, batch 8's area); recorded under Fort St. John since that is where it maintains an operating location. Oil &amp; gas is named as one of several served sectors, not the company's sole/core market, so it is not treated as a hard oil &amp; gas exclusion case - but this should be reconfirmed directly given how oil &amp; gas-dominated the Fort St. John region's economy is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Fort St. John, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Fusion Fabricating &amp; Custom Design Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://fusionfabricating.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Custom metal fabrication, precision welding and waterjet cutting; repair and modification services for agricultural, commercial and industrial clients</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Locally described client base (agricultural, commercial, industrial) does not explicitly name oil &amp; gas as a core market, unlike several other Fort St. John fabricators found in this pass - the closest thing to a non-oilfield-core structural/fabrication fit identified in this city.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (fusionfabricating.ca) describes custom fabrication, precision welding and waterjet cutting for agricultural, commercial and industrial clients.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://fusionfabricating.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; several similarly-named 'Fusion Fabricating'/'Fusion Industries' companies exist in other cities and were not confused with this Fort St. John entity. Only the company website's contact form was found.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://fusionfabricating.ca/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm directly what proportion of client work is oil &amp; gas-related, given the regional economy, before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -52,6 +52,8 @@
     <sheet name="Quesnel, BC" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="Williams Lake, BC" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="Fort St. John, BC" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="Dawson Creek, BC" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="Fort Nelson, BC" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -101,6 +103,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'Quesnel, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'Williams Lake, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'Fort St. John, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'Dawson Creek, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'Fort Nelson, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3116,7 +3120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4206,6 +4210,48 @@
       <c r="H26" s="10" t="inlineStr">
         <is>
           <t>https://precisionnorthmachining.ca/ ; https://precisionnorthmachining.ca/field-services/field-welding</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Dawson Creek, BC</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>NorTech Welding &amp; Fabricating Inc.</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>https://www.nortechweldandfab.ca/</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Long-established (since 1989), ISO 9001:2008-certified fabrication and welding company serving the Peace Region - but its own marketing describes serving 'the oil, forestry, and agricultural sectors' (oil named first) and the company is listed on oilfieldpages.ca, a directory specifically for oilfield service providers, suggesting oil &amp; gas may be a core rather than incidental market.</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Confirm what proportion of NorTech's actual work is oil &amp; gas-specific versus forestry/agricultural before deciding whether this is a hard oil &amp; gas exclusion case or a genuine multi-sector fit.</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>https://www.nortechweldandfab.ca/ ; https://oilfieldpages.ca/company/nortech-welding-fabricating-inc-dawson-creek-bc/</t>
         </is>
       </c>
     </row>
@@ -13547,7 +13593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A407"/>
+  <dimension ref="A1:A422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -16245,6 +16291,104 @@
       <c r="A407" s="9" t="inlineStr">
         <is>
           <t>Fab All North Services Inc. (Fort St. John) was found but excluded outright rather than routed to Review: its own marketing explicitly states it serves 'drilling rigs and the oil and gas industry' with 24-hour mobile welding trucks for that purpose - a clear-cut oil &amp; gas core-market case, not a borderline one. Precision North Machining Inc. (Fort St. John), a large 60+ year regional fabricator, was routed to Review instead: its marketing names 'gas compressor overhauls' among its core field services and lists oil &amp; gas first among its served sectors, which sits close to but is not as unambiguous as the Fab All North case. Monster Industries Ltd. was confirmed to be headquartered in Houston, BC with a genuine, separately-addressed Williams Lake division (named local contact Dan Herzog) - unlike the Black Fox Enterprises location ambiguity flagged in batch 22, this is a confirmed branch relationship, so it was recorded under Williams Lake rather than routed to Review. Priority Steel Erectors Ltd.'s corporate office was found to be in Chilliwack, BC (already covered in batch 8), but it maintains a genuine Fort St. John operating location, so it was recorded there rather than treated as a duplicate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="7" t="inlineStr">
+        <is>
+          <t>Batch 24: Dawson Creek, BC &amp; Fort Nelson, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="9" t="inlineStr">
+        <is>
+          <t>1. Dushay Welding Ltd. (Fort Nelson) - Score 4, Priority C - the only credible independent fabricator found in either city this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="9" t="inlineStr">
+        <is>
+          <t>Dawson Creek's main sheet is empty this pass - a genuine effect of the Peace Region's oil &amp; gas-saturated fabrication sector, not a research gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="8" t="inlineStr">
+        <is>
+          <t>Why Dawson Creek was thin</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="9" t="inlineStr">
+        <is>
+          <t>Every Dawson Creek fabricator identified either named oil &amp; gas as a core or first-listed market (NorTech Welding &amp; Fabricating, routed to Review; Precision Welding Ltd., excluded outright given its explicit 'CSG bowls/rig repairs, oil &amp; gas welding and fabrication, pipe fabrication' service list), was in the wrong location entirely (Iron Creek Industries is actually based in Armstrong, BC, not Dawson Creek - discarded, not a genuine city-boundary judgment call), or offered a service mix too far from AH Structures' structural/heavy-industrial scope (Red Weld Fabrication's described work is custom cabinets, truck/trailer repair and signworks).</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="9" t="inlineStr">
+        <is>
+          <t>Not applicable this batch - no qualifying segment emerged cleanly from either city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="9" t="inlineStr">
+        <is>
+          <t>Dushay Welding (Fort Nelson) as a lower-priority follow-up only, pending confirmation of its actual client-sector mix given the region's economy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="9" t="inlineStr">
+        <is>
+          <t>This batch continues the pattern flagged in batch 23: Peace Region cities (Fort St. John, Dawson Creek, and to a lesser extent Fort Nelson) sit inside BC's most oil &amp; gas-concentrated economic zone, and most fabrication/welding companies found there either state oil &amp; gas as a core or leading market (a hard exclusion or Review case) or are simply too small/thin on evidence to include with confidence. Macdonald Welding and Nahanni Ventures (Fort Nelson) were found but not added - only a phone number could be confirmed for either, with no service description, sector information, or named contact, consistent with this project's practice of not padding city sheets with bare directory listings.</t>
         </is>
       </c>
     </row>
@@ -20558,6 +20702,420 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Fort Nelson, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Dushay Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Fabrication &amp; Machining</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified welding and machine shop (6,800 sq ft) offering CNC machining, fabrication, lathe work, turning, mobile and TIG welding; steel and aluminum products</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (18 years), locally owned general industrial welding/fabrication and machine shop - the most credible independent fabricator found in Fort Nelson, though no marine or structural-engineering-overflow-specific evidence was found and its client sector mix (given the region's oil &amp; gas-dominated economy) was not confirmed.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Fort Nelson &amp; District Chamber of Commerce listing and directory listings describe an 18-year, CWB-certified welding and machine shop with CNC machining and fabrication capabilities.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone/address confirmed (250-774-4410, 5327 48th Ave).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fortnelsonchamber.com/list/member/dushay-welding-ltd-149 ; https://www.yellowpages.ca/bus/British-Columbia/Fort-Nelson/Dushay-Welding-Ltd/2827656.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm directly what proportion of client work is oil &amp; gas-related, given the regional economy, before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -54,6 +54,8 @@
     <sheet name="Fort St. John, BC" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="Dawson Creek, BC" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="Fort Nelson, BC" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="Kelowna, BC" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="Kamloops, BC" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -105,6 +107,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'Fort St. John, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'Dawson Creek, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'Fort Nelson, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'Kelowna, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'Kamloops, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13593,7 +13597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A422"/>
+  <dimension ref="A1:A439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -16389,6 +16393,118 @@
       <c r="A422" s="9" t="inlineStr">
         <is>
           <t>This batch continues the pattern flagged in batch 23: Peace Region cities (Fort St. John, Dawson Creek, and to a lesser extent Fort Nelson) sit inside BC's most oil &amp; gas-concentrated economic zone, and most fabrication/welding companies found there either state oil &amp; gas as a core or leading market (a hard exclusion or Review case) or are simply too small/thin on evidence to include with confidence. Macdonald Welding and Nahanni Ventures (Fort Nelson) were found but not added - only a phone number could be confirmed for either, with no service description, sector information, or named contact, consistent with this project's practice of not padding city sheets with bare directory listings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="7" t="inlineStr">
+        <is>
+          <t>Batch 25: Kelowna, BC &amp; Kamloops, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="9" t="inlineStr">
+        <is>
+          <t>1. Grizzly Metal Fab Inc. (Kelowna) - Score 7, Priority B - marina/dock structural fabrication plus in-house Tekla/Solidworks/Inventor modelling capability, the strongest fit found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="9" t="inlineStr">
+        <is>
+          <t>2. Mansini Steel Manufacturing Ltd. (Kamloops) - Score 7, Priority B - large-scale (24,000 sq ft), multi-decade heavy-industrial fabricator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="9" t="inlineStr">
+        <is>
+          <t>3. Warnaar Steel-Tech Ltd. (Kelowna) and International Steel Fabrication Inc. (Kamloops) - Score 6, Priority B - established, well-equipped regional structural steel fabricators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="9" t="inlineStr">
+        <is>
+          <t>4. Innovex Engineering Corp. (Kamloops) - Score 6, Priority B - a genuine peer structural/mechanical engineering consultancy, framed as a potential overflow-capacity partner rather than a typical fabrication client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="9" t="inlineStr">
+        <is>
+          <t>This was the richest interior-BC batch so far: both Kelowna and Kamloops have substantial, multi-decade heavy-industrial fabrication sectors (mining, forestry, sawmill/pulp) with several CWB-certified, large-scale shops, a marked contrast to the thinner Peace Region batches (23-24).</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="9" t="inlineStr">
+        <is>
+          <t>For Grizzly Metal Fab, lead specifically with the marina/dock structural work - the clearest marine-adjacent angle found in interior BC so far. For Innovex Engineering, approach peer-to-peer around overflow/subcontract structural engineering capacity rather than a standard client pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="9" t="inlineStr">
+        <is>
+          <t>Grizzly Metal Fab's in-house 3D modelling/detailing capability (Tekla, Solidworks, Inventor) and Okanagan Crane &amp; Rigging's heavy-lift capacity (up to 240 tons) are the two most specific overflow-adjacent signals found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Grizzly Metal Fab (Kelowna) and Mansini Steel Manufacturing (Kamloops). Warnaar Steel-Tech, International Steel Fabrication, and Innovex Engineering as close secondary follow-ups. Okanagan Crane &amp; Rigging and Acumen Machine as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="9" t="inlineStr">
+        <is>
+          <t>Both International Steel Fabrication and Innovex Engineering name oil &amp; gas as one of several served sectors alongside forestry/mining/construction; consistent with this project's established treatment of multi-sector fabricators (TW Industrial Group, batch 20; Priority Steel Erectors, batch 23), this was not treated as a hard exclusion, but outreach framing for both companies should lean on their non-oil-and-gas work given how the sector mix reads. No location-mismatch or defense-exclusion issues were found in this batch.</t>
         </is>
       </c>
     </row>
@@ -21116,6 +21232,1080 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Kelowna, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Grizzly Metal Fab Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://grizzlymetalfab.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified structural steel fabrication for sawmill equipment, marina/dock structures, and custom industrial fabrication; in-house 3D modelling and detailing using Tekla, Solidworks, Autodesk Inventor and AutoCAD</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>One of the stronger fits found in this batch: marina/dock structural fabrication is directly marine-adjacent, and in-house use of Tekla/Solidworks/Inventor for modelling and detailing suggests a design-capable fabricator that could plausibly use outside structural/FEA support on larger or more complex jobs.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>In-house 3D modelling/detailing capability (Tekla, Solidworks, Inventor) suggests the company already engages in some design work in-house, which could extend to overflow structural/FEA collaboration on larger marina/dock or sawmill-equipment projects.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (grizzlymetalfab.ca) describes structural steel, sawmill equipment, and marina/dock fabrication with named 3D modelling software capability.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Jim Bostock</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://grizzlymetalfab.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a directory source references an email for Jim Bostock but displays it only in masked/redacted form, which was not used per this project's no-guessing policy. Only phone confirmed (250-766-1566).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://grizzlymetalfab.ca/ ; https://rocketreach.co/jim-bostock-email_71781896</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lead with the marina/dock structural fabrication angle specifically, given its direct marine relevance, alongside sawmill-equipment structural work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Company materials also mention serving oil &amp; gas among several other sectors (structural steel, sawmill equipment, marina/dock); oil &amp; gas is one of several markets served, not the company's core business, so it is not treated as an oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Kelowna, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Warnaar Steel-Tech Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.warnaarsteel.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Industrial structural steel fabrication solutions including mining equipment structures</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established Kelowna industrial steel fabricator with a mining-equipment-structures focus - a solid general heavy-industrial structural fit, similar in scale to other regional fabricators recorded in this project.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the scale and structural focus of its mining-equipment work.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (warnaarsteel.com/company) describes structural steel fabrication solutions for mining equipment and other industrial applications.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.warnaarsteel.com/company/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@warnaarsteel.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); a BBB listing names Shannon Nelson as Controller, but this appears to be a finance rather than technical/decision-making role, so was not used as the primary contact.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.warnaarsteel.com/ ; https://www.bbb.org/ca/bc/kelowna/profile/metal-fabrication/warnaar-steel-tech-ltd-0037-1219006</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to mining-equipment structural fabrication.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Kelowna, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Okanagan Crane &amp; Rigging Services</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.okanagancraneandrigging.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Lift / Crane &amp; Rigging</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Heavy lifts up to 240 tons, pile driving, sheet piling, material hoisting platforms, dragline work, slope stabilization, demolition and recovery services</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Established (35+ years) local heavy-lift and rigging company with genuine heavy-capacity equipment (up to 240 tons) and specialized services (pile driving, sheet piling) - a plausible overflow-heavy-lift-engineering fit, similar to Sterling Crane (batch 20) and RKM Crane Services (earlier batches).</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the heavy-lift capacity and specialized pile-driving/sheet-piling services described.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (okanagancraneandrigging.com/products-and-services) describes heavy lifts up to 240 tons and pile driving/sheet piling services.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.okanagancraneandrigging.com/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; company has a contact page but the address was not displayed in search results. Only phone confirmed (250-212-9459).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.okanagancraneandrigging.com/contact-us</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a potential engineering-support partner for heavy-lift and pile-driving/sheet-piling project planning.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Kamloops, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Mansini Steel Manufacturing Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mansinisteel.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Steel Fabrication &amp; Machining</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>24,000 sq ft CWB-certified full-service fabrication, machine and material processing facility, established 1970</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1970), large-scale (24,000 sq ft) heavy-industrial fabricator serving mining, forestry, construction, railway and pulp industries - a strong general fit given its scale and multi-decade track record.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the facility's scale and multi-sector industrial client base.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (mansinisteel.com) describes a 24,000 sq ft CWB-certified fabrication facility serving mining, forestry, construction, railway and pulp industries.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Frank Potestio</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mansinisteel.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@mansinisteel.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); a second manager, Randy Dennison, is also listed and may be an equally valid contact.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mansinisteel.com/ ; https://www.ctidirectory.com/search/company.cfm?company=54914</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to mining and forestry plant fabrication work, given the facility's scale and multi-decade track record.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Kamloops, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>International Steel Fabrication Inc. (ISF)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.isfab.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/international-steel-fabrication-inc</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>23,000 sq ft CWB-certified steel fabrication facility on 5.5 acres, specializing in forestry, oil and gas, mining and construction industries</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Well-equipped, large-scale regional structural steel fabricator with a diversified (not purely oil &amp; gas) client base - a solid general heavy-industrial fit similar to Mansini Steel Manufacturing.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the facility's scale and multi-sector industrial client base.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (isfab.ca) describes a 23,000 sq ft CWB-certified fabrication facility serving forestry, oil &amp; gas, mining and construction clients.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Mitch Philpott</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.isfab.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@isfab.ca</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); Mitch Philpott's personal email is listed only in masked form on directory sites and was not used.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.isfab.ca/contact ; https://www.zoominfo.com/p/Mitch-Philpott/3188102382</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch framed around its forestry and mining work specifically, given oil &amp; gas is also a named client sector for this company.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Oil &amp; gas is named as one of four served sectors (forestry, oil &amp; gas, mining, construction), not the company's sole/core market, so it is not treated as a hard oil &amp; gas exclusion case, but outreach framing should lean on the non-oil-and-gas sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Kamloops, BC</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Acumen Machine Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.acumenmachine.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Machine Shop / Equipment Repair &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified 10,000 sq ft machine shop; welding, parts manufacturing, repairs and equipment maintenance for forestry, mining, pulp mill, transportation and agriculture, serving mills and mine sites across BC, Alberta and Saskatchewan</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Established (since 1992), diversified regional machine shop and equipment-repair company with a genuinely broad multi-provincial mining/forestry/pulp-mill client base - a solid general industrial fit.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; the company's core scope (equipment repair/parts manufacturing) is somewhat adjacent to rather than squarely within AH Structures' structural/FEA focus.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (acumenmachine.com/forestry-mining--drilling) describes equipment repair, parts manufacturing and maintenance services for mills and mine sites across BC, Alberta and Saskatchewan.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Len Woodd &amp; Wes Vath</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Co-Owners</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.acumenmachine.com/about-us</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (1-800-352-9993).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.acumenmachine.com/about-us ; https://www.acumenmachine.com/forestry-mining--drilling/</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm whether any structural design/FEA-adjacent work exists beyond equipment repair and parts manufacturing.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Kamloops, BC</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Innovex Engineering Corp.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>https://innovexeng.com/</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/casey-dundass-83b34714/</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Structural &amp; Mechanical Engineering Consulting</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Precision engineering and mechanical services, with structural design experience spanning mining, oil and gas, forestry and other heavy industry</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>A genuine structural/mechanical engineering consultancy (not a fabricator) with an explicitly heavy-industrial client base - the most direct professional-overlap fit found in this batch, though as a fellow engineering firm it is better approached as a potential overflow-capacity or subcontract-engineering partner than a typical fabrication client, similar to the framing used for Hatch and Ausenco in earlier batches.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>As a smaller structural/mechanical engineering consultancy itself, Innovex could plausibly need to subcontract overflow design capacity during busy periods, or vice versa - a partnership-style opportunity rather than a typical client relationship.</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Company website (innovexeng.com/area-of-expertise/structural-engineering) describes structural design experience across mining, oil &amp; gas, forestry and other heavy industry.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Casey Dundass</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Founder / Principal</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/casey-dundass-83b34714/</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>https://innovexeng.com/about</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (250-372-7676).</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>https://innovexeng.com/ ; https://www.linkedin.com/in/casey-dundass-83b34714/</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a peer engineering firm exploring overflow-capacity or subcontract-partnership opportunities, rather than a standard fabrication-client pitch.</t>
+        </is>
+      </c>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>Oil &amp; gas is named as one of several sectors served (alongside mining and forestry), not the company's sole/core market.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -56,6 +56,8 @@
     <sheet name="Fort Nelson, BC" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="Kelowna, BC" sheetId="52" state="visible" r:id="rId52"/>
     <sheet name="Kamloops, BC" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="Vernon, BC" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="Penticton, BC" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -109,6 +111,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'Fort Nelson, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'Kelowna, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'Kamloops, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'Vernon, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'Penticton, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3124,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4256,6 +4260,48 @@
       <c r="H27" s="10" t="inlineStr">
         <is>
           <t>https://www.nortechweldandfab.ca/ ; https://oilfieldpages.ca/company/nortech-welding-fabricating-inc-dawson-creek-bc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Vernon, BC</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>BC Boat Lift and Dock (WBL Marine)</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>https://bcboatliftanddock.com/</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Dock and boat-lift builder (Sunstream lifts, FLOE docks) marketed as serving Vernon's three lakes (Kalamalka, Okanagan and Swan Lakes) - but the company's actual registered address is 810 Riverside Ave, Sicamous, BC, a distinct town not currently on this project's city list, not Vernon itself.</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether Sicamous should be added as a separate target city, or whether this company's Vernon-area service work alone justifies inclusion under Vernon.</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>https://bcboatliftanddock.com/service-areas/vernon-bc/ ; https://bcboatliftsicamous.floedealers.com/</t>
         </is>
       </c>
     </row>
@@ -13597,7 +13643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A439"/>
+  <dimension ref="A1:A454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -16505,6 +16551,104 @@
       <c r="A439" s="9" t="inlineStr">
         <is>
           <t>Both International Steel Fabrication and Innovex Engineering name oil &amp; gas as one of several served sectors alongside forestry/mining/construction; consistent with this project's established treatment of multi-sector fabricators (TW Industrial Group, batch 20; Priority Steel Erectors, batch 23), this was not treated as a hard exclusion, but outreach framing for both companies should lean on their non-oil-and-gas work given how the sector mix reads. No location-mismatch or defense-exclusion issues were found in this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="7" t="inlineStr">
+        <is>
+          <t>Batch 26: Vernon, BC &amp; Penticton, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="9" t="inlineStr">
+        <is>
+          <t>1. Waycon Manufacturing Ltd. (Penticton) - Score 6, Priority B - well-equipped, growing industrial fabricator (precision components to large-scale structures, recent $575K government manufacturing job funding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="9" t="inlineStr">
+        <is>
+          <t>2. A-1 Machine &amp; Welding, Donald's Machine Works (Vernon), Mealing Welding (Penticton) - Score 4, Priority C - established general fabricators/welders with a more building-construction- or general-repair-oriented client base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="9" t="inlineStr">
+        <is>
+          <t>Vernon and Penticton were thinner than Kelowna/Kamloops (batch 25) - their fabrication shops lean more toward residential/commercial building steel and general repair rather than heavy-industrial or marine-adjacent work. The one genuine marine-adjacent find this pass (Shoreline Pile Driving) turned out to actually be a Kelowna company, not a Vernon or Penticton one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="9" t="inlineStr">
+        <is>
+          <t>For Waycon Manufacturing, lead with its demonstrated large-scale structural fabrication capability and recent growth investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal directly in Vernon or Penticton this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Waycon Manufacturing (Penticton). A-1 Machine &amp; Welding, Donald's Machine Works, and Mealing Welding as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="9" t="inlineStr">
+        <is>
+          <t>Shoreline Pile Driving, a genuine freshwater marine-construction company (pile driving, dock building, boat lifts on Okanagan Lake) discovered while researching this pair, was confirmed to be based in Kelowna, not Vernon or Penticton - it was added as a new row to the existing Kelowna, BC sheet (batch 25) rather than forced into this batch's cities, continuing this project's discipline around exact city attribution. BC Boat Lift and Dock (marketed under a Vernon service-area page) was found to be registered in Sicamous, BC, a distinct town not currently on this project's city list - routed to Review rather than added to Vernon, since unlike Shoreline Pile Driving there is no already-covered 'correct' sheet to move it to.</t>
         </is>
       </c>
     </row>
@@ -21238,7 +21382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="3" min="1" max="1"/>
@@ -21692,6 +21836,118 @@
         </is>
       </c>
       <c r="X4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Kelowna, BC</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Shoreline Pile Driving</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>https://shorelinepiledriving.com/</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Marine/Freshwater Construction</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Pile driving, dock building and boat lift installation on Okanagan Lake and other Okanagan waterways</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>A genuine freshwater marine-construction company - pile driving and dock-building work is directly structurally relevant to AH Structures' scope, similar in kind to the marina/dock work already flagged for Grizzly Metal Fab in this same batch, though on lakes rather than the ocean.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the structural engineering considerations inherent in pile driving and dock construction (load-bearing, ice/wave loading on a large lake).</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Company website (shorelinepiledriving.com/services/pile-driving) describes pile driving, dock building and boat lift services on Okanagan Lake.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Bob Jones</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>https://shorelinepiledriving.com/about/our-team/</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>info@shorelinepiledriving.com</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); Bob Jones's personal email is listed only in obfuscated/placeholder form in search results and was not used.</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>https://shorelinepiledriving.com/ ; https://www.yellowpages.ca/bus/British-Columbia/Kelowna/Shoreline-Pile-Driving/7885112.html</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA pitch specifically tied to dock and pile-driving structural design (load-bearing, ice/wave loading) - the clearest freshwater marine-construction angle found in the Okanagan.</t>
+        </is>
+      </c>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>Found during Vernon/Penticton research (batch 26) rather than the original Kelowna batch (25); added to the existing Kelowna, BC sheet since that is the company's correct city.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:X1"/>
@@ -22306,6 +22562,760 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Vernon, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>A-1 Machine &amp; Welding (1986) Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://a1machine.bc.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Supply &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel supply, delivery, framing and installation; custom fabrication and welding, CWB-certified crew</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established (35+ years) Okanagan structural steel supplier/fabricator with a CWB-certified crew - a general structural fit, though its client base (residential, industrial, commercial, institutional) is more building-construction-oriented than heavy-industrial/marine.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (a1machine.bc.ca) describes structural steel supply, framing and installation for residential, industrial, commercial and institutional projects across BC.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://a1machine.bc.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>machinery@a1machine.bc.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://a1machine.bc.ca/contact/ ; https://www.frasersdirectory.com/suppliers/a-1-machine-welding-1986-ltd-16573651387/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm what proportion of work is heavy-industrial versus building-construction structural steel before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Vernon, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Donald's Machine Works Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.donaldsmachine.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Steel Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Steel welding and aluminum fabrication for structural and industrial projects; family-run business</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established, family-run Vernon fabricator - a modest general industrial fit with no marine or heavy structural-engineering-specific evidence found in this pass.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (donaldsmachine.ca) describes steel welding and aluminum fabrication services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Shawn Donald</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.donaldsmachine.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a directory source displayed only a masked address (****@donaldsmachine.ca), which was not used per this project's no-guessing policy on masked addresses. Only phone confirmed (250-542-5557).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.donaldsmachine.ca/contact ; https://www.zoominfo.com/p/Shawn-Donald/3495749670</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm scope of work before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Penticton, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Waycon Manufacturing Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://waycon.net/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/waycon-manufacturing-ltd-</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial Fabrication &amp; Manufacturing</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CNC machining, custom metal fabrication and industrial steel work in carbon steel, stainless steel and aluminum, from precision components to large-scale structures; CWB- and AWS-certified welding</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Well-equipped, growing (recently awarded $575K in BC government manufacturing job funding) industrial fabricator explicitly spanning precision components to large-scale structures - a solid general heavy-industrial fit and the strongest candidate found in this batch.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the range of work described (precision components through large-scale structures) and the company's recent growth/investment.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (waycon.net/industrial-fabrication) and 2024 local news coverage (Penticton Herald, Castanet) describe CNC machining, custom fabrication and large-scale structural work, plus recent BC government manufacturing job funding.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>John O'Connell</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://waycon.net/about-us/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@waycon.net</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://waycon.net/ ; https://www.pentictonherald.ca/news/article_0fa8254a-4552-11ef-98e5-8b45676a6717.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its large-scale structural fabrication work, given the company's recent growth and investment.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Penticton, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Mealing Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mealingwelding.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Welding, fabrication, equipment repairs, structural steel and pressure pipe services, plus mobile welding</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established Penticton welding/fabrication shop offering structural steel and pressure pipe services - a modest general industrial fit with no marine or heavy structural-engineering-overflow-specific evidence found.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (mealingwelding.ca) describes welding, fabrication, structural steel and pressure pipe services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Garrett Mealing</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/garrett-mealing-bab6b098/</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mealingwelding.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>mealingweldingltd@gmail.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mealingwelding.ca/ ; https://www.linkedin.com/in/garrett-mealing-bab6b098/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm scope of structural work before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -58,6 +58,8 @@
     <sheet name="Kamloops, BC" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="Vernon, BC" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="Penticton, BC" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="Trail, BC" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="Castlegar, BC" sheetId="57" state="visible" r:id="rId57"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -113,6 +115,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="52" hidden="1">'Kamloops, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="53" hidden="1">'Vernon, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'Penticton, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'Trail, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'Castlegar, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13643,7 +13647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A454"/>
+  <dimension ref="A1:A470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -16649,6 +16653,111 @@
       <c r="A454" s="9" t="inlineStr">
         <is>
           <t>Shoreline Pile Driving, a genuine freshwater marine-construction company (pile driving, dock building, boat lifts on Okanagan Lake) discovered while researching this pair, was confirmed to be based in Kelowna, not Vernon or Penticton - it was added as a new row to the existing Kelowna, BC sheet (batch 25) rather than forced into this batch's cities, continuing this project's discipline around exact city attribution. BC Boat Lift and Dock (marketed under a Vernon service-area page) was found to be registered in Sicamous, BC, a distinct town not currently on this project's city list - routed to Review rather than added to Vernon, since unlike Shoreline Pile Driving there is no already-covered 'correct' sheet to move it to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="7" t="inlineStr">
+        <is>
+          <t>Batch 27: Trail, BC &amp; Castlegar, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="9" t="inlineStr">
+        <is>
+          <t>1. XL Quality Industrial Services Inc. (Trail) - Score 6, Priority B - positioned specifically to serve engineering and industrial contractors near Teck's Trail smelter, a genuine subcontract/overflow-capacity fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="9" t="inlineStr">
+        <is>
+          <t>2. Castlegar Machine &amp; Chrome Ltd. (Castlegar) - Score 6, Priority B - established, diversified 25+ year machine shop/fabricator with explicit structural steel component capability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="9" t="inlineStr">
+        <is>
+          <t>3. Columbia Steel Fabricating &amp; Welding (Trail) and Martech Electrical Systems' Steel Fabrication Division (Castlegar) - Score 4, Priority C - general/secondary fabrication fits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="9" t="inlineStr">
+        <is>
+          <t>Teck's Trail smelter operation (one of the world's largest integrated lead-zinc smelters) anchors a genuine heavy-industrial fabrication/contracting ecosystem, though the largest EPC players there (Jacobs Engineering, Allnorth) operate at a scale where AH Structures-style outside structural support is unlikely to be sought directly - similar to the LNG Canada situation in Kitimat (batch 21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="9" t="inlineStr">
+        <is>
+          <t>For XL Quality Industrial Services, approach as a potential subcontract/overflow-capacity partner given its own positioning toward serving other engineering and industrial contractors, rather than a standard end-client pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch, though XL Quality Industrial Services' engineering-contractor-facing business model is the closest thing to a structural overflow-capacity opportunity found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: XL Quality Industrial Services (Trail) and Castlegar Machine &amp; Chrome (Castlegar). Columbia Steel Fabricating &amp; Welding and Martech Electrical Systems' Steel Fabrication Division as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="9" t="inlineStr">
+        <is>
+          <t>Jacobs Engineering Group (a ~$50M sulfuric acid plant contract at Teck's Trail smelter, with fabrication work performed at Jacobs' own Pickering, Ontario facility) and Allnorth (design-build engineering for a smelter recycle building) were reviewed but not added as direct prospects: both are large multinational/national EPC firms operating at a scale where outside structural/FEA support from a small consultancy is unlikely, consistent with this project's treatment of the LNG Canada EPC ecosystem in Kitimat (batch 21). XL Quality Industrial Services' current principal could not be confirmed - two different names (John Lake as 'Owner'; Gary Megaw as 'Manager') surfaced from different sources, and neither was used as a confirmed Decision Maker Name pending verification.</t>
         </is>
       </c>
     </row>
@@ -23316,6 +23425,744 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Trail, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>XL Quality Industrial Services Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://xlquality.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial Fabrication, Welding &amp; Machining</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Specialized fabrication, welding, machining and corrosion prevention/industrial coatings services for engineering and industrial contractors</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Positioned specifically to serve engineering and industrial contractors (rather than end-users directly) near Teck's Trail smelter operations - one of the larger integrated lead-zinc smelters in the world - a strong general heavy-industrial fit given its explicit engineering-contractor client base.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Serving other engineering/industrial contractors as clients suggests a genuine capacity-sharing/subcontract relationship model that AH Structures could plausibly enter as an overflow structural/FEA partner.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (xlquality.com) describes fabrication, welding, machining and industrial coatings services for engineering and industrial contractors near the Trail smelter.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://xlquality.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; sources give conflicting names for the company's principal (John Lake as 'Owner' per one directory; Gary Megaw as 'Manager' with only a masked email per ZoomInfo) - neither was confirmed, so no Decision Maker Name is recorded. Only phone confirmed (250-367-6577).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://xlquality.com/ ; https://www.zoominfo.com/p/Gary-Megaw/1447895049</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a potential subcontract/overflow structural-engineering partner, given the company's own positioning toward engineering and industrial contractors rather than direct end-users.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Confirm the company's actual current principal/owner (conflicting names found) before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Trail, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Columbia Steel Fabricating &amp; Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.columbiasteelltd.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Steel Fabrication &amp; Welding</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Steel fabrication and welding (plasma cutting, sand blasting, custom railings) for clients across industries in Trail, Rossland and the West Kootenays</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established (19 years), CWB-certified regional steel fabricator - a general industrial fit, though its described services (railings, custom fabrication) lean somewhat more toward general/architectural steel work than heavy-industrial or marine-specific structural fabrication.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (columbiasteelltd.ca) describes steel fabrication and welding services for clients across the West Kootenays.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.columbiasteelltd.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; one source names a contact only as 'Jay' with no surname confirmed. Only phone confirmed (250-368-7707).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.columbiasteelltd.ca/ ; https://www.trailchamber.bc.ca/directory-local/listing/columbia-steel-fabricating-and-welding-ltd/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm scope of heavy-industrial versus architectural/railing work before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Castlegar, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Castlegar Machine &amp; Chrome Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://castlegarmachine.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Machining &amp; Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom machining, hydraulic cylinder repair, and a full fabricating shop (shearing, forming, rolling, structural steel components) serving forestry, construction, mining, transportation and power generation clients</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established (25+ years), family-owned Kootenay machine shop and fabricator with a genuinely diversified heavy-industrial client base and explicit structural steel component capability - a solid general fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (castlegarmachine.com/welding-fabrication) describes structural steel components, general welding and metal fabrication for forestry, mining, construction, transportation and power-generation clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Frank Zmavc</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://castlegarmachine.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@castlegarmachine.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://castlegarmachine.com/contact-2/ ; https://www.zoominfo.com/c/castlegar-machine--chrome/363649248</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its structural steel component and heavy-industrial equipment work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Castlegar, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Martech Electrical Systems Ltd. (Steel Fabrication Division)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://martechelectrical.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Contracting / Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel fabrication division (8,000 sq ft indoor fabricating area plus a large secured outdoor compound) alongside the company's primary electrical, powerline and automation services</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Primarily an electrical/powerline contractor with a secondary structural steel fabrication division - a plausible but secondary fit, since structural fabrication is not this company's core business.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (martechelectrical.com, via the linked Steel Fabrication Division page) describes an 8,000 sq ft indoor fabricating area and outdoor compound.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Mario DiBella</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://martechelectrical.com/about-us/our-team/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@martechelectrical.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://martechelectrical.com/contact/ ; http://martechelectrical.com/steel-fabrication/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm the scale and nature of structural fabrication work relative to the company's primary electrical business before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -60,6 +60,8 @@
     <sheet name="Penticton, BC" sheetId="55" state="visible" r:id="rId55"/>
     <sheet name="Trail, BC" sheetId="56" state="visible" r:id="rId56"/>
     <sheet name="Castlegar, BC" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="Cranbrook, BC" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="Nelson, BC" sheetId="59" state="visible" r:id="rId59"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -117,6 +119,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="54" hidden="1">'Penticton, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="55" hidden="1">'Trail, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'Castlegar, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="57" hidden="1">'Cranbrook, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'Nelson, BC'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13647,7 +13651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A470"/>
+  <dimension ref="A1:A486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -16758,6 +16762,111 @@
       <c r="A470" s="9" t="inlineStr">
         <is>
           <t>Jacobs Engineering Group (a ~$50M sulfuric acid plant contract at Teck's Trail smelter, with fabrication work performed at Jacobs' own Pickering, Ontario facility) and Allnorth (design-build engineering for a smelter recycle building) were reviewed but not added as direct prospects: both are large multinational/national EPC firms operating at a scale where outside structural/FEA support from a small consultancy is unlikely, consistent with this project's treatment of the LNG Canada EPC ecosystem in Kitimat (batch 21). XL Quality Industrial Services' current principal could not be confirmed - two different names (John Lake as 'Owner'; Gary Megaw as 'Manager') surfaced from different sources, and neither was used as a confirmed Decision Maker Name pending verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="7" t="inlineStr">
+        <is>
+          <t>Batch 28: Cranbrook, BC &amp; Nelson, BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="9" t="inlineStr">
+        <is>
+          <t>1. Fab-Rite Services Ltd. (Cranbrook) - Score 6, Priority B - 40+ year, two-shop structural-components fabricator serving mining, forestry, oil &amp; gas and construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="9" t="inlineStr">
+        <is>
+          <t>2. Zap Welding (Nelson) - Score 6, Priority B - self-described 'foremost fabricator and erector of structural steel' in BC's southern interior since 1986.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="9" t="inlineStr">
+        <is>
+          <t>3. Tiggin Ty's Welding (Cranbrook) - Score 3, Priority C - thin evidence, no website or named contact found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="9" t="inlineStr">
+        <is>
+          <t>This East Kootenay/West Kootenay pairing produced two credible, multi-decade structural steel fabricators (Fab-Rite Services in Cranbrook, Zap Welding in Nelson), each the clear leading player in its own sub-region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="9" t="inlineStr">
+        <is>
+          <t>For both Fab-Rite Services and Zap Welding, lead with their long track record specifically in structural steel fabrication/erection (as distinct from general welding or repair) - the closest professional overlap with AH Structures' scope found in either city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Fab-Rite Services (Cranbrook) and Zap Welding (Nelson). Tiggin Ty's Welding as a lower-priority follow-up pending a working contact channel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="9" t="inlineStr">
+        <is>
+          <t>Striker Industries, initially found in a Nelson-focused search, was confirmed to be based in Grand Forks, BC (not currently on this project's city list) and was not added anywhere, consistent with this project's discipline around exact city attribution. Both Zap Welding's and Fab-Rite Services' available email addresses were either an anti-scraping placeholder or a masked directory listing, so no usable email was recorded for either company in this pass - only named principals and phone numbers.</t>
         </is>
       </c>
     </row>
@@ -24163,6 +24272,632 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Cranbrook, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Fab-Rite Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fabriteservices.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Complete fabrication and installation packages of structural steel components (tanks, chutes, bins, walkways, stairs) for industrial and commercial applications, from 10,000 sq ft shops in Cranbrook and Sparwood</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1982), well-equipped regional fabricator with two shops and an explicit structural-components focus - a strong general heavy-industrial fit, serving mining, forestry, oil &amp; gas and construction clients across Western Canada.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the company's scale (two shops), 40+ year track record, and structural-components focus.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (fabriteservices.com/about) describes structural steel component fabrication for mining, forestry, oil &amp; gas and construction clients across Western Canada and the U.S.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Mike Kozinuk</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fabriteservices.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a directory source references an email for Mike Kozinuk but displays it only in masked form, which was not used per this project's no-guessing policy. Only phone confirmed (250-489-5328).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fabriteservices.com/ ; https://www.zoominfo.com/p/Mike-Kozinuk/851993978</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its structural-component fabrication work (tanks, chutes, bins, walkways) for mining and forestry clients.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Oil &amp; gas is named as one of several served sectors (alongside mining, forestry and construction), not the company's sole/core market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Cranbrook, BC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Tiggin Ty's Welding</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Fabrication and welding for mining, forestry, oil/gas, and commercial and residential construction clients</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Smaller Cranbrook fabrication/welding company with a similar multi-sector client base to Fab-Rite Services, but with substantially less available information (no website found, no named contact).</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings describe fabrication and welding services for mining, forestry, oil/gas and construction clients.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; no company website was found either. Only listed in business directories.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.ca/search/si/1/Welding/Cranbrook+BC</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up pending confirmation of a working contact channel.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Nelson, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Zap Welding</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>http://www.zapwelding.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication &amp; Erection</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel fabrication and erection, railings, and custom work in steel, aluminum and stainless; CWB-certified tradesmen</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1986), self-described 'foremost fabricator and erector of structural steel' in BC's southern interior, with completed projects throughout the Kootenays - the strongest structural-fabrication-specific fit found in either city this batch.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the company's 35+ year track record specifically in structural steel erection (a more complex, engineering-adjacent scope than general welding/repair).</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (zapwelding.ca) and a Kootenay Business feature article describe the company as the region's foremost structural steel fabricator/erector since 1986.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Jeff Shecter</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>http://www.zapwelding.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; the company website appears to display an email, but search results returned it only as an anti-scraping placeholder that did not resolve to a real address, so it was not recorded per this project's no-guessing policy. Only phone confirmed (250-352-6978).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>http://www.zapwelding.ca/ ; https://kootenaybiz.com/nelson/article/from_sparks_to_structures_the_evolution_of_zap_welding_in_nelson</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied specifically to structural steel erection projects, the company's stated specialty.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -62,6 +62,8 @@
     <sheet name="Castlegar, BC" sheetId="57" state="visible" r:id="rId57"/>
     <sheet name="Cranbrook, BC" sheetId="58" state="visible" r:id="rId58"/>
     <sheet name="Nelson, BC" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="Revelstoke, BC" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="Prince Albert, SK" sheetId="61" state="visible" r:id="rId61"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -121,6 +123,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="56" hidden="1">'Castlegar, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="57" hidden="1">'Cranbrook, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'Nelson, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="59" hidden="1">'Revelstoke, BC'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'Prince Albert, SK'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13651,7 +13655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A486"/>
+  <dimension ref="A1:A501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -16867,6 +16871,104 @@
       <c r="A486" s="9" t="inlineStr">
         <is>
           <t>Striker Industries, initially found in a Nelson-focused search, was confirmed to be based in Grand Forks, BC (not currently on this project's city list) and was not added anywhere, consistent with this project's discipline around exact city attribution. Both Zap Welding's and Fab-Rite Services' available email addresses were either an anti-scraping placeholder or a masked directory listing, so no usable email was recorded for either company in this pass - only named principals and phone numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="7" t="inlineStr">
+        <is>
+          <t>Batch 29: Revelstoke, BC &amp; Prince Albert, SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="9" t="inlineStr">
+        <is>
+          <t>1. Pineland Metal Products Inc. (Prince Albert) - Score 6, Priority B - combines metal building products with crane services, a heavy-lift-engineering-adjacent fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="9" t="inlineStr">
+        <is>
+          <t>2. Back Country Metal Works (Revelstoke) and VMW Cutting &amp; Design (Prince Albert) - Score 3, Priority C - thin, small-scale local shops with no marine/heavy-structural-specific evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="8" t="inlineStr">
+        <is>
+          <t>Milestone: last British Columbia city on the master list</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="9" t="inlineStr">
+        <is>
+          <t>Revelstoke completes this project's coverage of all British Columbia cities/towns on the master list (batches 1-29, spanning the Lower Mainland, Vancouver Island, Sunshine Coast, northern BC, the Peace Region, and the BC Interior/Kootenays). This batch pairs it with the first Saskatchewan city, Prince Albert, marking the transition to a new province.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="9" t="inlineStr">
+        <is>
+          <t>For Pineland Metal Products, lead with a structural/FEA pitch tied specifically to its crane-services line, given the direct heavy-lift-engineering relevance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="9" t="inlineStr">
+        <is>
+          <t>Pineland Metal Products' crane-services line is the clearest signal found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Pineland Metal Products (Prince Albert). Back Country Metal Works (Revelstoke) and VMW Cutting &amp; Design (Prince Albert) as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="9" t="inlineStr">
+        <is>
+          <t>Two companies found under Revelstoke-area searches were confirmed to be based elsewhere and not added there: Mt Ida Machine &amp; Welding is actually in Salmon Arm, BC (not currently on this project's city list), and Zap Welding is based in Nelson, BC and was already recorded in batch 28 - not duplicated. Elance Steel Fabricating, found while researching Prince Albert, was confirmed to be based in Saskatoon, SK - the next city on this project's master list - and was deliberately held back for that batch rather than added here, to keep it attributed to its correct city.</t>
         </is>
       </c>
     </row>
@@ -25281,6 +25383,632 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Revelstoke, BC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Back Country Metal Works</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.metalfabricationinrevelstokebc.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Metal Fabrication &amp; Mobile Welding</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom fabrication, metal fabrication and mobile welding services</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>The one genuine Revelstoke-based fabricator confirmed in this pass - a small shop with no marine or heavy-industrial-structural-specific evidence found, but the only locally-based option after two other candidates (Mt Ida Machine &amp; Welding, actually in Salmon Arm; Zap Welding, based in Nelson and already recorded there) turned out to be based elsewhere.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (metalfabricationinrevelstokebc.ca) describes custom fabrication, metal fabrication and mobile welding services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.metalfabricationinrevelstokebc.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone/address confirmed (250-341-1015, 107A 1240 Powerhouse Rd).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.metalfabricationinrevelstokebc.ca/contact/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm scope and scale of work before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Mt Ida Machine &amp; Welding (found under a Revelstoke-area search) is actually based in Salmon Arm, BC, a distinct town not currently on this project's city list - not added here. Zap Welding (also surfaced under Revelstoke) is based in Nelson, BC and was already recorded there in batch 28; not duplicated here.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Prince Albert, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Pineland Metal Products Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://pinelandmetal.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Metal Building Products &amp; Crane Services</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Metal building products and crane services</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely local Prince Albert company combining metal building products with crane services - the crane-services line is a plausible heavy-lift-engineering-adjacent fit, similar to other crane/rigging companies recorded elsewhere in this project.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>The combination of metal building products and crane services under one company suggests potential structural/lifting-engineering work that could benefit from outside FEA support on larger projects.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (pinelandmetal.com) describes metal building products and crane services from a Prince Albert facility.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Jim</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Likely a named individual (surname not confirmed)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://pinelandmetal.com/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>jim@pinelandmetal.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Email address associated with a contact identified only by first name ('Jim'); full name and title were not confirmed in this pass.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://pinelandmetal.com/ ; https://www.dnb.com/business-directory/company-profiles.pineland_metal_products_inc.f8e36e85907cf2ba461f7aeb8574b24e.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied specifically to its crane-services line, given the heavy-lift-engineering relevance.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Confirm 'Jim's' full name and title before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Prince Albert, SK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>VMW Cutting &amp; Design (Verge Metal Works)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Machining &amp; Custom Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Repair and custom machining, metal fabrication and cutting services</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Local Prince Albert-area machine shop and fabricator - a modest general industrial fit with no marine or heavy structural-engineering-specific evidence found in this pass.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings describe custom machining, metal fabrication and cutting services located east of Prince Albert.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only a directory listing with address (17 Street East, Prince Albert, SK) was found.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.ca/bus/Saskatchewan/Prince-Albert/VMW-Cutting-Design/102899079.html</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up pending confirmation of a working contact channel.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -64,6 +64,8 @@
     <sheet name="Nelson, BC" sheetId="59" state="visible" r:id="rId59"/>
     <sheet name="Revelstoke, BC" sheetId="60" state="visible" r:id="rId60"/>
     <sheet name="Prince Albert, SK" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="Saskatoon, SK" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="Regina, SK" sheetId="63" state="visible" r:id="rId63"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -125,6 +127,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="58" hidden="1">'Nelson, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="59" hidden="1">'Revelstoke, BC'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'Prince Albert, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="61" hidden="1">'Saskatoon, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'Regina, SK'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13655,7 +13659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A501"/>
+  <dimension ref="A1:A518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -16969,6 +16973,118 @@
       <c r="A501" s="9" t="inlineStr">
         <is>
           <t>Two companies found under Revelstoke-area searches were confirmed to be based elsewhere and not added there: Mt Ida Machine &amp; Welding is actually in Salmon Arm, BC (not currently on this project's city list), and Zap Welding is based in Nelson, BC and was already recorded in batch 28 - not duplicated. Elance Steel Fabricating, found while researching Prince Albert, was confirmed to be based in Saskatoon, SK - the next city on this project's master list - and was deliberately held back for that batch rather than added here, to keep it attributed to its correct city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="7" t="inlineStr">
+        <is>
+          <t>Batch 30: Saskatoon, SK &amp; Regina, SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="9" t="inlineStr">
+        <is>
+          <t>1. DyMark Industries Inc. (Saskatoon) - Score 7, Priority A - 20+ year structural steel/detailing/weighing-solutions supplier to Saskatchewan's mining and grain-terminal industries; the strongest fit found in either city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="9" t="inlineStr">
+        <is>
+          <t>2. IWL Steel Fabricators (Saskatoon) - Score 7, Priority B - 50+ year potash-industry specialist with named, technically specific product lines (hoppers, grizzlies, splitter gates).</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="9" t="inlineStr">
+        <is>
+          <t>3. Anlin Welding &amp; Steel Fabrication (Regina) and Shear Fabrication / Elance Steel Fabricating (Saskatoon) - Score 6, Priority B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="9" t="inlineStr">
+        <is>
+          <t>4. Eagle Crane (Saskatoon) and Regina Metal Industries - Score 5-6, Priority B/C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="9" t="inlineStr">
+        <is>
+          <t>Saskatchewan's potash-mining and grain-handling industries anchor a genuinely rich, technically specific structural fabrication sector in Saskatoon in particular - this was the richest single-city yield (5 companies) since Kelowna/Kamloops (batch 25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="9" t="inlineStr">
+        <is>
+          <t>For DyMark Industries and IWL Steel Fabricators, lead with structural/FEA support tied to their named technical specialties (steel detailing/weighing solutions; potash-handling equipment design) rather than a generic industrial pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="9" t="inlineStr">
+        <is>
+          <t>DyMark's in-house steel-detailing capability and Eagle Crane's 500-ton heavy-lift/precast-installation capacity are the two most specific overflow-adjacent signals found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: DyMark Industries and IWL Steel Fabricators (Saskatoon), and Anlin Welding &amp; Steel Fabrication (Regina). Shear Fabrication, Elance Steel Fabricating, and Eagle Crane (Saskatoon), and Regina Metal Industries (Regina) as secondary follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="9" t="inlineStr">
+        <is>
+          <t>Pro Metal Industries Ltd. (Regina) - a 100% Indigenous-owned (Pasqua First Nation), 50,000 sq ft metal fabrication facility - was found but excluded outright rather than added or routed to Review: it holds confirmed, substantial defense contracts with General Dynamics Land Systems Canada (~$1M in light armoured vehicle components), Mack Defense, and QinetiQ Target Systems, is 'Controlled Goods Registered,' and markets itself with 'Military &amp; Defence' as the second-listed line of its core business - the defense work is integrated into the same facility as its mining/construction/agriculture work rather than run through a clearly separate non-defense division, so this is treated as a clear-cut defense exclusion (similar to Babcock Canada in earlier batches), not a borderline case. Goodman Steel Ltd., initially found under a Regina-area search, was confirmed to be based in Rocanville, SK - a town not currently on this project's city list - and was not added anywhere. Elance Steel Fabricating, held back from batch 29 (Prince Albert) pending confirmation of its actual city, was confirmed here to be Saskatoon-based and added to this batch accordingly.</t>
         </is>
       </c>
     </row>
@@ -26009,6 +26125,1084 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatoon, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>DyMark Industries Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dymarkindustries.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication &amp; Weighing Solutions</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel, steel detailing, sandblasting/painting, steel erection, certified welding, and weighing solutions (truck scales, bulk weighers) for inland grain terminals, processing plants and farming operations</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established (20+ years) trusted supplier and onsite contractor to leading mining and industrial companies in Saskatchewan, with in-house steel detailing capability - a strong structural-engineering-adjacent fit and the strongest candidate found in this batch.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>In-house steel detailing capability suggests some design work already happens internally, which could extend to overflow structural/FEA collaboration on larger grain-terminal or processing-plant projects.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (dymarkindustries.ca) and a 2006 Canada.ca feature describe structural steel, detailing, erection and weighing-solutions work for grain terminals, processing plants and industrial/mining clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Marc Paquette</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dymarkindustries.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>admin@dymarkindustries.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dymarkindustries.ca/contact-us ; https://www.canada.ca/en/news/archive/2006/10/dymark-industries-inc-building-strong-reputation.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to grain-terminal and processing-plant structural steel work, given the company's in-house detailing capability and established industrial/mining client base.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatoon, SK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>IWL Steel Fabricators LP</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iwlsteel.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/iwlsteel-fabricators</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Potash &amp; Industrial Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Specialized potash-industry fabrication (hoppers, grizzlies, splitter gates, bucket elevators, conveyors, material handling and dust collection chutework) for industrial, mining and oilfield sectors</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>50+ year, potash-industry-specialized fabricator with named, technically specific product lines (hoppers, grizzlies, bucket elevators) - a precise, evidence-based heavy-industrial structural fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>The complexity of named potash-handling equipment (splitter gates, dust collection chutework) suggests genuine structural/mechanical design work that could benefit from outside FEA support on larger projects.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (iwlsteel.com/profile-of-iwl-steel) describes 50+ years supplying specialized potash-industry fabrication and equipment.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Patrick Kuprowski</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iwlsteel.com/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a source claimed an email-naming-pattern ('{first_initial}{last}@iwlsteel.com') but this was not used, per this project's no-guessing/no-pattern-inference policy. Only phone confirmed (306-242-4077).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iwlsteel.com/talk-to-iwl-steel ; https://www.bbb.org/ca/sk/saskatoon/profile/steel-fabrication/iwl-steel-fabricators-lp-0057-26666</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch specifically tied to potash-handling equipment design/verification, the company's named specialty.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Oil &amp; gas is named as one of three served sectors (industrial, mining, oilfield); potash-industry fabrication is described as the company's primary specialty, so this is not treated as a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Saskatoon, SK</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Shear Fabrication Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://shearfabrication.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Custom Fabrication</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>16,000 sq ft custom shearing, bending and fabricating facility serving mining, oil &amp; gas, agriculture, industrial, lumber, construction and trucking sectors</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Well-equipped, diversified Saskatoon fabricator with a broad multi-sector client base - a solid general heavy-industrial fit.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (shearfabrication.com/services) describes custom shearing, bending and fabrication for mining, oil &amp; gas, agriculture, industrial, lumber, construction and trucking clients.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Kenneth Hendriks</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://shearfabrication.com/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>shearfab@sasktel.net</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://shearfabrication.com/contact-us/ ; https://www.bbb.org/ca/sk/saskatoon/profile/metal-fabrication/shear-fabrication-ltd-0057-37727</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its mining and industrial fabrication work.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>Oil &amp; gas is named as one of several served sectors (alongside mining, agriculture, industrial, lumber, construction and trucking), not the company's sole/core market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Saskatoon, SK</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Elance Steel Fabricating Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>https://elancesteel.com/</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication &amp; Installation</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel fabrication and installation for potash mines, ethanol plants, co-generation facilities, grain processing operations, seed cleaning terminals, and oil field infrastructure</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (45+ years) Saskatchewan-wide structural steel fabricator with a strong potash-mining and grain-processing client base - a solid general heavy-industrial structural fit.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the scale and complexity of named client facilities (potash mines, ethanol plants, co-generation facilities).</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Company website (elancesteel.com/sector/industrial-agricultural/) describes structural steel work for potash mines, ethanol plants, grain processing and oil field infrastructure across Saskatchewan, Alberta and beyond.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Jim Baier</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>https://elancesteel.com/about/</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (306-931-4412).</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>https://elancesteel.com/ ; https://www.scrapmonster.com/company/elance-steel-fabricating-co-ltd/94321</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to potash-mine and grain-processing structural steel work.</t>
+        </is>
+      </c>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>Oil field infrastructure is named as one of several served markets (alongside potash mines, ethanol plants and grain processing), not the company's sole/core business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Saskatoon, SK</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Eagle Crane</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>https://eagle-crane.com/</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Lift / Crane &amp; Rigging</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Taxi crane services, rigging and precast concrete installation, up to 500-ton capacity, serving Saskatoon, Moose Jaw, North Battleford and Prince Albert</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Well-equipped regional heavy-lift crane and rigging company with genuine 500-ton capacity - a plausible overflow-heavy-lift-engineering fit, similar to Sterling Crane and Okanagan Crane &amp; Rigging recorded in earlier batches.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the heavy-lift capacity (up to 500 tons) and precast concrete installation specialty.</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Company website (eagle-crane.com/about-us) describes taxi crane, rigging and precast concrete installation services up to 500-ton capacity.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>https://eagle-crane.com/</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>info@eagle-crane.com</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>https://eagle-crane.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a potential engineering-support partner for heavy-lift and precast concrete installation project planning.</t>
+        </is>
+      </c>
+      <c r="X6" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Regina, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Anlin Welding &amp; Steel Fabrication Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://anlinwelding.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Steel Fabrication and Specialty Fabrication divisions (10,000 sq ft plant each) providing access/egress platforms, handrails and ladders for the mining sector, with complex structural steel fieldwork by qualified Iron Workers Local 771 crews</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established (since 1976) Regina structural steel fabricator with a specific mining-sector product line (access/egress platforms, handrails) and unionized fieldwork crews experienced in complex structural steel - a solid, evidence-based heavy-industrial structural fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the described complexity of its structural steel fieldwork for the mining sector.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (anlinwelding.ca/fabrication-services) describes access/egress platforms, handrails and ladders for mining clients, with fieldwork by Iron Workers Local 771 crews.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Ian Matt</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://anlinwelding.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (306-721-6566).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://anlinwelding.ca/ ; https://www.bbb.org/ca/sk/regina/profile/welding/anlin-welding-steel-fabrication-ltd-0057-41052</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to mining-sector access/egress platform and handrail structural work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Company was established in 1976 by Robert Matt; a separate source names Ian Matt as owner/controller 'as of 2013' - likely a family succession rather than a conflict, but not independently confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Regina, SK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Regina Metal Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.reginametal.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Custom Welding, Machining &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Custom welding, machine shop, repair and fabrication (lathe work, milling) for mining, construction equipment, food processing and farm equipment applications</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Long-established, family-owned Regina machine shop and fabricator (staff with 200+ years combined experience) with a genuinely diversified industrial client base - a solid general heavy-industrial fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (reginametal.com) describes machining, welding and fabrication services for mining, construction equipment, food processing and farm equipment clients.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Trevor Compton</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.reginametal.com/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a source claimed an email-naming-pattern ('first@reginametal.com') but this was not used, per this project's no-guessing/no-pattern-inference policy. Only phone confirmed (306-543-9444).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.reginametal.com/contact-us.php ; https://www.zoominfo.com/c/regina-metal-industries-ltd/389928933</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to mining and construction-equipment fabrication work.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -66,6 +66,8 @@
     <sheet name="Prince Albert, SK" sheetId="61" state="visible" r:id="rId61"/>
     <sheet name="Saskatoon, SK" sheetId="62" state="visible" r:id="rId62"/>
     <sheet name="Regina, SK" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="Moose Jaw, SK" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="Swift Current, SK" sheetId="65" state="visible" r:id="rId65"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -129,6 +131,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="60" hidden="1">'Prince Albert, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="61" hidden="1">'Saskatoon, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'Regina, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'Moose Jaw, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'Swift Current, SK'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3144,7 +3148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4318,6 +4322,48 @@
       <c r="H28" s="10" t="inlineStr">
         <is>
           <t>https://bcboatliftanddock.com/service-areas/vernon-bc/ ; https://bcboatliftsicamous.floedealers.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Swift Current, SK</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Wilf's Oilfield Service (87) Ltd.</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>https://wilfsoilfieldserviceltd.com/</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Offers structural steel construction and steel-building services, but the company's own name identifies it as an oilfield service company - its core business appears to be oil &amp; gas services, with structural steel/building work as a secondary offering.</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether the structural steel/building line is a genuinely separate, non-oilfield division, or simply part of the same oilfield-service business, before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>https://wilfsoilfieldserviceltd.com/buildings-steel-framing-sk.php</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A518"/>
+  <dimension ref="A1:A531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -17085,6 +17131,90 @@
       <c r="A518" s="9" t="inlineStr">
         <is>
           <t>Pro Metal Industries Ltd. (Regina) - a 100% Indigenous-owned (Pasqua First Nation), 50,000 sq ft metal fabrication facility - was found but excluded outright rather than added or routed to Review: it holds confirmed, substantial defense contracts with General Dynamics Land Systems Canada (~$1M in light armoured vehicle components), Mack Defense, and QinetiQ Target Systems, is 'Controlled Goods Registered,' and markets itself with 'Military &amp; Defence' as the second-listed line of its core business - the defense work is integrated into the same facility as its mining/construction/agriculture work rather than run through a clearly separate non-defense division, so this is treated as a clear-cut defense exclusion (similar to Babcock Canada in earlier batches), not a borderline case. Goodman Steel Ltd., initially found under a Regina-area search, was confirmed to be based in Rocanville, SK - a town not currently on this project's city list - and was not added anywhere. Elance Steel Fabricating, held back from batch 29 (Prince Albert) pending confirmation of its actual city, was confirmed here to be Saskatoon-based and added to this batch accordingly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="7" t="inlineStr">
+        <is>
+          <t>Batch 31: Moose Jaw, SK &amp; Swift Current, SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="9" t="inlineStr">
+        <is>
+          <t>1. Fabro Ltd. (Swift Current) - Score 5, Priority B - 55+ year fabricator with a genuinely diversified agricultural/potash/industrial client base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="9" t="inlineStr">
+        <is>
+          <t>2. Armstrong Welding Ltd. (Moose Jaw) and Wheatland Machine Shop Ltd. (Swift Current) - Score 4, Priority C - established general fabricators/welders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="9" t="inlineStr">
+        <is>
+          <t>For Fabro Ltd., frame outreach around its potash and agricultural-industrial work specifically, since oilfield is also a prominently named sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal in either city this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Fabro Ltd. (Swift Current). Armstrong Welding and Wheatland Machine Shop as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="9" t="inlineStr">
+        <is>
+          <t>JNE Welding Limited Partnership, a potash-industry OEM fabricator (evaporator tanks, process tanks) discovered while researching this pair, was confirmed to be based in Saskatoon, SK, not Moose Jaw or Swift Current - it was added as a new row to the existing Saskatoon, SK sheet (batch 30) rather than forced into this batch's cities, continuing this project's discipline around exact city attribution. Wilf's Oilfield Service (87) Ltd. (Swift Current) was found offering structural steel/building services, but its own company name identifies it as an oilfield service business first - routed to Low Confidence/Review rather than added or excluded outright, pending confirmation of whether the structural-steel line is a genuinely separate division.</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="3" min="1" max="1"/>
@@ -26821,6 +26951,114 @@
         </is>
       </c>
       <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Saskatoon, SK</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>JNE Welding Limited Partnership</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>https://jnewelding.com/</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Potash &amp; Mining Equipment Fabrication</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>OEM fabrication for the potash mining industry - evaporator tanks, process tanks, chutes, ducting and structural fabrications for potash extraction and milling processes</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>A second Saskatoon potash-industry specialist (alongside IWL Steel Fabricators, already recorded in batch 30) with named, technically specific process-vessel and structural work - a precise, evidence-based heavy-industrial structural fit.</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>The complexity of named potash-processing equipment (evaporator tanks, process tanks) suggests genuine structural/mechanical design work that could benefit from outside FEA support on larger projects.</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Company website (jnewelding.com/industries-served/) describes OEM fabrication of potash mining and processing equipment, including evaporator and process tanks.</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Dwi Nur Irfan</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>https://jnewelding.com/</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; a contact person (Adam Logue) is named in one directory listing, but no direct email was confirmed for either him or the owner. Only phone confirmed (306-242-0884).</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>https://jnewelding.com/contact-us/ ; https://saskchamber.com/initiatives/indigenous-business-directory/profile/jne-welding-lp-2/</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to potash-processing vessel and structural fabrication work, the company's named specialty.</t>
+        </is>
+      </c>
+      <c r="X7" s="5" t="inlineStr">
+        <is>
+          <t>Found during Moose Jaw/Swift Current research (batch 31) rather than the original Saskatoon batch (30); added to the existing Saskatoon, SK sheet since that is the company's correct city. JNE Welding is listed in the Saskatchewan Chamber of Commerce's Indigenous Business Directory.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:X1"/>
@@ -27203,6 +27441,636 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Moose Jaw, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Armstrong Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified welding shop offering everything from general repairs to structural steel fabrication and installation</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (50+ years) Moose Jaw welding/fabrication shop with a CWB-certified structural steel capability - a modest general industrial fit with no marine or heavy-industrial-specific evidence found beyond general structural fabrication.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (MooseJawToday.com, Dun &amp; Bradstreet) describe a CWB-certified shop offering general repairs through structural steel fabrication and installation, serving Moose Jaw and area for over 50 years.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone/address confirmed (306-692-4385, 1620 Stadacona St W).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.moosejawtoday.com/directory/welders/armstrong-welding-ltd-64984</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm scope of structural work before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Swift Current, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Fabro Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://fabro.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Custom Machining &amp; Industrial Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom machining, welding and fabrication for oilfield, agricultural, potash and industrial repair and manufacturing</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (55+ years) Swift Current fabricator with a genuinely diversified client base spanning agriculture, potash and general industrial work, alongside oilfield - a solid general industrial fit given its long track record and breadth of served sectors.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (fabro.ca) describes custom machining, welding and fabrication for oilfield, agricultural, potash and industrial clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Will Hyswick</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://fabro.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; company has a contact form but no direct email address was displayed in search results. Only phone confirmed (306-778-3955).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://fabro.ca/contact-us.php ; https://www.bbb.org/ca/sk/swift-current/profile/welding/fabro-enterprises-limited-0057-29604</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied specifically to its potash and agricultural-industrial fabrication work, given oilfield is only one of several served sectors.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Oilfield is named as one of several served sectors (alongside agricultural, potash and industrial); not treated as a hard oil &amp; gas exclusion case, but outreach framing should lean on the non-oilfield sectors given how prominently oilfield is listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Swift Current, SK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Wheatland Machine Shop Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.wheatlandmachine.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Aluminum &amp; Stainless Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Aluminum and stainless steel welding, repair and fabrication of exotic metals, servicing agricultural, construction, oilfield and residential sectors</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established Swift Current specialty fabricator (exotic metals, aluminum/stainless) - a modest fit given its more general/residential-leaning client mix relative to Fabro Ltd.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (wheatlandmachine.ca) and directory listings describe aluminum/stainless steel fabrication for agricultural, construction, oilfield and residential clients.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Joe Lorenzino</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.wheatlandmachine.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>wms@sasktel.net</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.wheatlandmachine.ca/contact ; https://www.bbb.org/ca/sk/swift-current/profile/welding/wheatland-machine-shop-ltd-0057-1000003891</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm scope of non-residential structural/industrial work before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -68,6 +68,8 @@
     <sheet name="Regina, SK" sheetId="63" state="visible" r:id="rId63"/>
     <sheet name="Moose Jaw, SK" sheetId="64" state="visible" r:id="rId64"/>
     <sheet name="Swift Current, SK" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="North Battleford, SK" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="Lloydminster, SK" sheetId="67" state="visible" r:id="rId67"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -133,6 +135,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="62" hidden="1">'Regina, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="63" hidden="1">'Moose Jaw, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'Swift Current, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'North Battleford, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'Lloydminster, SK'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13705,7 +13709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A531"/>
+  <dimension ref="A1:A546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -17215,6 +17219,104 @@
       <c r="A531" s="9" t="inlineStr">
         <is>
           <t>JNE Welding Limited Partnership, a potash-industry OEM fabricator (evaporator tanks, process tanks) discovered while researching this pair, was confirmed to be based in Saskatoon, SK, not Moose Jaw or Swift Current - it was added as a new row to the existing Saskatoon, SK sheet (batch 30) rather than forced into this batch's cities, continuing this project's discipline around exact city attribution. Wilf's Oilfield Service (87) Ltd. (Swift Current) was found offering structural steel/building services, but its own company name identifies it as an oilfield service business first - routed to Low Confidence/Review rather than added or excluded outright, pending confirmation of whether the structural-steel line is a genuinely separate division.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="7" t="inlineStr">
+        <is>
+          <t>Batch 32: North Battleford, SK &amp; Lloydminster, SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="9" t="inlineStr">
+        <is>
+          <t>1. Empire Welding &amp; Machining Ltd. and Sad Sacks' Welding &amp; Machine Ltd. (North Battleford) - Score 5, Priority B - established, diversified fabricators; Sad Sacks' in particular has no oil &amp; gas exposure found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="9" t="inlineStr">
+        <is>
+          <t>2. Triland Welding &amp; Machine Ltd. (Lloydminster) - Score 5, Priority B - 45+ year, family-owned, multi-sector fabricator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="8" t="inlineStr">
+        <is>
+          <t>A border-city note: Lloydminster</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="9" t="inlineStr">
+        <is>
+          <t>Lloydminster physically straddles the Alberta/Saskatchewan border and its economy is heavily oil-dependent; this project's master city list records it simply as 'Lloydminster, SK,' and the one qualifying company found (Triland Welding &amp; Machine) is registered on the Alberta side of the same city - recorded under the existing list entry rather than treated as a separate city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="9" t="inlineStr">
+        <is>
+          <t>For Sad Sacks' Welding &amp; Machine, no oil &amp; gas exposure was found at all, making it the cleanest fit of the three companies found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Sad Sacks' Welding &amp; Machine (North Battleford). Empire Welding &amp; Machining (North Battleford) and Triland Welding &amp; Machine (Lloydminster) as close secondary follow-ups, both with oil &amp; gas-adjacent client bases to frame around carefully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="9" t="inlineStr">
+        <is>
+          <t>No location mismatches, defense exclusions, or hard oil &amp; gas exclusions arose this batch - all three companies found have genuinely diversified (agricultural/commercial/industrial) client bases, even where oil is also a named sector, consistent with this project's established treatment of multi-sector fabricators rather than oil &amp; gas-core businesses.</t>
         </is>
       </c>
     </row>
@@ -28071,6 +28173,648 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>North Battleford, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Empire Welding &amp; Machining Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ewam.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Metal Fabrication &amp; Machining</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Engineered and manufactured metalwork for agricultural, construction and oil field sectors, since 1986</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established (since 1986) North Battleford fabricator with a diversified agricultural/construction client base - a modest general industrial fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (ewam.ca) describes metalwork manufacturing for agricultural, construction and oil field clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ewam.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; company has a contact form but no direct email address was displayed in search results. Only phone confirmed (306-446-3444).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://ewam.ca/contact/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its agricultural and construction fabrication work, given oil field is also a named sector.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Oil field is named as one of three served sectors (alongside agricultural and construction), not the company's sole/core market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>North Battleford, SK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Sad Sacks' Welding &amp; Machine Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://sadsackswelding.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Machining &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Welding, machining, fabrication and iron work (drive shafts, bearings, hydraulic hoses/tools) for commercial, industrial and agricultural sectors, since 1989</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established (since 1989) North Battleford shop with a diversified commercial/industrial/agricultural client base and no oil &amp; gas exposure found - a cleaner general industrial fit than several other Saskatchewan interior-town fabricators recorded in this project.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (sadsackswelding.com/services) describes welding, machining, fabrication and iron work for commercial, industrial and agricultural clients.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Ron &amp; Jim</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Co-Owners (surnames not confirmed)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://sadsackswelding.com/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>sadsacks@sasktel.net</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://sadsackswelding.com/ ; https://411.ca/business/profile/6209706</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its industrial and agricultural fabrication work.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Lloydminster, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan/Alberta (border city)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Triland Welding &amp; Machine Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.trilandmachining.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Machining &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, machining, maintenance, repair and new fabrication for agricultural, oil, construction, trucking and commercial sectors, since 1979</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (45+ years), family-owned Lloydminster fabricator with a diversified multi-sector client base - a solid general industrial fit, though oil is a prominently named sector given the region's economy.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (trilandmachining.ca) describes welding, machining and fabrication services for agricultural, oil, construction, trucking and commercial clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Tim Sawarin</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.trilandmachining.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; company has a contact page but no direct email address was displayed in search results. Only phone confirmed (780-875-6758).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.trilandmachining.ca/contact-us ; https://www.yellowpages.ca/bus/Alberta/Lloydminster/Triland-Welding-Machine-Ltd/2588438.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied specifically to its agricultural, construction and trucking-sector fabrication work, given oil is also a prominently named sector for this heavily oil-dependent border city.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Lloydminster straddles the Alberta/Saskatchewan border; this company's registered address is on the Alberta side (5316 51st Street, Lloydminster, AB), while this project's master city list records the city simply as 'Lloydminster, SK' - recorded here under that existing list entry rather than treated as a separate city.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -70,6 +70,8 @@
     <sheet name="Swift Current, SK" sheetId="65" state="visible" r:id="rId65"/>
     <sheet name="North Battleford, SK" sheetId="66" state="visible" r:id="rId66"/>
     <sheet name="Lloydminster, SK" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="Yorkton, SK" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="Estevan, SK" sheetId="69" state="visible" r:id="rId69"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -137,6 +139,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="64" hidden="1">'Swift Current, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="65" hidden="1">'North Battleford, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'Lloydminster, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'Yorkton, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'Estevan, SK'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13709,7 +13713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A546"/>
+  <dimension ref="A1:A561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -17317,6 +17321,104 @@
       <c r="A546" s="9" t="inlineStr">
         <is>
           <t>No location mismatches, defense exclusions, or hard oil &amp; gas exclusions arose this batch - all three companies found have genuinely diversified (agricultural/commercial/industrial) client bases, even where oil is also a named sector, consistent with this project's established treatment of multi-sector fabricators rather than oil &amp; gas-core businesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="7" t="inlineStr">
+        <is>
+          <t>Batch 33: Yorkton, SK &amp; Estevan, SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="9" t="inlineStr">
+        <is>
+          <t>1. Yorkton Welding &amp; Machine (1983) Ltd. (Yorkton) - Score 5, Priority B - 40+ year, diversified fabricator with no oil &amp; gas exposure found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="9" t="inlineStr">
+        <is>
+          <t>2. Smith Steel Service (Yorkton), Fusion Industries and KRJ Custom Fabricating (Estevan) - Score 3-4, Priority C - a steel distributor, a general welding shop, and a smaller-scale custom fabricator respectively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="8" t="inlineStr">
+        <is>
+          <t>Best industry segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="9" t="inlineStr">
+        <is>
+          <t>Yorkton's fabrication sector was a cleaner fit than Estevan's - Estevan sits in Saskatchewan's Bakken oil region, and even the two candidates found there without explicit oilfield naming in their own marketing (Fusion Industries, KRJ Custom Fabricating) warrant a closer look at their actual client mix before treating them as strong prospects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="9" t="inlineStr">
+        <is>
+          <t>For Yorkton Welding &amp; Machine, approach directly - no oil &amp; gas caveat is needed given its clean, diversified client base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Yorkton Welding &amp; Machine (Yorkton). Smith Steel Service (Yorkton), Fusion Industries and KRJ Custom Fabricating (Estevan) as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="9" t="inlineStr">
+        <is>
+          <t>Brent Gedak Welding Ltd. and TSB Oilfield Construction (both Estevan) were found but excluded outright, not routed to Review: both explicitly market themselves as oilfield-service companies, a clear-cut oil &amp; gas core-market case. Metular Fabricators Inc., initially listed under Estevan, was not added: one source placed it in Regina instead, and with only a phone number and no further detail available, the location conflict and thinness of evidence together made it unsafe to place confidently in either city. Fusion Industries (Estevan) was flagged for follow-up confirmation of its client mix, since it appears on at least one oilfield-specific business directory (Oilgaspages) despite its own marketing describing general welding/fabrication services rather than oilfield work specifically.</t>
         </is>
       </c>
     </row>
@@ -28815,6 +28917,756 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Yorkton, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Yorkton Welding &amp; Machine (1983) Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://yorktonwelding.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Machining &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, machining, custom fabrication (railings, steps, landings, deck frames) and specialty trailer manufacturing/repair, serving agriculture, industrial, manufacturing, commercial and private sectors</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (40+ years) east-central Saskatchewan fabricator with a genuinely diversified client base and no oil &amp; gas exposure found - a clean general industrial fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (yorktonwelding.com) describes welding, machining, fabrication and specialty trailer manufacturing for agriculture, industrial, manufacturing, commercial and private clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Jerry Holowatuik &amp; Bruce Cmoc</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Co-Owners</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://yorktonwelding.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>yorktonwelding@imagewireless.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://yorktonwelding.com/ ; https://www.dnb.com/business-directory/company-profiles.yorkton_welding__machine_(1983)_ltd.8b885f3a5b594b973653e6e16070a093.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its industrial and manufacturing fabrication work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Yorkton, SK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Smith Steel Service (Smith Steel Inc.)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://smithsteelservice.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Steel Supply &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Steel, trailer parts, welding supplies, industrial gases, bulk chain and cable, nuts and bolts supply</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established (since 1986) east-central Saskatchewan steel supplier - primarily a distributor rather than a fabricator/engineering firm, so a weaker structural-fit prospect than a design-and-build fabricator, but a useful secondary industry contact.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; the company's core business (steel supply/distribution) is not itself a fabrication or engineering service.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (smithsteelservice.com/products-services) describes steel, trailer parts and industrial supply distribution.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Michael Smith</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://smithsteelservice.com/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>mike@smithsteelservice.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Appears to be a named individual's direct email, sourced from public business listings; a general sales inbox (sales@smithsteelservice.com) is also available as a fallback.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://smithsteelservice.com/contact-us/ ; https://www.bbb.org/ca/sk/yorkton/profile/metal-specialties/smith-steel-inc-0057-25234</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up given its primary business is steel supply/distribution rather than fabrication or engineering.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Estevan, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Fusion Industries Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fusionindustries.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Quality-control pressure welding, CNC plasma cutting, fabrication, shearing, breaking and torch cutting</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Locally owned Estevan welding/fabrication shop with genuine technical capability (pressure welding, CNC plasma cutting) - a modest general industrial fit given the described service list is not sector-specific.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (Mysask411, 411.ca) describe pressure welding, CNC plasma cutting and general fabrication services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (306-634-6178).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://mysask411.com/estevan/welding/fusion-industries-inc/801371</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm client-sector mix given Estevan's oil &amp; gas-heavy regional economy (this company is listed on at least one oilfield-specific business directory) before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Estevan sits in Saskatchewan's Bakken oil region; while this company's own service description does not name oil &amp; gas specifically, it appears in an oilfield-industry business directory (Oilgaspages) alongside general listings, so its actual client-sector mix should be confirmed directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Estevan, SK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>KRJ Custom Fabricating Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://krjfabricating.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Custom Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Steel, aluminum and stainless steel welding, fabricating and repair; custom-order items (toolboxes, slip tanks, firepits, benches, signs, stairs)</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Recently changed ownership Estevan custom-fabrication shop with a genuine, verifiable named-individual contact email - useful as a documented local contact, though its described product line (toolboxes, firepits, benches, signs) reads as smaller-scale custom/retail fabrication rather than heavy-industrial or structural work.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; the company's described scope is smaller-scale custom fabrication rather than heavy-industrial structural work.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (krjfabricating.ca) and a local news article (DiscoverEstevan.com) describe custom steel/aluminum/stainless fabrication and repair, plus made-to-order items like toolboxes, slip tanks, firepits and stairs.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Daniel Peterson</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://discoverestevan.com/articles/new-ownership-continuing-krj-custom-fabricatings-legacy-of-craftsmanship-and-creativity</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>Daniel@krjfabricating.ca</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Appears to be a genuine, unmasked named-individual email, sourced directly from the company's own materials/local news coverage rather than a third-party directory.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://krjfabricating.ca/ ; https://discoverestevan.com/articles/new-ownership-continuing-krj-custom-fabricatings-legacy-of-craftsmanship-and-creativity</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up given the smaller-scale, custom/retail nature of its product line; confirm whether any larger structural or industrial work exists before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Recently changed ownership: Daniel Peterson purchased the business from a previous owner (Kenneth Mehler); confirmed via local news coverage rather than a directory listing alone.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -72,6 +72,8 @@
     <sheet name="Lloydminster, SK" sheetId="67" state="visible" r:id="rId67"/>
     <sheet name="Yorkton, SK" sheetId="68" state="visible" r:id="rId68"/>
     <sheet name="Estevan, SK" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="Weyburn, SK" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="Melfort, SK" sheetId="71" state="visible" r:id="rId71"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -141,6 +143,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="66" hidden="1">'Lloydminster, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="67" hidden="1">'Yorkton, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'Estevan, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'Weyburn, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'Melfort, SK'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3156,7 +3160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4374,6 +4378,82 @@
           <t>https://wilfsoilfieldserviceltd.com/buildings-steel-framing-sk.php</t>
         </is>
       </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Weyburn, SK</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Stewart Steel Inc.</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>https://stewartsteel.ca/</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Weyburn-based steel fabricator whose own marketing describes it as specializing in 'Oilfield, Industrial and Agricultural Manufacturing' - oilfield is named first, similar to other companies in this project routed to Review rather than approved outright, but the company also has genuine agricultural/industrial manufacturing lines.</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Confirm what proportion of Stewart Steel's actual work is oilfield-specific versus industrial/agricultural manufacturing before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>https://stewartsteel.ca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Weyburn, SK</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Gibson Welding Ltd</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Found in a general search for Weyburn-area welding services, but no service description, sector information, or named contact could be confirmed before this session's web search budget was exhausted.</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Complete basic research (services offered, client sectors, named contact) once web search capacity is available again.</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
@@ -13713,7 +13793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A561"/>
+  <dimension ref="A1:A571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -17419,6 +17499,69 @@
       <c r="A561" s="9" t="inlineStr">
         <is>
           <t>Brent Gedak Welding Ltd. and TSB Oilfield Construction (both Estevan) were found but excluded outright, not routed to Review: both explicitly market themselves as oilfield-service companies, a clear-cut oil &amp; gas core-market case. Metular Fabricators Inc., initially listed under Estevan, was not added: one source placed it in Regina instead, and with only a phone number and no further detail available, the location conflict and thinness of evidence together made it unsafe to place confidently in either city. Fusion Industries (Estevan) was flagged for follow-up confirmation of its client mix, since it appears on at least one oilfield-specific business directory (Oilgaspages) despite its own marketing describing general welding/fabrication services rather than oilfield work specifically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="7" t="inlineStr">
+        <is>
+          <t>Batch 34: Weyburn, SK &amp; Melfort, SK (INCOMPLETE - web search budget exhausted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="9" t="inlineStr">
+        <is>
+          <t>This session's web search capacity was exhausted mid-batch (200 of 200 calls used), immediately after the first Weyburn/Melfort searches returned initial candidates but before any could be verified, cross-checked for location, or matched to a named contact. Both city sheets are left empty rather than populated with unverified or unconfirmed entries, consistent with this project's standing rule against guessing or including unverified information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="8" t="inlineStr">
+        <is>
+          <t>What was found before the limit was reached</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="9" t="inlineStr">
+        <is>
+          <t>Stewart Steel Inc. (Weyburn) - explicitly markets itself as an 'Oilfield, Industrial and Agricultural Manufacturing' fabricator, oilfield named first; routed to Low Confidence/Review pending confirmation of its actual client-sector mix, consistent with this project's treatment of similar oilfield-adjacent companies in batches 32-33.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="9" t="inlineStr">
+        <is>
+          <t>Gibson Welding Ltd (Weyburn) - identified only by name in a general search; no service description, sector information, or contact could be confirmed before the search budget ran out. Routed to Review as an incomplete lead rather than dropped entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="9" t="inlineStr">
+        <is>
+          <t>Melfort, SK - no candidates could be identified at all before the search budget ran out; a preliminary search returned only companies later confirmed to be based elsewhere (e.g. McCrea's Welding, whose forestry-fabrication page did not specify a Melfort location) or generic out-of-province results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="8" t="inlineStr">
+        <is>
+          <t>Recommended next step</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="9" t="inlineStr">
+        <is>
+          <t>Resume Weyburn and Melfort research once web search capacity is available again (either next session, or if the per-session search limit is raised), rather than treating this batch as complete.</t>
         </is>
       </c>
     </row>
@@ -30046,6 +30189,332 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -3160,7 +3160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4378,82 +4378,6 @@
           <t>https://wilfsoilfieldserviceltd.com/buildings-steel-framing-sk.php</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Weyburn, SK</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Saskatchewan</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>Stewart Steel Inc.</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>https://stewartsteel.ca/</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Weyburn-based steel fabricator whose own marketing describes it as specializing in 'Oilfield, Industrial and Agricultural Manufacturing' - oilfield is named first, similar to other companies in this project routed to Review rather than approved outright, but the company also has genuine agricultural/industrial manufacturing lines.</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>Confirm what proportion of Stewart Steel's actual work is oilfield-specific versus industrial/agricultural manufacturing before deciding whether this is a hard oil &amp; gas exclusion case.</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>https://stewartsteel.ca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Weyburn, SK</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Saskatchewan</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Gibson Welding Ltd</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Found in a general search for Weyburn-area welding services, but no service description, sector information, or named contact could be confirmed before this session's web search budget was exhausted.</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>Complete basic research (services offered, client sectors, named contact) once web search capacity is available again.</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
@@ -13793,7 +13717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A571"/>
+  <dimension ref="A1:A575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -17505,63 +17429,91 @@
     <row r="563">
       <c r="A563" s="7" t="inlineStr">
         <is>
-          <t>Batch 34: Weyburn, SK &amp; Melfort, SK (INCOMPLETE - web search budget exhausted)</t>
+          <t>Batch 34: Weyburn, SK &amp; Melfort, SK</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="8" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Top prospects (this batch, ranked)</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="9" t="inlineStr">
         <is>
-          <t>This session's web search capacity was exhausted mid-batch (200 of 200 calls used), immediately after the first Weyburn/Melfort searches returned initial candidates but before any could be verified, cross-checked for location, or matched to a named contact. Both city sheets are left empty rather than populated with unverified or unconfirmed entries, consistent with this project's standing rule against guessing or including unverified information.</t>
+          <t>1. Stewart Steel Inc. (Weyburn) - Score 6, Priority B - the clearest example found in this project of a company with genuinely separate, named sales contacts for its Agricultural, Industrial and Oilfield divisions, allowing outreach to be targeted specifically away from the oilfield side.</t>
         </is>
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="8" t="inlineStr">
-        <is>
-          <t>What was found before the limit was reached</t>
+      <c r="A566" s="9" t="inlineStr">
+        <is>
+          <t>2. Dobson Welding Ltd. (Melfort) - Score 3, Priority C - family-owned repair/fabrication shop, mainly agricultural-equipment-oriented.</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="9" t="inlineStr">
         <is>
-          <t>Stewart Steel Inc. (Weyburn) - explicitly markets itself as an 'Oilfield, Industrial and Agricultural Manufacturing' fabricator, oilfield named first; routed to Low Confidence/Review pending confirmation of its actual client-sector mix, consistent with this project's treatment of similar oilfield-adjacent companies in batches 32-33.</t>
+          <t>3. Pedersons Welding Services (Melfort) - Score 2, Priority C - thin, mobile-only welding service with no structural evidence.</t>
         </is>
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="9" t="inlineStr">
-        <is>
-          <t>Gibson Welding Ltd (Weyburn) - identified only by name in a general search; no service description, sector information, or contact could be confirmed before the search budget ran out. Routed to Review as an incomplete lead rather than dropped entirely.</t>
+      <c r="A568" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="9" t="inlineStr">
         <is>
-          <t>Melfort, SK - no candidates could be identified at all before the search budget ran out; a preliminary search returned only companies later confirmed to be based elsewhere (e.g. McCrea's Welding, whose forestry-fabrication page did not specify a Melfort location) or generic out-of-province results.</t>
+          <t>For Stewart Steel, route outreach through the Agricultural Sales contact (tstewart@stewartsteel.com) rather than the Industrial &amp; Oilfield one, and frame the pitch around agricultural/industrial manufacturing specifically.</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="8" t="inlineStr">
         <is>
-          <t>Recommended next step</t>
+          <t>Overflow / FEA / heavy lift opportunities</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="9" t="inlineStr">
         <is>
-          <t>Resume Weyburn and Melfort research once web search capacity is available again (either next session, or if the per-session search limit is raised), rather than treating this batch as complete.</t>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Stewart Steel (Weyburn). Dobson Welding and Pedersons Welding Services (Melfort) as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="9" t="inlineStr">
+        <is>
+          <t>Gibson Welding Ltd. (Weyburn), initially logged to Review as an incomplete lead when this session's earlier web search budget ran out, was fully researched once search capacity reset: it is confirmed to be an oilfield trucking, construction and equipment-rental company (BBB category 'Oilfield Service,' serving oilfield clients across Southeast Saskatchewan and Manitoba) with no separate non-oilfield division - a clear-cut oil &amp; gas core-market exclusion, not a borderline case, so it was removed from Review rather than added anywhere. This batch supersedes an earlier incomplete version of itself: an initial pass at Weyburn/Melfort research was cut short mid-batch by an exhausted web search budget, leaving both city sheets empty and Stewart Steel/Gibson Welding logged to Review as incomplete leads; once search capacity reset, this batch's full research replaced that placeholder version.</t>
         </is>
       </c>
     </row>
@@ -30195,7 +30147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="3" min="1" max="1"/>
@@ -30346,6 +30298,122 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Weyburn, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Stewart Steel Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://stewartsteel.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/stewartsteelmfg</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Custom Fabrication, Manufacturing &amp; Repair</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom fabrication, manufacturing and repair, organized into distinct Oilfield, Industrial and Agricultural divisions, each with its own named sales contact</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established (founded as a machine shop in 1984, expanded into fabrication in 1994) Weyburn manufacturer with genuinely separate, named divisions for Agricultural, Industrial and Oilfield sales - the clearest example found in this project of a company structured with distinguishable non-oil-and-gas business lines, allowing outreach to be targeted specifically at its agricultural/industrial divisions.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (stewartsteel.ca) and a Canadian Metalworking business profile describe the company's history and its Oilfield, Industrial and Agricultural manufacturing divisions.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Brad Stewart</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President &amp; Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://stewartsteel.ca/contact/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>tstewart@stewartsteel.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Direct email for the company's Agricultural Sales contact, sourced from the company's own contact page; a separate Industrial &amp; Oilfield sales contact (jstewart@stewartsteel.com) also exists but was deliberately not used as the primary contact given this project's oil &amp; gas framing.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://stewartsteel.ca/contact/ ; https://www.canadianmetalworking.com/canadianfabricatingandwelding/article/fabricating/business-profile-stewart-steel-inc</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach specifically through the Agricultural/Industrial sales contact rather than the Oilfield one, and frame outreach around the company's agricultural and industrial manufacturing work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>The company markets itself with 'Oilfield' listed first among its three divisions, but unlike several other companies in this project, it maintains clearly separate, individually-staffed sales contacts for each division - a distinguishing factor in treating this as includable rather than excluded or Review-only.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30358,7 +30426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="3" min="1" max="1"/>
@@ -30508,6 +30576,194 @@
           <t>Research Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Melfort, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Dobson Welding Ltd. (Dobson Arc Welding)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Machining &amp; Repair</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Welding and machining, combine concave rebuilding, fabrication and repair</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Family-owned Melfort repair and fabrication shop - a modest general fit, oriented mainly toward agricultural-equipment repair (combine concave rebuilding) rather than heavy-industrial or structural work.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (BBB, Yellow Pages, Mysask411) describe welding, machining, combine concave rebuilding, fabrication and repair services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Bill Jung</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone/address confirmed (306-752-4313, 299 Central St W).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bbb.org/ca/sk/melfort/profile/welding/dobson-welding-ltd-0057-24768</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm scope of non-agricultural structural work before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Also listed under the names 'Dobson Arc Welding Ltd.' and 'Dobsons Arc Welding' in different directories - same company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Melfort, SK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Pedersons Welding Services</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Welding</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Mobile welding service with a fully equipped truck and 24/7 emergency on-call service, serving central to northern Saskatchewan</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Mobile welding/repair service - a thin general fit given the lack of any structural, marine, or heavy-industrial-specific evidence found; included mainly for completeness as a documented local welding contact.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings describe a mobile welding truck service with 24/7 emergency call-out for central/northern Saskatchewan.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email or named contact found in this pass.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.canpages.ca/business/SK/melfort/welding-shops/5884-931000.html</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lowest-priority follow-up; confirm any structural/industrial (versus emergency mobile-repair) scope before outreach.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:X1"/>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -74,6 +74,8 @@
     <sheet name="Estevan, SK" sheetId="69" state="visible" r:id="rId69"/>
     <sheet name="Weyburn, SK" sheetId="70" state="visible" r:id="rId70"/>
     <sheet name="Melfort, SK" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="Humboldt, SK" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="Kindersley, SK" sheetId="73" state="visible" r:id="rId73"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -145,6 +147,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="68" hidden="1">'Estevan, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="69" hidden="1">'Weyburn, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'Melfort, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'Humboldt, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'Kindersley, SK'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13717,7 +13721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A575"/>
+  <dimension ref="A1:A589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -17514,6 +17518,97 @@
       <c r="A575" s="9" t="inlineStr">
         <is>
           <t>Gibson Welding Ltd. (Weyburn), initially logged to Review as an incomplete lead when this session's earlier web search budget ran out, was fully researched once search capacity reset: it is confirmed to be an oilfield trucking, construction and equipment-rental company (BBB category 'Oilfield Service,' serving oilfield clients across Southeast Saskatchewan and Manitoba) with no separate non-oilfield division - a clear-cut oil &amp; gas core-market exclusion, not a borderline case, so it was removed from Review rather than added anywhere. This batch supersedes an earlier incomplete version of itself: an initial pass at Weyburn/Melfort research was cut short mid-batch by an exhausted web search budget, leaving both city sheets empty and Stewart Steel/Gibson Welding logged to Review as incomplete leads; once search capacity reset, this batch's full research replaced that placeholder version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="7" t="inlineStr">
+        <is>
+          <t>Batch 35: Humboldt, SK &amp; Kindersley, SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="9" t="inlineStr">
+        <is>
+          <t>1. Hill Acme Machine Ltd. (Kindersley) - Score 5, Priority B - 40+ year machine shop with a genuinely diversified client base (custom builds, oilfield rig-ups, farm equipment).</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="9" t="inlineStr">
+        <is>
+          <t>2. Hi-Tech Welding Machining &amp; Fabrication (Humboldt) - Score 4, Priority C - moderately sized machine shop with limited available sector detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="9" t="inlineStr">
+        <is>
+          <t>3. R S Welding &amp; Radiator Repair Ltd. (Humboldt) - Score 2, Priority C - primarily automotive-repair-focused, weak structural fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="9" t="inlineStr">
+        <is>
+          <t>For Hill Acme Machine, lead with custom fabrication and farm-equipment work, given oilfield rig-up work is only one of several named service lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Hill Acme Machine (Kindersley). Hi-Tech Welding Machining &amp; Fabrication and R S Welding &amp; Radiator Repair (Humboldt) as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="9" t="inlineStr">
+        <is>
+          <t>Amex Industries, initially surfaced under a Humboldt-area search, was not added: available sources describe it as serving 'Dundurn, Saskatoon, and surrounding areas' without confirming a Humboldt base, so it was left out rather than risk misattributing its city. This was a thinner batch overall - both towns are smaller agricultural service centers with correspondingly modest industrial fabrication sectors compared to the larger potash-region cities (Saskatoon, batch 30).</t>
         </is>
       </c>
     </row>
@@ -30771,6 +30866,624 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Humboldt, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Hi-Tech Welding Machining &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Machining, Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CNC machining and welding/fabrication shop</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established local Humboldt machine shop with a reported ~$1.27M annual revenue - a moderately sized general industrial fit, though no specific client-sector or structural-engineering-overflow evidence was found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (Canpages, 411.ca, Mysask411) describe CNC machining and welding/fabrication services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone/address confirmed (306-682-5832, 10562 8 Ave).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://mysask411.com/humboldt/hi-tech-welding-machining-fabricating/1057844</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm client-sector mix and any structural-engineering-adjacent work before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Humboldt, SK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>R S Welding &amp; Radiator Repair Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Welding &amp; Radiator Repair</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Radiator repair, mobile welding, fabricating and machining services</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Locally based Humboldt shop, but its core business (radiator repair) is automotive-equipment-repair-oriented rather than structural or heavy-industrial fabrication - a weak fit, included mainly for completeness as a documented local contact.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; the company's primary focus (radiator repair) is not structural/engineering-adjacent.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (Mysask411) describe radiator repair, mobile welding, fabricating and machining services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email or named contact found in this pass.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://mysask411.com/humboldt/welding/r-s-welding-radiator-repair-ltd/504896</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lowest-priority follow-up given its primary automotive-repair focus; confirm any structural/fabrication scope before outreach.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Kindersley, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Hill Acme Machine Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hillacme.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hillacme/</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Machining &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Full-service machining and welding shop with a full parts department, offering custom builds, oilfield truck rig-ups, and farm equipment repairs/modifications</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (40+ years) Kindersley machine shop with a genuinely diversified client base (custom fabrication, farm equipment, oilfield trucking) - a solid general industrial fit, though oilfield rig-up work is one of several named service lines.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (hillacme.ca) describes machining, welding, custom builds, oilfield truck rig-ups and farm equipment repair/modification services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>David R. Hill Jr.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hillacme.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>administrator@hillacme.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); a Manager-level contact (jordin@hillacme.ca) and a Parts contact (parts@hillacme.ca) are also available.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hillacme.ca/ ; https://www.kindersley.ca/business-directory/hill-acme-machine/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its custom fabrication and farm-equipment work, given oilfield rig-up work is only one of several named service lines.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Oilfield truck rig-ups are named as one of several services (alongside custom builds and farm equipment repair), not the company's sole/core market.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -76,6 +76,8 @@
     <sheet name="Melfort, SK" sheetId="71" state="visible" r:id="rId71"/>
     <sheet name="Humboldt, SK" sheetId="72" state="visible" r:id="rId72"/>
     <sheet name="Kindersley, SK" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="La Ronge, SK" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="Meadow Lake, SK" sheetId="75" state="visible" r:id="rId75"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -149,6 +151,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="70" hidden="1">'Melfort, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="71" hidden="1">'Humboldt, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'Kindersley, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'La Ronge, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'Meadow Lake, SK'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13721,7 +13725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A589"/>
+  <dimension ref="A1:A604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -17609,6 +17613,104 @@
       <c r="A589" s="9" t="inlineStr">
         <is>
           <t>Amex Industries, initially surfaced under a Humboldt-area search, was not added: available sources describe it as serving 'Dundurn, Saskatoon, and surrounding areas' without confirming a Humboldt base, so it was left out rather than risk misattributing its city. This was a thinner batch overall - both towns are smaller agricultural service centers with correspondingly modest industrial fabrication sectors compared to the larger potash-region cities (Saskatoon, batch 30).</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="7" t="inlineStr">
+        <is>
+          <t>Batch 36: La Ronge, SK &amp; Meadow Lake, SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="9" t="inlineStr">
+        <is>
+          <t>1. RobWel Constructors Limited Partnership (Meadow Lake) - Score 6, Priority B - Indigenous-owned (Clearwater River Dene Nation) structural steel fabricator with genuine potash-mining industry connections and COR safety certification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="9" t="inlineStr">
+        <is>
+          <t>2. Meadow Lake Welding &amp; Machine Ltd. (Meadow Lake) - Score 3, Priority C - general local welding/machine shop with limited available detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="8" t="inlineStr">
+        <is>
+          <t>Why La Ronge was empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="9" t="inlineStr">
+        <is>
+          <t>La Ronge is a small, remote northern Saskatchewan town; multiple targeted searches (general fabrication, mining-sector-specific, and a direct city-name search) returned no locally-based welding, machining, or fabrication company - only larger regional shops based in Saskatoon, Prince Albert, and Meadow Lake that serve the broader north but are not La Ronge-based themselves. Consistent with this project's treatment of other very small/remote towns (e.g. Fort Nelson, BC, batch 24), the sheet is left empty rather than populated with an out-of-town company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="9" t="inlineStr">
+        <is>
+          <t>For RobWel Constructors, lead with its mining-sector site-installation work, which often pairs structural design/verification with construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: RobWel Constructors (Meadow Lake). Meadow Lake Welding &amp; Machine as a lower-priority follow-up. No La Ronge prospects to prioritize this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="9" t="inlineStr">
+        <is>
+          <t>No location mismatches, defense exclusions, or oil &amp; gas exclusions arose this batch.</t>
         </is>
       </c>
     </row>
@@ -31484,6 +31586,516 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Meadow Lake, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>RobWel Constructors Limited Partnership</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.robwel.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company (Indigenous-owned)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication &amp; Site Installation</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Steel fabrication and welding for the industrial, commercial and institutional (ICI) market, plus pressure welding and COR-certified site installation for mining and industrial projects</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Indigenous-owned (Clearwater River Dene Nation Group of Companies) northwest Saskatchewan fabricator with genuine potash-mining industry connections (listed in a potash-mining business directory) and COR safety certification - a solid heavy-industrial structural fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from its site-installation work for mining and industrial projects, which often involves structural design/verification alongside construction.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (robwel.ca) and a potash-mining industry directory listing (potashworks.com) describe structural steel fabrication, welding and COR-certified site installation for mining and industrial clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.robwel.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; company has a 'Talk To Us' contact page but no direct email address was displayed in search results. Only phone confirmed (306-236-3099).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.robwel.ca/talk-to-us/ ; https://saskchamber.com/initiatives/indigenous-business-directory/profile/robwel-constructors/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its mining and industrial site-installation work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Meadow Lake, SK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Meadow Lake Welding &amp; Machine Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Machining</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>General welding and machine shop services</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Locally based Meadow Lake welding/machine shop - a modest general industrial fit with no specific sector or structural-engineering-overflow evidence found.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (Mysask411, Yellow Pages) describe general welding shop services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone/address confirmed (PG Hwy 4, Meadow Lake).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://mysask411.com/meadow-lake/welding/meadow-lake-welding-machine-ltd/358859</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm client-sector mix before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -78,6 +78,8 @@
     <sheet name="Kindersley, SK" sheetId="73" state="visible" r:id="rId73"/>
     <sheet name="La Ronge, SK" sheetId="74" state="visible" r:id="rId74"/>
     <sheet name="Meadow Lake, SK" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="Nipawin, SK" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="Martensville, SK" sheetId="77" state="visible" r:id="rId77"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -153,6 +155,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="72" hidden="1">'Kindersley, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="73" hidden="1">'La Ronge, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'Meadow Lake, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'Nipawin, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'Martensville, SK'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13725,7 +13729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A604"/>
+  <dimension ref="A1:A619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -17711,6 +17715,104 @@
       <c r="A604" s="9" t="inlineStr">
         <is>
           <t>No location mismatches, defense exclusions, or oil &amp; gas exclusions arose this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="7" t="inlineStr">
+        <is>
+          <t>Batch 37: Nipawin, SK &amp; Martensville, SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="9" t="inlineStr">
+        <is>
+          <t>1. LeCuyer Welding &amp; Machine Ltd. (Nipawin) - Score 6, Priority B - a fully equipped shop that notably lists 'marine' among its served sectors alongside agricultural, industrial, construction, forestry and mining work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="9" t="inlineStr">
+        <is>
+          <t>2. Automated Metal Processing Ltd. (Martensville) - Score 5, Priority B - a laser-cutting/metal-bending process specialist serving major manufacturers across Alberta, Saskatchewan and the northern US.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="8" t="inlineStr">
+        <is>
+          <t>Milestone: last Saskatchewan city on the master list</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="9" t="inlineStr">
+        <is>
+          <t>Martensville completes this project's coverage of all Saskatchewan cities/towns on the master list (batches 29-37, Prince Albert through Martensville). The next city on the list moves to a new region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="9" t="inlineStr">
+        <is>
+          <t>For LeCuyer Welding &amp; Machine, the explicit marine-sector mention is worth investigating directly - confirm what kind of marine work an inland Saskatchewan shop actually performs (river/lake infrastructure vs. boat/trailer repair) before treating it as a strong marine-relevant lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: LeCuyer Welding &amp; Machine (Nipawin) and Automated Metal Processing (Martensville).</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="9" t="inlineStr">
+        <is>
+          <t>While researching Martensville, IWL Steel Fabricators (already recorded under Saskatoon, batch 30) was discovered to also operate a 12,000 sq ft Martensville facility, and to have been purchased by the Clearwater River Dene First Nation, making it 100% First Nations-owned - a material ownership change not reflected in the original batch 30 entry. Rather than duplicate the company under Martensville, a research note was added to its existing Saskatoon row flagging this update for verification before outreach.</t>
         </is>
       </c>
     </row>
@@ -27124,7 +27226,7 @@
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Oil &amp; gas is named as one of three served sectors (industrial, mining, oilfield); potash-industry fabrication is described as the company's primary specialty, so this is not treated as a hard oil &amp; gas exclusion case.</t>
+          <t>Oil &amp; gas is named as one of three served sectors (industrial, mining, oilfield); potash-industry fabrication is described as the company's primary specialty, so this is not treated as a hard oil &amp; gas exclusion case. | Update (found during Martensville research, batch 37): IWL Steel Fabricators also operates a second facility in Martensville, SK (12,000 sq ft), and was purchased by the Clearwater River Dene First Nation, making it 100% First Nations-owned - this ownership change was not reflected in the original batch 30 research and should be verified before outreach (Patrick Kuprowski's current title/role was not reconfirmed against this ownership change).</t>
         </is>
       </c>
     </row>
@@ -32096,6 +32198,548 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Nipawin, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>LeCuyer Welding &amp; Machine Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lecuyerweldingmachine.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Machining &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom fabrication, hydraulic cylinder repair, machine work, sheet metal, plate rolling, shearing/forming, boom truck and crane services, mobile welding, serving agricultural, industrial, construction, forestry, marine and mining sectors</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Notably, this fully equipped Nipawin shop explicitly lists 'marine' among its served sectors, alongside a genuinely diversified industrial base - one of the few interior-Saskatchewan fabricators found in this project with a directly stated marine connection, worth confirming further.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the breadth of services (plate rolling, hydraulic cylinder repair, crane services) and the explicit marine-sector mention.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (lecuyerweldingmachine.com) and directory listings describe fabrication, machining and crane services for agricultural, industrial, construction, forestry, marine and mining clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Kevin LeCuyer &amp; Trevor LeCuyer</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Co-Owners</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lecuyerweldingmachine.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone/fax confirmed (306-862-4003 / 306-862-4038).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lecuyerweldingmachine.com/ ; https://www.bbb.org/ca/sk/nipawin/profile/welding/lecuyer-welding-machine-ltd-0057-29862</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch, and specifically ask about the nature of its marine-sector work given this is an unusual and specific claim for an inland Saskatchewan shop.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Confirm what 'marine' work actually means for this landlocked-Saskatchewan company (e.g. river infrastructure, lake docks, or simply boat/trailer repair) before treating the marine angle as a strong lead.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Martensville, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Automated Metal Processing Ltd. (AMP)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ampmetal.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Laser Cutting &amp; Metal Processing</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Laser cutting and metal bending services for major manufacturers across Alberta, Saskatchewan and the northern United States</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Well-established metal-processing specialist just north of Saskatoon serving major manufacturers across a wide region - a genuine industrial-supplier fit, though as a laser-cutting/bending process shop rather than a full-service structural fabricator, it is a supporting rather than a primary structural-engineering-client fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; the company's core business (laser cutting/bending as a process service to other manufacturers) is a step removed from structural design work itself.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (ampmetal.com) describes laser cutting and metal bending services to manufacturers across Alberta, Saskatchewan and the northern US.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Adam Carpenter</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ampmetal.com/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@ampmetal.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); named leadership also includes Tim Robinson (VP) and Ryan Holt (COO).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ampmetal.com/contact-us ; https://www.bbb.org/saskatchewan/business-reviews/steel-fabrication/automated-metal-processing-ltd-in-martensville-sk-20276</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a potential fabrication-capacity partner (process subcontracting) rather than a direct structural-engineering client, given its role as a laser-cutting/bending service to other manufacturers.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -80,6 +80,7 @@
     <sheet name="Meadow Lake, SK" sheetId="75" state="visible" r:id="rId75"/>
     <sheet name="Nipawin, SK" sheetId="76" state="visible" r:id="rId76"/>
     <sheet name="Martensville, SK" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet name="Warman, SK" sheetId="78" state="visible" r:id="rId78"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -157,6 +158,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="74" hidden="1">'Meadow Lake, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'Nipawin, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'Martensville, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'Warman, SK'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13729,7 +13731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A619"/>
+  <dimension ref="A1:A629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -17813,6 +17815,69 @@
       <c r="A619" s="9" t="inlineStr">
         <is>
           <t>While researching Martensville, IWL Steel Fabricators (already recorded under Saskatoon, batch 30) was discovered to also operate a 12,000 sq ft Martensville facility, and to have been purchased by the Clearwater River Dene First Nation, making it 100% First Nations-owned - a material ownership change not reflected in the original batch 30 entry. Rather than duplicate the company under Martensville, a research note was added to its existing Saskatoon row flagging this update for verification before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="7" t="inlineStr">
+        <is>
+          <t>Batch 38: Warman, SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="8" t="inlineStr">
+        <is>
+          <t>Milestone: true last Saskatchewan city on the master list</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="9" t="inlineStr">
+        <is>
+          <t>Warman was found one row after Martensville on the master city list (row 76, immediately before Alberta begins with Calgary) and had been missed when batch 37 was described as completing Saskatchewan - corrected here. Warman genuinely completes this project's Saskatchewan coverage (batches 29-38).</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="9" t="inlineStr">
+        <is>
+          <t>1. Pro Steel Fabrication - Score 3, Priority C - the only general steel fabricator confirmed based in this fast-growing Saskatoon-area bedroom community; very limited service/sector detail available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="9" t="inlineStr">
+        <is>
+          <t>'Warmans Welding Ltd', which surfaced in an initial search under the Warman, SK name, was confirmed to be a completely different, unrelated company (Warman's Welding Ltd., owned by Miranda Warman) based in Rexton, New Brunswick - a naming coincidence, not a genuine Warman, SK lead, and was discarded entirely rather than treated as a location mismatch. Warman Metals, an 18,000 sq ft metal roofing/wall panel manufacturer genuinely based in Warman, SK since 1994, was reviewed but not added: it is a building-products manufacturer (Tuff Rib roofing/wall panels) rather than a structural/heavy-industrial fabricator, consistent with this project's recurring exclusion of steel building-product suppliers (e.g. SpanMaster and Kalex Steel Buildings, noted but excluded in batch 23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="8" t="inlineStr">
+        <is>
+          <t>Next on the master list</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="9" t="inlineStr">
+        <is>
+          <t>Calgary, AB - the master list moves into Alberta after Warman.</t>
         </is>
       </c>
     </row>
@@ -32740,6 +32805,265 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Warman, SK</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Pro Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.prosteelfabrication.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Steel fabrication services</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>The one general steel fabricator confirmed to be based in Warman itself (a fast-growing Saskatoon-area bedroom community); no further service description, sector information, or named contact could be confirmed in this pass.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (prosteelfabrication.ca) and directory listings confirm the company's existence and location but provide limited service detail.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.prosteelfabrication.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (306-931-6789).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.prosteelfabrication.ca/contact ; https://www.yellowpages.ca/bus/Saskatchewan/Warman/Pro-Steel-Fabrication/101036326.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up pending confirmation of services and client sectors.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -81,6 +81,7 @@
     <sheet name="Nipawin, SK" sheetId="76" state="visible" r:id="rId76"/>
     <sheet name="Martensville, SK" sheetId="77" state="visible" r:id="rId77"/>
     <sheet name="Warman, SK" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="Calgary, AB" sheetId="79" state="visible" r:id="rId79"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -159,6 +160,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="75" hidden="1">'Nipawin, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'Martensville, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'Warman, SK'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'Calgary, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3174,7 +3176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4390,6 +4392,90 @@
       <c r="H29" s="10" t="inlineStr">
         <is>
           <t>https://wilfsoilfieldserviceltd.com/buildings-steel-framing-sk.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Calgary, AB</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Furlong Steel Industries Inc.</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>https://www.furlongsteel.ca/</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Founded 2006, structural steel and pressure pipe fabrication with industrial coating and package assembly capability - but the company's own marketing describes being 'particularly involved in the SAGD and gas processing sectors' (SAGD is an oil sands extraction technology) with a clientele of 'energy companies, EPCs, engineering firms, industrial project developers' - a strong oil &amp; gas/oil sands signal, though renewable energy and agriculture are also mentioned as served sectors.</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Confirm what proportion of Furlong Steel's actual work is SAGD/oil-sands/gas-processing-specific versus renewable energy and agriculture before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>https://www.furlongsteel.ca/ ; https://www.bbb.org/ca/ab/calgary/profile/steel-fabrication/furlong-steel-industries-inc-0017-112776</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Calgary, AB</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Waiward Industrial</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>https://www.waiward.com/</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Integrated structural steel fabrication, modular assembly, industrial construction and maintenance for complex energy, mining, infrastructure and industrial projects (winner of an IMPACT Project of the Year award for a Saskatchewan potash mine project) - but this is a large-scale, full EPC-style contractor operating across Western Canada, similar in scale to other large contractors excluded elsewhere in this project (e.g. the LNG Canada EPC ecosystem in Kitimat, batch 21) as unlikely to seek outside structural/FEA support from a small consultancy.</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether Waiward's scale genuinely rules out AH Structures-style outside support, or whether a specific business unit/project team could be a viable smaller-scale entry point.</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>https://www.waiward.com/</t>
         </is>
       </c>
     </row>
@@ -13731,7 +13817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A629"/>
+  <dimension ref="A1:A645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -17878,6 +17964,111 @@
       <c r="A629" s="9" t="inlineStr">
         <is>
           <t>Calgary, AB - the master list moves into Alberta after Warman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="7" t="inlineStr">
+        <is>
+          <t>Batch 39: Calgary, AB (first Alberta city - researched solo given the city's size)</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="9" t="inlineStr">
+        <is>
+          <t>1. Motion Steel Ltd. (Cyntech Group) - Score 6, Priority B - established structural/miscellaneous steel fabricator with no explicit oil &amp; gas-core positioning, unusual for Calgary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="9" t="inlineStr">
+        <is>
+          <t>2. Bow Ridge Steel Fabrication - Score 6, Priority B - 45+ year fabricator with in-house engineering and design capability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="9" t="inlineStr">
+        <is>
+          <t>3. Donald Rigging Ltd. (Omega Morgan Group) - Score 6, Priority B - 27+ year heavy-lift/rigging company with a genuinely diversified multi-sector client base and a directly confirmed named contact (Angus Donald).</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="8" t="inlineStr">
+        <is>
+          <t>Calgary's oil &amp; gas-dominated economy required careful screening</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="9" t="inlineStr">
+        <is>
+          <t>As Canada's energy-industry capital, Calgary's fabrication sector skews heavily toward oil &amp; gas/oil sands services; two otherwise well-established companies were routed to Review rather than approved outright: Furlong Steel Industries, whose own marketing names SAGD (oil sands) and gas processing as primary specialties, and Waiward Industrial, a large-scale EPC-style contractor likely too big to seek outside structural/FEA support, similar to the LNG Canada EPC ecosystem excluded in Kitimat (batch 21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="9" t="inlineStr">
+        <is>
+          <t>For Bow Ridge Steel Fabrication, lead with its in-house engineering/design capability - the clearest structural-engineering-adjacent signal found this batch. For Donald Rigging, frame outreach around its non-oil-and-gas sectors (mining, utilities, chemical, power) given oil &amp; gas is also a named client sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="9" t="inlineStr">
+        <is>
+          <t>Bow Ridge's in-house engineering/design work and Donald Rigging's heavy-lift/rigging capability are the two clearest overflow-adjacent signals found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Motion Steel, Bow Ridge Steel Fabrication, and Donald Rigging (all Calgary).</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="9" t="inlineStr">
+        <is>
+          <t>Given Calgary's scale, this batch covers only a first pass at general structural/heavy-lift fabricators; a follow-up pass focused specifically on naval-architecture-adjacent, structural engineering consultancies, or other AH Structures-specific niches (similar to the Innovex Engineering find in Kamloops, batch 25) may surface additional prospects in a future batch given the city's size.</t>
         </is>
       </c>
     </row>
@@ -33064,6 +33255,489 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Calgary, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Motion Steel Ltd. (Cyntech Group)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.motionsteel.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company (part of Cyntech Group)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural &amp; Miscellaneous Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel and miscellaneous steel fabrication</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established Calgary structural/miscellaneous steel fabricator operating as part of the Cyntech Group - a general heavy-industrial structural fit with no explicit oil &amp; gas-core positioning found, unusual for a Calgary-based fabricator.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (motionsteel.com) and directory/business listings describe structural and miscellaneous steel fabrication services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.motionsteel.com/en/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@cyntechgroup.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General parent-group inbox (not verified as an individual's address); sources give conflicting names for the company's President (Gerry Leudy vs. a more recently listed Randy Robertson) - neither used as a confirmed Decision Maker Name pending verification.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.motionsteel.com/en/contact-us ; https://www.dnb.com/business-directory/company-profiles.motion_steel_ltd.5079de01ded82c5211c3f7ebeb516b75.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its general structural/miscellaneous steel fabrication work; confirm current leadership before outreach given the conflicting President names found.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Calgary, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Bow Ridge Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bowridgefab.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Custom &amp; Specialty Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Welding, manufacturing, construction, engineering and design - custom and specialty steel fabrication since 1976</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1976) Calgary fabricator with an in-house engineering and design capability alongside fabrication - a genuine structural-engineering-adjacent fit, similar to other design-capable fabricators recorded elsewhere in this project.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>In-house engineering/design capability suggests some structural design work already happens internally, which could extend to overflow FEA collaboration on larger or more complex projects.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (bowridgefab.ca) describes welding, manufacturing, construction, engineering and design services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Brian Smit</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bowridgefab.ca/contact/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a source claimed an email-naming-pattern ('first.last@bowridgefab.ca') but this was not used, per this project's no-guessing/no-pattern-inference policy. Only phone confirmed (403-230-3705).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bowridgefab.ca/contact/ ; https://rocketreach.co/bow-ridge-steel-fabrication-email-format_b46a752cfc5c8867</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its in-house engineering/design and specialty fabrication capability.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Ed Smit is also listed as Vice President; company also does business/was historically listed as 'Bow Ridge Trailer Manufacturing Ltd.' at the same address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Calgary, AB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Donald Rigging Ltd. (Omega Morgan Group)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://donaldrigging.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company (part of Omega Morgan Group)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Lift / Rigging &amp; Machinery Moving</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Rigging, super-load transport, machinery moving and millwright services, serving energy, chemical, utilities, mining, oil &amp; gas, health and power industries</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Established (27+ years) Calgary heavy-lift/rigging company, now part of the Omega Morgan Group, with a genuinely diversified multi-sector client base - a solid overflow-heavy-lift-engineering fit, similar to Sterling Crane and Eagle Crane recorded in earlier batches, with a directly confirmed named contact.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the range of heavy-lift/rigging/millwright services and diversified client base.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (donaldrigging.com) describes rigging, super-load transport, machinery moving and millwright services across multiple industries.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Angus Donald</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Contact / Principal (title not fully confirmed)</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://donaldrigging.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>Angus.donald@donaldrigging.com</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Direct, unmasked email for a named individual, sourced from the company's own materials - a genuinely confirmed contact.</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://donaldrigging.com/contact-us/ ; https://www.zoominfo.com/c/donald-rigging-ltd/347612978</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a potential engineering-support partner for heavy-lift and rigging project planning, framing around its non-oil-and-gas sectors (mining, utilities, chemical, power) given oil &amp; gas is also a named client sector.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>Oil &amp; gas is named as one of several served sectors (alongside energy, chemical, utilities, mining, health and power), not the company's sole/core market; the company was acquired by the Omega Morgan Group of Companies.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -82,6 +82,7 @@
     <sheet name="Martensville, SK" sheetId="77" state="visible" r:id="rId77"/>
     <sheet name="Warman, SK" sheetId="78" state="visible" r:id="rId78"/>
     <sheet name="Calgary, AB" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet name="Edmonton, AB" sheetId="80" state="visible" r:id="rId80"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -161,6 +162,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="76" hidden="1">'Martensville, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'Warman, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'Calgary, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="79" hidden="1">'Edmonton, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13817,7 +13819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A645"/>
+  <dimension ref="A1:A659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -18069,6 +18071,97 @@
       <c r="A645" s="9" t="inlineStr">
         <is>
           <t>Given Calgary's scale, this batch covers only a first pass at general structural/heavy-lift fabricators; a follow-up pass focused specifically on naval-architecture-adjacent, structural engineering consultancies, or other AH Structures-specific niches (similar to the Innovex Engineering find in Kamloops, batch 25) may surface additional prospects in a future batch given the city's size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="7" t="inlineStr">
+        <is>
+          <t>Batch 40: Edmonton, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="9" t="inlineStr">
+        <is>
+          <t>1. Collins Steel (Collins Industries Ltd.) - Score 6, Priority B - 40+ year Edmonton structural steel fabricator, no oil &amp; gas-core positioning found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="9" t="inlineStr">
+        <is>
+          <t>2. L.A. Brayer Industries Ltd. - Score 6, Priority B - broad structural/plate/HVAC fabricator for industrial and institutional clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="9" t="inlineStr">
+        <is>
+          <t>3. Vulcan Machineworks Inc. - Score 4, Priority C - ISO-certified precision machining shop with a genuinely confirmed named contact (Keith Rowe).</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="9" t="inlineStr">
+        <is>
+          <t>Both Collins Steel and L.A. Brayer Industries can be approached directly with a standard structural/FEA overflow pitch - neither shows oil &amp; gas-core positioning, a useful contrast to several Calgary companies in the previous batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Collins Steel and L.A. Brayer Industries. Vulcan Machineworks as a lower-priority process-capacity contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="9" t="inlineStr">
+        <is>
+          <t>Two strong candidates found during Edmonton research were deliberately held back rather than added here, since they are based in other cities already on this project's master city list: Terrick Enterprises Ltd. (32+ year structural steel fabricator) is actually based in Sherwood Park, AB, and CJM Crane Services (heavy-lift/crane rental, 26-770 ton capacity) is actually based in Nisku, AB - both appear later in the master list and will be properly researched under their correct city entries rather than folded into Edmonton. A larger, similarly-named 'Vulcan Metals Corporation' (200-499 employees, $100-250M revenue) that surfaced in an initial broad search was confirmed to be based in Kansas City, Missouri, USA, not Edmonton, and was discarded entirely as an out-of-country false match rather than added anywhere.</t>
         </is>
       </c>
     </row>
@@ -34129,6 +34222,501 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Edmonton, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Collins Steel (Collins Industries Ltd.)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.collinssteel.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/collins-industries-ltd.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel fabrication and installation for commercial, industrial and institutional markets</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established (since 1984) Edmonton structural steel fabricator with a stable multi-decade ownership history (founder's sons purchased the company in 2012) and no oil &amp; gas-core positioning found - a clean general heavy-industrial structural fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (collinssteel.com) and an Edmonton Construction Association member listing describe structural steel fabrication for commercial, industrial and institutional clients since 1984.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Rob Wright</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.collinssteel.com/contact/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@collinssteel.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); Rob Wright's personal email is displayed only as an anti-scraping placeholder in search results and was not used.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.collinssteel.com/contact/ ; https://incitestrategy.ca/insights/case-study/advisor-to-collins-steel-on-their-ownership-transition/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its commercial/industrial/institutional structural steel work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>A business-advisory case study references a further ownership transition at the company beyond the 2012 sale to founder Paul Collins' sons; current ownership should be reconfirmed before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Edmonton, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>L.A. Brayer Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.labrayer.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel, Plate &amp; HVAC Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing, fabrication and installation of structural steel for industrial, institutional and large commercial construction, plus plate and HVAC fabrication</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established Edmonton fabricator with a broad structural/plate/HVAC fabrication capability for industrial and institutional clients - a solid general heavy-industrial structural fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (labrayer.com) describes structural steel, plate and HVAC fabrication for industrial, institutional and large commercial construction.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Dean Brayer</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.labrayer.com/about-la-brayer/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a directory source displayed only a masked address (d***@labrayer.com), which was not used per this project's no-guessing policy on masked addresses. Only phone confirmed (780-462-4812).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.labrayer.com/contact-us/ ; https://www.zoominfo.com/p/Dean-Brayer/205555906</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its industrial/institutional structural steel and plate fabrication work.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Edmonton, AB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Vulcan Machineworks Inc.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://vulcanmachineworks.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Precision Machining</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>ISO 9001:2015-registered precision metal machining, welding and fabricating services</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>ISO-certified Edmonton precision machining shop with no oil &amp; gas-core positioning found - a modest general industrial fit, more machining-focused than structural-design-adjacent.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; the company's core business (precision machining) is a step removed from structural design work itself.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (vulcanmachineworks.com) describes ISO 9001:2015-registered precision machining, welding and fabricating services.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Keith Rowe</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Contact (title not fully confirmed)</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://vulcanmachineworks.com/contact</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>Keith.Rowe@vulcanmachineworks.com</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Direct, unmasked email for a named individual, sourced from the company's own contact page - a genuinely confirmed contact, though his exact title/role was not confirmed.</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://vulcanmachineworks.com/contact ; https://www.dnb.com/business-directory/company-profiles.vulcan_machineworks_inc.34a7ef99460e552750491f5a005f7a7c.html</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a potential machining-capacity partner rather than a primary structural-engineering client, given its process-shop (machining) rather than design/fabrication focus.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>A larger, similarly-named company ('Vulcan Metals Corporation,' reporting 200-499 employees and $100-250M revenue) initially appeared in search results but was confirmed to be based in Kansas City, Missouri, USA - not Edmonton - and was discarded entirely as an out-of-country false match, not used or recorded anywhere.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -83,6 +83,7 @@
     <sheet name="Warman, SK" sheetId="78" state="visible" r:id="rId78"/>
     <sheet name="Calgary, AB" sheetId="79" state="visible" r:id="rId79"/>
     <sheet name="Edmonton, AB" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet name="Red Deer, AB" sheetId="81" state="visible" r:id="rId81"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -163,6 +164,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="77" hidden="1">'Warman, SK'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'Calgary, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="79" hidden="1">'Edmonton, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="80" hidden="1">'Red Deer, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13819,7 +13821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A659"/>
+  <dimension ref="A1:A673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -18162,6 +18164,97 @@
       <c r="A659" s="9" t="inlineStr">
         <is>
           <t>Two strong candidates found during Edmonton research were deliberately held back rather than added here, since they are based in other cities already on this project's master city list: Terrick Enterprises Ltd. (32+ year structural steel fabricator) is actually based in Sherwood Park, AB, and CJM Crane Services (heavy-lift/crane rental, 26-770 ton capacity) is actually based in Nisku, AB - both appear later in the master list and will be properly researched under their correct city entries rather than folded into Edmonton. A larger, similarly-named 'Vulcan Metals Corporation' (200-499 employees, $100-250M revenue) that surfaced in an initial broad search was confirmed to be based in Kansas City, Missouri, USA, not Edmonton, and was discarded entirely as an out-of-country false match rather than added anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="7" t="inlineStr">
+        <is>
+          <t>Batch 41: Red Deer, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="9" t="inlineStr">
+        <is>
+          <t>1. Antler Hill Welding Services Ltd. - Score 6, Priority B - CWB-certified structural welding/fabrication with a genuinely confirmed, unmasked named contact (Cody, Owner).</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="9" t="inlineStr">
+        <is>
+          <t>2. CAKI Fabrication Ltd. - Score 6, Priority B - diversified custom fabricator (agricultural, industrial, commercial, architectural) with no oil &amp; gas-core positioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="9" t="inlineStr">
+        <is>
+          <t>3. Red Deer Welding Pros - Score 4, Priority C - thinner listing with no confirmed named contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="9" t="inlineStr">
+        <is>
+          <t>For Antler Hill Welding, approach Cody directly - a genuinely confirmed, unmasked email is rare among the smaller shops recorded in this project, and worth acting on quickly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Antler Hill Welding Services and CAKI Fabrication. Red Deer Welding Pros as a lower-priority follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="9" t="inlineStr">
+        <is>
+          <t>Terrick Enterprises Ltd. (already held for its correct city, Sherwood Park, since batch 40) again surfaced under a Red Deer service-area page during this batch's research; not duplicated here, consistent with the earlier decision. No location mismatches, defense exclusions, or oil &amp; gas exclusions arose otherwise this batch.</t>
         </is>
       </c>
     </row>
@@ -34717,6 +34810,485 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Red Deer, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CAKI Fabrication Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cakifab.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Custom Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom metal fabrication (structural steel, aluminum, stainless steel) and mobile welding for agricultural, industrial, commercial, architectural and specialty projects across Central Alberta</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established Central Alberta custom fabricator with a genuinely diversified client base (agricultural, industrial, commercial, architectural) and no oil &amp; gas-core positioning found - a clean general industrial fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (cakifab.ca) describes structural steel fabrication and repair services for agricultural, industrial, commercial and architectural clients across Central Alberta.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Ashley Stewart</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cakifab.ca/about</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (403-877-5032).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cakifab.ca/ ; https://www.yelp.ca/biz/caki-fabrication-ltd-red-deer-county-3</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its industrial and architectural fabrication work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Red Deer, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Antler Hill Welding Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://antlerhillwelding.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/antler-hill-welding/</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>CWB Structural Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified structural welding and custom fabrication</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified structural welding/fabrication company near Red Deer with a genuinely confirmed, unmasked named contact - a solid general industrial structural fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (antlerhillwelding.com) and an Alignable business listing describe CWB-certified structural welding and custom fabrication services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Cody</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Owner (surname not confirmed)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://antlerhillwelding.com/about-ahws/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>cody@antlerhillwelding.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Direct, unmasked email for a named individual (Owner), sourced from the company's own materials - a genuinely confirmed contact.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://antlerhillwelding.com/contact-ahws/ ; https://www.alignable.com/red-deer-county-ab/antler-hill-welding-services-ltd/cwb-structural-welding-and-fabrication</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly with a structural/FEA overflow pitch tied to its CWB-certified structural welding capability.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>A second Owner, Amanda (amanda@antlerhillwelding.com), is also listed; both appear to be legitimate contacts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Red Deer, AB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Red Deer Welding Pros</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.reddeerwelding.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel to decorative aluminum work, large fabrication projects</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Locally based Red Deer fabricator offering a range from structural steel to decorative work - a modest general fit with no named contact or specific sector detail confirmed.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (reddeerwelding.com/services) describes structural steel through decorative aluminum fabrication work.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.reddeerwelding.com/about-us</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; company has a contact form but no direct email address was displayed in search results.</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.reddeerwelding.com/contact</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm named contact and client-sector mix before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -84,6 +84,7 @@
     <sheet name="Calgary, AB" sheetId="79" state="visible" r:id="rId79"/>
     <sheet name="Edmonton, AB" sheetId="80" state="visible" r:id="rId80"/>
     <sheet name="Red Deer, AB" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet name="Lethbridge, AB" sheetId="82" state="visible" r:id="rId82"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -165,6 +166,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="78" hidden="1">'Calgary, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="79" hidden="1">'Edmonton, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="80" hidden="1">'Red Deer, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="81" hidden="1">'Lethbridge, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13821,7 +13823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A673"/>
+  <dimension ref="A1:A687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -18255,6 +18257,97 @@
       <c r="A673" s="9" t="inlineStr">
         <is>
           <t>Terrick Enterprises Ltd. (already held for its correct city, Sherwood Park, since batch 40) again surfaced under a Red Deer service-area page during this batch's research; not duplicated here, consistent with the earlier decision. No location mismatches, defense exclusions, or oil &amp; gas exclusions arose otherwise this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="7" t="inlineStr">
+        <is>
+          <t>Batch 42: Lethbridge, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="9" t="inlineStr">
+        <is>
+          <t>1. C&amp;A Group of Companies (C&amp;A Industries) - Score 6, Priority B - 35,000 sq ft facility spanning machining, structural and mechanical fabrication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="9" t="inlineStr">
+        <is>
+          <t>2. Synergy Fabrication &amp; Welding - Score 6, Priority B - structural steel fabrication/erection with a confirmed named President.</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="9" t="inlineStr">
+        <is>
+          <t>3. Lethbridge Industries Ltd. - Score 5, Priority C - a niche, 80-year roller mill manufacturer serving Southern Alberta agriculture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="9" t="inlineStr">
+        <is>
+          <t>For C&amp;A Group, lead with its structural/mechanical fabrication capability given the facility's scale and breadth. For Synergy, note that the only confirmed email is an accounting inbox - request routing to Trevor Wandler specifically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: C&amp;A Group of Companies and Synergy Fabrication &amp; Welding. Lethbridge Industries as a lower-priority, niche follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="9" t="inlineStr">
+        <is>
+          <t>JPR Industries Inc., which surfaced prominently in an initial search (with a Facebook post specifically mentioning Lethbridge structural steel and agriculture), was confirmed to be based in Shaughnessy, AB - a distinct town not currently on this project's city list - and was not added here, consistent with this project's discipline around exact city attribution.</t>
         </is>
       </c>
     </row>
@@ -35289,6 +35382,489 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Lethbridge, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>C&amp;A Group of Companies (C&amp;A Industries)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.candagroup.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/c&amp;a-group-of-companies</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Metal Fabrication, Machining &amp; Structural/Mechanical</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Stainless steel, aluminum, carbon steel and sheet metal fabrication from a 35,000 sq ft facility; machining, structural and mechanical services</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Well-equipped, large-scale Lethbridge fabricator spanning machining, structural and mechanical work - a strong general heavy-industrial structural fit with no oil &amp; gas-core positioning found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the breadth of capability (machining, structural, mechanical) and facility scale.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (candagroup.ca/services/metal-fabrication-services) describes stainless steel, aluminum, carbon steel and sheet metal fabrication alongside machining and structural/mechanical services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Chris McPhee</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.candagroup.ca/contact-us/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@candagroup.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); a second source names Alan Lloyd as Chief Executive Officer at C &amp; A Industries - the exact relationship between the two named leaders was not confirmed.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.candagroup.ca/contact-us/ ; https://www.zoominfo.com/p/Alan-Lloyd/7838548334</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its structural/mechanical fabrication capability, given the facility's scale and breadth.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Confirm current leadership (Chris McPhee vs. Alan Lloyd) before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Lethbridge, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Synergy Fabrication &amp; Welding (Synergy Ltd.)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://synergyltd.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication &amp; Erection</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>General shop and portable welding, steel erection, fabrication and miscellaneous steel</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established Lethbridge-area structural steel fabricator/erector with a confirmed named President - a solid general heavy-industrial structural fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (synergyltd.ca) and directory listings describe structural steel fabrication, steel erection and miscellaneous steel services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Trevor Wandler</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://synergyltd.ca/contact-us/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>accounting@synergyltd.ca</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General accounting-department inbox (not verified as an individual's address or the appropriate department for a business-development inquiry, but the only confirmed email found).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://synergyltd.ca/contact-us/ ; https://www.canpages.ca/page/AB/lethbridge/synergy-ltd/100864812</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its steel erection and fabrication work; request routing to Trevor Wandler specifically given the available email is an accounting inbox.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Lethbridge, AB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Lethbridge Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://lil.ab.ca/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Roller Mill Manufacturing &amp; Millwright Services</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing and rebuilding of roller mills and related components, plus on-site millwright services including welding, serving the Southern Alberta agriculture industry since 1946</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1946), highly specialized Southern Alberta manufacturer of agricultural processing equipment (roller mills) - a niche but genuine mechanical/structural-engineering-adjacent fit given the complexity of roller mill design and rebuild work.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; the specialized nature of roller mill manufacturing/rebuilding could plausibly involve structural or mechanical design work.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (lil.ab.ca) describes roller mill manufacturing, rebuilding and millwright services for the Southern Alberta agriculture industry since 1946.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://lil.ab.ca/contact/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (403-328-4222).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://lil.ab.ca/contact/ ; https://www.dnb.com/business-directory/company-profiles.lethbridge_industries_limited.7ebe9aaea07e059eae05d355ecdc3731.html</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm whether any structural/FEA-adjacent design work exists in roller mill manufacturing before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -85,6 +85,7 @@
     <sheet name="Edmonton, AB" sheetId="80" state="visible" r:id="rId80"/>
     <sheet name="Red Deer, AB" sheetId="81" state="visible" r:id="rId81"/>
     <sheet name="Lethbridge, AB" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet name="Medicine Hat, AB" sheetId="83" state="visible" r:id="rId83"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -167,6 +168,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="79" hidden="1">'Edmonton, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="80" hidden="1">'Red Deer, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="81" hidden="1">'Lethbridge, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="82" hidden="1">'Medicine Hat, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13823,7 +13825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A687"/>
+  <dimension ref="A1:A701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -18348,6 +18350,97 @@
       <c r="A687" s="9" t="inlineStr">
         <is>
           <t>JPR Industries Inc., which surfaced prominently in an initial search (with a Facebook post specifically mentioning Lethbridge structural steel and agriculture), was confirmed to be based in Shaughnessy, AB - a distinct town not currently on this project's city list - and was not added here, consistent with this project's discipline around exact city attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="7" t="inlineStr">
+        <is>
+          <t>Batch 43: Medicine Hat, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="9" t="inlineStr">
+        <is>
+          <t>1. Hranco Industries Ltd. - Score 6, Priority B - 50+ year, self-described industry-leading structural steel/pressure piping fabricator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="9" t="inlineStr">
+        <is>
+          <t>2. Dynamic Industrial Solutions - Score 4, Priority C - regional (AB/BC/SK) industrial welding/piping fabricator; client-sector mix should be confirmed given its pressure/process piping emphasis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="9" t="inlineStr">
+        <is>
+          <t>3. Purist Welding Services Ltd. - Score 4, Priority C - architectural/industrial/custom welding shop with a confirmed named owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="9" t="inlineStr">
+        <is>
+          <t>For Hranco Industries, lead with its 50+ year structural steel and pressure piping track record - the clearest, most established fit found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Hranco Industries. Dynamic Industrial Solutions and Purist Welding Services as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="9" t="inlineStr">
+        <is>
+          <t>No location mismatches or defense exclusions arose this batch. Dynamic Industrial Solutions was flagged (Priority C rather than B) rather than excluded, since 'pressure piping' and 'process piping' terminology is commonly associated with oil &amp; gas/petrochemical facility work, but no explicit oil &amp; gas naming was found in the company's own materials - its actual client mix should be confirmed directly before a full pitch.</t>
         </is>
       </c>
     </row>
@@ -35865,6 +35958,473 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Medicine Hat, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Hranco Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://hranco.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel &amp; Pressure Piping Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>State-of-the-art welding and fabrication specializing in structural steel and pressure piping, 50+ years in business</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (50+ years), self-described industry-leading Medicine Hat fabricator - a strong general heavy-industrial structural fit and the most established candidate found in this batch.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the company's 50+ year track record and structural steel/pressure piping specialization.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (hranco.com) and a City of Medicine Hat feature article describe structural steel and pressure piping fabrication over 50+ years.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Cody Millington</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President (took over in 2015)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://hranco.com/contact/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a source claimed an email-naming-pattern ('{first_initial}{last}@hranco.com') but this was not used, per this project's no-guessing/no-pattern-inference policy. Only phone confirmed (403-527-4190).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://hranco.com/contact/ ; https://www.medicinehat.ca/en/news/diversity-in-super-steel.aspx</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its structural steel and pressure piping fabrication work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Medicine Hat, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Dynamic Industrial Solutions</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dynamicis.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Industrial Welding &amp; Piping Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Pressure piping, pressure vessel repairs, structural steel welding, custom fabrication, pipe fabrication and process piping, operating across Alberta, British Columbia and Saskatchewan</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established regional industrial welding/fabrication company with structural steel welding among its named services - a general heavy-industrial fit, though its heavy emphasis on pressure piping/process piping terminology (commonly associated with oil &amp; gas/petrochemical facilities) suggests its client base should be confirmed directly.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (dynamicis.ca/welding-fabrication) describes pressure piping, pressure vessel repairs, structural steel welding and process piping services across three provinces.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dynamicis.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only a contact form was found on the company website.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dynamicis.ca/welding-fabrication/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Confirm the company's actual client-sector mix (oil &amp; gas/petrochemical versus general industrial) before a tailored pitch, given the pressure/process piping terminology used.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Medicine Hat, AB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Purist Welding Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.puristwelding.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Architectural, Industrial &amp; Custom Welding</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Full-service welding and fabrication specializing in architectural, industrial and custom welding</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Established Medicine Hat welding/fabrication shop with a confirmed named owner - a modest general fit, its architectural-work emphasis suggesting a mix of building and industrial fabrication rather than purely heavy-industrial structural work.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (puristwelding.com) describes architectural, industrial and custom welding/fabrication services.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Wes Moch</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>President/Owner</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.puristwelding.com/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (403-526-4656).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.puristwelding.com/ ; https://www.bbb.org/ca/ab/medicine-hat/profile/welding-equipment-repair/purist-welding-services-ltd-0017-97465</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm proportion of industrial (versus architectural/decorative) work before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -86,6 +86,7 @@
     <sheet name="Red Deer, AB" sheetId="81" state="visible" r:id="rId81"/>
     <sheet name="Lethbridge, AB" sheetId="82" state="visible" r:id="rId82"/>
     <sheet name="Medicine Hat, AB" sheetId="83" state="visible" r:id="rId83"/>
+    <sheet name="Grande Prairie, AB" sheetId="84" state="visible" r:id="rId84"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -169,6 +170,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="80" hidden="1">'Red Deer, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="81" hidden="1">'Lethbridge, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="82" hidden="1">'Medicine Hat, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="83" hidden="1">'Grande Prairie, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13825,7 +13827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A701"/>
+  <dimension ref="A1:A717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -18441,6 +18443,111 @@
       <c r="A701" s="9" t="inlineStr">
         <is>
           <t>No location mismatches or defense exclusions arose this batch. Dynamic Industrial Solutions was flagged (Priority C rather than B) rather than excluded, since 'pressure piping' and 'process piping' terminology is commonly associated with oil &amp; gas/petrochemical facility work, but no explicit oil &amp; gas naming was found in the company's own materials - its actual client mix should be confirmed directly before a full pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="7" t="inlineStr">
+        <is>
+          <t>Batch 44: Grande Prairie, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="8" t="inlineStr">
+        <is>
+          <t>New screening criterion added this batch: DNV code/standard preference</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="9" t="inlineStr">
+        <is>
+          <t>Starting with this batch, research notes now explicitly check for and flag any company referencing DNV standards/certification (e.g. DNV-RP-C208), since this is a locked technical fit for AH Structures' own scope. This is a preference signal that boosts a candidate's fit when present, not a requirement - most inland/prairie fabricators will show no DNV reference at all, since DNV certification is concentrated in marine/offshore work. This should be checked going forward on every remaining batch, with particular attention once research reaches coastal cities in other provinces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="9" t="inlineStr">
+        <is>
+          <t>1. Risley Steel Services Ltd. - Score 6, Priority B - structural steel fabrication/repair explicitly serving 'general and oilfield steel' (not oilfield-exclusive), CWB-approved and ABSA quality-control certified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="9" t="inlineStr">
+        <is>
+          <t>2. 6S Fabrication Ltd. - Score 5, Priority B - owner-operated shop (Richard Shaw) with structural welding explicitly named.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="9" t="inlineStr">
+        <is>
+          <t>3. Weld FX - Score 4, Priority C - smaller structural welding shop with no confirmed named contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="8" t="inlineStr">
+        <is>
+          <t>No DNV references found this batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="9" t="inlineStr">
+        <is>
+          <t>As expected for an inland Peace Region city, none of the three companies researched showed any DNV code or standard reference; a dedicated search for DNV-certified fabricators in Grande Prairie also returned no local matches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Risley Steel Services and 6S Fabrication. Weld FX as a lower-priority follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="9" t="inlineStr">
+        <is>
+          <t>Universe Machine Corporation, initially found in a Grande Prairie-focused search, was confirmed to be based in Edmonton, AB (already covered in batch 40) rather than Grande Prairie - not added here, and not retroactively added to the existing Edmonton sheet either, since its own marketing names oilfield and petrochemical work as its primary mission (forestry is also served), making it a Review-level case at best rather than a clean addition. Terrick Enterprises (already held for Sherwood Park since batch 40) again surfaced under a Grande Prairie service-area page; not duplicated here.</t>
         </is>
       </c>
     </row>
@@ -36425,6 +36532,469 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Grande Prairie, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Risley Steel Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.risleysteelservices.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication &amp; Repair</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom structural steel fabrication and repairs on general and oilfield steel, Canadian Welding Bureau-approved and Alberta Boilers Safety Association quality-control certified, serving Northern Alberta</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established Grande Prairie structural steel fabricator explicitly serving both general and oilfield clients (not oilfield-exclusive) - a solid heavy-industrial structural fit for Northern Alberta.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (risleysteelservices.ca) describes custom structural steel fabrication and repairs on general and oilfield steel across Northern Alberta.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.risleysteelservices.ca/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (780-538-8240).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.risleysteelservices.ca/contact-us ; https://www.cwbgroup.org/directory/certified-companies/c29fa5ea-aa69-e811-a963-000d3af3d209</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its general (non-oilfield) structural steel fabrication and repair work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found for this company; a general search for DNV-certified fabricators in Grande Prairie returned no local matches - DNV certification is far more common in marine/offshore contexts than inland Alberta industrial fabrication, so its absence here is expected rather than a fit concern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Grande Prairie, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>6S Fabrication Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://6sfabrication.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Structural Welding &amp; Custom Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Structural welding and custom metal fabrication projects</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Owner-operated Grande Prairie custom fabrication shop with structural welding explicitly named among its services - a modest general structural fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (6sfabrication.com) and social media posts describe structural welding and custom metal fabrication projects.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Richard Shaw</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://6sfabrication.com/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only a contact form was found on the company website.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://6sfabrication.com/ ; https://www.facebook.com/6SFabrication/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its structural welding work.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Grande Prairie, AB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Weld FX</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.weldfx.ca/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Structural Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Structural welding services including platforms, ladders and stairs, skids, gates and custom fabrication</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Locally based Grande Prairie structural welding company with certified welders - a modest general fit, similar in scale to 6S Fabrication.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (weldfx.ca/services/structural-welding-and-fabrication) describes structural welding for platforms, ladders, stairs, skids and gates.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.weldfx.ca/</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass.</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.weldfx.ca/services/structural-welding-and-fabrication/</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm client-sector mix and named contact before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -87,6 +87,7 @@
     <sheet name="Lethbridge, AB" sheetId="82" state="visible" r:id="rId82"/>
     <sheet name="Medicine Hat, AB" sheetId="83" state="visible" r:id="rId83"/>
     <sheet name="Grande Prairie, AB" sheetId="84" state="visible" r:id="rId84"/>
+    <sheet name="Fort McMurray, AB" sheetId="85" state="visible" r:id="rId85"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -171,6 +172,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="81" hidden="1">'Lethbridge, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="82" hidden="1">'Medicine Hat, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="83" hidden="1">'Grande Prairie, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="84" hidden="1">'Fort McMurray, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3186,7 +3188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4486,6 +4488,48 @@
       <c r="H31" s="10" t="inlineStr">
         <is>
           <t>https://www.waiward.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Fort McMurray, AB</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Red River Welding</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>https://www.fortmcmurraywelding.ca/</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Certified welders serving mining, industrial, municipal and commercial purposes - a genuinely diversified client base - but the company's own service list also names 'oilfield and gas pipeline welding services' specifically, a stronger and more specific oil &amp; gas signal than several other Fort McMurray companies reviewed this batch.</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Confirm what proportion of Red River Welding's actual work is oilfield/pipeline-specific versus mining/municipal/commercial before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>https://www.fortmcmurraywelding.ca/welding-services</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A717"/>
+  <dimension ref="A1:A732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -18548,6 +18592,104 @@
       <c r="A717" s="9" t="inlineStr">
         <is>
           <t>Universe Machine Corporation, initially found in a Grande Prairie-focused search, was confirmed to be based in Edmonton, AB (already covered in batch 40) rather than Grande Prairie - not added here, and not retroactively added to the existing Edmonton sheet either, since its own marketing names oilfield and petrochemical work as its primary mission (forestry is also served), making it a Review-level case at best rather than a clean addition. Terrick Enterprises (already held for Sherwood Park since batch 40) again surfaced under a Grande Prairie service-area page; not duplicated here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="7" t="inlineStr">
+        <is>
+          <t>Batch 45: Fort McMurray, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="9" t="inlineStr">
+        <is>
+          <t>1. Northweld Welding &amp; Fabrication - Score 7, Priority B - the standout find of this batch: the only Fort McMurray shop with a proprietary in-house-designed helical screw pile foundation system, a genuine structural/geotechnical engineering product rather than pure fabrication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="9" t="inlineStr">
+        <is>
+          <t>2. Alberta Weld Pro Inc. and Scotian Welding Ltd. - Score 4, Priority C - general structural fabrication/welding shops with no named contact confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="8" t="inlineStr">
+        <is>
+          <t>Fort McMurray's oil sands economy required careful screening</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="9" t="inlineStr">
+        <is>
+          <t>As the heart of Canada's oil sands industry, nearly every Fort McMurray fabricator names oil field work among its services to some degree; Red River Welding was routed to Review given its explicit 'oilfield and gas pipeline welding services' line alongside mining/municipal/commercial work, while Northweld, Alberta Weld Pro and Scotian Welding were judged to have a more genuinely diversified or non-oilfield-specific service description and were included, with a caveat to verify actual client mix directly given the regional economy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="9" t="inlineStr">
+        <is>
+          <t>For Northweld Welding &amp; Fabrication, lead directly with foundation/pile design and load verification work - its proprietary helical pile system is a precise, evidence-based structural-engineering overflow opportunity, the strongest single signal found in several recent batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="9" t="inlineStr">
+        <is>
+          <t>Northweld's proprietary helical screw pile system is the clearest, most specific overflow-FEA signal found in this project since Fraser Custom Equipment (batch 20) and Royalite Industrial Maintenance (batch 22).</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Northweld Welding &amp; Fabrication. Alberta Weld Pro and Scotian Welding as lower-priority follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="9" t="inlineStr">
+        <is>
+          <t>Rosh Metal Ltd., which surfaced prominently for a Fort McMurray structural steel/warehouse project, was confirmed to actually be headquartered in Surrey, BC (already covered in this project, batch 6) and simply performed a project in Fort McMurray - not added here as a Fort McMurray-based company, consistent with this project's discipline around exact city attribution. None of the three included companies showed any DNV code/standard reference, consistent with the inland-Alberta pattern already noted in batch 44.</t>
         </is>
       </c>
     </row>
@@ -36995,6 +37137,461 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Fort McMurray, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Northweld Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://northweld.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Welding &amp; Fabrication / Foundation Systems</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified structural steel welding/fabrication, steel structured buildings, pile-caps, piping, heavy equipment repair; the only Fort McMurray shop to design and fabricate its own proprietary Helical screw pile system</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Notably, this company has genuine in-house structural/foundation design capability - its own proprietary helical screw pile system is a real engineering product, not just fabrication - making it one of the more precise engineering-adjacent fits found in this project, similar to Fraser Custom Equipment (batch 20) and Royalite Industrial Maintenance (batch 22).</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Designing and fabricating a proprietary pile foundation system requires genuine structural/geotechnical engineering input - a direct, evidence-based overflow-FEA opportunity (load-bearing capacity verification, pile design) rather than an inferred one.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (northweld.ca/fabrication) describes the proprietary Helical screw pile system alongside structural steel welding, steel structured buildings and pile-cap fabrication.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://northweld.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (780-531-6424).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://northweld.ca/fabrication/ ; https://www.yellowpages.ca/bus/Alberta/Fort-McMurray/Northweld-Welding-Fabrication/102655379.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly with a structural/FEA pitch specifically tied to its helical pile system - foundation design/load verification is a precise, evidence-based fit.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Company markets itself as serving 'commercial, industrial, oil field and mining sites' - oil field is one of several named client types in the heavily oil sands-dependent Fort McMurray economy, not confirmed as the company's sole/core market, but this should be verified directly given the regional economy. No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Fort McMurray, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta Weld Pro Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://albertaweldpro.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Stainless Steel Welding &amp; Structural Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Stainless steel welding and fabrication, handrails, stairways, and structural fabrications</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Locally owned Fort McMurray welding/fabrication company with structural fabrication explicitly named among its services - a modest general industrial fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (albertaweldpro.com) describes stainless steel welding, handrails, stairways and structural fabrication services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://albertaweldpro.com/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone/address confirmed (780-799-9917, 157 Simcoe Way).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dnb.com/business-directory/company-profiles.alberta_weld_pro_inc.edbf66f5534e9d9f2aaa9d7ec181fc98.html</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm client-sector mix (given the regional oil sands economy) and named contact before a tailored pitch. No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Fort McMurray, AB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Scotian Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.scotianweldingltd.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Coating &amp; Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Mobile welding, heavy equipment repairs, structural steel and metal fabrication, painting and coating for commercial and industrial applications, since 2005</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Established (since 2005) Fort McMurray welding/coating/fabrication company with structural steel work named among diverse commercial/industrial services - a modest general fit.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (scotianweldingltd.com/our-services) describes welding, coating, heavy equipment repairs and structural steel/metal fabrication for commercial and industrial clients.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.scotianweldingltd.com/contact</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; company has a contact form but no direct email address was displayed in search results.</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.scotianweldingltd.com/contact</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm client-sector mix and named contact before a tailored pitch. No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -88,6 +88,7 @@
     <sheet name="Medicine Hat, AB" sheetId="83" state="visible" r:id="rId83"/>
     <sheet name="Grande Prairie, AB" sheetId="84" state="visible" r:id="rId84"/>
     <sheet name="Fort McMurray, AB" sheetId="85" state="visible" r:id="rId85"/>
+    <sheet name="Fort Saskatchewan, AB" sheetId="86" state="visible" r:id="rId86"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -173,6 +174,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="82" hidden="1">'Medicine Hat, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="83" hidden="1">'Grande Prairie, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="84" hidden="1">'Fort McMurray, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="85" hidden="1">'Fort Saskatchewan, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13871,7 +13873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A732"/>
+  <dimension ref="A1:A746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -18690,6 +18692,97 @@
       <c r="A732" s="9" t="inlineStr">
         <is>
           <t>Rosh Metal Ltd., which surfaced prominently for a Fort McMurray structural steel/warehouse project, was confirmed to actually be headquartered in Surrey, BC (already covered in this project, batch 6) and simply performed a project in Fort McMurray - not added here as a Fort McMurray-based company, consistent with this project's discipline around exact city attribution. None of the three included companies showed any DNV code/standard reference, consistent with the inland-Alberta pattern already noted in batch 44.</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="7" t="inlineStr">
+        <is>
+          <t>Batch 46: Fort Saskatchewan, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="9" t="inlineStr">
+        <is>
+          <t>1. McSween Custom Fabricating, Welding, Erecting Ltd. - Score 6, Priority B - 45-year multi-discipline industrial contractor serving eight distinct process-industry sectors, with a directly confirmed named contact (Richard, richard@mcsweenfab.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="8" t="inlineStr">
+        <is>
+          <t>Why this batch is thin</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="9" t="inlineStr">
+        <is>
+          <t>Fort Saskatchewan sits at the center of Alberta's 'Industrial Heartland' petrochemical corridor; repeated searches for smaller, non-industrial or municipal/residential-focused fabricators in the city itself returned no further genuinely locally-based candidates with sufficient detail to include, only referrals back to McSween or listings for companies based in neighbouring Edmonton (already covered in batch 40). This reflects the town's genuinely narrow, heavy-industrial economic base rather than a research gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="9" t="inlineStr">
+        <is>
+          <t>For McSween, frame outreach around its non-oil-and-gas/petrochemical sectors specifically (mining, cement, pharmaceutical, power generation) given how central oil &amp; gas/petrochemical work is to the surrounding Industrial Heartland region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only): McSween Custom Fabricating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="9" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found for McSween Custom Fabricating.</t>
         </is>
       </c>
     </row>
@@ -37592,6 +37685,285 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Fort Saskatchewan, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>McSween Custom Fabricating, Welding, Erecting Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://mcsweenfab.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/mcsween-fabricating</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Multi-Discipline Industrial Fabrication &amp; Construction</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom fabrication, welding and erecting for the industrial plant community, spanning petrochemical, fertilizer, cement, mining, oil &amp; gas, pharmaceutical, heavy industrial, light industrial and power generation, since 1980</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1980) Fort Saskatchewan multi-discipline industrial contractor serving Alberta's 'Industrial Heartland' - genuinely diversified across eight distinct named sectors rather than an oil &amp; gas/petrochemical-exclusive business, with a directly confirmed named contact.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the breadth of multi-discipline industrial construction/fabrication work across process-industry facilities.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (mcsweenfab.com/about) describes multi-discipline industrial fabrication and construction serving petrochemical, fertilizer, cement, mining, oil &amp; gas, pharmaceutical, heavy industrial, light industrial and power generation clients since 1980.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Contact (title not fully confirmed)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://mcsweenfab.com/about/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>richard@mcsweenfab.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Direct, unmasked email for a named individual, sourced from the company's own contact listing - a genuinely confirmed contact, though his exact title/role was not confirmed.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://mcsweenfab.com/ ; https://www.fortsaskchamber.com/list/member/mcsween-custom-fabricating-1435</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch framed around its non-oil-and-gas sectors specifically (mining, cement, pharmaceutical, power generation), given how many process-industry sectors this company already serves and how oil &amp; gas/petrochemical-dominated the surrounding Industrial Heartland region is.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Oil &amp; gas and petrochemical are named among eight served sectors, not the company's sole/core market. No DNV code/standard reference was found; Fort Saskatchewan is part of Alberta's 'Industrial Heartland' petrochemical corridor, and this was the only genuinely locally-based fabricator identified with sufficient detail to include in this pass.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -89,6 +89,7 @@
     <sheet name="Grande Prairie, AB" sheetId="84" state="visible" r:id="rId84"/>
     <sheet name="Fort McMurray, AB" sheetId="85" state="visible" r:id="rId85"/>
     <sheet name="Fort Saskatchewan, AB" sheetId="86" state="visible" r:id="rId86"/>
+    <sheet name="Airdrie, AB" sheetId="87" state="visible" r:id="rId87"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -175,6 +176,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="83" hidden="1">'Grande Prairie, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="84" hidden="1">'Fort McMurray, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="85" hidden="1">'Fort Saskatchewan, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="86" hidden="1">'Airdrie, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13873,7 +13875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A746"/>
+  <dimension ref="A1:A760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -18783,6 +18785,97 @@
       <c r="A746" s="9" t="inlineStr">
         <is>
           <t>No DNV code/standard reference was found for McSween Custom Fabricating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="7" t="inlineStr">
+        <is>
+          <t>Batch 47: Airdrie, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="9" t="inlineStr">
+        <is>
+          <t>1. East Lake Manufacturing - Score 6, Priority B - 40+ year fabricator explicitly offering 'design to contract manufacturing,' a genuine engineering-through-production capability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="8" t="inlineStr">
+        <is>
+          <t>Why this batch is thin</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="9" t="inlineStr">
+        <is>
+          <t>As a Calgary-area bedroom/suburban community, Airdrie's own genuinely locally-based industrial fabrication base is narrow; several companies found in initial searches turned out to be based elsewhere (Kolt Tebb Fabrications in Carstairs, AB; Big Blue Portable Welding in Calgary, already covered batch 39) and were not added here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="9" t="inlineStr">
+        <is>
+          <t>For East Lake Manufacturing, lead with its 'design to contract manufacturing' service line - the clearest engineering-adjacent signal found, suggesting genuine in-house design capability that could extend to overflow FEA collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="9" t="inlineStr">
+        <is>
+          <t>East Lake Manufacturing's design-through-manufacturing capability is the clearest signal found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only): East Lake Manufacturing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="9" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. Williams Arc Welding, which surfaced during a related search, was confirmed to be based in Wetaskiwin, AB - a distinct town later on this project's master list - and was not added here; it will be properly researched when that city is reached.</t>
         </is>
       </c>
     </row>
@@ -37964,6 +38057,277 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Airdrie, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>East Lake Manufacturing</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://eastlakemanufacturing.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Metal Manufacturing &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom metal fabrication, pipe supports and powder coating in steel, aluminum and stainless, from design through contract manufacturing, 40+ years</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (40+ years), full-service Airdrie fabricator explicitly offering 'design to contract manufacturing' - a genuine engineering-through-production capability, and a strong general heavy-industrial structural fit with no oil &amp; gas-core positioning found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>The 'design to contract manufacturing' service line suggests in-house design capability that could extend to overflow structural/FEA collaboration on larger or more complex projects.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (eastlakemanufacturing.com) and a Manufacturing Technology Insights feature describe metal fabrication, pipe supports and powder coating services from design through contract manufacturing.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Hank Rietveld</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://eastlakemanufacturing.com/about/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (403-948-2202).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://eastlakemanufacturing.com/contact/ ; https://www.manufacturingtechnologyinsights.com/east-lake-manufacturing</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its 'design to contract manufacturing' capability, the clearest engineering-adjacent signal found this batch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Kevin Ham is also listed as Vice President. No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -90,6 +90,7 @@
     <sheet name="Fort McMurray, AB" sheetId="85" state="visible" r:id="rId85"/>
     <sheet name="Fort Saskatchewan, AB" sheetId="86" state="visible" r:id="rId86"/>
     <sheet name="Airdrie, AB" sheetId="87" state="visible" r:id="rId87"/>
+    <sheet name="Spruce Grove, AB" sheetId="88" state="visible" r:id="rId88"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -177,6 +178,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="84" hidden="1">'Fort McMurray, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="85" hidden="1">'Fort Saskatchewan, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="86" hidden="1">'Airdrie, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="87" hidden="1">'Spruce Grove, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13875,7 +13877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A760"/>
+  <dimension ref="A1:A773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -18876,6 +18878,90 @@
       <c r="A760" s="9" t="inlineStr">
         <is>
           <t>No DNV code/standard reference was found. Williams Arc Welding, which surfaced during a related search, was confirmed to be based in Wetaskiwin, AB - a distinct town later on this project's master list - and was not added here; it will be properly researched when that city is reached.</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="7" t="inlineStr">
+        <is>
+          <t>Batch 48: Spruce Grove, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="9" t="inlineStr">
+        <is>
+          <t>1. Grove Machine &amp; Welding Ltd. - Score 6, Priority B - 26+ year full-service shop near the Acheson Industrial Area, with a confirmed general contact email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="9" t="inlineStr">
+        <is>
+          <t>2. Parkland Welding Ltd. - Score 4, Priority C - CNC-equipped welding/machining shop with no confirmed named contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="9" t="inlineStr">
+        <is>
+          <t>For Grove Machine &amp; Welding, lead with its proximity to and likely servicing of the Acheson Industrial Area, one of Alberta's largest industrial concentrations outside Edmonton.</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Grove Machine &amp; Welding. Parkland Welding as a lower-priority follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="9" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found for either company. No location mismatches or defense/oil &amp; gas exclusions arose this batch.</t>
         </is>
       </c>
     </row>
@@ -38328,6 +38414,357 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Spruce Grove, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Grove Machine &amp; Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Machining, Welding &amp; Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Full-service welding, fabrication and machine shop services, 26+ years</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Well-established (26+ years) Spruce Grove machine/fabrication shop positioned near the Acheson Industrial Area, one of Alberta's largest industrial concentrations outside Edmonton - a solid general heavy-industrial fit with a confirmed general contact email.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (411.ca, Alignable) describe full-service welding, fabrication and machine shop services since the late 1990s.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Jim &amp; Laura Reynar</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owners (purchased 2019 from original owner Bob Siemens, still working with the company)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>Office@grovemachinewelding.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://411.ca/business/profile/12536615 ; https://www.alignable.com/spruce-grove-ab/grove-machine-welding</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its machining/fabrication capability serving the Acheson Industrial Area's manufacturing base.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Spruce Grove, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Parkland Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Machining &amp; Custom Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Welding, machining and fabrication of custom small and medium-sized projects; industrial and recreational CNC plasma table, CNC lathe, mill and steel sales</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established Spruce Grove welding/machining shop with CNC capability - a modest general industrial fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (Grande Prairie &amp; District Chamber of Commerce cross-listing, COSSD) describe welding, machining and CNC fabrication services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (780-962-3390).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.yellowpages.ca/bus/Alberta/Spruce-Grove/Parkland-Welding-Ltd/1197113.html</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm named contact and client-sector mix before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -91,6 +91,7 @@
     <sheet name="Fort Saskatchewan, AB" sheetId="86" state="visible" r:id="rId86"/>
     <sheet name="Airdrie, AB" sheetId="87" state="visible" r:id="rId87"/>
     <sheet name="Spruce Grove, AB" sheetId="88" state="visible" r:id="rId88"/>
+    <sheet name="St. Albert, AB" sheetId="89" state="visible" r:id="rId89"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -179,6 +180,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="85" hidden="1">'Fort Saskatchewan, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="86" hidden="1">'Airdrie, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="87" hidden="1">'Spruce Grove, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="88" hidden="1">'St. Albert, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3194,7 +3196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4536,6 +4538,48 @@
       <c r="H32" s="10" t="inlineStr">
         <is>
           <t>https://www.fortmcmurraywelding.ca/welding-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>St. Albert, AB</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>SDB Welding and Fabrication Ltd.</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>https://www.sdbweldingandfabricationltd.com/</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>15+ year custom metal/structural steel fabricator with genuinely relevant work (structural steel for tall skyscrapers and industrial buildings) - but the company is registered in Sturgeon County, AB, a distinct rural municipality not currently on this project's city list, and only serves St. Albert as part of a broader Edmonton-area service area rather than being headquartered there.</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether Sturgeon County should be added as a separate target municipality, or whether this company's St. Albert-area service work alone justifies inclusion under St. Albert.</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>https://www.sdbweldingandfabricationltd.com/structural-steel</t>
         </is>
       </c>
     </row>
@@ -13877,7 +13921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A773"/>
+  <dimension ref="A1:A785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -18962,6 +19006,83 @@
       <c r="A773" s="9" t="inlineStr">
         <is>
           <t>No DNV code/standard reference was found for either company. No location mismatches or defense/oil &amp; gas exclusions arose this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="7" t="inlineStr">
+        <is>
+          <t>Batch 49: St. Albert, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="9" t="inlineStr">
+        <is>
+          <t>1. Wesmark Welding Ltd. - Score 6, Priority B - structural/industrial welding shop led by a credentialed CWB Structural Welding Inspector, with a directly confirmed named owner and email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="9" t="inlineStr">
+        <is>
+          <t>Approach Wesley Markle directly - his CWB Structural Welding Inspector credential is a specific, verifiable quality signal distinguishing this shop from general welding services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only): Wesmark Welding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="9" t="inlineStr">
+        <is>
+          <t>SDB Welding and Fabrication Ltd., a genuinely relevant structural steel fabricator (skyscraper and industrial-building work), was routed to Review rather than added directly: it is registered in Sturgeon County, AB, a rural municipality not currently on this project's city list, and only serves St. Albert as part of a broader Edmonton-area service area. ABSK Builders Structures, a large-volume (~500 tonnes/year) structural steel fabricator also serving St. Albert, was confirmed to be based in Leduc, AB - later on this project's master list - and was deliberately held back for that city rather than added here. No DNV code/standard reference was found for Wesmark Welding.</t>
         </is>
       </c>
     </row>
@@ -38765,6 +38886,281 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>St. Albert, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Wesmark Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.wesmarkwelding.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural and industrial welding, custom fabrication, repairs and CNC plasma cutting; shop led by a CWB Structural Welding Inspector, 15+ years</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely St. Albert-based industrial welding/fabrication shop led by a credentialed CWB Structural Welding Inspector - a solid, technically-verified structural fit with a directly confirmed named owner and email.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (wesmarkwelding.ca) describes structural and industrial welding, custom fabrication and CNC plasma cutting, with the shop led by a CWB Structural Welding Inspector.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Wesley Markle</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.wesmarkwelding.ca/contact</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@wesmarkwelding.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address), but the company itself is small/owner-operated so this likely reaches Wesley Markle directly.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.wesmarkwelding.ca/contact ; https://m.yelp.com/biz/wesmark-welding-st-albert</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly with a structural/FEA overflow pitch, given the shop's CWB Structural Welding Inspector credential - a specific, verifiable quality signal.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -92,6 +92,7 @@
     <sheet name="Airdrie, AB" sheetId="87" state="visible" r:id="rId87"/>
     <sheet name="Spruce Grove, AB" sheetId="88" state="visible" r:id="rId88"/>
     <sheet name="St. Albert, AB" sheetId="89" state="visible" r:id="rId89"/>
+    <sheet name="Leduc, AB" sheetId="90" state="visible" r:id="rId90"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -181,6 +182,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="86" hidden="1">'Airdrie, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="87" hidden="1">'Spruce Grove, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="88" hidden="1">'St. Albert, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="89" hidden="1">'Leduc, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3196,7 +3198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4580,6 +4582,48 @@
       <c r="H33" s="10" t="inlineStr">
         <is>
           <t>https://www.sdbweldingandfabricationltd.com/structural-steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Leduc, AB</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>R.O.Y. Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>https://www.royindustries.com/</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Welding, fabrication and industrial services company in the Leduc Business Park - but available sources describe its work as specifically 'related to the oil and gas industries,' framing oil &amp; gas as the company's defining market rather than one of several served sectors.</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Confirm whether R.O.Y. Industries has any genuinely non-oil-and-gas work before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>https://www.dnb.com/business-directory/company-profiles.roy_industries_ltd.e97832c1d5a799f10b2481f262966aba.html</t>
         </is>
       </c>
     </row>
@@ -13921,7 +13965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A785"/>
+  <dimension ref="A1:A800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -19083,6 +19127,104 @@
       <c r="A785" s="9" t="inlineStr">
         <is>
           <t>SDB Welding and Fabrication Ltd., a genuinely relevant structural steel fabricator (skyscraper and industrial-building work), was routed to Review rather than added directly: it is registered in Sturgeon County, AB, a rural municipality not currently on this project's city list, and only serves St. Albert as part of a broader Edmonton-area service area. ABSK Builders Structures, a large-volume (~500 tonnes/year) structural steel fabricator also serving St. Albert, was confirmed to be based in Leduc, AB - later on this project's master list - and was deliberately held back for that city rather than added here. No DNV code/standard reference was found for Wesmark Welding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="7" t="inlineStr">
+        <is>
+          <t>Batch 50: Leduc, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="8" t="inlineStr">
+        <is>
+          <t>Milestone: 50 batches / 100 cities-towns researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="9" t="inlineStr">
+        <is>
+          <t>This batch brings the project to 50 completed batches (99 city/town sheets total, spanning British Columbia, Saskatchewan, and Alberta through Leduc on the master list), a useful checkpoint given the scale of the underlying 314-city list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="9" t="inlineStr">
+        <is>
+          <t>1. ABSK Builders Structures Inc. - Score 6, Priority B - sizeable (~500 tonnes/year) structural steel fabricator with no oil &amp; gas-core positioning found, also confirmed as the Leduc-based company behind the St. Albert-area service work noted in batch 49.</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="9" t="inlineStr">
+        <is>
+          <t>2. AMP Works Welding &amp; Fabrication Inc. - Score 5, Priority B - locally based fabricator specializing specifically in structural steel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="9" t="inlineStr">
+        <is>
+          <t>For ABSK Builders Structures, lead with its large-scale structural steel fabrication capacity (500 tonnes/year) - among the larger single-facility volumes recorded in recent Alberta batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: ABSK Builders Structures and AMP Works Welding &amp; Fabrication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="9" t="inlineStr">
+        <is>
+          <t>R.O.Y. Industries Ltd. was routed to Review rather than added or excluded outright: available sources describe its fabrication/industrial work as specifically 'related to the oil and gas industries,' framing it as the company's defining market rather than one of several sectors served - a stronger signal than the multi-sector cases included elsewhere in this project, but not as unambiguous as companies whose own names or marketing explicitly identify as oilfield service providers. No DNV code/standard reference was found for either included company.</t>
         </is>
       </c>
     </row>
@@ -39534,4 +39676,387 @@
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Leduc, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>ABSK Builders Structures Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://abskinc.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/samir-mejri-9410a59a</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel fabrication, welding and installation for commercial, industrial and residential buildings, fabricating close to 500 tonnes of structural steel a year in a 400 sq m workshop, serving Edmonton, St. Albert and surrounding area 24/7</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Well-equipped, sizeable (500 tonnes/year) Leduc structural steel fabricator with no oil &amp; gas-core positioning found - a strong general heavy-industrial structural fit for the greater Edmonton region.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the company's scale and stated state-of-the-art equipment.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (abskinc.com/about-us) describes ~500 tonnes/year of structural steel fabrication for commercial, industrial and residential clients across the Edmonton area.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Samir Mejri</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Principal (title not fully confirmed)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/samir-mejri-9410a59a</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://abskinc.com/about-us/index.html</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (780-446-2549).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://abskinc.com/about-us/index.html ; https://www.konaequity.com/company/absk-builders-structures-4848809308/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its large-scale structural steel fabrication capacity.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. Also found while researching St. Albert (batch 49), where it serves as one of several service-area providers; recorded here under Leduc since that is the company's actual base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Leduc, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AMP Works Welding &amp; Fabrication Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>http://www.ampworks.ca</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel welding and fabrication</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Locally based Leduc fabricator specializing specifically in structural steel - a modest but focused general structural fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (Dun &amp; Bradstreet, COSSD) describe the company as specialized in structural steel.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Howard Evans</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Key Principal</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only address confirmed (3910 77 Ave, Leduc, AB).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dnb.com/business-directory/company-profiles.amp_works_welding__fabrication_inc.f5086c8df2238974bd985b3f6826ee66.html ; https://www.cossd.com/biz/11527/amp-works-welding-fabrication-inc</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its structural steel specialization.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -93,6 +93,7 @@
     <sheet name="Spruce Grove, AB" sheetId="88" state="visible" r:id="rId88"/>
     <sheet name="St. Albert, AB" sheetId="89" state="visible" r:id="rId89"/>
     <sheet name="Leduc, AB" sheetId="90" state="visible" r:id="rId90"/>
+    <sheet name="Nisku, AB" sheetId="91" state="visible" r:id="rId91"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -183,6 +184,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="87" hidden="1">'Spruce Grove, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="88" hidden="1">'St. Albert, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="89" hidden="1">'Leduc, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="90" hidden="1">'Nisku, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13965,7 +13967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A800"/>
+  <dimension ref="A1:A815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -19225,6 +19227,104 @@
       <c r="A800" s="9" t="inlineStr">
         <is>
           <t>R.O.Y. Industries Ltd. was routed to Review rather than added or excluded outright: available sources describe its fabrication/industrial work as specifically 'related to the oil and gas industries,' framing it as the company's defining market rather than one of several sectors served - a stronger signal than the multi-sector cases included elsewhere in this project, but not as unambiguous as companies whose own names or marketing explicitly identify as oilfield service providers. No DNV code/standard reference was found for either included company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="7" t="inlineStr">
+        <is>
+          <t>Batch 51: Nisku, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="9" t="inlineStr">
+        <is>
+          <t>1. Steelhead Fabrication Corp. - Score 7, Priority B - genuine in-house design and drafting capability alongside structural module fabrication, with three named, unmasked contact emails (Steve, Amy, Jim).</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="9" t="inlineStr">
+        <is>
+          <t>2. Element Steel Inc. and CJM Crane Services Ltd. - Score 6, Priority B - a diversified non-oilfield fabricator and a well-equipped heavy-lift company with a confirmed named President, respectively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="8" t="inlineStr">
+        <is>
+          <t>This batch closes a loop from earlier research</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="9" t="inlineStr">
+        <is>
+          <t>CJM Crane Services Ltd. was originally identified during Edmonton research (batch 40) and deliberately held back for Nisku, its correct city - now properly researched and added here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="9" t="inlineStr">
+        <is>
+          <t>For Steelhead Fabrication, lead directly with structural module design/drafting collaboration - the clearest engineering-adjacent signal found in several recent Alberta batches, framed around its non-oil-and-gas structural module projects where possible given oil and gas skids/structures is also a named service line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="9" t="inlineStr">
+        <is>
+          <t>Steelhead Fabrication's in-house design/drafting service and CJM Crane Services' explicitly listed 'consulting' service are the two clearest overflow-adjacent signals found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Steelhead Fabrication, Element Steel, and CJM Crane Services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="9" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found for any of the three companies.</t>
         </is>
       </c>
     </row>
@@ -40059,4 +40159,495 @@
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Nisku, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Steelhead Fabrication Corp.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.steelheadfabrication.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Module Fabrication &amp; Design</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>In-house design and drafting services, structural module fabrication, oil and gas skids/structures, and general fabrication services</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Notable for genuine in-house design and drafting capability alongside structural module fabrication - one of the more precise engineering-adjacent fits found in this project's Alberta batches, though oil and gas skids/structures is one of its named service lines given the region's economy.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>In-house design and drafting services for structural modules is a direct, evidence-based overflow-FEA pathway (structural verification, module design collaboration) rather than an inferred one.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (steelheadfabrication.com) describes design and drafting services, structural module fabrication, and oil and gas skids/structures.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Contact (title not fully confirmed)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.steelheadfabrication.com/contact.html</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>Steve@SteelheadFabrication.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Direct, unmasked email for a named individual, sourced from the company's own contact page - a genuinely confirmed contact; Amy and Jim are also listed with similarly formatted emails.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.steelheadfabrication.com/contact.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied specifically to its design/drafting and structural module fabrication work, framed around its non-oil-and-gas structural module projects where possible.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nisku, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Element Steel Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://elementsteel.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/element-steel-inc</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Precisely crafted steel products for construction, industrial manufacturing and agricultural sectors</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Nisku-based steel fabricator with a diversified, non-oil-and-gas-named client base - a clean general industrial fit relative to several other Nisku fabricators serving oilfield-heavy markets.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (elementsteel.ca) describes steel fabrication for construction, industrial manufacturing and agricultural clients.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://elementsteel.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@elementsteel.ca</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://elementsteel.ca/ ; https://members.edmca.com/member-directory/Details/element-steel-inc-1967605</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its construction and industrial manufacturing work.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nisku, AB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CJM Crane Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://cjmcrane.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Lift / Crane Rental &amp; Rigging</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Heavy lifting, rigging, bare crane rentals, fabrication and consulting, with equipment ranging from 26-ton boom trucks up to 770-ton All Terrain Cranes</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Well-equipped Nisku heavy-lift/crane company with a genuinely confirmed named President and a directly relevant, sizeable equipment fleet - a strong overflow-heavy-lift-engineering fit, similar to Sterling Crane and Eagle Crane recorded in earlier batches.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the range of heavy-lift capacity (26-770 tons) and 'consulting' listed among services.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (cjmcrane.com) describes heavy lifting, rigging, crane rentals, fabrication and consulting services with a fleet up to 770-ton capacity.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Manuel Channon</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/cjm-crane-services-ltd</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a source claimed an email-naming-pattern ('{first_initial}{last}@cjmcrane.com') but this was not used, per this project's no-guessing/no-pattern-inference policy. Only phone confirmed (780-298-4074).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://cjmcrane.com/ ; https://www.zoominfo.com/p/Manuel-Channon/3045008627</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a potential engineering-support partner for heavy-lift project planning, given 'consulting' is explicitly listed among its services.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. Originally identified during Edmonton research (batch 40) and deliberately held back for this, its correct city.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -94,6 +94,7 @@
     <sheet name="St. Albert, AB" sheetId="89" state="visible" r:id="rId89"/>
     <sheet name="Leduc, AB" sheetId="90" state="visible" r:id="rId90"/>
     <sheet name="Nisku, AB" sheetId="91" state="visible" r:id="rId91"/>
+    <sheet name="Sherwood Park, AB" sheetId="92" state="visible" r:id="rId92"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -185,6 +186,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="88" hidden="1">'St. Albert, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="89" hidden="1">'Leduc, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="90" hidden="1">'Nisku, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="91" hidden="1">'Sherwood Park, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3200,7 +3202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4626,6 +4628,48 @@
       <c r="H34" s="10" t="inlineStr">
         <is>
           <t>https://www.dnb.com/business-directory/company-profiles.roy_industries_ltd.e97832c1d5a799f10b2481f262966aba.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Sherwood Park, AB</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Structure Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>https://www.structureind.com/</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Industrial maintenance and repair contractor offering welding, pipe fitting, millwrighting, electrical work, fabrication and rope access services, with a confirmed named President (Christopher J Aziz) - but the company's own materials describe its specialty as 'industrial maintenance and repair services, particularly in mining and refining,' and refining is a strong oil &amp; gas-processing signal.</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Confirm what proportion of Structure Group's work is refinery/oil &amp; gas-specific versus mining and other industrial maintenance before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>https://www.structureind.com/who-we-are ; https://www.structureind.com/who-we-are/leadership</t>
         </is>
       </c>
     </row>
@@ -13967,7 +14011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A815"/>
+  <dimension ref="A1:A830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -19325,6 +19369,104 @@
       <c r="A815" s="9" t="inlineStr">
         <is>
           <t>No DNV code/standard reference was found for any of the three companies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="7" t="inlineStr">
+        <is>
+          <t>Batch 52: Sherwood Park, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="8" t="inlineStr">
+        <is>
+          <t>This batch closes a loop from three earlier batches</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="9" t="inlineStr">
+        <is>
+          <t>Terrick Enterprises Ltd. surfaced repeatedly under service-area pages for Edmonton (batch 40), Red Deer (batch 41) and Grande Prairie (batch 44), and was deliberately held back each time for its correct city - now properly researched and added here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="9" t="inlineStr">
+        <is>
+          <t>1. Terrick Enterprises Ltd. - Score 6, Priority B - 24,000 sq ft, 30-year fabricator with a genuinely diversified six-sector client base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="9" t="inlineStr">
+        <is>
+          <t>2. Fullster Iron Ltd. (formerly Eskimo Steel) - Score 6, Priority B - structural steel fabricator with a Quality Management System audited to the CISC Steel Fabrication Quality Systems Guideline, a specific verifiable quality credential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="9" t="inlineStr">
+        <is>
+          <t>For Terrick Enterprises, frame outreach around its non-oil-and-gas sectors (mining, pulp mills, manufacturing). For Fullster Iron, its CISC quality audit is a useful shared quality-standards touchpoint even without a DNV reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Terrick Enterprises and Fullster Iron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="9" t="inlineStr">
+        <is>
+          <t>Structure Group Ltd., an industrial maintenance/repair contractor with a confirmed named President, was routed to Review rather than added directly: its own materials describe its specialty as industrial maintenance 'particularly in mining and refining,' and refining is a strong oil &amp; gas-processing signal without the clear multi-sector diversification seen in Terrick Enterprises. No DNV code/standard reference was found for either included company.</t>
         </is>
       </c>
     </row>
@@ -40650,4 +40792,391 @@
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Sherwood Park, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Terrick Enterprises Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.terrick.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/terrick-enterprises-ltd</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Custom Steel &amp; Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom steel and metal fabrication from a 24,000 sq ft facility, serving oil and gas, agriculture, construction, mining, pulp mills and manufacturing since 1994</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Well-established (since 1994), large-scale Sherwood Park fabricator with a genuinely diversified client base spanning six named sectors - a strong general heavy-industrial structural fit, with oil &amp; gas as one of several markets rather than the sole business.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the facility's scale and multi-sector industrial client base.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (terrick.com) and directory listings describe custom fabrication for oil and gas, agriculture, construction, mining, pulp mills and manufacturing clients since 1994.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Terry Dahlstrom &amp; Richard Dahlstrom</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owners</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.terrick.com/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No usable public email found; a directory source displayed only a masked address (****@terrick.com), which was not used per this project's no-guessing policy on masked addresses. Only phone confirmed (780-417-3043).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.terrick.com/contact-us ; https://www.bbb.org/ca/ab/sherwood-park/profile/industrial-supply/terrick-enterprises-ltd-0017-135038</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch framed around its non-oil-and-gas sectors (mining, pulp mills, manufacturing) given oil &amp; gas is also a named client sector.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. This company was found earlier under service-area pages for Edmonton (batch 40), Red Deer (batch 41), and Grande Prairie (batch 44) and deliberately held back each time for its correct city; now properly researched here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Sherwood Park, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Fullster Iron Ltd. (formerly Eskimo Steel Ltd.)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://fullsteriron.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel fabrication from a 20,000 sq ft facility with a Quality Management System audited to the CISC Steel Fabrication Quality Systems Guideline</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established Sherwood Park structural steel fabricator with a specific, verifiable quality certification (CISC Quality Systems Guideline audit) - a genuine technical-credibility signal distinguishing it from general fabrication shops.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (fullsteriron.com/steel-fabrication) describes structural steel fabrication with a CISC-audited Quality Management System.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Shawn Watson</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Director of Operations</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://fullsteriron.com/contact/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>mail@fullsteriron.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://fullsteriron.com/contact/ ; https://fullsteriron.com/news/new-name/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch, citing its CISC-audited quality certification as a shared quality-standards touchpoint.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Company was formerly named Eskimo Steel Ltd.; rebranded as Fullster Iron Ltd. No DNV code/standard reference was found, though the CISC Quality Systems Guideline audit is a comparable Canadian structural steel quality credential.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -95,6 +95,7 @@
     <sheet name="Leduc, AB" sheetId="90" state="visible" r:id="rId90"/>
     <sheet name="Nisku, AB" sheetId="91" state="visible" r:id="rId91"/>
     <sheet name="Sherwood Park, AB" sheetId="92" state="visible" r:id="rId92"/>
+    <sheet name="Beaumont, AB" sheetId="93" state="visible" r:id="rId93"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -187,6 +188,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="89" hidden="1">'Leduc, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="90" hidden="1">'Nisku, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="91" hidden="1">'Sherwood Park, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="92" hidden="1">'Beaumont, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14011,7 +14013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A830"/>
+  <dimension ref="A1:A836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -19467,6 +19469,41 @@
       <c r="A830" s="9" t="inlineStr">
         <is>
           <t>Structure Group Ltd., an industrial maintenance/repair contractor with a confirmed named President, was routed to Review rather than added directly: its own materials describe its specialty as industrial maintenance 'particularly in mining and refining,' and refining is a strong oil &amp; gas-processing signal without the clear multi-sector diversification seen in Terrick Enterprises. No DNV code/standard reference was found for either included company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="7" t="inlineStr">
+        <is>
+          <t>Batch 53: Beaumont, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="8" t="inlineStr">
+        <is>
+          <t>Why this city is empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="9" t="inlineStr">
+        <is>
+          <t>Multiple targeted searches (general fabrication, an Alberta-disambiguated search, and a direct check of the town's own business directory and 'Invest in Beaumont' materials) found no established welding, machining, or structural fabrication company genuinely based in Beaumont. The town's own promotional materials describe its light-industrial zones (e.g. Innovation Park) as still in development rather than an established fabrication base, and it is primarily a residential Edmonton-area bedroom community. The sheet is left empty rather than populated with an Edmonton-area company that merely lists Beaumont as part of its service area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="8" t="inlineStr">
+        <is>
+          <t>Recommended next step</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="9" t="inlineStr">
+        <is>
+          <t>Revisit Beaumont if its light-industrial development matures in future years; for now, no action items from this batch.</t>
         </is>
       </c>
     </row>
@@ -41179,4 +41216,167 @@
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -96,6 +96,7 @@
     <sheet name="Nisku, AB" sheetId="91" state="visible" r:id="rId91"/>
     <sheet name="Sherwood Park, AB" sheetId="92" state="visible" r:id="rId92"/>
     <sheet name="Beaumont, AB" sheetId="93" state="visible" r:id="rId93"/>
+    <sheet name="Camrose, AB" sheetId="94" state="visible" r:id="rId94"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -189,6 +190,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="90" hidden="1">'Nisku, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="91" hidden="1">'Sherwood Park, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="92" hidden="1">'Beaumont, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="93" hidden="1">'Camrose, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14013,7 +14015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A836"/>
+  <dimension ref="A1:A848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -19504,6 +19506,83 @@
       <c r="A836" s="9" t="inlineStr">
         <is>
           <t>Revisit Beaumont if its light-industrial development matures in future years; for now, no action items from this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="7" t="inlineStr">
+        <is>
+          <t>Batch 54: Camrose, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="9" t="inlineStr">
+        <is>
+          <t>1. Camrose Machine &amp; Welding (2014) Ltd. - Score 6, Priority B - genuinely local machine/welding shop with a clear agricultural-equipment specialty (auger flighting rebuilding) and no oilfield focus found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="9" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its structural fabrication and custom design work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only): Camrose Machine &amp; Welding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="9" t="inlineStr">
+        <is>
+          <t>4E Welding &amp; Design Inc., which surfaced prominently for its 'Structural Fabrication' service line and design-oriented name, was confirmed to be based in Aldersyde, AB (near High River), not Camrose - a distinct town not currently on this project's city list - and was not added here. No DNV code/standard reference was found for Camrose Machine &amp; Welding.</t>
         </is>
       </c>
     </row>
@@ -41379,4 +41458,275 @@
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Camrose, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Camrose Machine &amp; Welding (2014) Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.camrosemachine.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Machining, Welding &amp; Structural Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Fabrication and structural welding for stainless steel, aluminum and iron; custom design and fabrication; auger flighting rebuilding for area farms; certified mobile welding (TIG, MIG, stick, gas); custom decks and utility units</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely Camrose-based machine/welding shop with a clear agricultural-equipment specialty (auger flighting rebuilding) and no oilfield focus found - a clean general fit for this farming-region city.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (camrosemachine.ca/services) describes structural welding, custom fabrication, auger flighting rebuilding and mobile welding services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Steve Kushnerik</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Key Principal</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.camrosemachine.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (780-672-2273).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.camrosemachine.ca/ ; https://www.camrosechamber.ca/members/camrose-machine-welding-2014-ltd/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its structural fabrication and custom design work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -97,6 +97,8 @@
     <sheet name="Sherwood Park, AB" sheetId="92" state="visible" r:id="rId92"/>
     <sheet name="Beaumont, AB" sheetId="93" state="visible" r:id="rId93"/>
     <sheet name="Camrose, AB" sheetId="94" state="visible" r:id="rId94"/>
+    <sheet name="Lloydminster, AB" sheetId="95" state="visible" r:id="rId95"/>
+    <sheet name="Wetaskiwin, AB" sheetId="96" state="visible" r:id="rId96"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -191,6 +193,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="91" hidden="1">'Sherwood Park, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="92" hidden="1">'Beaumont, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="93" hidden="1">'Camrose, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="95" hidden="1">'Wetaskiwin, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -280,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -308,6 +311,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3206,7 +3212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4674,6 +4680,86 @@
       <c r="H35" s="10" t="inlineStr">
         <is>
           <t>https://www.structureind.com/who-we-are ; https://www.structureind.com/who-we-are/leadership</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Wetaskiwin, AB</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Manluk Industries Inc.</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>https://manluk.com/</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>ISO 9001-certified steel fabrication and forging company with CNC machining capability - but its Yellow Pages business category listing is specifically 'Oil Field Services,' a strong oil &amp; gas core-market signal despite the company's genuine quality certification.</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Confirm what proportion of Manluk's actual work is oilfield-specific versus general industrial fabrication before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>https://manluk.com/quality/ ; https://www.yellowpages.ca/bus/Alberta/Wetaskiwin/Manluk-Industries-2008-Inc/1008355.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Wetaskiwin, AB</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Williams Arc Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>In-shop and mobile custom welding for Central Alberta clients, including structural fabrication among its named capabilities - but one source explicitly states the company 'operates in the Oil and Gas sector,' a stronger oil &amp; gas signal than the general Central Alberta client description alone would suggest.</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Confirm the company's actual client-sector mix before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>https://www.mfg.com/manufacturer/williams-arc-welding-wetaskiwin-alberta-1409862/</t>
         </is>
       </c>
     </row>
@@ -14015,7 +14101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A848"/>
+  <dimension ref="A1:A862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -19583,6 +19669,97 @@
       <c r="A848" s="9" t="inlineStr">
         <is>
           <t>4E Welding &amp; Design Inc., which surfaced prominently for its 'Structural Fabrication' service line and design-oriented name, was confirmed to be based in Aldersyde, AB (near High River), not Camrose - a distinct town not currently on this project's city list - and was not added here. No DNV code/standard reference was found for Camrose Machine &amp; Welding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="7" t="inlineStr">
+        <is>
+          <t>Batch 55-56: Lloydminster, AB &amp; Wetaskiwin, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="8" t="inlineStr">
+        <is>
+          <t>Lloydminster, AB is a cross-reference, not new research</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="9" t="inlineStr">
+        <is>
+          <t>Lloydminster physically straddles the Alberta/Saskatchewan border and appears twice on this project's master city list - once as 'Lloydminster, SK' (row 65, researched in batch 32) and again as 'Lloydminster, AB' (row 93). Rather than duplicate research, the 'Lloydminster, AB' sheet is a short cross-reference note pointing back to the existing 'Lloydminster, SK' sheet, which already contains this city's one qualifying company (Triland Welding &amp; Machine Ltd., registered on the Alberta side).</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="8" t="inlineStr">
+        <is>
+          <t>Wetaskiwin top prospects</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="9" t="inlineStr">
+        <is>
+          <t>1. Kimto Manufacturing Co. Ltd. - Score 6, Priority B - 45-year manufacturer with a genuine engineering-adjacent specialty (custom conveyor design) and no oil &amp; gas-core positioning found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="9" t="inlineStr">
+        <is>
+          <t>For Kimto Manufacturing, lead with its custom conveyor design work - a genuine structural/mechanical engineering scope that could benefit from outside FEA support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="9" t="inlineStr">
+        <is>
+          <t>Kimto Manufacturing's custom conveyor design work is the clearest signal found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only, for Wetaskiwin): Kimto Manufacturing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="9" t="inlineStr">
+        <is>
+          <t>Two Wetaskiwin candidates were routed to Review rather than added directly: Manluk Industries Inc. (ISO 9001-certified, but categorized under 'Oil Field Services' on Yellow Pages) and Williams Arc Welding Ltd. (one source states it 'operates in the Oil and Gas sector'). Glenmore Fabricators Ltd., initially thought to be Wetaskiwin-based with a cranes/hoists specialty, was confirmed to actually be headquartered in Calgary (already covered batch 39) and was not added to either city. TG Watch Industries, found while researching Lloydminster, was confirmed to be based in North Battleford, SK (already covered batch 32) and was not added anywhere, given its industrial-container manufacturing work is a step removed from structural fabrication.</t>
         </is>
       </c>
     </row>
@@ -41729,4 +41906,324 @@
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" style="3" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1" s="3">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Lloydminster, AB is the same physical city as "Lloydminster, SK" (row 65 on the master city list, researched in batch 32).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Lloydminster straddles the Alberta/Saskatchewan border, and this project's master city list happens to list it twice, once under each province. Rather than duplicate research, this project's one qualifying company for the city - Triland Welding &amp; Machine Ltd. (family-owned since 1979, agricultural/oil/construction/trucking/commercial sectors, registered on the Alberta side of the city) - was already recorded under the "Lloydminster, SK" sheet in batch 32 and is not repeated here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>A supplementary search for this batch found no additional genuinely Lloydminster-based company beyond what batch 32 already identified. One candidate, TG Watch Industries (an industrial container manufacturer for waste management/recycling), was found to actually be based in North Battleford, SK - already covered in batch 32 - and was not added to either city given its work is a step removed from structural/heavy-industrial fabrication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>See the "Lloydminster, SK" sheet for this city's full research.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Wetaskiwin, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Kimto Manufacturing Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kimtomfg.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kimto-manufacturing-co-ltd</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel &amp; Conveyor Manufacturing</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom-designed conveyors, structural steel, custom fabrication and repairs, serving Western Canada since 1980</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (45+ years) Wetaskiwin manufacturer with a genuine engineering-adjacent specialty (custom conveyor design) alongside structural steel work - a solid fit with no oil &amp; gas-core positioning found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Custom conveyor design suggests genuine structural/mechanical engineering work that could benefit from outside FEA support on larger or more complex systems.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (kimtomfg.ca/about-us) and a Wetaskiwin News feature describe custom conveyor design, structural steel and custom fabrication since 1980.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Jeremy Belbeck</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Partner/Owner (joined 2007; became owner after founders' retirement in 2012 and 2019)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kimtomfg.ca/about-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (780-352-5727).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kimtomfg.ca/contact-us ; https://www.pipestoneflyer.ca/marketplace/if-something-needs-welding-fabricating-or-moving-this-wetaskiwin-team-makes-it-happen-6873635</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied specifically to custom conveyor design work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -99,6 +99,7 @@
     <sheet name="Camrose, AB" sheetId="94" state="visible" r:id="rId94"/>
     <sheet name="Lloydminster, AB" sheetId="95" state="visible" r:id="rId95"/>
     <sheet name="Wetaskiwin, AB" sheetId="96" state="visible" r:id="rId96"/>
+    <sheet name="Rocky Mountain House, AB" sheetId="97" state="visible" r:id="rId97"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -194,6 +195,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="92" hidden="1">'Beaumont, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="93" hidden="1">'Camrose, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="95" hidden="1">'Wetaskiwin, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="96" hidden="1">'Rocky Mountain House, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14101,7 +14103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A862"/>
+  <dimension ref="A1:A870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -19760,6 +19762,55 @@
       <c r="A862" s="9" t="inlineStr">
         <is>
           <t>Two Wetaskiwin candidates were routed to Review rather than added directly: Manluk Industries Inc. (ISO 9001-certified, but categorized under 'Oil Field Services' on Yellow Pages) and Williams Arc Welding Ltd. (one source states it 'operates in the Oil and Gas sector'). Glenmore Fabricators Ltd., initially thought to be Wetaskiwin-based with a cranes/hoists specialty, was confirmed to actually be headquartered in Calgary (already covered batch 39) and was not added to either city. TG Watch Industries, found while researching Lloydminster, was confirmed to be based in North Battleford, SK (already covered batch 32) and was not added anywhere, given its industrial-container manufacturing work is a step removed from structural fabrication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="7" t="inlineStr">
+        <is>
+          <t>Batch 57: Rocky Mountain House, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="9" t="inlineStr">
+        <is>
+          <t>1. Metal Industries Welding &amp; Fabrication Corp. - Score 4, Priority C - the one confirmed genuinely locally-based welding/fabrication company, with no named contact found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="9" t="inlineStr">
+        <is>
+          <t>McCrea's Welding Ltd., which appeared prominently in search results for its 'forestry industry fabrication' service page, was confirmed to actually be based in Campbell River, BC (already covered in this project, batch 15) - not added here. Bunch Clearwater Fabrication Facility, also based in Rocky Mountain House, was excluded outright given its confirmed core focus on oil and gas construction, a clear-cut case rather than a borderline one. No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only, with caution given the thin evidence): Metal Industries Welding &amp; Fabrication Corp.</t>
         </is>
       </c>
     </row>
@@ -42226,4 +42277,259 @@
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet97.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Rocky Mountain House, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Metal Industries Welding &amp; Fabrication Corp.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Aluminum welding, CNC high-definition plasma cutting and bending services</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>The one confirmed genuinely Rocky Mountain House-based welding/fabrication company found in this pass - a modest general fit with no oilfield-only positioning found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (Canpages, 411.ca, Facebook) describe aluminum welding, CNC plasma cutting and bending services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (403-846-6927).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.canpages.ca/page/AB/rocky-mountain-house/metal-industries-welding/101188728</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm named contact and client-sector mix before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. McCrea's Welding Ltd., initially thought to be Rocky Mountain House-based due to a 'forestry industry fabrication' service page, was confirmed to actually be based in Campbell River, BC (already covered in batch 15) - not added here. Bunch Clearwater Fabrication Facility, also found in Rocky Mountain House, was excluded outright given its confirmed core focus on oil and gas construction.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -100,6 +100,7 @@
     <sheet name="Lloydminster, AB" sheetId="95" state="visible" r:id="rId95"/>
     <sheet name="Wetaskiwin, AB" sheetId="96" state="visible" r:id="rId96"/>
     <sheet name="Rocky Mountain House, AB" sheetId="97" state="visible" r:id="rId97"/>
+    <sheet name="Drayton Valley, AB" sheetId="98" state="visible" r:id="rId98"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -196,6 +197,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="93" hidden="1">'Camrose, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="95" hidden="1">'Wetaskiwin, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="96" hidden="1">'Rocky Mountain House, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="97" hidden="1">'Drayton Valley, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3214,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -4762,6 +4764,48 @@
       <c r="H37" s="10" t="inlineStr">
         <is>
           <t>https://www.mfg.com/manufacturer/williams-arc-welding-wetaskiwin-alberta-1409862/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Drayton Valley, AB</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Big West Machine &amp; Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>https://bigwestmachine.com/</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>17,000 sq ft facility offering welding, custom metal fabrication, CNC machining, and mobile welding crews that assist forestry, agriculture and ranching operations - but the company's own website is titled 'Welding, Metal Fabrication, CNC, Rig Maintenance Alberta,' it is listed on an oilfield-specific business directory (Oilgaspages), and its own materials describe serving 'the energy and manufacturing sectors' - together a stronger oil &amp; gas signal than the forestry/agriculture work alone would suggest.</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Confirm what proportion of Big West's actual work is rig-maintenance/energy-sector-specific versus forestry/agriculture/ranching before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>https://bigwestmachine.com/ ; https://oilgaspages.com/ca/details/big-west-machine-MTQ1NQ</t>
         </is>
       </c>
     </row>
@@ -14103,7 +14147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A870"/>
+  <dimension ref="A1:A882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -19811,6 +19855,83 @@
       <c r="A870" s="9" t="inlineStr">
         <is>
           <t>Contact first (and only, with caution given the thin evidence): Metal Industries Welding &amp; Fabrication Corp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="7" t="inlineStr">
+        <is>
+          <t>Batch 58: Drayton Valley, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="9" t="inlineStr">
+        <is>
+          <t>1. Advantage Manufacturing Ltd. - Score 6, Priority B - agricultural-equipment fabrication specialist with no oilfield-only positioning found and a directly confirmed named owner and email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="9" t="inlineStr">
+        <is>
+          <t>Approach Kelly Colwell directly with a structural/FEA overflow pitch tied to agricultural equipment/storage structural steel work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only, for direct outreach): Advantage Manufacturing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="9" t="inlineStr">
+        <is>
+          <t>Big West Machine &amp; Welding Ltd. - a well-equipped 17,000 sq ft shop with genuine forestry/agriculture/ranching mobile welding work - was routed to Review rather than added directly: its own website is titled 'Rig Maintenance Alberta,' it appears on an oilfield-specific business directory (Oilgaspages), and its materials describe serving 'the energy and manufacturing sectors,' together a stronger oil &amp; gas signal than its forestry/agriculture work alone would suggest. No DNV code/standard reference was found for Advantage Manufacturing.</t>
         </is>
       </c>
     </row>
@@ -42532,4 +42653,279 @@
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet98.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Drayton Valley, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Advantage Manufacturing Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.advantagemanufacturingltd.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Custom Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom steel fabrication for agricultural equipment and storage; manual cutting of plate and structural steel, bending and forming, certified welding, serving Drayton Valley and Edmonton</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely Drayton Valley-based custom fabricator with an explicit agricultural-equipment specialty and no oilfield-only positioning found - a clean general fit for this forestry/agriculture-adjacent region, with a directly confirmed named owner and email.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (advantagemanufacturingltd.com/fabrication) describes structural steel cutting, bending and forming for agricultural equipment and storage.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Kelly Colwell</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner/Manager</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.advantagemanufacturingltd.com/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>kelly@amltd.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Direct, unmasked email for a named individual, sourced from the company's own listing - a genuinely confirmed contact.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.advantagemanufacturingltd.com/contact-us ; https://www.bbb.org/ca/ab/drayton-valley/profile/welding/advantage-manufacturing-ltd-0017-192314</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly with a structural/FEA overflow pitch tied to its agricultural equipment/storage structural steel work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -101,6 +101,7 @@
     <sheet name="Wetaskiwin, AB" sheetId="96" state="visible" r:id="rId96"/>
     <sheet name="Rocky Mountain House, AB" sheetId="97" state="visible" r:id="rId97"/>
     <sheet name="Drayton Valley, AB" sheetId="98" state="visible" r:id="rId98"/>
+    <sheet name="Grande Cache, AB" sheetId="99" state="visible" r:id="rId99"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -198,6 +199,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="95" hidden="1">'Wetaskiwin, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="96" hidden="1">'Rocky Mountain House, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="97" hidden="1">'Drayton Valley, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="98" hidden="1">'Grande Cache, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14147,7 +14149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A882"/>
+  <dimension ref="A1:A895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -19932,6 +19934,90 @@
       <c r="A882" s="9" t="inlineStr">
         <is>
           <t>Big West Machine &amp; Welding Ltd. - a well-equipped 17,000 sq ft shop with genuine forestry/agriculture/ranching mobile welding work - was routed to Review rather than added directly: its own website is titled 'Rig Maintenance Alberta,' it appears on an oilfield-specific business directory (Oilgaspages), and its materials describe serving 'the energy and manufacturing sectors,' together a stronger oil &amp; gas signal than its forestry/agriculture work alone would suggest. No DNV code/standard reference was found for Advantage Manufacturing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="7" t="inlineStr">
+        <is>
+          <t>Batch 59: Grande Cache, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="9" t="inlineStr">
+        <is>
+          <t>1. CC's Welding and Fabrication Ltd. - Score 6, Priority B - Grande Cache's longest-serving welder (since 2007), with a genuinely diversified four-sector client base and wide regional mobile service reach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="9" t="inlineStr">
+        <is>
+          <t>2. Aseniwuche Development Corporation (ADC) - Score 6, Priority B - Indigenous-owned contractor with a distinct Welding &amp; Fabrication division separated from its Energy Field Services division.</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="9" t="inlineStr">
+        <is>
+          <t>For ADC, approach specifically through the Welding &amp; Fabrication division, mirroring the divisional-separation approach used for Stewart Steel (batch 34).</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: CC's Welding and Fabrication and Aseniwuche Development Corporation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="9" t="inlineStr">
+        <is>
+          <t>No location mismatches or defense exclusions arose this batch. No DNV code/standard reference was found for either company.</t>
         </is>
       </c>
     </row>
@@ -42928,4 +43014,375 @@
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet99.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Grande Cache, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CC's Welding and Fabrication Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://ccsweldingandfabrication.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Fabrication and repair services for oil &amp; gas, mining, forestry &amp; logging, and power generation industries, with a mobile service department covering Grande Cache, Grande Prairie, Edson, Hinton, Fox Creek, Grovedale, Valleyview and Red Deer</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established (since 2007) Grande Cache's longest-serving welding company with a genuinely diversified four-sector client base (oil &amp; gas, mining, forestry &amp; logging, power generation) and a wide regional mobile service area - a solid general fit given the diversification.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (ccsweldingandfabrication.ca) describes fabrication and repair services for oil &amp; gas, mining, forestry &amp; logging and power generation clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://ccsweldingandfabrication.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>ccweldandfab@gmail.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://ccsweldingandfabrication.ca/ ; https://www.facebook.com/ccsweldingandfab/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch framed around its mining, forestry and power-generation work given oil &amp; gas is one of four named sectors.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Grande Cache, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Aseniwuche Development Corporation (ADC)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.adcalberta.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/aseniwuche-development-corporation</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company (Indigenous-owned)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>General Contracting &amp; Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>State-of-the-art welding and fabrication facility operating through three distinct divisions: Welding &amp; Fabrication, Automotive, and Energy Field Services</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Indigenous-owned (tied to the Aseniwuche Winewak Nation) Grande Cache contractor with a genuinely separate Welding &amp; Fabrication division distinct from its Energy Field Services division - a structurally clearer case than most multi-sector fabricators in this project, similar to Stewart Steel (batch 34).</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (adcalberta.com) and its parent organization's site (aseniwuche.ca/adc-and-aec) describe three distinct operating divisions including Welding &amp; Fabrication.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.adcalberta.com/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass; company has a website but no direct email address was displayed in search results.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.adcalberta.com/ ; https://www.aseniwuche.ca/adc-and-aec/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach specifically through the Welding &amp; Fabrication division rather than Energy Field Services, given the company's own divisional separation.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -102,6 +102,7 @@
     <sheet name="Rocky Mountain House, AB" sheetId="97" state="visible" r:id="rId97"/>
     <sheet name="Drayton Valley, AB" sheetId="98" state="visible" r:id="rId98"/>
     <sheet name="Grande Cache, AB" sheetId="99" state="visible" r:id="rId99"/>
+    <sheet name="Hinton, AB" sheetId="100" state="visible" r:id="rId100"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -200,6 +201,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="96" hidden="1">'Rocky Mountain House, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="97" hidden="1">'Drayton Valley, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="98" hidden="1">'Grande Cache, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="99" hidden="1">'Hinton, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3212,6 +3214,269 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Hinton, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Summit Machining &amp; Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.summitmachining.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Machining, Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Equipment repairs, portable welding, steel sales and complete machine shop services for mining, lumber, pulp, oil &amp; gas and construction industries</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Certified Hinton fabrication shop with a genuinely diversified five-sector client base (mining, lumber, pulp, oil &amp; gas, construction) - a solid general fit for this pulp-mill/forestry region, with oil &amp; gas as one of several markets.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (summitmachining.com) describes equipment repairs, portable welding and machine shop services for mining, lumber, pulp, oil &amp; gas and construction clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.summitmachining.com/contact/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (780-865-7770).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.summitmachining.com/contact/ ; https://www.canpages.ca/page/AB/hinton/summit-machining-welding-ltd/2560338</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch framed around its lumber, pulp and mining work, given oil &amp; gas is one of five named sectors.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. Quadra Industrial Group, a multi-location machining/fabricating/millwrighting company with a Hinton facility, also operates in Cochrane and Sundre, AB - Cochrane is a later city on this project's master list, so Quadra was deliberately held back for proper research there rather than added here.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -14149,7 +14414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A895"/>
+  <dimension ref="A1:A907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -20018,6 +20283,83 @@
       <c r="A895" s="9" t="inlineStr">
         <is>
           <t>No location mismatches or defense exclusions arose this batch. No DNV code/standard reference was found for either company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="7" t="inlineStr">
+        <is>
+          <t>Batch 60: Hinton, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="9" t="inlineStr">
+        <is>
+          <t>1. Summit Machining &amp; Welding Ltd. - Score 6, Priority B - certified fabrication shop with a genuinely diversified five-sector client base (mining, lumber, pulp, oil &amp; gas, construction).</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="9" t="inlineStr">
+        <is>
+          <t>Frame outreach around lumber, pulp and mining work given oil &amp; gas is one of five named sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only): Summit Machining &amp; Welding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="9" t="inlineStr">
+        <is>
+          <t>Quadra Industrial Group, a multi-location machining/fabricating/millwrighting company with a Hinton facility, also operates in Cochrane and Sundre, AB; Cochrane appears later on this project's master list, so Quadra was deliberately held back for proper research there rather than added here. No DNV code/standard reference was found for Summit Machining &amp; Welding.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -103,6 +103,7 @@
     <sheet name="Drayton Valley, AB" sheetId="98" state="visible" r:id="rId98"/>
     <sheet name="Grande Cache, AB" sheetId="99" state="visible" r:id="rId99"/>
     <sheet name="Hinton, AB" sheetId="100" state="visible" r:id="rId100"/>
+    <sheet name="Edson, AB" sheetId="101" state="visible" r:id="rId101"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -202,6 +203,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="97" hidden="1">'Drayton Valley, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="98" hidden="1">'Grande Cache, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="99" hidden="1">'Hinton, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="100" hidden="1">'Edson, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3477,6 +3479,261 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet101.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Edson, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Welco Welding Maintenance Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Fabrication &amp; Millwright Services</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Fabrication and welding, machining, equipment overhauls, millwright services and field service</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>The one confirmed genuinely Edson-based welding/fabrication company found in this pass - a modest general fit with no named contact or specific sector detail confirmed.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (COSSD) describe fabrication, welding, machining, equipment overhauls, millwright and field services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email or named contact found in this pass. Only phone confirmed (780-723-4505).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cossd.com/l/edson-ab/welding</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm named contact and client-sector mix before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. Edvan Custom Metal Processing Ltd., which surfaced prominently for its forestry/construction/agriculture focus, was confirmed to actually be based in Nisku, AB (already covered in batch 51), not Edson - not added here. Battle River Ironworks Inc. was also found but is based in Forestburg, AB, a town not currently on this project's city list and not genuinely near Edson - not added anywhere.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -14414,7 +14671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A907"/>
+  <dimension ref="A1:A915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -20360,6 +20617,55 @@
       <c r="A907" s="9" t="inlineStr">
         <is>
           <t>Quadra Industrial Group, a multi-location machining/fabricating/millwrighting company with a Hinton facility, also operates in Cochrane and Sundre, AB; Cochrane appears later on this project's master list, so Quadra was deliberately held back for proper research there rather than added here. No DNV code/standard reference was found for Summit Machining &amp; Welding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="7" t="inlineStr">
+        <is>
+          <t>Batch 61: Edson, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="9" t="inlineStr">
+        <is>
+          <t>1. Welco Welding Maintenance Services Ltd. - Score 4, Priority C - the one confirmed genuinely local fabricator, with limited available detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="9" t="inlineStr">
+        <is>
+          <t>Edvan Custom Metal Processing Ltd., a promising forestry/construction/agriculture-focused fabricator that surfaced prominently for this search, was confirmed to actually be based in Nisku, AB (already covered in batch 51) - not added here. Battle River Ironworks Inc. was also found but is based in Forestburg, AB, a distinct town not currently on this project's city list and not genuinely near Edson - not added anywhere. No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only, with caution given thin evidence): Welco Welding Maintenance Services.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -104,6 +104,7 @@
     <sheet name="Grande Cache, AB" sheetId="99" state="visible" r:id="rId99"/>
     <sheet name="Hinton, AB" sheetId="100" state="visible" r:id="rId100"/>
     <sheet name="Edson, AB" sheetId="101" state="visible" r:id="rId101"/>
+    <sheet name="Whitecourt, AB" sheetId="102" state="visible" r:id="rId102"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -204,6 +205,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="98" hidden="1">'Grande Cache, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="99" hidden="1">'Hinton, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="100" hidden="1">'Edson, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="101" hidden="1">'Whitecourt, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3734,6 +3736,377 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet102.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Whitecourt, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>C-5 Chadd Contractors Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.c5chadd.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company (family-owned)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial Design, Machining, Welding &amp; Millwright Services</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Industrial design, machining, welding, fabrication and millwright support for lumber mills, power plants, paper mills, OSB facilities, agricultural operations and heavy industrial sites</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Second-generation family-owned contractor with a genuine in-house design capability alongside fabrication and millwright work, serving Whitecourt and surrounding communities - one of the stronger engineering-adjacent fits found in this project's Alberta interior batches, with no oil &amp; gas exposure found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>In-house design service alongside fabrication/millwright work for mills and power plants is a direct, evidence-based overflow-FEA pathway (structural verification, equipment design collaboration) rather than an inferred one.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (c5chadd.ca/design-machine-welding-services) describes design, machining, welding, fabrication and millwright services for lumber mills, power plants, paper mills, OSB facilities and agricultural operations.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Lowell Chadd &amp; Quentin Chadd</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Co-Owners (second-generation family ownership)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.c5chadd.ca/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Address confirmed (58126 Range Road 72, Sangudo, AB).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.c5chadd.ca/contact-us ; https://www.c5chadd.ca/our-capabilities</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly with a structural/FEA overflow pitch tied to its in-house design service for mills and power plants - the clearest engineering-adjacent signal found in this batch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>The company's registered address is in Sangudo, AB, a small community not currently on this project's city list; it was recorded under Whitecourt since that is the largest city it serves and the primary hub of its stated service area (Whitecourt, Blue Ridge, Fox Creek, Slave Lake, Edson, Mayerthorpe, Barrhead, Sangudo, High Prairie). No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Whitecourt, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Schaffer's Custom Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.schafferswelding.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company (family-owned)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Piping &amp; Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>In-house piping and structural steel fabrication, plus portable, structural and pressure welding, serving Whitecourt for 20+ years</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established, genuinely Whitecourt-based family fabricator with structural steel work explicitly named among its services - a solid general fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (schafferswelding.ca) describes piping and structural steel fabrication, plus portable, structural and pressure welding services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.schafferswelding.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (780-778-5611).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.schafferswelding.ca/ ; https://www.cossd.com/biz/14019/schaffers-custom-welding-ltd</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its structural steel fabrication work.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -14671,7 +15044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A915"/>
+  <dimension ref="A1:A928"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -20666,6 +21039,90 @@
       <c r="A915" s="9" t="inlineStr">
         <is>
           <t>Contact first (and only, with caution given thin evidence): Welco Welding Maintenance Services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="7" t="inlineStr">
+        <is>
+          <t>Batch 62: Whitecourt, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="9" t="inlineStr">
+        <is>
+          <t>1. C-5 Chadd Contractors Ltd. - Score 7, Priority A - second-generation family contractor with a genuine in-house design capability for lumber mills and power plants, one of the stronger engineering-adjacent fits found in this project's Alberta interior batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="9" t="inlineStr">
+        <is>
+          <t>2. Schaffer's Custom Welding Ltd. - Score 6, Priority B - established (20+ years), genuinely Whitecourt-based structural steel fabricator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="9" t="inlineStr">
+        <is>
+          <t>For C-5 Chadd Contractors, lead directly with structural/FEA support for its in-house design service on mills and power-plant projects - a direct, evidence-based fit rather than an inferred one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="9" t="inlineStr">
+        <is>
+          <t>C-5 Chadd Contractors' in-house design service is the clearest signal found this batch, comparable to Northweld Welding &amp; Fabrication (batch 45) and Steelhead Fabrication (batch 51).</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: C-5 Chadd Contractors. Schaffer's Custom Welding as a close secondary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="9" t="inlineStr">
+        <is>
+          <t>C-5 Chadd Contractors' registered address is in Sangudo, AB, a small community not on this project's city list; it was recorded under Whitecourt since that is the largest city in its named service area, similar to the Priority Steel Erectors treatment in batch 23. Universe Machine Corporation, which surfaced again in this search, was already confirmed as Edmonton-based (batches 40 and 44) and not added here. No DNV code/standard reference was found for either included company.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -105,6 +105,7 @@
     <sheet name="Hinton, AB" sheetId="100" state="visible" r:id="rId100"/>
     <sheet name="Edson, AB" sheetId="101" state="visible" r:id="rId101"/>
     <sheet name="Whitecourt, AB" sheetId="102" state="visible" r:id="rId102"/>
+    <sheet name="Peace River, AB" sheetId="103" state="visible" r:id="rId103"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -206,6 +207,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="99" hidden="1">'Hinton, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="100" hidden="1">'Edson, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="101" hidden="1">'Whitecourt, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="102" hidden="1">'Peace River, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4107,6 +4109,385 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet103.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Peace River, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Ace Machining &amp; Welding (Peace River) Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.acemachiningandwelding.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Machining, Welding &amp; Custom Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>In-house machine shop; custom fabrication and welding of steel, aluminum, trailers and drive shafts, plus hitch installation; COR/SECOR safety certified</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely Peace River-based machine/welding shop with no oilfield-only positioning found and a confirmed named President - a clean general fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (acemachiningandwelding.ca/services) describes custom fabrication and welding for steel, aluminum, trailers and drive shafts.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Gilles Legace</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.acemachiningandwelding.ca/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@acemachiningandwelding.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.acemachiningandwelding.ca/contact-us ; https://www.peaceriver.ca/business-development/business-directory/ace-machine-welding-pr-ltd</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its custom fabrication capability.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Peace River, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Channico Machine &amp; Millwright Services Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.channico.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Fabrication, Machining &amp; Millwright Services</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Fabrication and welding, machining, equipment overhauls, millwright services, field service, 24-hour emergency service and plant startups</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely Peace River-based small fabrication/millwright company with no oilfield-only positioning found; a general fit, though its small scale (1-4 employees) limits capacity for larger overflow projects.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (channico.ca) describes fabrication, welding, machining, equipment overhauls and millwright services.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.channico.ca/contact-us</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>Info@channico.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.channico.ca/contact-us ; https://www.peaceriver.ca/business-development/business-directory/channico-machine-millwright-services-ltd</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up given the company's small scale; confirm named contact before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -15044,7 +15425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A928"/>
+  <dimension ref="A1:A941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -21123,6 +21504,90 @@
       <c r="A928" s="9" t="inlineStr">
         <is>
           <t>C-5 Chadd Contractors' registered address is in Sangudo, AB, a small community not on this project's city list; it was recorded under Whitecourt since that is the largest city in its named service area, similar to the Priority Steel Erectors treatment in batch 23. Universe Machine Corporation, which surfaced again in this search, was already confirmed as Edmonton-based (batches 40 and 44) and not added here. No DNV code/standard reference was found for either included company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="7" t="inlineStr">
+        <is>
+          <t>Batch 63: Peace River, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch, ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="9" t="inlineStr">
+        <is>
+          <t>1. Ace Machining &amp; Welding (Peace River) Ltd. - Score 6, Priority B - genuinely local machine/welding shop with a confirmed named President and no oilfield-only positioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="9" t="inlineStr">
+        <is>
+          <t>2. Channico Machine &amp; Millwright Services Ltd. - Score 5, Priority C - genuinely local small fabricator/millwright company; small scale limits its capacity for larger overflow projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="9" t="inlineStr">
+        <is>
+          <t>For Ace Machining &amp; Welding, approach Gilles Legace directly with a structural/FEA overflow pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Ace Machining &amp; Welding. Channico Machine &amp; Millwright Services as a lower-priority follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="9" t="inlineStr">
+        <is>
+          <t>Weaver Group Limited, a Peace River-based pipeline and facilities construction company, was excluded outright rather than routed to Review: its own history describes growing with 'the expanding oil and gas sector' as its core business, a clear-cut oil &amp; gas exclusion case. No DNV code/standard reference was found for either included company.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -106,6 +106,7 @@
     <sheet name="Edson, AB" sheetId="101" state="visible" r:id="rId101"/>
     <sheet name="Whitecourt, AB" sheetId="102" state="visible" r:id="rId102"/>
     <sheet name="Peace River, AB" sheetId="103" state="visible" r:id="rId103"/>
+    <sheet name="High Level, AB" sheetId="104" state="visible" r:id="rId104"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -208,6 +209,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="100" hidden="1">'Edson, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="101" hidden="1">'Whitecourt, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="102" hidden="1">'Peace River, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="103" hidden="1">'High Level, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4488,6 +4490,169 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet104.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -15425,7 +15590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A941"/>
+  <dimension ref="A1:A947"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -21588,6 +21753,41 @@
       <c r="A941" s="9" t="inlineStr">
         <is>
           <t>Weaver Group Limited, a Peace River-based pipeline and facilities construction company, was excluded outright rather than routed to Review: its own history describes growing with 'the expanding oil and gas sector' as its core business, a clear-cut oil &amp; gas exclusion case. No DNV code/standard reference was found for either included company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="7" t="inlineStr">
+        <is>
+          <t>Batch 64: High Level, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="8" t="inlineStr">
+        <is>
+          <t>Why this city is empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="9" t="inlineStr">
+        <is>
+          <t>Multiple targeted searches (general fabrication, direct city-name search) found no locally-based welding, machining, or structural fabrication company - only companies based in other Alberta towns (Drayton Valley, Peace River, Southern Alberta) that came up in broader regional searches. This very small, remote northern Alberta town (near the NWT border) appears to lack an established fabrication sector of its own, similar to other remote northern towns found empty in this project (e.g. Fort Nelson, BC and La Ronge, SK).</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="9" t="inlineStr">
+        <is>
+          <t>SLS Metalworks &amp; Fabricating, an Indigenous-owned (seven First Nations) company that surfaced under a 'High Level, Alberta' search, was confirmed to actually be headquartered in Bonnyville, AB with operations in Cold Lake, AB - both later cities on this project's master list - and was deliberately held back for proper research there rather than added here. Notably, it is described as 'a division of Seven Lakes Oilfield Services Corporation,' a signal worth flagging when that city is researched.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -107,6 +107,7 @@
     <sheet name="Whitecourt, AB" sheetId="102" state="visible" r:id="rId102"/>
     <sheet name="Peace River, AB" sheetId="103" state="visible" r:id="rId103"/>
     <sheet name="High Level, AB" sheetId="104" state="visible" r:id="rId104"/>
+    <sheet name="Cold Lake, AB" sheetId="105" state="visible" r:id="rId105"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -210,6 +211,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="101" hidden="1">'Whitecourt, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="102" hidden="1">'Peace River, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="103" hidden="1">'High Level, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="104" hidden="1">'Cold Lake, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4653,13 +4655,280 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet105.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Cold Lake, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>True Metalworks</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://truemetalworks.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Machining &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, machining, line boring, fabrication and repairs, both in-shop and portable, led by a Red Seal Machinist &amp; Welder with 20+ years of experience</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely local, independently owned Cold Lake metal shop with no oilfield-only positioning found - a clean general fit with a directly confirmed general contact email.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (truemetalworks.ca) and social media describe welding, machining, line boring, fabrication and repair services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.truemetalworks.com/contact</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>truemetalworkscoldlake@gmail.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://truemetalworks.ca/ ; https://www.facebook.com/people/True-Metalworks/61555719535631/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its machining/fabrication capability.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -6249,6 +6518,48 @@
       <c r="H38" s="10" t="inlineStr">
         <is>
           <t>https://bigwestmachine.com/ ; https://oilgaspages.com/ca/details/big-west-machine-MTQ1NQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Cold Lake, AB</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>SLS Metalworks &amp; Fabricating</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>https://slsfab.ca/</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>CWB-certified structural steel fabrication, custom welding, brake and shear services, galvanizing and powder coating, with locations in Cold Lake and Bonnyville, AB - genuinely relevant services on their own, and Indigenous-owned (seven First Nations) - but the company is explicitly described as 'a division of Seven Lakes Oilfield Services Corporation,' making its parent company's core business oilfield services even though the fabrication division's own service list does not name oil &amp; gas exclusively.</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Confirm what proportion of SLS Metalworks' actual client base is oilfield-related through its parent company relationship versus genuinely independent structural fabrication work before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>https://slsfab.ca/about/ ; https://slsfab.ca/indigenous-owned-services/</t>
         </is>
       </c>
     </row>
@@ -15590,7 +15901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A947"/>
+  <dimension ref="A1:A959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -21788,6 +22099,83 @@
       <c r="A947" s="9" t="inlineStr">
         <is>
           <t>SLS Metalworks &amp; Fabricating, an Indigenous-owned (seven First Nations) company that surfaced under a 'High Level, Alberta' search, was confirmed to actually be headquartered in Bonnyville, AB with operations in Cold Lake, AB - both later cities on this project's master list - and was deliberately held back for proper research there rather than added here. Notably, it is described as 'a division of Seven Lakes Oilfield Services Corporation,' a signal worth flagging when that city is researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="7" t="inlineStr">
+        <is>
+          <t>Batch 65: Cold Lake, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="9" t="inlineStr">
+        <is>
+          <t>1. True Metalworks - Score 6, Priority B - independently owned, Red Seal-led metal shop with no oilfield-only positioning and a confirmed general contact email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="9" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its machining/fabrication capability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only): True Metalworks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="9" t="inlineStr">
+        <is>
+          <t>SLS Metalworks &amp; Fabricating - the Indigenous-owned (seven First Nations) company deferred from batch 64 (High Level) - was routed to Review rather than added directly: its structural fabrication services and CWB certification are genuinely relevant, but the company is explicitly described as 'a division of Seven Lakes Oilfield Services Corporation,' a parent-company signal that warrants confirming how independent the fabrication division's actual client base is. Terrick Enterprises Ltd. (already recorded under Sherwood Park, batch 52) and Sea-Can Containers Ltd. (Edmonton-headquartered container supplier, batch 40) both surfaced again for Cold Lake but were not duplicated or added, the latter because container sales/rental is a step removed from structural fabrication. No DNV code/standard reference was found for True Metalworks.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -108,6 +108,7 @@
     <sheet name="Peace River, AB" sheetId="103" state="visible" r:id="rId103"/>
     <sheet name="High Level, AB" sheetId="104" state="visible" r:id="rId104"/>
     <sheet name="Cold Lake, AB" sheetId="105" state="visible" r:id="rId105"/>
+    <sheet name="Bonnyville, AB" sheetId="106" state="visible" r:id="rId106"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -212,6 +213,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="102" hidden="1">'Peace River, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="103" hidden="1">'High Level, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="104" hidden="1">'Cold Lake, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="105" hidden="1">'Bonnyville, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4922,6 +4924,389 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet106.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Bonnyville, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Canadian Fabrication Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://canadianfabrication.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Locally owned and operated welding and fabrication services</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely local, independently owned Bonnyville fabricator with no oilfield-only positioning found and a confirmed named owner - a clean general fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Directory listings (Town of Bonnyville business directory, Facebook) describe locally owned welding and fabrication services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Dwayne Langer</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://canadianfabrication.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (780-812-2430).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://town.bonnyville.ab.ca/directory/business-directory/canadian-fabrication/ ; https://www.yellowpages.ca/bus/Alberta/Bonnyville/Canadian-Fabrication-Ltd/101909963.html</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its general fabrication capability.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Bonnyville, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>BrightSide Fabrication</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.brightsidefabrication.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Custom Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Precision TIG welding and custom fabrication in aluminum, steel, stainless and other alloys for the oilfield and agriculture sectors</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Bonnyville custom fabrication shop, but its own service description names only two sectors (oilfield first, agriculture second) - a thinner diversification signal than most other included companies in this project.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (brightsidefabrication.com) and directory listings describe TIG welding and custom fabrication for oilfield and agriculture clients.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Jeff Lemay</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Owner (per one source; a separate LinkedIn profile also names Tyler Thomson as Owner - not reconciled)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.brightsidefabrication.com/contact-us</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@brightsidefabrication.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.brightsidefabrication.com/contact-us ; https://ca.linkedin.com/in/tyler-thomson-024a52112</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>If pursued, frame outreach narrowly around agricultural fabrication work, given oilfield is named first among only two served sectors; confirm current ownership before outreach.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -15901,7 +16286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A959"/>
+  <dimension ref="A1:A972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -22176,6 +22561,90 @@
       <c r="A959" s="9" t="inlineStr">
         <is>
           <t>SLS Metalworks &amp; Fabricating - the Indigenous-owned (seven First Nations) company deferred from batch 64 (High Level) - was routed to Review rather than added directly: its structural fabrication services and CWB certification are genuinely relevant, but the company is explicitly described as 'a division of Seven Lakes Oilfield Services Corporation,' a parent-company signal that warrants confirming how independent the fabrication division's actual client base is. Terrick Enterprises Ltd. (already recorded under Sherwood Park, batch 52) and Sea-Can Containers Ltd. (Edmonton-headquartered container supplier, batch 40) both surfaced again for Cold Lake but were not duplicated or added, the latter because container sales/rental is a step removed from structural fabrication. No DNV code/standard reference was found for True Metalworks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="7" t="inlineStr">
+        <is>
+          <t>Batch 66: Bonnyville, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="9" t="inlineStr">
+        <is>
+          <t>1. Canadian Fabrication Ltd. - Score 6, Priority B - independently owned local fabricator with no oilfield-only positioning and a confirmed named owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="9" t="inlineStr">
+        <is>
+          <t>2. BrightSide Fabrication - Score 4, Priority C - custom TIG welding shop, but its own service description names only two sectors (oilfield first, agriculture second), a thinner diversification signal than most included companies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="9" t="inlineStr">
+        <is>
+          <t>For BrightSide Fabrication, if pursued, frame outreach narrowly around agricultural fabrication work rather than a generic industrial pitch, given the thin sector diversification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Canadian Fabrication. BrightSide Fabrication as a lower-priority follow-up, contingent on confirming its sector balance and current ownership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="9" t="inlineStr">
+        <is>
+          <t>SLS Metalworks &amp; Fabricating's Bonnyville location was already routed to Review under Cold Lake (batch 65), given its 'Seven Lakes Oilfield Services Corporation' parent company - not duplicated here. A. Amyotte &amp; Son Welding Ltd. was found but is based in Mallaig, AB, a distinct small community not currently on this project's city list and with no clear larger city to attribute it to - not added here. No DNV code/standard reference was found for either included company.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -109,6 +109,7 @@
     <sheet name="High Level, AB" sheetId="104" state="visible" r:id="rId104"/>
     <sheet name="Cold Lake, AB" sheetId="105" state="visible" r:id="rId105"/>
     <sheet name="Bonnyville, AB" sheetId="106" state="visible" r:id="rId106"/>
+    <sheet name="Brooks, AB" sheetId="107" state="visible" r:id="rId107"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -214,6 +215,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="103" hidden="1">'High Level, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="104" hidden="1">'Cold Lake, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="105" hidden="1">'Bonnyville, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="106" hidden="1">'Brooks, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5307,13 +5309,292 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet107.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Brooks, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Brooks Industrial Metals Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://brooksindustrialmetals.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/brooks-industrial-metals-ltd-</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Metal Distribution &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Full-service metal distributor, fabrication shop and welding supply distributor; shearing, bending, rolling, laser cutting, waterjet cutting, CNC flame and plasma cutting</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Well-equipped Brooks fabricator with a broad in-house processing capability (laser/waterjet/plasma cutting) and no oilfield-only positioning found - a solid general fit with a directly confirmed named owner.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (brooksindustrialmetals.com) describes a full-service fabrication shop with shearing, bending, rolling and various cutting capabilities.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>John Duenk</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://brooksindustrialmetals.com/contact/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@brooksindustrialmetals.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); John Duenk's personal email is listed only in masked form on directory sites and was not used.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://brooksindustrialmetals.com/contact/ ; https://www.zoominfo.com/p/John-Duenk/389873667</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its fabrication and processing capability.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -6945,6 +7226,48 @@
       <c r="H39" s="10" t="inlineStr">
         <is>
           <t>https://slsfab.ca/about/ ; https://slsfab.ca/indigenous-owned-services/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Brooks, AB</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>DaPaJo Construction Ltd.</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>https://www.dapajo.ca/</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Metal fabrication and machinery manufacturing company in Brooks - but its own service list includes 'well abandonment' (an oil &amp; gas well decommissioning service), a specific and unambiguous oilfield-services signal alongside pressure vessel installation and custom plate rolling.</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Confirm what proportion of DaPaJo's actual work is oilfield/well-abandonment-specific versus general metal fabrication before deciding whether this is a hard oil &amp; gas exclusion case.</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>https://www.dapajo.ca/</t>
         </is>
       </c>
     </row>
@@ -16286,7 +16609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A972"/>
+  <dimension ref="A1:A984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -22645,6 +22968,83 @@
       <c r="A972" s="9" t="inlineStr">
         <is>
           <t>SLS Metalworks &amp; Fabricating's Bonnyville location was already routed to Review under Cold Lake (batch 65), given its 'Seven Lakes Oilfield Services Corporation' parent company - not duplicated here. A. Amyotte &amp; Son Welding Ltd. was found but is based in Mallaig, AB, a distinct small community not currently on this project's city list and with no clear larger city to attribute it to - not added here. No DNV code/standard reference was found for either included company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="7" t="inlineStr">
+        <is>
+          <t>Batch 67: Brooks, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="9" t="inlineStr">
+        <is>
+          <t>1. Brooks Industrial Metals Ltd. - Score 6, Priority B - well-equipped full-service fabricator (laser/waterjet/plasma cutting) with a confirmed named owner and no oilfield-only positioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="9" t="inlineStr">
+        <is>
+          <t>Approach John Duenk directly with a structural/FEA overflow pitch tied to its fabrication and processing capability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="9" t="inlineStr">
+        <is>
+          <t>Contact first (and only): Brooks Industrial Metals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="9" t="inlineStr">
+        <is>
+          <t>DaPaJo Construction Ltd. was routed to Review rather than added directly: its own service list includes 'well abandonment,' a specific and unambiguous oil &amp; gas well-decommissioning service. Eastend Iron Industries Ltd., which surfaced prominently for its agriculture/oil sector fit, was confirmed to actually be based in Taber, AB - a town not currently on this project's city list - and is itself categorized as 'Oil Field Services' on Yellow Pages; not added anywhere. No DNV code/standard reference was found for Brooks Industrial Metals.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -110,6 +110,7 @@
     <sheet name="Cold Lake, AB" sheetId="105" state="visible" r:id="rId105"/>
     <sheet name="Bonnyville, AB" sheetId="106" state="visible" r:id="rId106"/>
     <sheet name="Brooks, AB" sheetId="107" state="visible" r:id="rId107"/>
+    <sheet name="Okotoks, AB" sheetId="108" state="visible" r:id="rId108"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -216,6 +217,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="104" hidden="1">'Cold Lake, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="105" hidden="1">'Bonnyville, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="106" hidden="1">'Brooks, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="107" hidden="1">'Okotoks, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5588,6 +5590,389 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet108.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Okotoks, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>3D Industries Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.3dindustries.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CWB W47.1-certified structural steel fabrication since 2005; custom aluminum and steel fabrication, serving Okotoks, Calgary and the Foothills region</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established, CWB-certified Okotoks structural steel fabricator with no oilfield-only positioning found - a clean general fit with a confirmed named owner.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (3dindustries.ca) describes CWB W47.1-certified structural steel fabrication since 2005.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>François Draghi</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.3dindustries.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@3dindustries.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.3dindustries.ca/ ; https://okotoks-ab.findstorenearme.ca/3d-industries-welding-fabrication/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its CWB-certified structural steel work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Okotoks, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Integrity Fabrication</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://integritybuilt.com/building-products/fabrication/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company (part of Integrity Building Products)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Custom Welding &amp; Metalwork</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Custom welding and metalwork, led by a third-generation fabricator</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Custom fabrication division of a post-frame building products company; the parent company's core business (post-frame agricultural/farm buildings) is more building-products-oriented than heavy industrial structural fabrication, so this is a secondary rather than primary prospect.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; the parent company's focus on building products is a step removed from AH Structures' heavy-industrial/marine structural scope.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (integritybuilt.com/building-products/fabrication) describes custom welding and metalwork led by a third-generation fabricator.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Ian Hoyle</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Third-generation fabricator (exact title/role not confirmed)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://integritybuilt.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (403-995-0524).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://integritybuilt.com/contact-us/ ; https://www.alignable.com/okotoks-ab/integrity-fabrication</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm whether any heavy-industrial (versus agricultural building-product) fabrication work exists before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -16609,7 +16994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A984"/>
+  <dimension ref="A1:A997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -23045,6 +23430,90 @@
       <c r="A984" s="9" t="inlineStr">
         <is>
           <t>DaPaJo Construction Ltd. was routed to Review rather than added directly: its own service list includes 'well abandonment,' a specific and unambiguous oil &amp; gas well-decommissioning service. Eastend Iron Industries Ltd., which surfaced prominently for its agriculture/oil sector fit, was confirmed to actually be based in Taber, AB - a town not currently on this project's city list - and is itself categorized as 'Oil Field Services' on Yellow Pages; not added anywhere. No DNV code/standard reference was found for Brooks Industrial Metals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="7" t="inlineStr">
+        <is>
+          <t>Batch 68: Okotoks, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="9" t="inlineStr">
+        <is>
+          <t>1. 3D Industries Welding &amp; Fabrication - Score 6, Priority B - CWB W47.1-certified structural steel fabricator since 2005, with a confirmed named owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="9" t="inlineStr">
+        <is>
+          <t>2. Integrity Fabrication - Score 4, Priority C - custom welding/metalwork division of a post-frame agricultural building products company; secondary given the parent company's building-products focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this city pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="9" t="inlineStr">
+        <is>
+          <t>For 3D Industries, approach François Draghi directly with a structural/FEA overflow pitch given its CWB W47.1 structural certification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="9" t="inlineStr">
+        <is>
+          <t>None with a dated, current signal this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: 3D Industries. Integrity Fabrication as a lower-priority follow-up, contingent on confirming any heavy-industrial (versus building-product) fabrication work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="9" t="inlineStr">
+        <is>
+          <t>No location mismatches or defense/oil &amp; gas exclusions arose this batch. No DNV code/standard reference was found for either company.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -111,6 +111,10 @@
     <sheet name="Bonnyville, AB" sheetId="106" state="visible" r:id="rId106"/>
     <sheet name="Brooks, AB" sheetId="107" state="visible" r:id="rId107"/>
     <sheet name="Okotoks, AB" sheetId="108" state="visible" r:id="rId108"/>
+    <sheet name="Cochrane, AB" sheetId="109" state="visible" r:id="rId109"/>
+    <sheet name="Canmore, AB" sheetId="110" state="visible" r:id="rId110"/>
+    <sheet name="Banff, AB" sheetId="111" state="visible" r:id="rId111"/>
+    <sheet name="Strathmore, AB" sheetId="112" state="visible" r:id="rId112"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -218,6 +222,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="105" hidden="1">'Bonnyville, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="106" hidden="1">'Brooks, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="107" hidden="1">'Okotoks, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="108" hidden="1">'Cochrane, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="109" hidden="1">'Canmore, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="110" hidden="1">'Banff, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="111" hidden="1">'Strathmore, AB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5973,6 +5981,385 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet109.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Cochrane, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Quadra Industrial Group</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.quadra-industrial.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Machining, Fabrication &amp; Millwrighting</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Machining, fabricating and millwrighting, CWB CSA W47.1-certified for structural steel; mobile services for construction, demolition and shutdown needs, pipe fabrication and equipment installation/maintenance</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Multi-location (Exshaw, Cochrane, Sundre, Hinton AB and Mackenzie BC) structural-steel-certified fabricator with no oilfield-only positioning found and a confirmed named owner and location-specific email - a solid general fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (quadra-industrial.com) describes CWB CSA W47.1-certified structural steel fabrication, machining and millwrighting across five locations.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Nicole Monaghan</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.quadra-industrial.com/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>cochraneshop@quadra-industrial.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Location-specific company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.quadra-industrial.com/contact-us ; https://www.ccib.ca/main/member/quadra-industrial-group/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its CWB-certified structural steel work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>This company was already noted (but deliberately held back) during Hinton research (batch 60), given its multi-location structure; now properly researched here under Cochrane, one of its five locations. No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Cochrane, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta Metal Works Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://albertametalworks.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Steel Service Center</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Cutting and bending plate materials for manufacturing, construction, commercial and industrial applications; staffed with Journeyman Welders, CWB Welders, Millwrights and Machinists</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>The only local Cochrane-area steel service center, with a genuinely diversified client base and no oilfield-only positioning found - a solid general fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (albertametalworks.ca) describes plate cutting/bending services for manufacturing, construction, commercial and industrial clients.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://albertametalworks.ca/contact/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>contact.us@albertametalworks.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://albertametalworks.ca/contact/ ; https://www.yellowpages.ca/bus/Alberta/Cochrane/Alberta-Metal-Works-Ltd/7214709.html</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its manufacturing/construction/industrial plate work.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7658,6 +8045,919 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet110.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Canmore, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Lavacrow Metalworks</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://lavacrow.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Custom Steel Fabrication &amp; Erection</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Concept design, engineering, laser/plasma cutting, CNC machining, crane and rigging services, plus full fabrication and erection packages for residential, commercial and industrial builds</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Notable for offering concept design and engineering in-house alongside fabrication and crane/rigging services - one of the more precise engineering-adjacent fits found in this project's Alberta batches, with a confirmed named owner.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>In-house concept design and engineering services directly alongside fabrication and crane/rigging work is a direct, evidence-based overflow-FEA pathway rather than an inferred one.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (lavacrow.ca) describes concept design, engineering, laser/plasma cutting, CNC machining and crane/rigging services for industrial builds.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Remi Michaud</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner/Operator</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://lavacrow.ca/about-or-lavacrow-metalworks-or-canmore-ab</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>metalworks@lavacrow.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://lavacrow.ca/contact-or-lavacrow-metalworks-or-canmore-ab</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly with a structural/FEA overflow pitch tied to its in-house concept design and engineering service - the clearest engineering-adjacent signal found in this batch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Canmore, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Bow-Cor Custom Welding (2007) Ltd.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bowcorwelding.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel, staircases, railings, stainless steel, custom designs and aluminum fabrication; works with Engineers and a drafting technologist to create shop drawings; CWB shop certified to National Building Code and CSA standards, serving Canmore, Banff, Kananaskis and Lake Louise</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified structural steel fabricator that explicitly works with outside Engineers and a drafting technologist for shop drawings - a genuine, named overflow-engineering pathway similar to Lavacrow Metalworks in the same batch.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>The stated practice of working with outside Engineers for shop drawings is a direct, evidence-based overflow-engineering signal.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (bowcorwelding.ca/structural-steel) describes working with Engineers and a drafting technologist for CSA/National Building Code-compliant shop drawings.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Ahsan Syed &amp; Gwen Earl</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Owners</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bowcorwelding.ca/our-team</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (403-678-2361).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bowcorwelding.ca/contact-us ; https://www.bbb.org/ca/ab/canmore/profile/welding/bow-cor-custom-welding-2007-ltd-0017-95016</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA pitch specifically offering to work alongside its existing outside-engineer relationship for CSA-compliant shop drawings.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet111.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet112.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Strathmore, AB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Colpoys Welding Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.colpoyswelding.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Custom Fabrication &amp; Welding</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom fabrication and welding repair for industrial and agricultural clients, including equipment repair, cast iron welding, stainless steel welding and machining</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely Strathmore-based fabricator with a clean industrial/agricultural client base and no oilfield-only positioning found - a solid general fit with a confirmed general contact email.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (colpoyswelding.ca/services/industrial) describes custom fabrication and welding for industrial and agricultural clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.colpoyswelding.ca/contact</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@colpoyswelding.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.colpoyswelding.ca/contact ; https://411.ca/business/profile/6010852</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its industrial fabrication work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Strathmore, AB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>BurndRed Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://burndredwelding.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Custom Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Custom welding, custom fabrication, structural skids, portable loading ramps and CNC plasma cutting from a 4,000 sq ft shop, serving construction, homebuilders, oil &amp; gas and landscaping clients</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established (30+ years) Strathmore-Calgary area fabricator with structural skid fabrication among its services, but its client base spans construction, homebuilders, oil &amp; gas and landscaping - a more mixed, less clearly heavy-industrial client mix than Colpoys Welding.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (burndredwelding.com) describes custom welding, structural skids and CNC plasma cutting for construction, homebuilders, oil &amp; gas and landscaping clients.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://burndredwelding.com/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://burndredwelding.com/who-we-are/our-facility</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Lower-priority follow-up; confirm proportion of heavy-industrial (versus homebuilder/landscaping) work before a tailored pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16994,7 +18294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A997"/>
+  <dimension ref="A1:A1017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -23514,6 +24814,139 @@
       <c r="A997" s="9" t="inlineStr">
         <is>
           <t>No location mismatches or defense/oil &amp; gas exclusions arose this batch. No DNV code/standard reference was found for either company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="7" t="inlineStr">
+        <is>
+          <t>Batches 69-72: Cochrane, Canmore, Banff &amp; Strathmore, AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="8" t="inlineStr">
+        <is>
+          <t>Milestone: last Alberta cities on the master list</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="9" t="inlineStr">
+        <is>
+          <t>Strathmore completes this project's coverage of all distinct Alberta cities/towns on the master list (batches 39-72). The next city on the master list, 'Airdrie, AB,' is a duplicate entry (already researched in batch 47) and was not re-researched. The master list now moves into Manitoba, starting with Winnipeg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects across this group (ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="9" t="inlineStr">
+        <is>
+          <t>1. Lavacrow Metalworks (Canmore) - Score 7, Priority A - genuine in-house concept design and engineering alongside fabrication and crane/rigging services, one of the strongest engineering-adjacent fits found in this project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="9" t="inlineStr">
+        <is>
+          <t>2. Bow-Cor Custom Welding (Canmore) - Score 6, Priority B - CWB-certified fabricator that explicitly works with outside Engineers and a drafting technologist for CSA-compliant shop drawings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="9" t="inlineStr">
+        <is>
+          <t>3. Quadra Industrial Group and Alberta Metal Works (Cochrane) - Score 6, Priority B each - a multi-location CWB-certified structural fabricator and the only local Cochrane-area steel service center, respectively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="9" t="inlineStr">
+        <is>
+          <t>4. Colpoys Welding (Strathmore) - Score 6, Priority B - clean industrial/agricultural fabricator with no oilfield exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="9" t="inlineStr">
+        <is>
+          <t>5. BurndRed Welding &amp; Fabrication (Strathmore) - Score 4, Priority C - mixed client base (construction, homebuilders, oil &amp; gas, landscaping).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="8" t="inlineStr">
+        <is>
+          <t>Why Banff was empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="9" t="inlineStr">
+        <is>
+          <t>No genuinely Banff-based fabricator was found after multiple searches; Banff National Park's strict development restrictions leave the town without an established industrial fabrication base of its own. Bow-Cor Custom Welding (Canmore, already recorded) serves Banff as part of its regional mobile-welding coverage, including backcountry work in Banff National Park itself, but was not duplicated under Banff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this group</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="9" t="inlineStr">
+        <is>
+          <t>Lavacrow Metalworks and Bow-Cor Custom Welding (both Canmore) offer the clearest engineering-adjacent angles in this group - lead with structural/FEA support tied to their existing in-house design or outside-engineer relationships respectively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="9" t="inlineStr">
+        <is>
+          <t>Lavacrow Metalworks' in-house concept design/engineering service is the standout signal across this group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Lavacrow Metalworks (Canmore). Bow-Cor Custom Welding, Quadra Industrial Group, Alberta Metal Works, and Colpoys Welding as close secondary follow-ups. BurndRed Welding as a lower-priority follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="9" t="inlineStr">
+        <is>
+          <t>Quadra Industrial Group, deliberately held back from Hinton (batch 60), is a multi-location company (Exshaw, Cochrane, Sundre, Hinton AB and Mackenzie BC); it was recorded under Cochrane, one of its locations, with a location-specific confirmed email. No DNV code/standard reference was found for any company across this group of cities.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -115,6 +115,10 @@
     <sheet name="Canmore, AB" sheetId="110" state="visible" r:id="rId110"/>
     <sheet name="Banff, AB" sheetId="111" state="visible" r:id="rId111"/>
     <sheet name="Strathmore, AB" sheetId="112" state="visible" r:id="rId112"/>
+    <sheet name="Winnipeg, MB" sheetId="113" state="visible" r:id="rId113"/>
+    <sheet name="Brandon, MB" sheetId="114" state="visible" r:id="rId114"/>
+    <sheet name="Thompson, MB" sheetId="115" state="visible" r:id="rId115"/>
+    <sheet name="Portage la Prairie, MB" sheetId="116" state="visible" r:id="rId116"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -226,6 +230,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="109" hidden="1">'Canmore, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="110" hidden="1">'Banff, AB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="111" hidden="1">'Strathmore, AB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="112" hidden="1">'Winnipeg, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="113" hidden="1">'Brandon, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="114" hidden="1">'Thompson, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="115" hidden="1">'Portage la Prairie, MB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8962,6 +8970,1638 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet113.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Winnipeg, MB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Merit Iron Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://meritiron.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel &amp; Frame Manufacturing</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Full-service welding, structural steel and frame manufacturing/processing; custom fabrication of mild steel, stainless steel and aluminum products</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Established Winnipeg structural steel and frame manufacturer with no oil &amp; gas exposure at all - Manitoba's diversified manufacturing economy (unlike the oil &amp; gas-heavy Prairie provinces further west) is a genuinely cleaner fit overall.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (meritiron.ca) describes full-service welding, structural steel and frame manufacturing/processing.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Tony Felix</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://meritiron.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@meritiron.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://meritiron.ca/ ; https://www.bbb.org/ca/mb/winnipeg/profile/welding/merit-iron-ltd-0057-32599</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its structural steel and frame manufacturing work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Winnipeg, MB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Logic Industries</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.logicindustries.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Structural &amp; Miscellaneous Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Certified structural and miscellaneous steel fabrication serving Manitoba</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Established, CWB-certified Winnipeg structural steel fabricator with no oil &amp; gas exposure found.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (logicindustries.ca) describes certified structural and miscellaneous steel fabrication.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Doug McConnell</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Associated with the business (exact title not confirmed)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.logicindustries.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>admin@logicindustries.ca</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.logicindustries.ca/ ; https://www.yelp.ca/biz/logic-industries-winnipeg</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its certified structural steel fabrication work.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Winnipeg, MB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Abesco Ltd.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.abesco.ca/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/company/abescoltd</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Detailing, Fabrication &amp; Erection</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>50+ years detailing, fabricating and erecting steel for commercial and industrial projects</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (50+ years) Winnipeg structural steel company with an in-house detailing capability alongside fabrication and erection - a genuine structural-engineering-adjacent fit.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>In-house structural steel detailing suggests design-adjacent capability that could extend to overflow FEA collaboration on larger or more complex projects.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (abesco.ca) describes 50+ years of structural steel detailing, fabrication and erection for commercial and industrial projects.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Jim Veitch</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Owner (Wally Fast also listed as President - roles not fully reconciled)</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.abesco.ca/contact-us</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (204-667-3981).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.abesco.ca/contact-us ; https://www.bbb.org/ca/mb/winnipeg/profile/steel-fabrication/abesco-ltd-0057-50726</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its in-house detailing capability.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Winnipeg, MB</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Skyline Crane Inc.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.skylinecrane.ca/</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skyline-crane-inc</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Lift / Industrial Rigging</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Industrial rigging services for machinery moves and installations</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Winnipeg-based heavy-lift/rigging company with a directly confirmed general contact email - a plausible overflow-heavy-lift-engineering fit, similar to other crane/rigging companies recorded elsewhere in this project.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the nature of industrial rigging/machinery-moving work.</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Company website (skylinecrane.ca/service/industrial-rigging-winnipeg) describes industrial rigging services for machinery moves and installations.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.skylinecrane.ca/contact-us</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>office@skylinecrane.ca</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.skylinecrane.ca/contact-us</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>Approach as a potential engineering-support partner for heavy-lift and machinery-installation project planning.</t>
+        </is>
+      </c>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Winnipeg, MB</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Parr Metal Fabricators Ltd. (Empire Industries)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.parrmetal.com/</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Private company (part of Empire Industries Ltd.)</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Industrial Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Metal fabrication for pulp and paper, mining, chemical, distilleries, food, beverage, water treatment, commercial/industrial construction, aerospace, and power generation &amp; distribution, since 1976</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1976), highly diversified Winnipeg fabricator with a genuinely broad multi-sector client base spanning aerospace, power generation and heavy industrial process facilities - one of the more diversified fabricators found in this project, with a directly confirmed named contact and no oil &amp; gas exposure found.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the scale and technical complexity of its named sectors (aerospace, power generation, chemical processing).</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Company website (parrmetal.com/about.equipment.html) and parent company site (empind.com/empire-companies/parr-metal-fabricators) describe fabrication for aerospace, mining, power generation, pulp and paper and other heavy industrial sectors.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Randy Daviduik</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>General Manager / Senior Estimator / Senior Project Manager</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.parrmetal.com/contact.html</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>randyd@parrmetal.com</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>Direct, unmasked email for a named individual, sourced from the company's own materials - a genuinely confirmed contact.</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.parrmetal.com/contact.html ; http://empind.com/empire-companies/parr-metal-fabricators/</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly with a structural/FEA overflow pitch tied to its aerospace and power-generation fabrication work, given the technical complexity and diversification.</t>
+        </is>
+      </c>
+      <c r="X6" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. Found while researching Portage la Prairie (this batch); confirmed as Winnipeg-based and recorded here rather than under Portage la Prairie.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet114.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Brandon, MB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Fire Line Group</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://firelinegroup.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural &amp; Specialist Welding</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural and specialist welding meeting Brandon's industrial requirements; robotic production and heavy-gauge welding in carbon steel, stainless steel, aluminum and high-grade alloys</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Well-equipped Brandon fabricator with robotic production capability - a strong general heavy-industrial structural fit with no oil &amp; gas exposure found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (firelinegroup.ca/metal-fabrication-brandon-manufacturing) describes structural/specialist welding and robotic production capability.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://firelinegroup.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://firelinegroup.ca/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its robotic production and heavy-gauge welding capability.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Brandon, MB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Morningstar Metal</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.morningstarmetal.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Metal Fabrication &amp; Manufacturing</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Custom manufacturing of steel, stainless steel and aluminum; raw steel sales, serving Southwestern Manitoba</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely local Brandon metal shop with no oil &amp; gas exposure found and a confirmed named owner.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (morningstarmetal.ca) describes custom manufacturing and raw steel sales for Southwestern Manitoba.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Dave Morningstar</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.morningstarmetal.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>morningstarmetal@hotmail.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Direct email associated with the named owner, sourced from public business listings.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.yelp.ca/biz/morningstar-metals-brandon ; https://www.morningstarmetal.ca/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach Dave Morningstar directly with a structural/FEA overflow pitch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet115.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Thompson, MB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Settarc Welding &amp; Septic Services</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.settarcwelding.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Welding, Machining &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel fabrication, welding and machining serving Northern Manitoba's mining sector</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely Thompson-based fabricator (near Vale's nickel mining operations) with a confirmed named owner - a solid general fit for this mining town.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (settarcwelding.ca) describes welding, fabrication and machining services for Northern Manitoba.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Ken Paterson</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner (founded 2008)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.settarcwelding.ca/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (204-778-3701).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.settarcwelding.ca/ ; https://www.canpages.ca/page/MB/thompson/settarc-welding/101030586</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its mining-sector structural fabrication work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. The company's registered business name also includes 'Septic Services' alongside welding/machining, suggesting a diversified small-town service business rather than a pure heavy-industrial fabricator; worth confirming scope directly.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet116.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Portage la Prairie, MB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Portage Iron</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://portageiron.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Miscellaneous Metals &amp; Millwright Services</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Full-service welding, fabrication, installation and millwright services in carbon steel, stainless steel and aluminum, from CNC drill line/plasma cutting/CNC brake/plate roller equipment; project experience from ornamental metalwork to industrial process equipment installation</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely local, well-equipped Portage la Prairie fabricator with a broad range from ornamental to industrial process equipment work, and no oil &amp; gas exposure found - a solid general fit for this agricultural-processing hub (home to major food processors like McCain Foods and Simplot).</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the range of industrial process equipment installation work described.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (portageiron.ca/about-us) describes CWB-certified welding, fabrication, installation and millwright services from ornamental to industrial process equipment.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://portageiron.ca/contact-us/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@portageiron.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://portageiron.ca/contact-us/ ; https://portageiron.ca/about-us/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its industrial process equipment installation work, given Portage la Prairie's concentration of large food-processing plants.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -18294,7 +19934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1017"/>
+  <dimension ref="A1:A1034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -24947,6 +26587,118 @@
       <c r="A1017" s="9" t="inlineStr">
         <is>
           <t>Quadra Industrial Group, deliberately held back from Hinton (batch 60), is a multi-location company (Exshaw, Cochrane, Sundre, Hinton AB and Mackenzie BC); it was recorded under Cochrane, one of its locations, with a location-specific confirmed email. No DNV code/standard reference was found for any company across this group of cities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="7" t="inlineStr">
+        <is>
+          <t>Batches 73-74: Winnipeg, Brandon, Thompson &amp; Portage la Prairie, MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="8" t="inlineStr">
+        <is>
+          <t>Milestone: master list moves into Manitoba</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="9" t="inlineStr">
+        <is>
+          <t>This is the first Manitoba batch, following the completion of all Alberta cities. Manitoba's economy is far more diversified (manufacturing, aerospace, agri-food processing, mining) and much less oil &amp; gas-concentrated than Alberta or Saskatchewan, which showed clearly in this batch: no company was excluded or routed to Review for oil &amp; gas exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects across this group (ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="9" t="inlineStr">
+        <is>
+          <t>1. Parr Metal Fabricators Ltd. (Winnipeg, part of Empire Industries) - Score 7, Priority A - highly diversified fabricator (since 1976) serving aerospace, power generation, pulp &amp; paper and mining, with a directly confirmed named contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="9" t="inlineStr">
+        <is>
+          <t>2. Merit Iron, Logic Industries, Abesco Ltd. (all Winnipeg) - Score 6, Priority B - established structural steel fabricators; Abesco notably offers in-house structural detailing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="9" t="inlineStr">
+        <is>
+          <t>3. Fire Line Group and Morningstar Metal (Brandon), Settarc Welding (Thompson), Portage Iron (Portage la Prairie) - Score 6, Priority B each - locally established fabricators with clean, non-oil-and-gas client bases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="9" t="inlineStr">
+        <is>
+          <t>4. Skyline Crane Inc. (Winnipeg) - Score 6, Priority C - heavy-lift/rigging company, a plausible overflow-engineering partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this group</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="9" t="inlineStr">
+        <is>
+          <t>For Parr Metal Fabricators, lead with its aerospace and power-generation fabrication work given the technical complexity involved - the strongest single find across this batch. For Abesco, its in-house structural detailing capability is a genuine design-adjacent touchpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="9" t="inlineStr">
+        <is>
+          <t>Parr Metal Fabricators' aerospace/power-generation scope and Abesco's in-house detailing are the clearest signals found this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Parr Metal Fabricators (Winnipeg). Merit Iron, Logic Industries, and Abesco (Winnipeg), plus Fire Line Group, Morningstar Metal, Settarc Welding and Portage Iron, as close secondary follow-ups. Skyline Crane as a lower-priority heavy-lift-specific contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="9" t="inlineStr">
+        <is>
+          <t>Parr Metal Fabricators was found while researching Portage la Prairie but confirmed to be Winnipeg-based, and was recorded there instead. No DNV code/standard reference was found for any company across this group. Settarc Welding's registered business name includes 'Septic Services' alongside welding/machining, suggesting a diversified small-town service business - worth confirming scope directly before a tailored pitch.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -119,6 +119,11 @@
     <sheet name="Brandon, MB" sheetId="114" state="visible" r:id="rId114"/>
     <sheet name="Thompson, MB" sheetId="115" state="visible" r:id="rId115"/>
     <sheet name="Portage la Prairie, MB" sheetId="116" state="visible" r:id="rId116"/>
+    <sheet name="Steinbach, MB" sheetId="117" state="visible" r:id="rId117"/>
+    <sheet name="Winkler, MB" sheetId="118" state="visible" r:id="rId118"/>
+    <sheet name="Selkirk, MB" sheetId="119" state="visible" r:id="rId119"/>
+    <sheet name="The Pas, MB" sheetId="120" state="visible" r:id="rId120"/>
+    <sheet name="Dauphin, MB" sheetId="121" state="visible" r:id="rId121"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -234,6 +239,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="113" hidden="1">'Brandon, MB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="114" hidden="1">'Thompson, MB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="115" hidden="1">'Portage la Prairie, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="116" hidden="1">'Steinbach, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="117" hidden="1">'Winkler, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="118" hidden="1">'Selkirk, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="119" hidden="1">'The Pas, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="120" hidden="1">'Dauphin, MB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10602,6 +10612,819 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet117.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Steinbach, MB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Steinbach Precision Enterprises (1973) Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://steinbachprecision.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Machining, Welding &amp; Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Machining, welding (aluminum and stainless steel), line boring, manufacturing/fabricating, hydraulic cylinder repair, heavy equipment hitch installation, plate shearing/bending and ornamental iron work for construction, forestry, agriculture and excavating</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (100+ years) Steinbach precision shop with a genuinely diversified, entirely non-oil-and-gas client base - a clean general fit with a directly confirmed named owner.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (steinbachprecision.com) describes machining, welding, fabrication and precision repair services for construction, forestry, agriculture and excavating clients.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Harold Kihn</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://steinbachprecision.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>hkihn@mts.net</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Direct email associated with the named owner, sourced from public business directories.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mysteinbach.ca/business/steinbach-precision-enterprises/ ; https://steinbachprecision.com/</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach Harold Kihn directly with a structural/FEA overflow pitch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet118.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Winkler, MB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>General Metal Fabrication Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://generalmetal.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Steel Fabrication &amp; Custom Manufacturing</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CWB-certified structural, aluminum and stainless steel fabrication from a 34,000 sq ft facility; also manufactures proprietary equipment lines - BAU-MAN (potato handling/transport equipment) and EVEREST (mower/snowblower components) - serving agricultural, mining, construction, oilfield, medical, waste handling and transportation industries</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1985), large-scale, family-owned fabricator notable for its own proprietary branded equipment lines (BAU-MAN, EVEREST) - genuine in-house product design and engineering capability, one of the stronger engineering-adjacent fits found in this project.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturing and maintaining two proprietary branded equipment lines requires genuine ongoing structural/mechanical engineering work - a direct, evidence-based overflow-FEA opportunity rather than an inferred one.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (generalmetal.ca) and its BAU-MAN product line page (generalmetal.ca/bau-man/about-us) describe CWB-certified fabrication and proprietary equipment manufacturing.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Leon Bauman / Gerald Bauman</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Leon Bauman: Chief Financial Officer; Gerald Bauman also listed as a contact (family business, roles not fully reconciled)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://generalmetal.ca/contact</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@generalmetal.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); named contacts Leon Bauman and Gerald Bauman also have individual emails on file but were not used directly per this project's practice of preferring general inboxes over unconfirmed personal emails.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://generalmetal.ca/contact ; https://www.zoominfo.com/p/Leon-Bauman/1857317262</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch specifically tied to its proprietary BAU-MAN/EVEREST product engineering, the clearest evidence-based overflow signal found in this batch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Oilfield is named as one of several served sectors (alongside agricultural, mining, construction, medical, waste handling and transportation), not the company's sole/core market. No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet119.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Selkirk, MB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Selkirk Machine Works (1982) Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.selkirkmachine.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Marine, Industrial &amp; Hydro-Electric Fabrication</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Custom manufacturer of fabricated products for marine, mining and industrial sectors, established in the early 1950s as a shipbuilder; boat building, industrial and custom machining/millwrighting; manufacturing and refurbishment of gates and guides for the hydro-electric power generating industry; CWB Division 2-certified welders</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Notable for a genuine marine/shipbuilding heritage dating to the early 1950s, alongside hydro-electric gate/guide manufacturing - directly relevant to AH Structures' marine/naval-architecture-adjacent structural engineering scope, one of the strongest marine-relevant fits found outside British Columbia in this project.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Hydro-electric gate/guide manufacturing and marine/boat building both involve genuine structural engineering considerations (hydrodynamic loading, corrosion, fatigue) that could benefit from outside FEA support.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (selkirkmachine.ca/about-us) describes the company's shipbuilding origins, boat building services, and hydro-electric gate/guide manufacturing and refurbishment.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.selkirkmachine.ca/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (204-482-3414).</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.selkirkmachine.ca/contact-us ; https://www.selkirkmachine.ca/about-us</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly with a structural/FEA pitch tied specifically to its marine/boat-building heritage and hydro-electric gate/guide work - the clearest marine-relevant angle found in this batch.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found, though given the company's marine heritage this is worth confirming directly - DNV certification would be an unusually strong fit signal if present.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -10872,6 +11695,444 @@
       <c r="X2" s="5" t="inlineStr">
         <is>
           <t>Kay-Son's own materials list processing-plant sectors including oil/gas and pulp &amp; paper alongside marine - per AH Structures' house convention of never framing its own services around oil &amp; gas, any outreach or case-study material used with this contact should reference the marine/bulk-handling side of their work only. No individual decision-maker's title was confirmed beyond General Manager; re-verify Paul Buchmann's current role before outreach.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet120.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet121.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Dauphin, MB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>RITZ Machine Works Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ritzmachine.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Tube Bending &amp; Custom Manufacturing</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Tube bending specialist and custom manufacturer serving transportation, construction, agriculture, mining and recreational sectors across North America, established 1998</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Sizeable (10-49 employees, $5-10M revenue), genuinely Dauphin-based manufacturer with a specific technical specialty (tube bending) and no oil &amp; gas exposure found - a solid, evidence-based general fit.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Tube bending for transportation/mining/agricultural equipment across North America suggests genuine structural/mechanical engineering demand that could benefit from outside FEA support on complex projects.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (ritzmachine.com) describes tube bending expertise and custom manufacturing for transportation, construction, agriculture, mining and recreational clients across North America.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Tom Zaporzan &amp; Rick Ilnisky</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founders</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ritzmachine.com/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>quotes@ritzmachine.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); a named contact (laurie@ritzmachine.com) is also listed.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ritzmachine.com/contact-us ; https://wcmbnews.com/dauphin-business-directory/21:ritz-machine-works-inc</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its tube-bending/custom manufacturing work for transportation and mining equipment.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. Fire Line Group (already recorded under Brandon) also surfaced under a Dauphin-specific service page, but this reflects mobile/regional service coverage from its Brandon base rather than a separate Dauphin location - not duplicated here.</t>
         </is>
       </c>
     </row>
@@ -19934,7 +21195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1034"/>
+  <dimension ref="A1:A1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -26699,6 +27960,118 @@
       <c r="A1034" s="9" t="inlineStr">
         <is>
           <t>Parr Metal Fabricators was found while researching Portage la Prairie but confirmed to be Winnipeg-based, and was recorded there instead. No DNV code/standard reference was found for any company across this group. Settarc Welding's registered business name includes 'Septic Services' alongside welding/machining, suggesting a diversified small-town service business - worth confirming scope directly before a tailored pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="7" t="inlineStr">
+        <is>
+          <t>Batch 75: Steinbach, Winkler, Selkirk, The Pas &amp; Dauphin, MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="8" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="9" t="inlineStr">
+        <is>
+          <t>Second Manitoba group. Continues the province's pattern of a diversified, largely non-oil-and-gas manufacturing economy - no company was excluded or routed to Review for oil &amp; gas or defense exposure in this batch. The Pas returned no qualified local fabricator after search and was left with an empty main sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects across this group (ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="9" t="inlineStr">
+        <is>
+          <t>1. Selkirk Machine Works (1982) Ltd. (Selkirk) - Score 7, Priority A - genuine marine/shipbuilding heritage dating to the early 1950s plus hydro-electric gate/guide manufacturing and refurbishment; one of the strongest marine-relevant fits found outside British Columbia in this entire project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="9" t="inlineStr">
+        <is>
+          <t>2. General Metal Fabrication Ltd. (Winkler) - Score 7, Priority A - large, long-established (since 1985) CWB-certified fabricator with two proprietary branded equipment lines (BAU-MAN potato handling equipment, EVEREST mower/snowblower components) - genuine in-house product engineering, a direct evidence-based overflow-FEA signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="9" t="inlineStr">
+        <is>
+          <t>3. RITZ Machine Works Inc. (Dauphin) - Score 6, Priority B - established tube-bending specialist and custom manufacturer serving transportation, construction, agriculture and mining across North America.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="9" t="inlineStr">
+        <is>
+          <t>4. Steinbach Precision Enterprises (1973) Ltd. (Steinbach) - Score 6, Priority B - long-established (100+ years) precision machining/welding/fabrication shop with a confirmed named owner and a clean, diversified client base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this group</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="9" t="inlineStr">
+        <is>
+          <t>Selkirk Machine Works offers the clearest marine-relevant angle found anywhere in this project outside BC - lead with a structural/FEA pitch tied specifically to its shipbuilding heritage and hydro-electric gate/guide work. General Metal Fabrication's proprietary BAU-MAN/EVEREST product lines are the strongest evidence-based overflow-engineering signal in this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="9" t="inlineStr">
+        <is>
+          <t>General Metal Fabrication's in-house proprietary equipment design (BAU-MAN, EVEREST) and Selkirk Machine Works' hydro-electric gate/guide manufacturing and marine/boat building both involve genuine ongoing structural engineering considerations that could benefit from outside FEA support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Selkirk Machine Works and General Metal Fabrication (both Priority A). RITZ Machine Works and Steinbach Precision Enterprises as close secondary follow-ups. No qualified contact found for The Pas this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="9" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found for any company in this group, though Selkirk Machine Works' marine heritage makes this worth confirming directly - DNV certification would be an unusually strong fit signal if present there. Fire Line Group (already recorded under Brandon, batch 74) also surfaced under a Dauphin-specific service page but reflects mobile/regional coverage from its Brandon base, not a separate Dauphin location, and was not duplicated. No publicly available email was found for Selkirk Machine Works or The Pas in this pass; only phone confirmed for Selkirk (204-482-3414).</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -124,6 +124,11 @@
     <sheet name="Selkirk, MB" sheetId="119" state="visible" r:id="rId119"/>
     <sheet name="The Pas, MB" sheetId="120" state="visible" r:id="rId120"/>
     <sheet name="Dauphin, MB" sheetId="121" state="visible" r:id="rId121"/>
+    <sheet name="Flin Flon, MB" sheetId="122" state="visible" r:id="rId122"/>
+    <sheet name="Morden, MB" sheetId="123" state="visible" r:id="rId123"/>
+    <sheet name="Neepawa, MB" sheetId="124" state="visible" r:id="rId124"/>
+    <sheet name="Gimli, MB" sheetId="125" state="visible" r:id="rId125"/>
+    <sheet name="Churchill, MB" sheetId="126" state="visible" r:id="rId126"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -244,6 +249,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="118" hidden="1">'Selkirk, MB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="119" hidden="1">'The Pas, MB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="120" hidden="1">'Dauphin, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="121" hidden="1">'Flin Flon, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="122" hidden="1">'Morden, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="123" hidden="1">'Neepawa, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="124" hidden="1">'Gimli, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="125" hidden="1">'Churchill, MB'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12142,6 +12152,1045 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet122.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Flin Flon, MB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>RK's Metal Construction</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>http://www.rksmetal.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Pre-Engineered Metal Structures &amp; Construction</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>General contracting including pre-engineered metal structures, metal siding, flat and built-up roofing, residential continuous eavestroughing, foundation and concrete, with in-house design and engineering capability, offering full contracting from concrete, electrical, mechanical to design and engineering; 24+ years in operation</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (24+ years) Flin Flon contractor that explicitly names design and engineering as part of its own service offering alongside pre-engineered metal structures - a genuine structural-engineering-adjacent fit with a directly confirmed named contact and no oil &amp; gas exposure found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Company's own stated in-house design and engineering capability for pre-engineered metal structures suggests plausible overflow/FEA collaboration on more complex structural projects.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (rksmetal.com) describes pre-engineered metal structures, metal siding, roofing and full contracting services including design and engineering.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Mr. Mote</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Principal contact (exact title not confirmed)</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>http://www.rksmetal.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>rkmote@mymts.net</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Direct email associated with the named principal contact, sourced from public business directories.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>http://www.rksmetal.com/ ; https://www.bbb.org/ca/mb/flin-flon/profile/gutters/rks-metal-construction-0057-27283</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach Mr. Mote directly with a structural/FEA overflow pitch tied to its pre-engineered metal structures and in-house design/engineering work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found. Korte Sheet Metal, a small custom sheet metal fabricator also based in Flin Flon (established 1991), was found but had no confirmed website or verifiable service/contact details beyond directory listings, so it was not added this pass.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet123.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Morden, MB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Elite Metal Works</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.elitemetalworks.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Custom &amp; Structural Metalwork</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>On-site welding, cutting, repair and fabrication with 24/7 availability; finish-grade custom metalwork including railings, farm equipment repair/enhancement and bespoke furniture, blending wood and metal for rustic-to-industrial aesthetics</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Family-owned Morden shop led by a founder holding Canada's Red Seal in welding and Canadian Welding Bureau accreditation for structural welding - genuine structural welding credentials, though the visible work skews toward finish-grade/custom and farm-equipment jobs rather than heavy industrial fabrication. No oil &amp; gas exposure found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; CWB structural welding accreditation is a positive credential but current visible project scope is mostly small-scale custom/farm work.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (elitemetalworks.ca/about-us) describes the founder's Red Seal and CWB structural welding accreditation alongside on-site welding, repair and custom metalwork services.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Founder/Owner</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.elitemetalworks.ca/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>Lucas@elitemetalworks.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Direct email associated with the named founder, sourced from the company's own website.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.elitemetalworks.ca/about-us ; https://www.elitemetalworks.ca/contact-us</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach Lucas with a structural/FEA overflow pitch tied specifically to his CWB structural welding accreditation, positioning it as a step up from the shop's current custom/farm-equipment work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet124.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet125.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet126.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -21195,7 +22244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1051"/>
+  <dimension ref="A1:A1068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -28072,6 +29121,118 @@
       <c r="A1051" s="9" t="inlineStr">
         <is>
           <t>No DNV code/standard reference was found for any company in this group, though Selkirk Machine Works' marine heritage makes this worth confirming directly - DNV certification would be an unusually strong fit signal if present there. Fire Line Group (already recorded under Brandon, batch 74) also surfaced under a Dauphin-specific service page but reflects mobile/regional coverage from its Brandon base, not a separate Dauphin location, and was not duplicated. No publicly available email was found for Selkirk Machine Works or The Pas in this pass; only phone confirmed for Selkirk (204-482-3414).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="7" t="inlineStr">
+        <is>
+          <t>Batch 76: Flin Flon, Morden, Neepawa, Gimli &amp; Churchill, MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="8" t="inlineStr">
+        <is>
+          <t>Milestone: completes Manitoba coverage on the master list</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="9" t="inlineStr">
+        <is>
+          <t>This batch completes all Manitoba cities on the master list (batches 73-76). The master list now moves into Ontario, starting with Toronto. This was a thinner batch than most: three of the five towns (Neepawa, Gimli, Churchill) returned no genuinely qualified local fabricator with a verifiable website after search, reflecting these towns' small size and, for Churchill, its extreme remoteness (accessible only by rail/air).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects across this group (ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="9" t="inlineStr">
+        <is>
+          <t>1. RK's Metal Construction (Flin Flon) - Score 6, Priority B - 24+ year Flin Flon contractor explicitly naming design and engineering as part of its own service offering alongside pre-engineered metal structures; directly confirmed named contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="9" t="inlineStr">
+        <is>
+          <t>2. Elite Metal Works (Morden) - Score 5, Priority C - family-owned shop led by a Red Seal / CWB structural-welding-accredited founder, though current visible work skews toward finish-grade custom and farm-equipment jobs rather than heavy industrial fabrication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="8" t="inlineStr">
+        <is>
+          <t>Why Neepawa, Gimli and Churchill were left empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="9" t="inlineStr">
+        <is>
+          <t>Neepawa: the only candidates found (Ridge Road Welding, Penno's Machining &amp; Mfg.) are actually based in Kelwood and Eden respectively - neither hamlet appears on the master list, so both were excluded per this project's location-mismatch discipline rather than misattributed to Neepawa. Gimli: only thin, website-less directory listings (Tom's Welding, Gimli Welding &amp; Machining) were found despite Gimli's active commercial-fishing harbour on Lake Winnipeg; no dedicated marine/boat-building fabricator was confirmed. Churchill: 'Anything Custom,' the one company with historical Churchill roots, now operates out of Winnipeg, not Churchill itself, so it was not recorded under either city this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this group</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="9" t="inlineStr">
+        <is>
+          <t>RK's Metal Construction is the clear lead - its own stated in-house design and engineering capability for pre-engineered metal structures is a genuine, evidence-based structural-engineering-adjacent touchpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="9" t="inlineStr">
+        <is>
+          <t>RK's Metal Construction's pre-engineered metal structures work is the only concrete overflow signal found in this batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: RK's Metal Construction (Flin Flon). Elite Metal Works (Morden) as a lower-priority follow-up, framed around upgrading from custom/farm work to structural projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="9" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found for either company recorded in this batch. Korte Sheet Metal (Flin Flon, established 1991) was found but had no confirmed website or verifiable service/contact details beyond directory listings, so it was not added to the main sheet - noted in RK's Metal Construction's Research Notes instead of a separate Review entry, since there was no oil &amp; gas/defense/location ambiguity to flag, only thin public evidence.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -129,6 +129,9 @@
     <sheet name="Neepawa, MB" sheetId="124" state="visible" r:id="rId124"/>
     <sheet name="Gimli, MB" sheetId="125" state="visible" r:id="rId125"/>
     <sheet name="Churchill, MB" sheetId="126" state="visible" r:id="rId126"/>
+    <sheet name="Toronto, ON" sheetId="127" state="visible" r:id="rId127"/>
+    <sheet name="Mississauga, ON" sheetId="128" state="visible" r:id="rId128"/>
+    <sheet name="Hamilton, ON" sheetId="129" state="visible" r:id="rId129"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -254,6 +257,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="123" hidden="1">'Neepawa, MB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="124" hidden="1">'Gimli, MB'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="125" hidden="1">'Churchill, MB'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="126" hidden="1">'Toronto, ON'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="127" hidden="1">'Mississauga, ON'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="128" hidden="1">'Hamilton, ON'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6394,7 +6400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="3" min="1" max="1"/>
@@ -8068,6 +8074,48 @@
       <c r="H40" s="10" t="inlineStr">
         <is>
           <t>https://www.dapajo.ca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Hamilton, ON</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Ontario Shipyards (formerly Heddle Shipyards)</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.onshipyards.com/</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Largest Canadian-owned ship repair and construction business on the Great Lakes, headquartered in Hamilton with additional yards in Port Weller and Thunder Bay - a very strong marine/offshore-engineering-adjacent fit (offshore energy sector fabrication, marine infrastructure, civil infrastructure, resource extraction). However, it is currently executing the CCGS icebreaker Terry Fox vessel life extension for the Canadian Coast Guard (the largest such project ever undertaken) and is actively pursuing a potential federal contract to build up to 12 corvettes for Canada's Navy - genuine, significant defense/government-vessel exposure alongside its clearly diversified commercial marine work (30-year relationship with McKeil Marine, civil infrastructure, resource extraction fabrication for fish farming/mining/forestry).</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Confirm the current balance between its commercial/civil marine work and defense/naval shipbuilding work before outreach - if the Navy corvette program advances, this could become a primarily defense-focused yard; if it remains diversified with commercial marine and offshore-energy fabrication as a substantial, clearly separate line of business, it would be a strong, clean prospect given AH Structures' offshore/marine structural engineering scope.</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.onshipyards.com/about-us ; https://www.onshipyards.com/services ; https://canadiandefencereview.com/shipbuilding-ontario-shipyards/ ; https://www.hamiltonchamber.ca/member/heddle-shipyards/</t>
         </is>
       </c>
     </row>
@@ -13191,6 +13239,1023 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet127.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Toronto, ON</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>EIW Structural Steel &amp; Scaffolding (Etobicoke Ironworks Ltd.)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.eiw.ca/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication &amp; Scaffolding</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CWB Division 1-certified structural steel fabrication and system scaffolding since 1955; supports major commercial, industrial and institutional projects across the GTA and Ontario, up to 10,000 short tons of fabricated steel annually</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Large-scale (10,000+ ton annual capacity), long-established (since 1955) Toronto structural steel fabricator with a directly confirmed named CEO and dedicated structural sales contact - a strong, high-capacity general fit with no oil &amp; gas or defense exposure found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass; inferred from the scale (10,000+ ton annual capacity) and complexity of commercial/industrial/institutional projects handled.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (eiw.ca/structural-steel-fabrication-toronto) describes CWB Division 1 certification, annual fabrication capacity and project scope across the GTA.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Cameron Chafee</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.eiw.ca/contact</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>StructuralSales@eiw.ca</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Direct department contact email sourced from the company's own website, not a general info@ inbox but not confirmed as tied to a specific individual either.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.eiw.ca/structural-steel-fabrication-toronto ; https://www.eiw.ca/contact</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach via StructuralSales@eiw.ca with a structural/FEA overflow pitch tied to its large-scale fabrication capacity and complex institutional/commercial project work.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Toronto, ON</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Dry Dock Limited</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.torontodrydock.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Marine Repair &amp; Ship Servicing</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Complete marine facilities including dry dock ship repairs and marine engine services for tugs, barges, project cargo and other marine vessels, operating from Toronto's Turning Basin since 1989</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Genuinely active Toronto marine repair facility with a confirmed general contact email - one of the strongest marine/naval-architecture-adjacent fits found in Ontario so far, directly aligned with AH Structures' offshore/marine structural engineering scope.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Dry dock ship repair and marine engine servicing for tugs, barges and project cargo vessels involves genuine structural engineering considerations (hull integrity, load paths, fatigue) that could benefit from outside FEA support.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (torontodrydock.com) describes dry dock ship repair and marine engine services for tugs, barges and project cargo, operating since 1989.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.torontodrydock.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>info@torontodrydock.com</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address).</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.torontodrydock.com/ ; https://www.torontodrydock.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach directly with a structural/FEA pitch tied specifically to its dry dock ship repair and marine engine servicing work - the clearest marine-relevant angle found in this batch.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found, though given the company's marine ship-repair focus this is worth confirming directly - DNV certification would be an unusually strong fit signal if present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Toronto, ON</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Scarboro Steel Works Inc.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.scarborosteelworks.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Structural, Architectural &amp; Miscellaneous Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Full-service structural steel, steel deck, architectural and miscellaneous metal fabrication and erection for residential, commercial and industrial projects across the GTA, established 1950</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1950) Scarborough/Toronto fabricator, a member of the Toronto Construction Association, Professional Engineers of Ontario (PEO) and the Canadian Welding Bureau - a solid general fit with a large customer base and no oil &amp; gas or defense exposure found.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Company website (scarborosteelworks.com) describes full-service structural steel fabrication and erection, and lists membership in PEO and CWB.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://scarborosteelworks.com/contact.html</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass. Only phone confirmed (416-751-5033).</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://scarborosteelworks.com/ ; https://www.yellowpages.ca/bus/Ontario/Scarborough/Scarboro-Steel-Works-Ltd/1405462.html</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its long project history and PEO/CWB membership.</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet128.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Mississauga, ON</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>IBL Structural Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iblsteel.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication, Erection &amp; Detailing</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>In-house structural steel fabrication, erection, detailing and mobile welding for industrial, commercial, institutional and infrastructure projects, serving the GTA and Golden Horseshoe since 2003; computerized drafting office staffed by Professional Engineers and qualified steel detailers</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Notable for genuinely employing Professional Engineers in-house alongside fabrication and detailing - one of the strongest structural-engineering-adjacent fits found in Ontario so far, with a directly confirmed named principal and no oil &amp; gas or defense exposure found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>In-house Professional Engineers handling complex, technically challenging projects is a direct, evidence-based overflow-FEA collaboration signal rather than an inferred one.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (iblsteel.com) describes an in-house team of Professional Engineers and qualified steel detailers handling complex and technically challenging structural steel projects.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Antonio Biancucci</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iblsteel.com/</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>ab@iblsteel.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Direct email associated with the named principal, sourced from public business records.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.iblsteel.com/ ; https://www.zoominfo.com/c/ibl-structural-steel-ltd/354562688</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Approach Antonio Biancucci directly with a structural/FEA overflow pitch, positioning it as collaboration alongside IBL's existing in-house Professional Engineers on technically challenging projects.</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Mississauga, ON</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Techno-Weld Limited</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://technoweld.ca/</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Structural &amp; Miscellaneous Steel Fabrication</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Supply, fabrication, installation and welding of structural and miscellaneous steel for residential, commercial and industrial projects, family owned and operated since 1985, CWB-certified</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Long-established (since 1985), family-owned, CWB-certified Mississauga fabricator with no oil &amp; gas or defense exposure found - a solid general fit.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No specific overflow signal found this pass.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Company website (technoweld.ca) describes structural and miscellaneous steel fabrication, installation and welding services since 1985.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://technoweld.ca/</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>No publicly available email found in this pass.</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://technoweld.ca/ ; http://technoweld.ca/our-services/</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Approach with a structural/FEA overflow pitch tied to its long-established structural and miscellaneous steel fabrication work.</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet129.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -22244,7 +23309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1068"/>
+  <dimension ref="A1:A1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" style="3" min="1" max="1"/>
@@ -29233,6 +30298,139 @@
       <c r="A1068" s="9" t="inlineStr">
         <is>
           <t>No DNV code/standard reference was found for either company recorded in this batch. Korte Sheet Metal (Flin Flon, established 1991) was found but had no confirmed website or verifiable service/contact details beyond directory listings, so it was not added to the main sheet - noted in RK's Metal Construction's Research Notes instead of a separate Review entry, since there was no oil &amp; gas/defense/location ambiguity to flag, only thin public evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="7" t="inlineStr">
+        <is>
+          <t>Batch 77: Toronto, Mississauga &amp; Hamilton, ON (partial - web search budget reached)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="8" t="inlineStr">
+        <is>
+          <t>Milestone: master list moves into Ontario</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="9" t="inlineStr">
+        <is>
+          <t>First Ontario batch, following the completion of all Manitoba cities. This session's web search budget (200 calls) was reached partway through researching this group of cities, so this batch covers Toronto, Mississauga and Hamilton only. Brampton and Vaughan (rows 128 and 130 on the master list) were not yet researched and remain pending for the next session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="8" t="inlineStr">
+        <is>
+          <t>Top prospects across this group (ranked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="9" t="inlineStr">
+        <is>
+          <t>1. Toronto Dry Dock Limited (Toronto) - Score 7, Priority A - genuinely active marine repair facility doing dry dock ship repairs and marine engine servicing for tugs, barges and project cargo since 1989; one of the strongest marine/naval-architecture-adjacent fits found in Ontario so far.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="9" t="inlineStr">
+        <is>
+          <t>2. IBL Structural Steel Ltd. (Mississauga) - Score 7, Priority A - genuinely employs Professional Engineers in-house for complex, technically challenging structural steel projects; directly confirmed named principal (Antonio Biancucci) and email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="9" t="inlineStr">
+        <is>
+          <t>3. EIW Structural Steel &amp; Scaffolding (Toronto) - Score 7, Priority A - large-scale (10,000+ ton annual capacity), CWB Division 1-certified fabricator since 1955, with confirmed CEO (Cameron Chafee) and a dedicated structural sales contact email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="9" t="inlineStr">
+        <is>
+          <t>4. Scarboro Steel Works Inc. (Toronto) - Score 6, Priority B - long-established (since 1950) full-service structural/architectural fabricator, PEO and CWB member.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="9" t="inlineStr">
+        <is>
+          <t>5. Techno-Weld Limited (Mississauga) - Score 5, Priority C - family-owned, CWB-certified structural fabricator since 1985.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="8" t="inlineStr">
+        <is>
+          <t>Hamilton: routed to Review, not the main sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="9" t="inlineStr">
+        <is>
+          <t>Ontario Shipyards (formerly Heddle Shipyards), headquartered in Hamilton, is the largest Canadian-owned ship repair and construction business on the Great Lakes and a very strong marine/offshore-engineering fit on paper - but it is currently executing a major Canadian Coast Guard vessel life extension and actively pursuing a potential federal contract to build up to 12 corvettes for Canada's Navy. Given this genuine, significant defense/government-vessel exposure alongside its clearly diversified commercial marine work (30-year McKeil Marine relationship, offshore energy and civil infrastructure fabrication), it was logged to the Low Confidence - Review sheet rather than included or excluded outright. Hamilton's main sheet was left empty this pass as a result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="8" t="inlineStr">
+        <is>
+          <t>Best outreach angle for this group</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="9" t="inlineStr">
+        <is>
+          <t>Toronto Dry Dock and IBL Structural Steel offer the clearest angles - lead with marine ship-repair structural work for Toronto Dry Dock, and with collaboration alongside IBL's existing in-house Professional Engineers for IBL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="8" t="inlineStr">
+        <is>
+          <t>Overflow / FEA / heavy lift opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="9" t="inlineStr">
+        <is>
+          <t>IBL Structural Steel's in-house Professional Engineers handling technically challenging projects is the clearest evidence-based overflow-FEA signal in this batch. Toronto Dry Dock's ship repair and marine engine servicing work also involves genuine structural engineering considerations (hull integrity, load paths, fatigue).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="8" t="inlineStr">
+        <is>
+          <t>Recommended outreach priority (this group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="9" t="inlineStr">
+        <is>
+          <t>Contact first: Toronto Dry Dock, IBL Structural Steel, and EIW Structural Steel (all Priority A). Scarboro Steel Works and Techno-Weld as secondary follow-ups. Ontario Shipyards held in Review pending verification of its defense-vs-commercial balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="8" t="inlineStr">
+        <is>
+          <t>Quality-control notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="9" t="inlineStr">
+        <is>
+          <t>No DNV code/standard reference was found for any company in this batch, though this is worth revisiting for marine-focused Toronto/Hamilton-area companies as research continues. Kubes Steel (Stoney Creek, a district of Hamilton not separately listed on the master list) was identified as a well-equipped 100,000 sq ft fabrication shop with an 80-ton crane, but contact details could not be verified before the search budget was reached, so it was not added this pass. Brampton and Vaughan remain unresearched and will be covered in the next Ontario batch.</t>
         </is>
       </c>
     </row>

--- a/Canada _Outreach AH Structures.xlsx
+++ b/Canada _Outreach AH Structures.xlsx
@@ -132,6 +132,8 @@
     <sheet name="Toronto, ON" sheetId="127" state="visible" r:id="rId127"/>
     <sheet name="Mississauga, ON" sheetId="128" state="visible" r:id="rId128"/>
     <sheet name="Hamilton, ON" sheetId="129" state="visible" r:id="rId129"/>
+    <sheet name="Brampton, ON" sheetId="130" state="visible" r:id="rId130"/>
+    <sheet name="Vaughan, ON" sheetId="131" state="visible" r:id="rId131"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vancouver, BC'!$A$1:$X$1</definedName>
@@ -260,6 +262,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="126" hidden="1">'Toronto, ON'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="127" hidden="1">'Mississauga, ON'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="128" hidden="1">'Hamilton, ON'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="129" hidden="1">'Brampton, ON'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="130" hidden="1">'Vaughan, ON'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14635,6 +14639,768 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet130.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="24" customWidth="1" style="3" min="4" max="4"/>
+    <col width="26" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="7" max="7"/>
+    <col width="20" customWidth="1" style="3" min="8" max="8"/>
+    <col width="26" customWidth="1" style="3" min="9" max="9"/>
+    <col width="34" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16" customWidth="1" style="3" min="11" max="11"/>
+    <col width="34" customWidth="1" style="3" min="12" max="12"/>
+    <col width="34" customWidth="1" style="3" min="13" max="13"/>
+    <col width="16" customWidth="1" style="3" min="14" max="14"/>
+    <col width="20" customWidth="1" style="3" min="15" max="15"/>
+    <col width="26" customWidth="1" style="3" min="16" max="16"/>
+    <col width="28" customWidth="1" style="3" min="17" max="17"/>
+    <col width="22" customWidth="1" style="3" min="18" max="18"/>
+    <col width="22" customWidth="1" style="3" min="19" max="19"/>
+    <col width="26" customWidth="1" style="3" min="20" max="20"/>
+    <col width="10" customWidth="1" style="3" min="21" max="21"/>
+    <col width="8" customWidth="1" style="3" min="22" max="22"/>
+    <col width="34" customWidth="1" style="3" min="23" max="23"/>
+    <col width="30" customWidth="1" style="3" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Province/State</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Company LinkedIn</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Company Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Industry/Sector</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Services</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Why AH Structures Is Relevant</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Potential Overflow Opportunity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Overflow/Opportunity Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Relevant Project or Work Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Job Title</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker LinkedIn</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Decision Maker Company Profile/Website</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Public Business Email</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Contact Source</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Company Relevance Source</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Relevance Score</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Outreach Angle</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Brampton, ON</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Steelcon Fabrication Inc.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.steelcongoc.com/</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Private company</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Structural Steel Fabrication &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Structural steel fabrication and installation supported by an in-house drafting team and Professional Engineers with over 25 years of consulting background, established 2002</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Notable for genuinely employing Professional Engineers in-house with a long consulting background - one of the strongest structural-engineering-adjacent fits found in Ontario, with a directly confirmed named president and no oil &amp; gas or defense exposure found.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>In-house Professional Engineers with 25+ years of consulting background is a direct, evidence-based overflow-FEA collaboration signal rather than an inferred one.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Company website (steelcongoc.com) describes an in-house drafting team and Professional Engineers with over 25 years of consulting background supporting fabrication.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Danny Bianco</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.steelcongoc.com/contact-us</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>info@steelcongoc.com</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>General company inbox (not verified as an individual's address); Danny Bianco's individual email is masked in public directory listings and was not used per this project's practice of discarding masked addresses.</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.steelcongoc.com/ ; https://www.steelcongoc.com/about-us ; https://www.zoominfo.com/c/steelcon-fabricati